--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FEDD02-1BBF-429A-A075-9615F2111180}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412BC674-4DDB-4418-A506-73EE1AA9CB6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="1692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="1690">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -4668,15 +4668,6 @@
     <t>Csortos Gyula utca</t>
   </si>
   <si>
-    <t>NFD6-09-05-XWRZ/1</t>
-  </si>
-  <si>
-    <t>NFD6-09-05-XWRZ</t>
-  </si>
-  <si>
-    <t>Szondi utca</t>
-  </si>
-  <si>
     <t>202609072601888401</t>
   </si>
   <si>
@@ -5104,6 +5095,9 @@
   </si>
   <si>
     <t>159995579543939398</t>
+  </si>
+  <si>
+    <t>K-915</t>
   </si>
 </sst>
 </file>
@@ -5457,7 +5451,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H445"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -14605,13 +14599,13 @@
         <v>1546</v>
       </c>
       <c r="C398" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D398" t="s">
         <v>1547</v>
       </c>
       <c r="E398" t="s">
-        <v>188</v>
+        <v>226</v>
       </c>
       <c r="F398" t="s">
         <v>8</v>
@@ -14628,19 +14622,19 @@
         <v>1549</v>
       </c>
       <c r="C399" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D399" t="s">
         <v>1550</v>
       </c>
       <c r="E399" t="s">
-        <v>226</v>
+        <v>1551</v>
       </c>
       <c r="F399" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G399" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H399" t="s">
         <v>28</v>
@@ -14648,22 +14642,22 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="C400" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="D400" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E400" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F400" t="s">
-        <v>29</v>
+        <v>1556</v>
       </c>
       <c r="G400" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="H400" t="s">
         <v>28</v>
@@ -14671,22 +14665,22 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="C401" t="s">
         <v>57</v>
       </c>
       <c r="D401" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E401" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F401" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G401" t="s">
         <v>1557</v>
-      </c>
-      <c r="E401" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F401" t="s">
-        <v>1559</v>
-      </c>
-      <c r="G401" t="s">
-        <v>1560</v>
       </c>
       <c r="H401" t="s">
         <v>28</v>
@@ -14694,22 +14688,22 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C402" t="s">
+        <v>106</v>
+      </c>
+      <c r="D402" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E402" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F402" t="s">
+        <v>968</v>
+      </c>
+      <c r="G402" t="s">
         <v>1561</v>
-      </c>
-      <c r="C402" t="s">
-        <v>57</v>
-      </c>
-      <c r="D402" t="s">
-        <v>1557</v>
-      </c>
-      <c r="E402" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F402" t="s">
-        <v>1559</v>
-      </c>
-      <c r="G402" t="s">
-        <v>1560</v>
       </c>
       <c r="H402" t="s">
         <v>28</v>
@@ -14720,19 +14714,19 @@
         <v>1562</v>
       </c>
       <c r="C403" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="D403" t="s">
         <v>1563</v>
       </c>
       <c r="E403" t="s">
-        <v>1467</v>
+        <v>1564</v>
       </c>
       <c r="F403" t="s">
-        <v>968</v>
+        <v>1565</v>
       </c>
       <c r="G403" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="H403" t="s">
         <v>28</v>
@@ -14740,22 +14734,22 @@
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C404" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D404" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="E404" t="s">
-        <v>1567</v>
+        <v>1513</v>
       </c>
       <c r="F404" t="s">
-        <v>1568</v>
+        <v>8</v>
       </c>
       <c r="G404" t="s">
-        <v>1569</v>
+        <v>1529</v>
       </c>
       <c r="H404" t="s">
         <v>28</v>
@@ -14763,22 +14757,22 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C405" t="s">
+        <v>10</v>
+      </c>
+      <c r="D405" t="s">
         <v>1570</v>
       </c>
-      <c r="C405" t="s">
-        <v>43</v>
-      </c>
-      <c r="D405" t="s">
+      <c r="E405" t="s">
+        <v>263</v>
+      </c>
+      <c r="F405" t="s">
+        <v>44</v>
+      </c>
+      <c r="G405" t="s">
         <v>1571</v>
-      </c>
-      <c r="E405" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F405" t="s">
-        <v>8</v>
-      </c>
-      <c r="G405" t="s">
-        <v>1529</v>
       </c>
       <c r="H405" t="s">
         <v>28</v>
@@ -14792,7 +14786,7 @@
         <v>10</v>
       </c>
       <c r="D406" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="E406" t="s">
         <v>263</v>
@@ -14801,7 +14795,7 @@
         <v>44</v>
       </c>
       <c r="G406" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="H406" t="s">
         <v>28</v>
@@ -14809,22 +14803,22 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C407" t="s">
+        <v>17</v>
+      </c>
+      <c r="D407" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E407" t="s">
+        <v>63</v>
+      </c>
+      <c r="F407" t="s">
+        <v>29</v>
+      </c>
+      <c r="G407" t="s">
         <v>1575</v>
-      </c>
-      <c r="C407" t="s">
-        <v>10</v>
-      </c>
-      <c r="D407" t="s">
-        <v>1573</v>
-      </c>
-      <c r="E407" t="s">
-        <v>263</v>
-      </c>
-      <c r="F407" t="s">
-        <v>44</v>
-      </c>
-      <c r="G407" t="s">
-        <v>1574</v>
       </c>
       <c r="H407" t="s">
         <v>28</v>
@@ -14835,19 +14829,19 @@
         <v>1576</v>
       </c>
       <c r="C408" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="D408" t="s">
         <v>1577</v>
       </c>
       <c r="E408" t="s">
-        <v>63</v>
+        <v>1378</v>
       </c>
       <c r="F408" t="s">
-        <v>29</v>
+        <v>1379</v>
       </c>
       <c r="G408" t="s">
-        <v>1578</v>
+        <v>212</v>
       </c>
       <c r="H408" t="s">
         <v>28</v>
@@ -14855,22 +14849,22 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C409" t="s">
+        <v>84</v>
+      </c>
+      <c r="D409" t="s">
         <v>1579</v>
       </c>
-      <c r="C409" t="s">
-        <v>185</v>
-      </c>
-      <c r="D409" t="s">
+      <c r="E409" t="s">
         <v>1580</v>
       </c>
-      <c r="E409" t="s">
-        <v>1378</v>
-      </c>
       <c r="F409" t="s">
-        <v>1379</v>
+        <v>1581</v>
       </c>
       <c r="G409" t="s">
-        <v>212</v>
+        <v>1582</v>
       </c>
       <c r="H409" t="s">
         <v>28</v>
@@ -14878,19 +14872,19 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C410" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D410" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="E410" t="s">
-        <v>1583</v>
+        <v>107</v>
       </c>
       <c r="F410" t="s">
-        <v>1584</v>
+        <v>108</v>
       </c>
       <c r="G410" t="s">
         <v>1585</v>
@@ -14907,7 +14901,7 @@
         <v>106</v>
       </c>
       <c r="D411" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="E411" t="s">
         <v>107</v>
@@ -14916,7 +14910,7 @@
         <v>108</v>
       </c>
       <c r="G411" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="H411" t="s">
         <v>28</v>
@@ -14924,13 +14918,13 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="C412" t="s">
         <v>106</v>
       </c>
       <c r="D412" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="E412" t="s">
         <v>107</v>
@@ -14939,7 +14933,7 @@
         <v>108</v>
       </c>
       <c r="G412" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="H412" t="s">
         <v>28</v>
@@ -14947,22 +14941,22 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C413" t="s">
+        <v>15</v>
+      </c>
+      <c r="D413" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E413" t="s">
         <v>1590</v>
       </c>
-      <c r="C413" t="s">
-        <v>106</v>
-      </c>
-      <c r="D413" t="s">
-        <v>1587</v>
-      </c>
-      <c r="E413" t="s">
-        <v>107</v>
-      </c>
       <c r="F413" t="s">
-        <v>108</v>
+        <v>1591</v>
       </c>
       <c r="G413" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="H413" t="s">
         <v>28</v>
@@ -14970,22 +14964,22 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C414" t="s">
-        <v>15</v>
+        <v>413</v>
       </c>
       <c r="D414" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="E414" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="F414" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="G414" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="H414" t="s">
         <v>28</v>
@@ -14993,22 +14987,22 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C415" t="s">
-        <v>413</v>
+        <v>192</v>
       </c>
       <c r="D415" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="E415" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="F415" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="G415" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="H415" t="s">
         <v>28</v>
@@ -15016,19 +15010,19 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="C416" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D416" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="E416" t="s">
-        <v>1603</v>
+        <v>1365</v>
       </c>
       <c r="F416" t="s">
-        <v>1604</v>
+        <v>120</v>
       </c>
       <c r="G416" t="s">
         <v>1605</v>
@@ -15042,19 +15036,19 @@
         <v>1606</v>
       </c>
       <c r="C417" t="s">
-        <v>198</v>
+        <v>1689</v>
       </c>
       <c r="D417" t="s">
         <v>1607</v>
       </c>
       <c r="E417" t="s">
-        <v>1365</v>
+        <v>1608</v>
       </c>
       <c r="F417" t="s">
-        <v>120</v>
+        <v>1609</v>
       </c>
       <c r="G417" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="H417" t="s">
         <v>28</v>
@@ -15062,19 +15056,19 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="C418" t="s">
-        <v>127</v>
+        <v>943</v>
       </c>
       <c r="D418" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="E418" t="s">
-        <v>1611</v>
+        <v>45</v>
       </c>
       <c r="F418" t="s">
-        <v>1612</v>
+        <v>46</v>
       </c>
       <c r="G418" t="s">
         <v>1613</v>
@@ -15088,19 +15082,19 @@
         <v>1614</v>
       </c>
       <c r="C419" t="s">
-        <v>943</v>
+        <v>57</v>
       </c>
       <c r="D419" t="s">
         <v>1615</v>
       </c>
       <c r="E419" t="s">
-        <v>45</v>
+        <v>1616</v>
       </c>
       <c r="F419" t="s">
-        <v>46</v>
+        <v>1617</v>
       </c>
       <c r="G419" t="s">
-        <v>1616</v>
+        <v>23</v>
       </c>
       <c r="H419" t="s">
         <v>28</v>
@@ -15108,22 +15102,22 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="C420" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="D420" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="E420" t="s">
-        <v>1619</v>
+        <v>89</v>
       </c>
       <c r="F420" t="s">
+        <v>8</v>
+      </c>
+      <c r="G420" t="s">
         <v>1620</v>
-      </c>
-      <c r="G420" t="s">
-        <v>23</v>
       </c>
       <c r="H420" t="s">
         <v>28</v>
@@ -15134,13 +15128,13 @@
         <v>1621</v>
       </c>
       <c r="C421" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D421" t="s">
         <v>1622</v>
       </c>
       <c r="E421" t="s">
-        <v>89</v>
+        <v>705</v>
       </c>
       <c r="F421" t="s">
         <v>8</v>
@@ -15157,19 +15151,19 @@
         <v>1624</v>
       </c>
       <c r="C422" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D422" t="s">
         <v>1625</v>
       </c>
       <c r="E422" t="s">
-        <v>705</v>
+        <v>1626</v>
       </c>
       <c r="F422" t="s">
-        <v>8</v>
+        <v>1627</v>
       </c>
       <c r="G422" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H422" t="s">
         <v>28</v>
@@ -15177,22 +15171,22 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C423" t="s">
-        <v>33</v>
+        <v>413</v>
       </c>
       <c r="D423" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="E423" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="F423" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="G423" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="H423" t="s">
         <v>28</v>
@@ -15200,22 +15194,22 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="C424" t="s">
-        <v>413</v>
+        <v>37</v>
       </c>
       <c r="D424" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="E424" t="s">
-        <v>1634</v>
+        <v>48</v>
       </c>
       <c r="F424" t="s">
-        <v>1635</v>
+        <v>8</v>
       </c>
       <c r="G424" t="s">
-        <v>1636</v>
+        <v>960</v>
       </c>
       <c r="H424" t="s">
         <v>28</v>
@@ -15223,22 +15217,22 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C425" t="s">
+        <v>7</v>
+      </c>
+      <c r="D425" t="s">
         <v>1637</v>
       </c>
-      <c r="C425" t="s">
-        <v>37</v>
-      </c>
-      <c r="D425" t="s">
+      <c r="E425" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F425" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G425" t="s">
         <v>1638</v>
-      </c>
-      <c r="E425" t="s">
-        <v>48</v>
-      </c>
-      <c r="F425" t="s">
-        <v>8</v>
-      </c>
-      <c r="G425" t="s">
-        <v>960</v>
       </c>
       <c r="H425" t="s">
         <v>28</v>
@@ -15249,19 +15243,19 @@
         <v>1639</v>
       </c>
       <c r="C426" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D426" t="s">
         <v>1640</v>
       </c>
       <c r="E426" t="s">
-        <v>1567</v>
+        <v>1641</v>
       </c>
       <c r="F426" t="s">
-        <v>1568</v>
+        <v>1642</v>
       </c>
       <c r="G426" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="H426" t="s">
         <v>28</v>
@@ -15269,19 +15263,19 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="C427" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D427" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="E427" t="s">
-        <v>1644</v>
+        <v>229</v>
       </c>
       <c r="F427" t="s">
-        <v>1645</v>
+        <v>230</v>
       </c>
       <c r="G427" t="s">
         <v>1646</v>
@@ -15295,19 +15289,19 @@
         <v>1647</v>
       </c>
       <c r="C428" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="D428" t="s">
         <v>1648</v>
       </c>
       <c r="E428" t="s">
-        <v>229</v>
+        <v>1649</v>
       </c>
       <c r="F428" t="s">
-        <v>230</v>
+        <v>1650</v>
       </c>
       <c r="G428" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="H428" t="s">
         <v>28</v>
@@ -15315,22 +15309,22 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C429" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="D429" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="E429" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="F429" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="G429" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="H429" t="s">
         <v>28</v>
@@ -15338,22 +15332,22 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="C430" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D430" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="E430" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="F430" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="G430" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="H430" t="s">
         <v>28</v>
@@ -15361,19 +15355,19 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C431" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D431" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="E431" t="s">
-        <v>1662</v>
+        <v>612</v>
       </c>
       <c r="F431" t="s">
-        <v>1663</v>
+        <v>613</v>
       </c>
       <c r="G431" t="s">
         <v>1664</v>
@@ -15387,39 +15381,39 @@
         <v>1665</v>
       </c>
       <c r="C432" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="D432" t="s">
         <v>1666</v>
       </c>
       <c r="E432" t="s">
-        <v>612</v>
+        <v>1667</v>
       </c>
       <c r="F432" t="s">
-        <v>613</v>
+        <v>1668</v>
       </c>
       <c r="G432" t="s">
-        <v>1667</v>
+        <v>162</v>
       </c>
       <c r="H432" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="C433" t="s">
         <v>80</v>
       </c>
       <c r="D433" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="E433" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="F433" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G433" t="s">
         <v>162</v>
@@ -15430,19 +15424,19 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="C434" t="s">
         <v>80</v>
       </c>
       <c r="D434" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="E434" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="F434" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G434" t="s">
         <v>162</v>
@@ -15453,19 +15447,19 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C435" t="s">
         <v>80</v>
       </c>
       <c r="D435" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="E435" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="F435" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G435" t="s">
         <v>162</v>
@@ -15476,19 +15470,19 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C436" t="s">
         <v>80</v>
       </c>
       <c r="D436" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="E436" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="F436" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G436" t="s">
         <v>162</v>
@@ -15499,22 +15493,22 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C437" t="s">
+        <v>37</v>
+      </c>
+      <c r="D437" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E437" t="s">
+        <v>225</v>
+      </c>
+      <c r="F437" t="s">
+        <v>8</v>
+      </c>
+      <c r="G437" t="s">
         <v>1675</v>
-      </c>
-      <c r="C437" t="s">
-        <v>80</v>
-      </c>
-      <c r="D437" t="s">
-        <v>1669</v>
-      </c>
-      <c r="E437" t="s">
-        <v>1670</v>
-      </c>
-      <c r="F437" t="s">
-        <v>1671</v>
-      </c>
-      <c r="G437" t="s">
-        <v>162</v>
       </c>
       <c r="H437" t="s">
         <v>53</v>
@@ -15528,7 +15522,7 @@
         <v>37</v>
       </c>
       <c r="D438" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="E438" t="s">
         <v>225</v>
@@ -15537,7 +15531,7 @@
         <v>8</v>
       </c>
       <c r="G438" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="H438" t="s">
         <v>53</v>
@@ -15545,13 +15539,13 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C439" t="s">
         <v>37</v>
       </c>
       <c r="D439" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="E439" t="s">
         <v>225</v>
@@ -15560,7 +15554,7 @@
         <v>8</v>
       </c>
       <c r="G439" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="H439" t="s">
         <v>53</v>
@@ -15568,25 +15562,25 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C440" t="s">
+        <v>40</v>
+      </c>
+      <c r="D440" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E440" t="s">
+        <v>99</v>
+      </c>
+      <c r="F440" t="s">
+        <v>100</v>
+      </c>
+      <c r="G440" t="s">
+        <v>210</v>
+      </c>
+      <c r="H440" t="s">
         <v>1680</v>
-      </c>
-      <c r="C440" t="s">
-        <v>37</v>
-      </c>
-      <c r="D440" t="s">
-        <v>1677</v>
-      </c>
-      <c r="E440" t="s">
-        <v>225</v>
-      </c>
-      <c r="F440" t="s">
-        <v>8</v>
-      </c>
-      <c r="G440" t="s">
-        <v>1678</v>
-      </c>
-      <c r="H440" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.3">
@@ -15594,79 +15588,79 @@
         <v>1681</v>
       </c>
       <c r="C441" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D441" t="s">
         <v>1682</v>
       </c>
       <c r="E441" t="s">
-        <v>99</v>
+        <v>1683</v>
       </c>
       <c r="F441" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="G441" t="s">
-        <v>210</v>
+        <v>1684</v>
       </c>
       <c r="H441" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="C442" t="s">
         <v>17</v>
       </c>
       <c r="D442" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="E442" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="F442" t="s">
         <v>29</v>
       </c>
       <c r="G442" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="H442" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="C443" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D443" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="E443" t="s">
-        <v>1686</v>
+        <v>181</v>
       </c>
       <c r="F443" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="G443" t="s">
-        <v>1687</v>
+        <v>1495</v>
       </c>
       <c r="H443" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C444" t="s">
         <v>40</v>
       </c>
       <c r="D444" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="E444" t="s">
         <v>181</v>
@@ -15678,30 +15672,7 @@
         <v>1495</v>
       </c>
       <c r="H444" t="s">
-        <v>1683</v>
-      </c>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A445" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C445" t="s">
-        <v>40</v>
-      </c>
-      <c r="D445" t="s">
-        <v>1690</v>
-      </c>
-      <c r="E445" t="s">
-        <v>181</v>
-      </c>
-      <c r="F445" t="s">
-        <v>182</v>
-      </c>
-      <c r="G445" t="s">
-        <v>1495</v>
-      </c>
-      <c r="H445" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FA5001-9BA4-4195-8338-CA2C5AB3E4B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC50321-B679-4BE8-80F3-2983F7B00C3D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="685">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -2071,6 +2071,18 @@
   </si>
   <si>
     <t>1040959940/1</t>
+  </si>
+  <si>
+    <t>2026K/726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEGLÉD </t>
+  </si>
+  <si>
+    <t>FÜRDŐ ÚT</t>
+  </si>
+  <si>
+    <t>RUDIBP</t>
   </si>
 </sst>
 </file>
@@ -2424,7 +2436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -7174,6 +7186,29 @@
         <v>10</v>
       </c>
     </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>681</v>
+      </c>
+      <c r="C207" t="s">
+        <v>31</v>
+      </c>
+      <c r="D207" t="s">
+        <v>681</v>
+      </c>
+      <c r="E207">
+        <v>2700</v>
+      </c>
+      <c r="F207" t="s">
+        <v>682</v>
+      </c>
+      <c r="G207" t="s">
+        <v>683</v>
+      </c>
+      <c r="H207" t="s">
+        <v>684</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="C1:H305" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216EAD6A-0221-4452-B22C-2ADB5D7282C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4968137C-804A-4CEA-AD46-3C58E481E681}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -6775,7 +6775,7 @@
         <v>396</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>397</v>
@@ -8776,7 +8776,7 @@
         <v>664</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>665</v>
@@ -8799,7 +8799,7 @@
         <v>667</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>665</v>
@@ -8822,7 +8822,7 @@
         <v>668</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>665</v>
@@ -9397,7 +9397,7 @@
         <v>746</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>747</v>
@@ -12433,7 +12433,7 @@
         <v>1156</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>1157</v>
@@ -12456,7 +12456,7 @@
         <v>1159</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>1157</v>
@@ -12548,7 +12548,7 @@
         <v>1171</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>1172</v>
@@ -13192,7 +13192,7 @@
         <v>1264</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>1265</v>
@@ -13215,7 +13215,7 @@
         <v>1267</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>1265</v>
@@ -13238,7 +13238,7 @@
         <v>1268</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>1269</v>
@@ -13376,7 +13376,7 @@
         <v>1284</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>1285</v>
@@ -14457,7 +14457,7 @@
         <v>1431</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>1432</v>
@@ -14480,7 +14480,7 @@
         <v>1435</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>1432</v>
@@ -15078,7 +15078,7 @@
         <v>1514</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>1515</v>
@@ -15262,7 +15262,7 @@
         <v>1542</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D412" s="1" t="s">
         <v>1543</v>
@@ -15400,7 +15400,7 @@
         <v>1564</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>1565</v>
@@ -15423,7 +15423,7 @@
         <v>1567</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>1565</v>
@@ -15791,7 +15791,7 @@
         <v>1619</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>1620</v>
@@ -16136,7 +16136,7 @@
         <v>1667</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>1668</v>
@@ -16159,7 +16159,7 @@
         <v>1670</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>1671</v>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CACFD4-597F-44C2-9ABA-EB7CDB4DC371}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A5CBC2-2E72-4A4F-B515-03DD78C0433A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -163,6 +163,18 @@
   </si>
   <si>
     <t>327310801</t>
+  </si>
+  <si>
+    <t>260831-F00002936</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>6aa8f831f7fbdc73ea01538f</t>
+  </si>
+  <si>
+    <t>TELEKOM</t>
   </si>
 </sst>
 </file>
@@ -516,7 +528,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -781,6 +793,20 @@
         <v>8</v>
       </c>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="C1:H11" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A5CBC2-2E72-4A4F-B515-03DD78C0433A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D7FC9D-C674-4B99-9709-28207CCC5C44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -171,10 +171,10 @@
     <t>SZ-821</t>
   </si>
   <si>
-    <t>6aa8f831f7fbdc73ea01538f</t>
-  </si>
-  <si>
     <t>TELEKOM</t>
+  </si>
+  <si>
+    <t>6aa8f831f7fbdc73ea0a538f</t>
   </si>
 </sst>
 </file>
@@ -795,7 +795,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -804,7 +804,7 @@
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5216EA-EA22-4E34-98B1-A54AC9C9FB4B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185E00BE-6CAF-45EB-917B-017576A35B2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="1529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="1530">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -4615,6 +4615,9 @@
   </si>
   <si>
     <t>Losonci tér</t>
+  </si>
+  <si>
+    <t>K-920</t>
   </si>
 </sst>
 </file>
@@ -6805,16 +6808,16 @@
         <v>164</v>
       </c>
       <c r="D80" t="s">
-        <v>468</v>
+        <v>697</v>
       </c>
       <c r="E80" t="s">
-        <v>469</v>
+        <v>698</v>
       </c>
       <c r="F80" t="s">
-        <v>470</v>
+        <v>699</v>
       </c>
       <c r="G80" t="s">
-        <v>13</v>
+        <v>700</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -8300,19 +8303,19 @@
         <v>164</v>
       </c>
       <c r="D145" t="s">
-        <v>693</v>
+        <v>1332</v>
       </c>
       <c r="E145" t="s">
-        <v>694</v>
+        <v>1333</v>
       </c>
       <c r="F145" t="s">
-        <v>695</v>
+        <v>1334</v>
       </c>
       <c r="G145" t="s">
-        <v>131</v>
+        <v>1335</v>
       </c>
       <c r="H145" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -8323,16 +8326,16 @@
         <v>164</v>
       </c>
       <c r="D146" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E146" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F146" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="G146" t="s">
-        <v>700</v>
+        <v>131</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -9493,19 +9496,19 @@
         <v>860</v>
       </c>
       <c r="C197" t="s">
-        <v>164</v>
+        <v>1529</v>
       </c>
       <c r="D197" t="s">
-        <v>861</v>
+        <v>1431</v>
       </c>
       <c r="E197" t="s">
-        <v>862</v>
+        <v>165</v>
       </c>
       <c r="F197" t="s">
-        <v>863</v>
+        <v>166</v>
       </c>
       <c r="G197" t="s">
-        <v>349</v>
+        <v>1432</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -9516,22 +9519,22 @@
         <v>864</v>
       </c>
       <c r="C198" t="s">
-        <v>164</v>
+        <v>1529</v>
       </c>
       <c r="D198" t="s">
-        <v>861</v>
+        <v>1278</v>
       </c>
       <c r="E198" t="s">
-        <v>862</v>
+        <v>1279</v>
       </c>
       <c r="F198" t="s">
-        <v>863</v>
+        <v>1280</v>
       </c>
       <c r="G198" t="s">
-        <v>349</v>
+        <v>169</v>
       </c>
       <c r="H198" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -12598,22 +12601,22 @@
         <v>1277</v>
       </c>
       <c r="C332" t="s">
-        <v>164</v>
+        <v>1529</v>
       </c>
       <c r="D332" t="s">
-        <v>1278</v>
+        <v>861</v>
       </c>
       <c r="E332" t="s">
-        <v>1279</v>
+        <v>862</v>
       </c>
       <c r="F332" t="s">
-        <v>1280</v>
+        <v>863</v>
       </c>
       <c r="G332" t="s">
-        <v>169</v>
+        <v>349</v>
       </c>
       <c r="H332" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
@@ -12667,22 +12670,22 @@
         <v>1289</v>
       </c>
       <c r="C335" t="s">
-        <v>164</v>
+        <v>1529</v>
       </c>
       <c r="D335" t="s">
-        <v>1290</v>
+        <v>861</v>
       </c>
       <c r="E335" t="s">
-        <v>1291</v>
+        <v>862</v>
       </c>
       <c r="F335" t="s">
-        <v>1292</v>
+        <v>863</v>
       </c>
       <c r="G335" t="s">
-        <v>1293</v>
+        <v>349</v>
       </c>
       <c r="H335" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
@@ -12920,19 +12923,19 @@
         <v>1331</v>
       </c>
       <c r="C346" t="s">
-        <v>164</v>
+        <v>1529</v>
       </c>
       <c r="D346" t="s">
-        <v>1332</v>
+        <v>1356</v>
       </c>
       <c r="E346" t="s">
-        <v>1333</v>
+        <v>1357</v>
       </c>
       <c r="F346" t="s">
-        <v>1334</v>
+        <v>1358</v>
       </c>
       <c r="G346" t="s">
-        <v>1335</v>
+        <v>177</v>
       </c>
       <c r="H346" t="s">
         <v>10</v>
@@ -13104,22 +13107,22 @@
         <v>1355</v>
       </c>
       <c r="C354" t="s">
-        <v>164</v>
+        <v>1529</v>
       </c>
       <c r="D354" t="s">
-        <v>1356</v>
+        <v>468</v>
       </c>
       <c r="E354" t="s">
-        <v>1357</v>
+        <v>469</v>
       </c>
       <c r="F354" t="s">
-        <v>1358</v>
+        <v>470</v>
       </c>
       <c r="G354" t="s">
-        <v>177</v>
+        <v>13</v>
       </c>
       <c r="H354" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
@@ -13590,19 +13593,19 @@
         <v>164</v>
       </c>
       <c r="D375" t="s">
-        <v>1431</v>
+        <v>1290</v>
       </c>
       <c r="E375" t="s">
-        <v>165</v>
+        <v>1291</v>
       </c>
       <c r="F375" t="s">
-        <v>166</v>
+        <v>1292</v>
       </c>
       <c r="G375" t="s">
-        <v>1432</v>
+        <v>1293</v>
       </c>
       <c r="H375" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
@@ -14296,7 +14299,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:H405" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
+  <autoFilter ref="C1:H405" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}">
+    <sortState ref="C80:H375">
+      <sortCondition ref="E1:E405"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBEF2D6-1B91-41AA-A01C-13D70B9E6141}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A3F107-A764-425F-A44C-44A4BF9E4DFE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$402</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="1518">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -4579,6 +4579,9 @@
   </si>
   <si>
     <t xml:space="preserve">Kossuth utca </t>
+  </si>
+  <si>
+    <t>K-917</t>
   </si>
 </sst>
 </file>
@@ -6743,7 +6746,7 @@
         <v>492</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D79" t="s">
         <v>493</v>
@@ -6766,7 +6769,7 @@
         <v>497</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D80" t="s">
         <v>493</v>
@@ -8905,7 +8908,7 @@
         <v>805</v>
       </c>
       <c r="C173" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D173" t="s">
         <v>806</v>
@@ -8928,7 +8931,7 @@
         <v>810</v>
       </c>
       <c r="C174" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D174" t="s">
         <v>811</v>
@@ -9549,7 +9552,7 @@
         <v>893</v>
       </c>
       <c r="C201" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D201" t="s">
         <v>894</v>
@@ -9733,7 +9736,7 @@
         <v>924</v>
       </c>
       <c r="C209" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D209" t="s">
         <v>925</v>
@@ -9756,7 +9759,7 @@
         <v>927</v>
       </c>
       <c r="C210" t="s">
-        <v>79</v>
+        <v>1517</v>
       </c>
       <c r="D210" t="s">
         <v>925</v>
@@ -14182,7 +14185,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:H378" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}">
+  <autoFilter ref="C1:H402" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}">
     <sortState ref="C76:H351">
       <sortCondition ref="E1:E378"/>
     </sortState>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E647B9-ACE8-455C-AAAE-46370BAE2633}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ED21A9-E468-420A-A9E5-1FF70931C9E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$377</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="1419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="1404">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -1740,18 +1740,6 @@
     <t>260922-F00000704</t>
   </si>
   <si>
-    <t>6ab25c5973749ba5fc07d504</t>
-  </si>
-  <si>
-    <t>260922-F00007547</t>
-  </si>
-  <si>
-    <t>4283</t>
-  </si>
-  <si>
-    <t>LÉTAVÉRTES</t>
-  </si>
-  <si>
     <t>6ab4f703219e3d74bbe3c0e9</t>
   </si>
   <si>
@@ -2280,24 +2268,6 @@
     <t>260923-F00004255</t>
   </si>
   <si>
-    <t>6ab39b0d219e3d74bbe3a4ed</t>
-  </si>
-  <si>
-    <t>260923-F00004414</t>
-  </si>
-  <si>
-    <t>4138</t>
-  </si>
-  <si>
-    <t>KOMÁDI</t>
-  </si>
-  <si>
-    <t>Munkás utca</t>
-  </si>
-  <si>
-    <t>6ab39b0d219e3d74bbe3a4ef</t>
-  </si>
-  <si>
     <t>6ab3b65b219e3d74bbe3aa0f</t>
   </si>
   <si>
@@ -2656,21 +2626,6 @@
   </si>
   <si>
     <t>ÚJFEHÉRTÓ</t>
-  </si>
-  <si>
-    <t>6ab3d211219e3d74bbe3aee8</t>
-  </si>
-  <si>
-    <t>260923-W00008256</t>
-  </si>
-  <si>
-    <t>4700</t>
-  </si>
-  <si>
-    <t>MÁTÉSZALKA</t>
-  </si>
-  <si>
-    <t>Alkotmány út</t>
   </si>
   <si>
     <t>6ab3d0ea219e3d74bbe3aec0</t>
@@ -4638,7 +4593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H368"/>
+  <dimension ref="A1:H364"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -5414,7 +5369,7 @@
         <v>311</v>
       </c>
       <c r="C34" t="s">
-        <v>1418</v>
+        <v>1403</v>
       </c>
       <c r="D34" t="s">
         <v>312</v>
@@ -6932,7 +6887,7 @@
         <v>540</v>
       </c>
       <c r="C100" t="s">
-        <v>1418</v>
+        <v>1403</v>
       </c>
       <c r="D100" t="s">
         <v>541</v>
@@ -6955,7 +6910,7 @@
         <v>542</v>
       </c>
       <c r="C101" t="s">
-        <v>1418</v>
+        <v>1403</v>
       </c>
       <c r="D101" t="s">
         <v>541</v>
@@ -7162,7 +7117,7 @@
         <v>570</v>
       </c>
       <c r="C110" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D110" t="s">
         <v>571</v>
@@ -7174,7 +7129,7 @@
         <v>573</v>
       </c>
       <c r="G110" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -7185,7 +7140,7 @@
         <v>574</v>
       </c>
       <c r="C111" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D111" t="s">
         <v>575</v>
@@ -7197,7 +7152,7 @@
         <v>577</v>
       </c>
       <c r="G111" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -7211,13 +7166,13 @@
         <v>32</v>
       </c>
       <c r="D112" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E112" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F112" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G112" t="s">
         <v>98</v>
@@ -7228,22 +7183,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>579</v>
+      </c>
+      <c r="C113" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" t="s">
+        <v>580</v>
+      </c>
+      <c r="E113" t="s">
+        <v>581</v>
+      </c>
+      <c r="F113" t="s">
         <v>582</v>
       </c>
-      <c r="C113" t="s">
-        <v>32</v>
-      </c>
-      <c r="D113" t="s">
-        <v>579</v>
-      </c>
-      <c r="E113" t="s">
-        <v>580</v>
-      </c>
-      <c r="F113" t="s">
-        <v>581</v>
-      </c>
       <c r="G113" t="s">
-        <v>98</v>
+        <v>583</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -7251,22 +7206,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C114" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D114" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E114" t="s">
-        <v>585</v>
+        <v>89</v>
       </c>
       <c r="F114" t="s">
+        <v>7</v>
+      </c>
+      <c r="G114" t="s">
         <v>586</v>
-      </c>
-      <c r="G114" t="s">
-        <v>587</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -7274,22 +7229,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>587</v>
+      </c>
+      <c r="C115" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" t="s">
         <v>588</v>
       </c>
-      <c r="C115" t="s">
-        <v>77</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>589</v>
       </c>
-      <c r="E115" t="s">
-        <v>89</v>
-      </c>
       <c r="F115" t="s">
-        <v>7</v>
+        <v>590</v>
       </c>
       <c r="G115" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -7297,22 +7252,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C116" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D116" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E116" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F116" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G116" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -7320,22 +7275,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C117" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D117" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E117" t="s">
-        <v>598</v>
+        <v>308</v>
       </c>
       <c r="F117" t="s">
+        <v>309</v>
+      </c>
+      <c r="G117" t="s">
         <v>599</v>
-      </c>
-      <c r="G117" t="s">
-        <v>600</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -7343,22 +7298,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>600</v>
+      </c>
+      <c r="C118" t="s">
+        <v>56</v>
+      </c>
+      <c r="D118" t="s">
         <v>601</v>
       </c>
-      <c r="C118" t="s">
-        <v>22</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>602</v>
       </c>
-      <c r="E118" t="s">
-        <v>308</v>
-      </c>
       <c r="F118" t="s">
-        <v>309</v>
+        <v>603</v>
       </c>
       <c r="G118" t="s">
-        <v>603</v>
+        <v>126</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -7369,7 +7324,7 @@
         <v>604</v>
       </c>
       <c r="C119" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D119" t="s">
         <v>605</v>
@@ -7381,7 +7336,7 @@
         <v>607</v>
       </c>
       <c r="G119" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -7392,7 +7347,7 @@
         <v>608</v>
       </c>
       <c r="C120" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D120" t="s">
         <v>609</v>
@@ -7404,7 +7359,7 @@
         <v>611</v>
       </c>
       <c r="G120" t="s">
-        <v>28</v>
+        <v>612</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -7412,22 +7367,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C121" t="s">
         <v>51</v>
       </c>
       <c r="D121" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E121" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="F121" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G121" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -7435,22 +7390,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>614</v>
+      </c>
+      <c r="C122" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" t="s">
+        <v>615</v>
+      </c>
+      <c r="E122" t="s">
+        <v>616</v>
+      </c>
+      <c r="F122" t="s">
         <v>617</v>
       </c>
-      <c r="C122" t="s">
-        <v>51</v>
-      </c>
-      <c r="D122" t="s">
-        <v>613</v>
-      </c>
-      <c r="E122" t="s">
-        <v>614</v>
-      </c>
-      <c r="F122" t="s">
-        <v>615</v>
-      </c>
       <c r="G122" t="s">
-        <v>616</v>
+        <v>214</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -7461,19 +7416,19 @@
         <v>618</v>
       </c>
       <c r="C123" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
         <v>619</v>
       </c>
       <c r="E123" t="s">
+        <v>185</v>
+      </c>
+      <c r="F123" t="s">
+        <v>186</v>
+      </c>
+      <c r="G123" t="s">
         <v>620</v>
-      </c>
-      <c r="F123" t="s">
-        <v>621</v>
-      </c>
-      <c r="G123" t="s">
-        <v>214</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -7481,22 +7436,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>621</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D124" t="s">
         <v>622</v>
       </c>
-      <c r="C124" t="s">
-        <v>21</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>623</v>
       </c>
-      <c r="E124" t="s">
-        <v>185</v>
-      </c>
       <c r="F124" t="s">
-        <v>186</v>
+        <v>624</v>
       </c>
       <c r="G124" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -7504,19 +7459,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C125" t="s">
-        <v>1418</v>
+        <v>69</v>
       </c>
       <c r="D125" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E125" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F125" t="s">
-        <v>628</v>
+        <v>7</v>
       </c>
       <c r="G125" t="s">
         <v>629</v>
@@ -7530,7 +7485,7 @@
         <v>630</v>
       </c>
       <c r="C126" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D126" t="s">
         <v>631</v>
@@ -7539,10 +7494,10 @@
         <v>632</v>
       </c>
       <c r="F126" t="s">
-        <v>7</v>
+        <v>633</v>
       </c>
       <c r="G126" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -7550,22 +7505,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C127" t="s">
         <v>45</v>
       </c>
       <c r="D127" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E127" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F127" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="G127" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -7573,22 +7528,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>636</v>
+      </c>
+      <c r="C128" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" t="s">
+        <v>637</v>
+      </c>
+      <c r="E128" t="s">
+        <v>638</v>
+      </c>
+      <c r="F128" t="s">
         <v>639</v>
       </c>
-      <c r="C128" t="s">
-        <v>45</v>
-      </c>
-      <c r="D128" t="s">
-        <v>635</v>
-      </c>
-      <c r="E128" t="s">
-        <v>636</v>
-      </c>
-      <c r="F128" t="s">
-        <v>637</v>
-      </c>
       <c r="G128" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -7596,22 +7551,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C129" t="s">
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E129" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F129" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="G129" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -7619,22 +7574,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C130" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D130" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E130" t="s">
-        <v>642</v>
+        <v>198</v>
       </c>
       <c r="F130" t="s">
-        <v>643</v>
+        <v>199</v>
       </c>
       <c r="G130" t="s">
-        <v>644</v>
+        <v>60</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -7642,22 +7597,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>644</v>
+      </c>
+      <c r="C131" t="s">
+        <v>41</v>
+      </c>
+      <c r="D131" t="s">
+        <v>645</v>
+      </c>
+      <c r="E131" t="s">
+        <v>545</v>
+      </c>
+      <c r="F131" t="s">
+        <v>546</v>
+      </c>
+      <c r="G131" t="s">
         <v>646</v>
-      </c>
-      <c r="C131" t="s">
-        <v>33</v>
-      </c>
-      <c r="D131" t="s">
-        <v>647</v>
-      </c>
-      <c r="E131" t="s">
-        <v>198</v>
-      </c>
-      <c r="F131" t="s">
-        <v>199</v>
-      </c>
-      <c r="G131" t="s">
-        <v>60</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -7665,22 +7620,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>647</v>
+      </c>
+      <c r="C132" t="s">
+        <v>31</v>
+      </c>
+      <c r="D132" t="s">
         <v>648</v>
       </c>
-      <c r="C132" t="s">
-        <v>41</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
+        <v>202</v>
+      </c>
+      <c r="F132" t="s">
+        <v>203</v>
+      </c>
+      <c r="G132" t="s">
         <v>649</v>
-      </c>
-      <c r="E132" t="s">
-        <v>545</v>
-      </c>
-      <c r="F132" t="s">
-        <v>546</v>
-      </c>
-      <c r="G132" t="s">
-        <v>650</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -7688,22 +7643,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>650</v>
+      </c>
+      <c r="C133" t="s">
+        <v>249</v>
+      </c>
+      <c r="D133" t="s">
         <v>651</v>
       </c>
-      <c r="C133" t="s">
-        <v>31</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
         <v>652</v>
       </c>
-      <c r="E133" t="s">
-        <v>202</v>
-      </c>
       <c r="F133" t="s">
-        <v>203</v>
+        <v>653</v>
       </c>
       <c r="G133" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -7711,22 +7666,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C134" t="s">
-        <v>249</v>
+        <v>145</v>
       </c>
       <c r="D134" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E134" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F134" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G134" t="s">
-        <v>658</v>
+        <v>216</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -7737,7 +7692,7 @@
         <v>659</v>
       </c>
       <c r="C135" t="s">
-        <v>145</v>
+        <v>1403</v>
       </c>
       <c r="D135" t="s">
         <v>660</v>
@@ -7746,10 +7701,10 @@
         <v>661</v>
       </c>
       <c r="F135" t="s">
+        <v>113</v>
+      </c>
+      <c r="G135" t="s">
         <v>662</v>
-      </c>
-      <c r="G135" t="s">
-        <v>216</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -7760,19 +7715,19 @@
         <v>663</v>
       </c>
       <c r="C136" t="s">
-        <v>1418</v>
+        <v>1403</v>
       </c>
       <c r="D136" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E136" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="F136" t="s">
         <v>113</v>
       </c>
       <c r="G136" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -7780,22 +7735,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>664</v>
+      </c>
+      <c r="C137" t="s">
+        <v>53</v>
+      </c>
+      <c r="D137" t="s">
+        <v>665</v>
+      </c>
+      <c r="E137" t="s">
+        <v>666</v>
+      </c>
+      <c r="F137" t="s">
         <v>667</v>
       </c>
-      <c r="C137" t="s">
-        <v>1418</v>
-      </c>
-      <c r="D137" t="s">
-        <v>664</v>
-      </c>
-      <c r="E137" t="s">
-        <v>665</v>
-      </c>
-      <c r="F137" t="s">
-        <v>113</v>
-      </c>
       <c r="G137" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -7803,22 +7758,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C138" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D138" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E138" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F138" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G138" t="s">
-        <v>672</v>
+        <v>66</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -7832,13 +7787,13 @@
         <v>34</v>
       </c>
       <c r="D139" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E139" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="F139" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="G139" t="s">
         <v>66</v>
@@ -7849,22 +7804,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>674</v>
+      </c>
+      <c r="C140" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" t="s">
+        <v>675</v>
+      </c>
+      <c r="E140" t="s">
+        <v>676</v>
+      </c>
+      <c r="F140" t="s">
         <v>677</v>
       </c>
-      <c r="C140" t="s">
-        <v>34</v>
-      </c>
-      <c r="D140" t="s">
-        <v>674</v>
-      </c>
-      <c r="E140" t="s">
-        <v>675</v>
-      </c>
-      <c r="F140" t="s">
-        <v>676</v>
-      </c>
       <c r="G140" t="s">
-        <v>66</v>
+        <v>678</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -7872,22 +7827,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C141" t="s">
         <v>21</v>
       </c>
       <c r="D141" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E141" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F141" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G141" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -7895,22 +7850,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>680</v>
+      </c>
+      <c r="C142" t="s">
+        <v>46</v>
+      </c>
+      <c r="D142" t="s">
+        <v>681</v>
+      </c>
+      <c r="E142" t="s">
+        <v>682</v>
+      </c>
+      <c r="F142" t="s">
         <v>683</v>
       </c>
-      <c r="C142" t="s">
-        <v>21</v>
-      </c>
-      <c r="D142" t="s">
-        <v>679</v>
-      </c>
-      <c r="E142" t="s">
-        <v>680</v>
-      </c>
-      <c r="F142" t="s">
-        <v>681</v>
-      </c>
       <c r="G142" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -7918,19 +7873,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C143" t="s">
-        <v>46</v>
+        <v>255</v>
       </c>
       <c r="D143" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E143" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F143" t="s">
-        <v>687</v>
+        <v>35</v>
       </c>
       <c r="G143" t="s">
         <v>688</v>
@@ -7944,7 +7899,7 @@
         <v>689</v>
       </c>
       <c r="C144" t="s">
-        <v>255</v>
+        <v>22</v>
       </c>
       <c r="D144" t="s">
         <v>690</v>
@@ -7953,10 +7908,10 @@
         <v>691</v>
       </c>
       <c r="F144" t="s">
-        <v>35</v>
+        <v>692</v>
       </c>
       <c r="G144" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -7964,22 +7919,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>249</v>
       </c>
       <c r="D145" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E145" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F145" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G145" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -7987,22 +7942,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C146" t="s">
-        <v>249</v>
+        <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E146" t="s">
-        <v>700</v>
+        <v>86</v>
       </c>
       <c r="F146" t="s">
+        <v>87</v>
+      </c>
+      <c r="G146" t="s">
         <v>701</v>
-      </c>
-      <c r="G146" t="s">
-        <v>702</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -8010,22 +7965,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>702</v>
+      </c>
+      <c r="C147" t="s">
+        <v>50</v>
+      </c>
+      <c r="D147" t="s">
         <v>703</v>
       </c>
-      <c r="C147" t="s">
-        <v>16</v>
-      </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>704</v>
       </c>
-      <c r="E147" t="s">
-        <v>86</v>
-      </c>
       <c r="F147" t="s">
-        <v>87</v>
+        <v>705</v>
       </c>
       <c r="G147" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -8033,22 +7988,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C148" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D148" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E148" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F148" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G148" t="s">
-        <v>710</v>
+        <v>331</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -8062,13 +8017,13 @@
         <v>34</v>
       </c>
       <c r="D149" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E149" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F149" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G149" t="s">
         <v>331</v>
@@ -8079,22 +8034,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>712</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D150" t="s">
+        <v>713</v>
+      </c>
+      <c r="E150" t="s">
+        <v>714</v>
+      </c>
+      <c r="F150" t="s">
         <v>715</v>
       </c>
-      <c r="C150" t="s">
-        <v>34</v>
-      </c>
-      <c r="D150" t="s">
-        <v>712</v>
-      </c>
-      <c r="E150" t="s">
-        <v>713</v>
-      </c>
-      <c r="F150" t="s">
-        <v>714</v>
-      </c>
       <c r="G150" t="s">
-        <v>331</v>
+        <v>716</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -8102,22 +8057,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>717</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D151" t="s">
+        <v>713</v>
+      </c>
+      <c r="E151" t="s">
+        <v>714</v>
+      </c>
+      <c r="F151" t="s">
+        <v>715</v>
+      </c>
+      <c r="G151" t="s">
         <v>716</v>
-      </c>
-      <c r="C151" t="s">
-        <v>1418</v>
-      </c>
-      <c r="D151" t="s">
-        <v>717</v>
-      </c>
-      <c r="E151" t="s">
-        <v>718</v>
-      </c>
-      <c r="F151" t="s">
-        <v>719</v>
-      </c>
-      <c r="G151" t="s">
-        <v>720</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -8125,22 +8080,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>718</v>
+      </c>
+      <c r="C152" t="s">
+        <v>45</v>
+      </c>
+      <c r="D152" t="s">
+        <v>719</v>
+      </c>
+      <c r="E152" t="s">
+        <v>720</v>
+      </c>
+      <c r="F152" t="s">
         <v>721</v>
       </c>
-      <c r="C152" t="s">
-        <v>1418</v>
-      </c>
-      <c r="D152" t="s">
-        <v>717</v>
-      </c>
-      <c r="E152" t="s">
-        <v>718</v>
-      </c>
-      <c r="F152" t="s">
-        <v>719</v>
-      </c>
       <c r="G152" t="s">
-        <v>720</v>
+        <v>68</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -8154,13 +8109,13 @@
         <v>45</v>
       </c>
       <c r="D153" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E153" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F153" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G153" t="s">
         <v>68</v>
@@ -8171,22 +8126,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>723</v>
+      </c>
+      <c r="C154" t="s">
+        <v>37</v>
+      </c>
+      <c r="D154" t="s">
+        <v>724</v>
+      </c>
+      <c r="E154" t="s">
+        <v>725</v>
+      </c>
+      <c r="F154" t="s">
         <v>726</v>
       </c>
-      <c r="C154" t="s">
-        <v>45</v>
-      </c>
-      <c r="D154" t="s">
-        <v>723</v>
-      </c>
-      <c r="E154" t="s">
-        <v>724</v>
-      </c>
-      <c r="F154" t="s">
-        <v>725</v>
-      </c>
       <c r="G154" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -8209,7 +8164,7 @@
         <v>730</v>
       </c>
       <c r="G155" t="s">
-        <v>57</v>
+        <v>731</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -8217,22 +8172,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C156" t="s">
         <v>37</v>
       </c>
       <c r="D156" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="E156" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F156" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G156" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -8240,19 +8195,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C157" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D157" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E157" t="s">
-        <v>733</v>
+        <v>666</v>
       </c>
       <c r="F157" t="s">
-        <v>734</v>
+        <v>667</v>
       </c>
       <c r="G157" t="s">
         <v>735</v>
@@ -8263,22 +8218,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>736</v>
+      </c>
+      <c r="C158" t="s">
+        <v>279</v>
+      </c>
+      <c r="D158" t="s">
         <v>737</v>
       </c>
-      <c r="C158" t="s">
-        <v>53</v>
-      </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>204</v>
+      </c>
+      <c r="F158" t="s">
+        <v>205</v>
+      </c>
+      <c r="G158" t="s">
         <v>738</v>
-      </c>
-      <c r="E158" t="s">
-        <v>670</v>
-      </c>
-      <c r="F158" t="s">
-        <v>671</v>
-      </c>
-      <c r="G158" t="s">
-        <v>739</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -8286,22 +8241,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>739</v>
+      </c>
+      <c r="C159" t="s">
+        <v>37</v>
+      </c>
+      <c r="D159" t="s">
         <v>740</v>
       </c>
-      <c r="C159" t="s">
-        <v>279</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
         <v>741</v>
       </c>
-      <c r="E159" t="s">
-        <v>204</v>
-      </c>
       <c r="F159" t="s">
-        <v>205</v>
+        <v>742</v>
       </c>
       <c r="G159" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -8309,22 +8264,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C160" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D160" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E160" t="s">
-        <v>745</v>
+        <v>134</v>
       </c>
       <c r="F160" t="s">
-        <v>746</v>
+        <v>135</v>
       </c>
       <c r="G160" t="s">
-        <v>747</v>
+        <v>162</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -8332,22 +8287,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>746</v>
+      </c>
+      <c r="C161" t="s">
+        <v>54</v>
+      </c>
+      <c r="D161" t="s">
+        <v>747</v>
+      </c>
+      <c r="E161" t="s">
         <v>748</v>
       </c>
-      <c r="C161" t="s">
-        <v>33</v>
-      </c>
-      <c r="D161" t="s">
+      <c r="F161" t="s">
         <v>749</v>
       </c>
-      <c r="E161" t="s">
-        <v>134</v>
-      </c>
-      <c r="F161" t="s">
-        <v>135</v>
-      </c>
       <c r="G161" t="s">
-        <v>162</v>
+        <v>331</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -8358,19 +8313,19 @@
         <v>750</v>
       </c>
       <c r="C162" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D162" t="s">
         <v>751</v>
       </c>
       <c r="E162" t="s">
+        <v>131</v>
+      </c>
+      <c r="F162" t="s">
+        <v>132</v>
+      </c>
+      <c r="G162" t="s">
         <v>752</v>
-      </c>
-      <c r="F162" t="s">
-        <v>753</v>
-      </c>
-      <c r="G162" t="s">
-        <v>754</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -8378,22 +8333,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>753</v>
+      </c>
+      <c r="C163" t="s">
+        <v>37</v>
+      </c>
+      <c r="D163" t="s">
+        <v>754</v>
+      </c>
+      <c r="E163" t="s">
+        <v>177</v>
+      </c>
+      <c r="F163" t="s">
+        <v>101</v>
+      </c>
+      <c r="G163" t="s">
         <v>755</v>
-      </c>
-      <c r="C163" t="s">
-        <v>33</v>
-      </c>
-      <c r="D163" t="s">
-        <v>751</v>
-      </c>
-      <c r="E163" t="s">
-        <v>752</v>
-      </c>
-      <c r="F163" t="s">
-        <v>753</v>
-      </c>
-      <c r="G163" t="s">
-        <v>754</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -8404,7 +8359,7 @@
         <v>756</v>
       </c>
       <c r="C164" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D164" t="s">
         <v>757</v>
@@ -8416,7 +8371,7 @@
         <v>759</v>
       </c>
       <c r="G164" t="s">
-        <v>331</v>
+        <v>102</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -8427,19 +8382,19 @@
         <v>760</v>
       </c>
       <c r="C165" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D165" t="s">
         <v>761</v>
       </c>
       <c r="E165" t="s">
-        <v>131</v>
+        <v>762</v>
       </c>
       <c r="F165" t="s">
-        <v>132</v>
+        <v>763</v>
       </c>
       <c r="G165" t="s">
-        <v>762</v>
+        <v>28</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -8447,22 +8402,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>764</v>
+      </c>
+      <c r="C166" t="s">
+        <v>53</v>
+      </c>
+      <c r="D166" t="s">
+        <v>761</v>
+      </c>
+      <c r="E166" t="s">
+        <v>762</v>
+      </c>
+      <c r="F166" t="s">
         <v>763</v>
       </c>
-      <c r="C166" t="s">
-        <v>37</v>
-      </c>
-      <c r="D166" t="s">
-        <v>764</v>
-      </c>
-      <c r="E166" t="s">
-        <v>177</v>
-      </c>
-      <c r="F166" t="s">
-        <v>101</v>
-      </c>
       <c r="G166" t="s">
-        <v>765</v>
+        <v>28</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -8470,22 +8425,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>765</v>
+      </c>
+      <c r="C167" t="s">
+        <v>53</v>
+      </c>
+      <c r="D167" t="s">
         <v>766</v>
       </c>
-      <c r="C167" t="s">
-        <v>34</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>767</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>768</v>
       </c>
-      <c r="F167" t="s">
-        <v>769</v>
-      </c>
       <c r="G167" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -8493,22 +8448,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C168" t="s">
         <v>53</v>
       </c>
       <c r="D168" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E168" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="F168" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="G168" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -8516,10 +8471,10 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C169" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D169" t="s">
         <v>771</v>
@@ -8531,7 +8486,7 @@
         <v>773</v>
       </c>
       <c r="G169" t="s">
-        <v>28</v>
+        <v>774</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -8542,19 +8497,19 @@
         <v>775</v>
       </c>
       <c r="C170" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D170" t="s">
         <v>776</v>
       </c>
       <c r="E170" t="s">
-        <v>777</v>
+        <v>210</v>
       </c>
       <c r="F170" t="s">
-        <v>778</v>
+        <v>211</v>
       </c>
       <c r="G170" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -8562,22 +8517,22 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C171" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D171" t="s">
         <v>776</v>
       </c>
       <c r="E171" t="s">
-        <v>777</v>
+        <v>210</v>
       </c>
       <c r="F171" t="s">
-        <v>778</v>
+        <v>211</v>
       </c>
       <c r="G171" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -8585,22 +8540,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>778</v>
+      </c>
+      <c r="C172" t="s">
+        <v>39</v>
+      </c>
+      <c r="D172" t="s">
+        <v>779</v>
+      </c>
+      <c r="E172" t="s">
         <v>780</v>
       </c>
-      <c r="C172" t="s">
-        <v>70</v>
-      </c>
-      <c r="D172" t="s">
+      <c r="F172" t="s">
         <v>781</v>
       </c>
-      <c r="E172" t="s">
-        <v>782</v>
-      </c>
-      <c r="F172" t="s">
-        <v>783</v>
-      </c>
       <c r="G172" t="s">
-        <v>784</v>
+        <v>29</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -8608,22 +8563,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C173" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E173" t="s">
-        <v>210</v>
+        <v>435</v>
       </c>
       <c r="F173" t="s">
-        <v>211</v>
+        <v>7</v>
       </c>
       <c r="G173" t="s">
-        <v>125</v>
+        <v>784</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -8631,22 +8586,22 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C174" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D174" t="s">
         <v>786</v>
       </c>
       <c r="E174" t="s">
-        <v>210</v>
+        <v>787</v>
       </c>
       <c r="F174" t="s">
-        <v>211</v>
+        <v>788</v>
       </c>
       <c r="G174" t="s">
-        <v>125</v>
+        <v>789</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -8654,22 +8609,22 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C175" t="s">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="D175" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E175" t="s">
-        <v>790</v>
+        <v>129</v>
       </c>
       <c r="F175" t="s">
-        <v>791</v>
+        <v>130</v>
       </c>
       <c r="G175" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -8680,19 +8635,19 @@
         <v>792</v>
       </c>
       <c r="C176" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="D176" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E176" t="s">
-        <v>435</v>
+        <v>129</v>
       </c>
       <c r="F176" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="G176" t="s">
-        <v>794</v>
+        <v>128</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -8700,22 +8655,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>793</v>
+      </c>
+      <c r="C177" t="s">
+        <v>39</v>
+      </c>
+      <c r="D177" t="s">
+        <v>794</v>
+      </c>
+      <c r="E177" t="s">
+        <v>158</v>
+      </c>
+      <c r="F177" t="s">
+        <v>159</v>
+      </c>
+      <c r="G177" t="s">
         <v>795</v>
-      </c>
-      <c r="C177" t="s">
-        <v>59</v>
-      </c>
-      <c r="D177" t="s">
-        <v>796</v>
-      </c>
-      <c r="E177" t="s">
-        <v>797</v>
-      </c>
-      <c r="F177" t="s">
-        <v>798</v>
-      </c>
-      <c r="G177" t="s">
-        <v>799</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -8723,22 +8678,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C178" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="D178" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E178" t="s">
-        <v>129</v>
+        <v>456</v>
       </c>
       <c r="F178" t="s">
-        <v>130</v>
+        <v>457</v>
       </c>
       <c r="G178" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -8746,22 +8701,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C179" t="s">
-        <v>146</v>
+        <v>69</v>
       </c>
       <c r="D179" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E179" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="F179" t="s">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="G179" t="s">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -8769,22 +8724,22 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C180" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D180" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="E180" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="F180" t="s">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="G180" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -8792,22 +8747,22 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>802</v>
+      </c>
+      <c r="C181" t="s">
+        <v>36</v>
+      </c>
+      <c r="D181" t="s">
+        <v>803</v>
+      </c>
+      <c r="E181" t="s">
+        <v>804</v>
+      </c>
+      <c r="F181" t="s">
+        <v>805</v>
+      </c>
+      <c r="G181" t="s">
         <v>806</v>
-      </c>
-      <c r="C181" t="s">
-        <v>46</v>
-      </c>
-      <c r="D181" t="s">
-        <v>807</v>
-      </c>
-      <c r="E181" t="s">
-        <v>456</v>
-      </c>
-      <c r="F181" t="s">
-        <v>457</v>
-      </c>
-      <c r="G181" t="s">
-        <v>66</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -8815,22 +8770,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C182" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="D182" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E182" t="s">
-        <v>85</v>
+        <v>804</v>
       </c>
       <c r="F182" t="s">
-        <v>7</v>
+        <v>805</v>
       </c>
       <c r="G182" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -8838,22 +8793,22 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C183" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D183" t="s">
         <v>809</v>
       </c>
       <c r="E183" t="s">
-        <v>85</v>
+        <v>810</v>
       </c>
       <c r="F183" t="s">
-        <v>7</v>
+        <v>811</v>
       </c>
       <c r="G183" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -8861,22 +8816,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C184" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D184" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E184" t="s">
-        <v>814</v>
+        <v>345</v>
       </c>
       <c r="F184" t="s">
+        <v>44</v>
+      </c>
+      <c r="G184" t="s">
         <v>815</v>
-      </c>
-      <c r="G184" t="s">
-        <v>816</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -8884,22 +8839,22 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C185" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D185" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E185" t="s">
-        <v>814</v>
+        <v>345</v>
       </c>
       <c r="F185" t="s">
+        <v>44</v>
+      </c>
+      <c r="G185" t="s">
         <v>815</v>
-      </c>
-      <c r="G185" t="s">
-        <v>816</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -8907,22 +8862,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>817</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D186" t="s">
         <v>818</v>
       </c>
-      <c r="C186" t="s">
-        <v>146</v>
-      </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>819</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>820</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>821</v>
-      </c>
-      <c r="G186" t="s">
-        <v>822</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -8930,22 +8885,22 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>822</v>
+      </c>
+      <c r="C187" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" t="s">
         <v>823</v>
       </c>
-      <c r="C187" t="s">
-        <v>43</v>
-      </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
+        <v>676</v>
+      </c>
+      <c r="F187" t="s">
+        <v>677</v>
+      </c>
+      <c r="G187" t="s">
         <v>824</v>
-      </c>
-      <c r="E187" t="s">
-        <v>345</v>
-      </c>
-      <c r="F187" t="s">
-        <v>44</v>
-      </c>
-      <c r="G187" t="s">
-        <v>825</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -8953,22 +8908,22 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>826</v>
+        <v>171</v>
       </c>
       <c r="C188" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D188" t="s">
-        <v>824</v>
+        <v>172</v>
       </c>
       <c r="E188" t="s">
-        <v>345</v>
+        <v>173</v>
       </c>
       <c r="F188" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="G188" t="s">
-        <v>825</v>
+        <v>175</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -8976,22 +8931,22 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>827</v>
+        <v>176</v>
       </c>
       <c r="C189" t="s">
-        <v>1418</v>
+        <v>56</v>
       </c>
       <c r="D189" t="s">
-        <v>828</v>
+        <v>172</v>
       </c>
       <c r="E189" t="s">
-        <v>829</v>
+        <v>173</v>
       </c>
       <c r="F189" t="s">
-        <v>830</v>
+        <v>174</v>
       </c>
       <c r="G189" t="s">
-        <v>831</v>
+        <v>175</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -8999,22 +8954,22 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C190" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D190" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E190" t="s">
-        <v>680</v>
+        <v>827</v>
       </c>
       <c r="F190" t="s">
-        <v>681</v>
+        <v>828</v>
       </c>
       <c r="G190" t="s">
-        <v>834</v>
+        <v>58</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -9022,22 +8977,22 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>171</v>
+        <v>829</v>
       </c>
       <c r="C191" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D191" t="s">
-        <v>172</v>
+        <v>830</v>
       </c>
       <c r="E191" t="s">
-        <v>173</v>
+        <v>831</v>
       </c>
       <c r="F191" t="s">
-        <v>174</v>
+        <v>832</v>
       </c>
       <c r="G191" t="s">
-        <v>175</v>
+        <v>331</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -9045,22 +9000,22 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>176</v>
+        <v>833</v>
       </c>
       <c r="C192" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D192" t="s">
-        <v>172</v>
+        <v>834</v>
       </c>
       <c r="E192" t="s">
-        <v>173</v>
+        <v>835</v>
       </c>
       <c r="F192" t="s">
-        <v>174</v>
+        <v>836</v>
       </c>
       <c r="G192" t="s">
-        <v>175</v>
+        <v>13</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -9068,22 +9023,22 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C193" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D193" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E193" t="s">
-        <v>837</v>
+        <v>14</v>
       </c>
       <c r="F193" t="s">
-        <v>838</v>
+        <v>15</v>
       </c>
       <c r="G193" t="s">
-        <v>58</v>
+        <v>839</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -9091,22 +9046,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>840</v>
+      </c>
+      <c r="C194" t="s">
+        <v>19</v>
+      </c>
+      <c r="D194" t="s">
+        <v>838</v>
+      </c>
+      <c r="E194" t="s">
+        <v>14</v>
+      </c>
+      <c r="F194" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" t="s">
         <v>839</v>
-      </c>
-      <c r="C194" t="s">
-        <v>36</v>
-      </c>
-      <c r="D194" t="s">
-        <v>840</v>
-      </c>
-      <c r="E194" t="s">
-        <v>841</v>
-      </c>
-      <c r="F194" t="s">
-        <v>842</v>
-      </c>
-      <c r="G194" t="s">
-        <v>331</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -9114,22 +9069,22 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C195" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D195" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="E195" t="s">
-        <v>845</v>
+        <v>14</v>
       </c>
       <c r="F195" t="s">
-        <v>846</v>
+        <v>15</v>
       </c>
       <c r="G195" t="s">
-        <v>13</v>
+        <v>839</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -9137,22 +9092,22 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C196" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D196" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="E196" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F196" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="G196" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -9160,22 +9115,22 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C197" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="E197" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F197" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="G197" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -9183,22 +9138,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C198" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D198" t="s">
+        <v>847</v>
+      </c>
+      <c r="E198" t="s">
         <v>848</v>
       </c>
-      <c r="E198" t="s">
-        <v>14</v>
-      </c>
       <c r="F198" t="s">
-        <v>15</v>
+        <v>849</v>
       </c>
       <c r="G198" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -9206,22 +9161,22 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>851</v>
+      </c>
+      <c r="C199" t="s">
+        <v>59</v>
+      </c>
+      <c r="D199" t="s">
         <v>852</v>
       </c>
-      <c r="C199" t="s">
-        <v>70</v>
-      </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
         <v>853</v>
       </c>
-      <c r="E199" t="s">
-        <v>61</v>
-      </c>
       <c r="F199" t="s">
-        <v>62</v>
+        <v>854</v>
       </c>
       <c r="G199" t="s">
-        <v>854</v>
+        <v>38</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -9232,19 +9187,19 @@
         <v>855</v>
       </c>
       <c r="C200" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D200" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E200" t="s">
-        <v>61</v>
+        <v>857</v>
       </c>
       <c r="F200" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="G200" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -9252,22 +9207,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C201" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D201" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E201" t="s">
-        <v>858</v>
+        <v>212</v>
       </c>
       <c r="F201" t="s">
-        <v>859</v>
+        <v>7</v>
       </c>
       <c r="G201" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -9275,22 +9230,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C202" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E202" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F202" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G202" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -9298,22 +9253,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C203" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D203" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E203" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F203" t="s">
-        <v>96</v>
+        <v>869</v>
       </c>
       <c r="G203" t="s">
-        <v>868</v>
+        <v>72</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -9321,22 +9276,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C204" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="D204" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E204" t="s">
-        <v>212</v>
+        <v>872</v>
       </c>
       <c r="F204" t="s">
-        <v>7</v>
+        <v>873</v>
       </c>
       <c r="G204" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -9344,22 +9299,22 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C205" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D205" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E205" t="s">
-        <v>874</v>
+        <v>451</v>
       </c>
       <c r="F205" t="s">
-        <v>875</v>
+        <v>452</v>
       </c>
       <c r="G205" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -9367,22 +9322,22 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C206" t="s">
         <v>34</v>
       </c>
       <c r="D206" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E206" t="s">
-        <v>878</v>
+        <v>451</v>
       </c>
       <c r="F206" t="s">
-        <v>879</v>
+        <v>452</v>
       </c>
       <c r="G206" t="s">
-        <v>880</v>
+        <v>72</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -9390,22 +9345,22 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>878</v>
+      </c>
+      <c r="C207" t="s">
+        <v>145</v>
+      </c>
+      <c r="D207" t="s">
+        <v>879</v>
+      </c>
+      <c r="E207" t="s">
+        <v>880</v>
+      </c>
+      <c r="F207" t="s">
         <v>881</v>
       </c>
-      <c r="C207" t="s">
-        <v>51</v>
-      </c>
-      <c r="D207" t="s">
-        <v>882</v>
-      </c>
-      <c r="E207" t="s">
-        <v>883</v>
-      </c>
-      <c r="F207" t="s">
-        <v>884</v>
-      </c>
       <c r="G207" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -9413,22 +9368,22 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>882</v>
+      </c>
+      <c r="C208" t="s">
+        <v>241</v>
+      </c>
+      <c r="D208" t="s">
+        <v>883</v>
+      </c>
+      <c r="E208" t="s">
+        <v>884</v>
+      </c>
+      <c r="F208" t="s">
+        <v>7</v>
+      </c>
+      <c r="G208" t="s">
         <v>885</v>
-      </c>
-      <c r="C208" t="s">
-        <v>145</v>
-      </c>
-      <c r="D208" t="s">
-        <v>886</v>
-      </c>
-      <c r="E208" t="s">
-        <v>887</v>
-      </c>
-      <c r="F208" t="s">
-        <v>888</v>
-      </c>
-      <c r="G208" t="s">
-        <v>889</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -9436,22 +9391,22 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C209" t="s">
         <v>34</v>
       </c>
       <c r="D209" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="E209" t="s">
-        <v>451</v>
+        <v>888</v>
       </c>
       <c r="F209" t="s">
-        <v>452</v>
+        <v>889</v>
       </c>
       <c r="G209" t="s">
-        <v>72</v>
+        <v>890</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -9459,22 +9414,22 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>891</v>
+      </c>
+      <c r="C210" t="s">
+        <v>50</v>
+      </c>
+      <c r="D210" t="s">
         <v>892</v>
       </c>
-      <c r="C210" t="s">
-        <v>34</v>
-      </c>
-      <c r="D210" t="s">
-        <v>891</v>
-      </c>
       <c r="E210" t="s">
-        <v>451</v>
+        <v>149</v>
       </c>
       <c r="F210" t="s">
-        <v>452</v>
+        <v>150</v>
       </c>
       <c r="G210" t="s">
-        <v>72</v>
+        <v>893</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -9482,22 +9437,22 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C211" t="s">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="D211" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E211" t="s">
-        <v>895</v>
+        <v>167</v>
       </c>
       <c r="F211" t="s">
+        <v>7</v>
+      </c>
+      <c r="G211" t="s">
         <v>896</v>
-      </c>
-      <c r="G211" t="s">
-        <v>67</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -9508,7 +9463,7 @@
         <v>897</v>
       </c>
       <c r="C212" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="D212" t="s">
         <v>898</v>
@@ -9517,10 +9472,10 @@
         <v>899</v>
       </c>
       <c r="F212" t="s">
-        <v>7</v>
+        <v>900</v>
       </c>
       <c r="G212" t="s">
-        <v>900</v>
+        <v>124</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -9531,7 +9486,7 @@
         <v>901</v>
       </c>
       <c r="C213" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D213" t="s">
         <v>902</v>
@@ -9543,7 +9498,7 @@
         <v>904</v>
       </c>
       <c r="G213" t="s">
-        <v>905</v>
+        <v>20</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -9551,22 +9506,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>905</v>
+      </c>
+      <c r="C214" t="s">
+        <v>145</v>
+      </c>
+      <c r="D214" t="s">
         <v>906</v>
       </c>
-      <c r="C214" t="s">
-        <v>50</v>
-      </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>907</v>
       </c>
-      <c r="E214" t="s">
-        <v>149</v>
-      </c>
       <c r="F214" t="s">
-        <v>150</v>
+        <v>908</v>
       </c>
       <c r="G214" t="s">
-        <v>908</v>
+        <v>331</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -9577,16 +9532,16 @@
         <v>909</v>
       </c>
       <c r="C215" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="D215" t="s">
         <v>910</v>
       </c>
       <c r="E215" t="s">
-        <v>167</v>
+        <v>287</v>
       </c>
       <c r="F215" t="s">
-        <v>7</v>
+        <v>288</v>
       </c>
       <c r="G215" t="s">
         <v>911</v>
@@ -9600,7 +9555,7 @@
         <v>912</v>
       </c>
       <c r="C216" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D216" t="s">
         <v>913</v>
@@ -9609,10 +9564,10 @@
         <v>914</v>
       </c>
       <c r="F216" t="s">
+        <v>7</v>
+      </c>
+      <c r="G216" t="s">
         <v>915</v>
-      </c>
-      <c r="G216" t="s">
-        <v>124</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -9623,19 +9578,19 @@
         <v>916</v>
       </c>
       <c r="C217" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="D217" t="s">
         <v>917</v>
       </c>
       <c r="E217" t="s">
-        <v>918</v>
+        <v>193</v>
       </c>
       <c r="F217" t="s">
-        <v>919</v>
+        <v>7</v>
       </c>
       <c r="G217" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -9643,22 +9598,22 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>918</v>
+      </c>
+      <c r="C218" t="s">
+        <v>408</v>
+      </c>
+      <c r="D218" t="s">
+        <v>919</v>
+      </c>
+      <c r="E218" t="s">
         <v>920</v>
       </c>
-      <c r="C218" t="s">
-        <v>145</v>
-      </c>
-      <c r="D218" t="s">
+      <c r="F218" t="s">
         <v>921</v>
       </c>
-      <c r="E218" t="s">
-        <v>922</v>
-      </c>
-      <c r="F218" t="s">
-        <v>923</v>
-      </c>
       <c r="G218" t="s">
-        <v>331</v>
+        <v>162</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -9666,19 +9621,19 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>922</v>
+      </c>
+      <c r="C219" t="s">
+        <v>56</v>
+      </c>
+      <c r="D219" t="s">
+        <v>923</v>
+      </c>
+      <c r="E219" t="s">
         <v>924</v>
       </c>
-      <c r="C219" t="s">
-        <v>49</v>
-      </c>
-      <c r="D219" t="s">
+      <c r="F219" t="s">
         <v>925</v>
-      </c>
-      <c r="E219" t="s">
-        <v>287</v>
-      </c>
-      <c r="F219" t="s">
-        <v>288</v>
       </c>
       <c r="G219" t="s">
         <v>926</v>
@@ -9692,7 +9647,7 @@
         <v>927</v>
       </c>
       <c r="C220" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D220" t="s">
         <v>928</v>
@@ -9701,10 +9656,10 @@
         <v>929</v>
       </c>
       <c r="F220" t="s">
-        <v>7</v>
+        <v>930</v>
       </c>
       <c r="G220" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -9712,22 +9667,22 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C221" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="D221" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E221" t="s">
-        <v>193</v>
+        <v>934</v>
       </c>
       <c r="F221" t="s">
-        <v>7</v>
+        <v>935</v>
       </c>
       <c r="G221" t="s">
-        <v>194</v>
+        <v>936</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -9735,22 +9690,22 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="C222" t="s">
-        <v>408</v>
+        <v>41</v>
       </c>
       <c r="D222" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="E222" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="F222" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="G222" t="s">
-        <v>162</v>
+        <v>941</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -9758,22 +9713,22 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C223" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D223" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="E223" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="F223" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="G223" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -9781,22 +9736,22 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C224" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="D224" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="E224" t="s">
-        <v>944</v>
+        <v>84</v>
       </c>
       <c r="F224" t="s">
-        <v>945</v>
+        <v>7</v>
       </c>
       <c r="G224" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -9804,22 +9759,22 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C225" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D225" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E225" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="F225" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="G225" t="s">
-        <v>951</v>
+        <v>68</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -9827,19 +9782,19 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C226" t="s">
-        <v>41</v>
+        <v>255</v>
       </c>
       <c r="D226" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="E226" t="s">
-        <v>954</v>
+        <v>184</v>
       </c>
       <c r="F226" t="s">
-        <v>955</v>
+        <v>35</v>
       </c>
       <c r="G226" t="s">
         <v>956</v>
@@ -9853,19 +9808,19 @@
         <v>957</v>
       </c>
       <c r="C227" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D227" t="s">
         <v>958</v>
       </c>
       <c r="E227" t="s">
-        <v>959</v>
+        <v>208</v>
       </c>
       <c r="F227" t="s">
-        <v>960</v>
+        <v>209</v>
       </c>
       <c r="G227" t="s">
-        <v>961</v>
+        <v>103</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -9873,22 +9828,22 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C228" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="D228" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="E228" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="F228" t="s">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="G228" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -9896,22 +9851,22 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C229" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D229" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="E229" t="s">
-        <v>967</v>
+        <v>165</v>
       </c>
       <c r="F229" t="s">
-        <v>968</v>
+        <v>166</v>
       </c>
       <c r="G229" t="s">
-        <v>68</v>
+        <v>961</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -9919,22 +9874,22 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C230" t="s">
-        <v>255</v>
+        <v>9</v>
       </c>
       <c r="D230" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="E230" t="s">
-        <v>184</v>
+        <v>965</v>
       </c>
       <c r="F230" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G230" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -9942,22 +9897,22 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="C231" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D231" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="E231" t="s">
-        <v>208</v>
+        <v>969</v>
       </c>
       <c r="F231" t="s">
-        <v>209</v>
+        <v>970</v>
       </c>
       <c r="G231" t="s">
-        <v>103</v>
+        <v>971</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -9965,19 +9920,19 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>972</v>
+      </c>
+      <c r="C232" t="s">
+        <v>46</v>
+      </c>
+      <c r="D232" t="s">
+        <v>973</v>
+      </c>
+      <c r="E232" t="s">
         <v>974</v>
       </c>
-      <c r="C232" t="s">
-        <v>49</v>
-      </c>
-      <c r="D232" t="s">
+      <c r="F232" t="s">
         <v>975</v>
-      </c>
-      <c r="E232" t="s">
-        <v>165</v>
-      </c>
-      <c r="F232" t="s">
-        <v>166</v>
       </c>
       <c r="G232" t="s">
         <v>976</v>
@@ -9991,19 +9946,19 @@
         <v>977</v>
       </c>
       <c r="C233" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D233" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="E233" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F233" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G233" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -10011,22 +9966,22 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>980</v>
+      </c>
+      <c r="C234" t="s">
+        <v>56</v>
+      </c>
+      <c r="D234" t="s">
         <v>978</v>
       </c>
-      <c r="C234" t="s">
-        <v>9</v>
-      </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
+        <v>147</v>
+      </c>
+      <c r="F234" t="s">
+        <v>148</v>
+      </c>
+      <c r="G234" t="s">
         <v>979</v>
-      </c>
-      <c r="E234" t="s">
-        <v>980</v>
-      </c>
-      <c r="F234" t="s">
-        <v>7</v>
-      </c>
-      <c r="G234" t="s">
-        <v>981</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -10034,22 +9989,22 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>981</v>
+      </c>
+      <c r="C235" t="s">
+        <v>33</v>
+      </c>
+      <c r="D235" t="s">
         <v>982</v>
       </c>
-      <c r="C235" t="s">
-        <v>53</v>
-      </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>983</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>984</v>
       </c>
-      <c r="F235" t="s">
-        <v>985</v>
-      </c>
       <c r="G235" t="s">
-        <v>986</v>
+        <v>331</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -10057,114 +10012,114 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>985</v>
+      </c>
+      <c r="C236" t="s">
+        <v>25</v>
+      </c>
+      <c r="D236" t="s">
+        <v>986</v>
+      </c>
+      <c r="E236" t="s">
         <v>987</v>
       </c>
-      <c r="C236" t="s">
-        <v>46</v>
-      </c>
-      <c r="D236" t="s">
+      <c r="F236" t="s">
+        <v>7</v>
+      </c>
+      <c r="G236" t="s">
         <v>988</v>
       </c>
-      <c r="E236" t="s">
-        <v>989</v>
-      </c>
-      <c r="F236" t="s">
-        <v>990</v>
-      </c>
-      <c r="G236" t="s">
-        <v>991</v>
-      </c>
       <c r="H236" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C237" t="s">
-        <v>56</v>
+        <v>279</v>
       </c>
       <c r="D237" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E237" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="F237" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="G237" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="H237" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C238" t="s">
-        <v>56</v>
+        <v>279</v>
       </c>
       <c r="D238" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E238" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="F238" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="G238" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="H238" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C239" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D239" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="E239" t="s">
-        <v>998</v>
+        <v>160</v>
       </c>
       <c r="F239" t="s">
-        <v>999</v>
+        <v>161</v>
       </c>
       <c r="G239" t="s">
-        <v>331</v>
+        <v>995</v>
       </c>
       <c r="H239" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C240" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D240" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="E240" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="F240" t="s">
         <v>7</v>
       </c>
       <c r="G240" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="H240" t="s">
         <v>111</v>
@@ -10172,22 +10127,22 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C241" t="s">
-        <v>279</v>
+        <v>183</v>
       </c>
       <c r="D241" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="E241" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="F241" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="G241" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="H241" t="s">
         <v>111</v>
@@ -10195,22 +10150,22 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C242" t="s">
-        <v>279</v>
+        <v>56</v>
       </c>
       <c r="D242" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E242" t="s">
+        <v>147</v>
+      </c>
+      <c r="F242" t="s">
+        <v>148</v>
+      </c>
+      <c r="G242" t="s">
         <v>1005</v>
-      </c>
-      <c r="E242" t="s">
-        <v>187</v>
-      </c>
-      <c r="F242" t="s">
-        <v>188</v>
-      </c>
-      <c r="G242" t="s">
-        <v>1006</v>
       </c>
       <c r="H242" t="s">
         <v>111</v>
@@ -10218,19 +10173,19 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C243" t="s">
+        <v>56</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E243" t="s">
         <v>1008</v>
       </c>
-      <c r="C243" t="s">
-        <v>45</v>
-      </c>
-      <c r="D243" t="s">
+      <c r="F243" t="s">
         <v>1009</v>
-      </c>
-      <c r="E243" t="s">
-        <v>160</v>
-      </c>
-      <c r="F243" t="s">
-        <v>161</v>
       </c>
       <c r="G243" t="s">
         <v>1010</v>
@@ -10244,7 +10199,7 @@
         <v>1011</v>
       </c>
       <c r="C244" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D244" t="s">
         <v>1012</v>
@@ -10253,10 +10208,10 @@
         <v>1013</v>
       </c>
       <c r="F244" t="s">
-        <v>7</v>
+        <v>1014</v>
       </c>
       <c r="G244" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H244" t="s">
         <v>111</v>
@@ -10264,206 +10219,206 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C245" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="D245" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E245" t="s">
-        <v>84</v>
+        <v>1018</v>
       </c>
       <c r="F245" t="s">
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="H245" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="C246" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D246" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="E246" t="s">
-        <v>147</v>
+        <v>1022</v>
       </c>
       <c r="F246" t="s">
-        <v>148</v>
+        <v>1023</v>
       </c>
       <c r="G246" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="H246" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C247" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D247" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="E247" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="F247" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="G247" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="H247" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C248" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D248" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="E248" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="F248" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="G248" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="H248" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C249" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D249" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E249" t="s">
-        <v>1033</v>
+        <v>178</v>
       </c>
       <c r="F249" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="G249" t="s">
-        <v>1034</v>
+        <v>58</v>
       </c>
       <c r="H249" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1035</v>
+        <v>180</v>
       </c>
       <c r="C250" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="D250" t="s">
-        <v>1036</v>
+        <v>181</v>
       </c>
       <c r="E250" t="s">
-        <v>1037</v>
+        <v>106</v>
       </c>
       <c r="F250" t="s">
-        <v>1038</v>
+        <v>107</v>
       </c>
       <c r="G250" t="s">
-        <v>1039</v>
+        <v>182</v>
       </c>
       <c r="H250" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C251" t="s">
+        <v>49</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E251" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F251" t="s">
         <v>1040</v>
       </c>
-      <c r="C251" t="s">
-        <v>41</v>
-      </c>
-      <c r="D251" t="s">
+      <c r="G251" t="s">
         <v>1041</v>
       </c>
-      <c r="E251" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F251" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G251" t="s">
-        <v>1044</v>
-      </c>
       <c r="H251" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C252" t="s">
+        <v>408</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F252" t="s">
+        <v>479</v>
+      </c>
+      <c r="G252" t="s">
         <v>1045</v>
       </c>
-      <c r="C252" t="s">
-        <v>146</v>
-      </c>
-      <c r="D252" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E252" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F252" t="s">
-        <v>1048</v>
-      </c>
-      <c r="G252" t="s">
-        <v>1049</v>
-      </c>
       <c r="H252" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C253" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D253" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="E253" t="s">
-        <v>178</v>
+        <v>1048</v>
       </c>
       <c r="F253" t="s">
-        <v>179</v>
+        <v>1049</v>
       </c>
       <c r="G253" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H253" t="s">
         <v>10</v>
@@ -10471,22 +10426,22 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>180</v>
+        <v>1050</v>
       </c>
       <c r="C254" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D254" t="s">
-        <v>181</v>
+        <v>1051</v>
       </c>
       <c r="E254" t="s">
-        <v>106</v>
+        <v>1052</v>
       </c>
       <c r="F254" t="s">
-        <v>107</v>
+        <v>1053</v>
       </c>
       <c r="G254" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="H254" t="s">
         <v>10</v>
@@ -10494,22 +10449,22 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="C255" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D255" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="E255" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F255" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="G255" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="H255" t="s">
         <v>10</v>
@@ -10517,22 +10472,22 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C256" t="s">
-        <v>408</v>
+        <v>71</v>
       </c>
       <c r="D256" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E256" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F256" t="s">
-        <v>479</v>
+        <v>7</v>
       </c>
       <c r="G256" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="H256" t="s">
         <v>10</v>
@@ -10540,22 +10495,22 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C257" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D257" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E257" t="s">
-        <v>1063</v>
+        <v>133</v>
       </c>
       <c r="F257" t="s">
-        <v>1064</v>
+        <v>7</v>
       </c>
       <c r="G257" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="H257" t="s">
         <v>10</v>
@@ -10566,7 +10521,7 @@
         <v>1065</v>
       </c>
       <c r="C258" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D258" t="s">
         <v>1066</v>
@@ -10575,10 +10530,10 @@
         <v>1067</v>
       </c>
       <c r="F258" t="s">
+        <v>7</v>
+      </c>
+      <c r="G258" t="s">
         <v>1068</v>
-      </c>
-      <c r="G258" t="s">
-        <v>60</v>
       </c>
       <c r="H258" t="s">
         <v>10</v>
@@ -10589,19 +10544,19 @@
         <v>1069</v>
       </c>
       <c r="C259" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="D259" t="s">
         <v>1070</v>
       </c>
       <c r="E259" t="s">
+        <v>85</v>
+      </c>
+      <c r="F259" t="s">
+        <v>7</v>
+      </c>
+      <c r="G259" t="s">
         <v>1071</v>
-      </c>
-      <c r="F259" t="s">
-        <v>1072</v>
-      </c>
-      <c r="G259" t="s">
-        <v>1073</v>
       </c>
       <c r="H259" t="s">
         <v>10</v>
@@ -10609,22 +10564,22 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C260" t="s">
+        <v>45</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E260" t="s">
         <v>1074</v>
       </c>
-      <c r="C260" t="s">
-        <v>71</v>
-      </c>
-      <c r="D260" t="s">
+      <c r="F260" t="s">
         <v>1075</v>
       </c>
-      <c r="E260" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F260" t="s">
-        <v>7</v>
-      </c>
       <c r="G260" t="s">
-        <v>1077</v>
+        <v>216</v>
       </c>
       <c r="H260" t="s">
         <v>10</v>
@@ -10632,22 +10587,22 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C261" t="s">
+        <v>54</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E261" t="s">
         <v>1078</v>
       </c>
-      <c r="C261" t="s">
-        <v>18</v>
-      </c>
-      <c r="D261" t="s">
+      <c r="F261" t="s">
         <v>1079</v>
       </c>
-      <c r="E261" t="s">
-        <v>133</v>
-      </c>
-      <c r="F261" t="s">
-        <v>7</v>
-      </c>
       <c r="G261" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="H261" t="s">
         <v>10</v>
@@ -10658,19 +10613,19 @@
         <v>1080</v>
       </c>
       <c r="C262" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D262" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E262" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="F262" t="s">
-        <v>7</v>
+        <v>1079</v>
       </c>
       <c r="G262" t="s">
-        <v>1083</v>
+        <v>13</v>
       </c>
       <c r="H262" t="s">
         <v>10</v>
@@ -10678,22 +10633,22 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C263" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D263" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="E263" t="s">
-        <v>85</v>
+        <v>1078</v>
       </c>
       <c r="F263" t="s">
-        <v>7</v>
+        <v>1079</v>
       </c>
       <c r="G263" t="s">
-        <v>1086</v>
+        <v>13</v>
       </c>
       <c r="H263" t="s">
         <v>10</v>
@@ -10701,22 +10656,22 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="C264" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D264" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="E264" t="s">
-        <v>1089</v>
+        <v>89</v>
       </c>
       <c r="F264" t="s">
-        <v>1090</v>
+        <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>216</v>
+        <v>1084</v>
       </c>
       <c r="H264" t="s">
         <v>10</v>
@@ -10724,22 +10679,22 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="C265" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D265" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="E265" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F265" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="G265" t="s">
-        <v>13</v>
+        <v>1089</v>
       </c>
       <c r="H265" t="s">
         <v>10</v>
@@ -10747,22 +10702,22 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="C266" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D266" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="E266" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F266" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="G266" t="s">
-        <v>13</v>
+        <v>1089</v>
       </c>
       <c r="H266" t="s">
         <v>10</v>
@@ -10770,10 +10725,10 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="C267" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D267" t="s">
         <v>1092</v>
@@ -10782,10 +10737,10 @@
         <v>1093</v>
       </c>
       <c r="F267" t="s">
+        <v>7</v>
+      </c>
+      <c r="G267" t="s">
         <v>1094</v>
-      </c>
-      <c r="G267" t="s">
-        <v>13</v>
       </c>
       <c r="H267" t="s">
         <v>10</v>
@@ -10793,22 +10748,22 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C268" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="D268" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="E268" t="s">
-        <v>89</v>
+        <v>1093</v>
       </c>
       <c r="F268" t="s">
         <v>7</v>
       </c>
       <c r="G268" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="H268" t="s">
         <v>10</v>
@@ -10816,22 +10771,22 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C269" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="D269" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E269" t="s">
-        <v>1102</v>
+        <v>123</v>
       </c>
       <c r="F269" t="s">
-        <v>1103</v>
+        <v>64</v>
       </c>
       <c r="G269" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="H269" t="s">
         <v>10</v>
@@ -10839,22 +10794,22 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="C270" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="D270" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E270" t="s">
-        <v>1102</v>
+        <v>123</v>
       </c>
       <c r="F270" t="s">
-        <v>1103</v>
+        <v>64</v>
       </c>
       <c r="G270" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="H270" t="s">
         <v>10</v>
@@ -10862,22 +10817,22 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="C271" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D271" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="E271" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="F271" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="G271" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="H271" t="s">
         <v>10</v>
@@ -10885,22 +10840,22 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="C272" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D272" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E272" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F272" t="s">
+        <v>96</v>
+      </c>
+      <c r="G272" t="s">
         <v>1107</v>
-      </c>
-      <c r="E272" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F272" t="s">
-        <v>7</v>
-      </c>
-      <c r="G272" t="s">
-        <v>1109</v>
       </c>
       <c r="H272" t="s">
         <v>10</v>
@@ -10908,22 +10863,22 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C273" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D273" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="E273" t="s">
-        <v>123</v>
+        <v>1106</v>
       </c>
       <c r="F273" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="G273" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="H273" t="s">
         <v>10</v>
@@ -10931,22 +10886,22 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="C274" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="D274" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="E274" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="F274" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="G274" t="s">
-        <v>1113</v>
+        <v>949</v>
       </c>
       <c r="H274" t="s">
         <v>10</v>
@@ -10954,22 +10909,22 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C275" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="D275" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="E275" t="s">
-        <v>1117</v>
+        <v>84</v>
       </c>
       <c r="F275" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="G275" t="s">
-        <v>1118</v>
+        <v>949</v>
       </c>
       <c r="H275" t="s">
         <v>10</v>
@@ -10977,22 +10932,22 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="C276" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D276" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="E276" t="s">
-        <v>1121</v>
+        <v>89</v>
       </c>
       <c r="F276" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="G276" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
       <c r="H276" t="s">
         <v>10</v>
@@ -11000,22 +10955,22 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="C277" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D277" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="E277" t="s">
-        <v>1121</v>
+        <v>99</v>
       </c>
       <c r="F277" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G277" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="H277" t="s">
         <v>10</v>
@@ -11023,22 +10978,22 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="C278" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="D278" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="E278" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="F278" t="s">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="G278" t="s">
-        <v>964</v>
+        <v>1120</v>
       </c>
       <c r="H278" t="s">
         <v>10</v>
@@ -11046,22 +11001,22 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="C279" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="D279" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="E279" t="s">
-        <v>84</v>
+        <v>810</v>
       </c>
       <c r="F279" t="s">
-        <v>7</v>
+        <v>811</v>
       </c>
       <c r="G279" t="s">
-        <v>964</v>
+        <v>1123</v>
       </c>
       <c r="H279" t="s">
         <v>10</v>
@@ -11069,22 +11024,22 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C280" t="s">
+        <v>22</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E280" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F280" t="s">
         <v>1127</v>
       </c>
-      <c r="C280" t="s">
-        <v>77</v>
-      </c>
-      <c r="D280" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E280" t="s">
-        <v>89</v>
-      </c>
-      <c r="F280" t="s">
-        <v>7</v>
-      </c>
       <c r="G280" t="s">
-        <v>1129</v>
+        <v>120</v>
       </c>
       <c r="H280" t="s">
         <v>10</v>
@@ -11092,22 +11047,22 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C281" t="s">
+        <v>65</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E281" t="s">
         <v>1130</v>
       </c>
-      <c r="C281" t="s">
-        <v>37</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
+        <v>7</v>
+      </c>
+      <c r="G281" t="s">
         <v>1131</v>
-      </c>
-      <c r="E281" t="s">
-        <v>99</v>
-      </c>
-      <c r="F281" t="s">
-        <v>100</v>
-      </c>
-      <c r="G281" t="s">
-        <v>1132</v>
       </c>
       <c r="H281" t="s">
         <v>10</v>
@@ -11115,22 +11070,22 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C282" t="s">
+        <v>9</v>
+      </c>
+      <c r="D282" t="s">
         <v>1133</v>
       </c>
-      <c r="C282" t="s">
-        <v>69</v>
-      </c>
-      <c r="D282" t="s">
+      <c r="E282" t="s">
+        <v>965</v>
+      </c>
+      <c r="F282" t="s">
+        <v>7</v>
+      </c>
+      <c r="G282" t="s">
         <v>1134</v>
-      </c>
-      <c r="E282" t="s">
-        <v>152</v>
-      </c>
-      <c r="F282" t="s">
-        <v>153</v>
-      </c>
-      <c r="G282" t="s">
-        <v>1135</v>
       </c>
       <c r="H282" t="s">
         <v>10</v>
@@ -11138,22 +11093,22 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C283" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="D283" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="E283" t="s">
-        <v>820</v>
+        <v>965</v>
       </c>
       <c r="F283" t="s">
-        <v>821</v>
+        <v>7</v>
       </c>
       <c r="G283" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="H283" t="s">
         <v>10</v>
@@ -11161,22 +11116,22 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C284" t="s">
+        <v>30</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F284" t="s">
+        <v>7</v>
+      </c>
+      <c r="G284" t="s">
         <v>1139</v>
-      </c>
-      <c r="C284" t="s">
-        <v>22</v>
-      </c>
-      <c r="D284" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E284" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F284" t="s">
-        <v>1142</v>
-      </c>
-      <c r="G284" t="s">
-        <v>120</v>
       </c>
       <c r="H284" t="s">
         <v>10</v>
@@ -11184,22 +11139,22 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="C285" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D285" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E285" t="s">
-        <v>1145</v>
+        <v>84</v>
       </c>
       <c r="F285" t="s">
         <v>7</v>
       </c>
       <c r="G285" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="H285" t="s">
         <v>10</v>
@@ -11207,22 +11162,22 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="C286" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D286" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E286" t="s">
-        <v>980</v>
+        <v>345</v>
       </c>
       <c r="F286" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G286" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="H286" t="s">
         <v>10</v>
@@ -11230,22 +11185,22 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="C287" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D287" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E287" t="s">
-        <v>980</v>
+        <v>345</v>
       </c>
       <c r="F287" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G287" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="H287" t="s">
         <v>10</v>
@@ -11253,22 +11208,22 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C288" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D288" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="E288" t="s">
-        <v>1153</v>
+        <v>345</v>
       </c>
       <c r="F288" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G288" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
       <c r="H288" t="s">
         <v>10</v>
@@ -11276,22 +11231,22 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="C289" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D289" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="E289" t="s">
-        <v>84</v>
+        <v>1150</v>
       </c>
       <c r="F289" t="s">
-        <v>7</v>
+        <v>1151</v>
       </c>
       <c r="G289" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="H289" t="s">
         <v>10</v>
@@ -11299,22 +11254,22 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="C290" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D290" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="E290" t="s">
-        <v>345</v>
+        <v>1155</v>
       </c>
       <c r="F290" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G290" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="H290" t="s">
         <v>10</v>
@@ -11322,22 +11277,22 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C291" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D291" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E291" t="s">
+        <v>200</v>
+      </c>
+      <c r="F291" t="s">
+        <v>201</v>
+      </c>
+      <c r="G291" t="s">
         <v>1159</v>
-      </c>
-      <c r="E291" t="s">
-        <v>345</v>
-      </c>
-      <c r="F291" t="s">
-        <v>44</v>
-      </c>
-      <c r="G291" t="s">
-        <v>1160</v>
       </c>
       <c r="H291" t="s">
         <v>10</v>
@@ -11345,22 +11300,22 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C292" t="s">
+        <v>63</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E292" t="s">
+        <v>360</v>
+      </c>
+      <c r="F292" t="s">
+        <v>64</v>
+      </c>
+      <c r="G292" t="s">
         <v>1162</v>
-      </c>
-      <c r="C292" t="s">
-        <v>43</v>
-      </c>
-      <c r="D292" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E292" t="s">
-        <v>345</v>
-      </c>
-      <c r="F292" t="s">
-        <v>44</v>
-      </c>
-      <c r="G292" t="s">
-        <v>1160</v>
       </c>
       <c r="H292" t="s">
         <v>10</v>
@@ -11371,7 +11326,7 @@
         <v>1163</v>
       </c>
       <c r="C293" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="D293" t="s">
         <v>1164</v>
@@ -11383,7 +11338,7 @@
         <v>1166</v>
       </c>
       <c r="G293" t="s">
-        <v>1167</v>
+        <v>58</v>
       </c>
       <c r="H293" t="s">
         <v>10</v>
@@ -11391,22 +11346,22 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C294" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="D294" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="E294" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F294" t="s">
-        <v>7</v>
+        <v>1166</v>
       </c>
       <c r="G294" t="s">
-        <v>1171</v>
+        <v>58</v>
       </c>
       <c r="H294" t="s">
         <v>10</v>
@@ -11414,22 +11369,22 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="C295" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D295" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="E295" t="s">
-        <v>200</v>
+        <v>1170</v>
       </c>
       <c r="F295" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="G295" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="H295" t="s">
         <v>10</v>
@@ -11437,22 +11392,22 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="C296" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D296" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="E296" t="s">
-        <v>360</v>
+        <v>1170</v>
       </c>
       <c r="F296" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="G296" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="H296" t="s">
         <v>10</v>
@@ -11460,22 +11415,22 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="C297" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D297" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="E297" t="s">
-        <v>1180</v>
+        <v>729</v>
       </c>
       <c r="F297" t="s">
-        <v>1181</v>
+        <v>730</v>
       </c>
       <c r="G297" t="s">
-        <v>58</v>
+        <v>1175</v>
       </c>
       <c r="H297" t="s">
         <v>10</v>
@@ -11483,22 +11438,22 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="C298" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D298" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E298" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F298" t="s">
         <v>1179</v>
       </c>
-      <c r="E298" t="s">
+      <c r="G298" t="s">
         <v>1180</v>
-      </c>
-      <c r="F298" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G298" t="s">
-        <v>58</v>
       </c>
       <c r="H298" t="s">
         <v>10</v>
@@ -11506,22 +11461,22 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C299" t="s">
+        <v>69</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E299" t="s">
         <v>1183</v>
-      </c>
-      <c r="C299" t="s">
-        <v>77</v>
-      </c>
-      <c r="D299" t="s">
-        <v>1184</v>
-      </c>
-      <c r="E299" t="s">
-        <v>1185</v>
       </c>
       <c r="F299" t="s">
         <v>7</v>
       </c>
       <c r="G299" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="H299" t="s">
         <v>10</v>
@@ -11529,22 +11484,22 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C300" t="s">
+        <v>31</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E300" t="s">
         <v>1187</v>
       </c>
-      <c r="C300" t="s">
-        <v>77</v>
-      </c>
-      <c r="D300" t="s">
-        <v>1184</v>
-      </c>
-      <c r="E300" t="s">
-        <v>1185</v>
-      </c>
       <c r="F300" t="s">
-        <v>7</v>
+        <v>1188</v>
       </c>
       <c r="G300" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="H300" t="s">
         <v>10</v>
@@ -11552,22 +11507,22 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C301" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D301" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E301" t="s">
-        <v>733</v>
+        <v>195</v>
       </c>
       <c r="F301" t="s">
-        <v>734</v>
+        <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="H301" t="s">
         <v>10</v>
@@ -11575,22 +11530,22 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="C302" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D302" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E302" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="F302" t="s">
-        <v>1194</v>
+        <v>7</v>
       </c>
       <c r="G302" t="s">
-        <v>1195</v>
+        <v>170</v>
       </c>
       <c r="H302" t="s">
         <v>10</v>
@@ -11601,19 +11556,19 @@
         <v>1196</v>
       </c>
       <c r="C303" t="s">
-        <v>69</v>
+        <v>279</v>
       </c>
       <c r="D303" t="s">
         <v>1197</v>
       </c>
       <c r="E303" t="s">
-        <v>1198</v>
+        <v>80</v>
       </c>
       <c r="F303" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="G303" t="s">
-        <v>1199</v>
+        <v>76</v>
       </c>
       <c r="H303" t="s">
         <v>10</v>
@@ -11621,22 +11576,22 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C304" t="s">
+        <v>30</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E304" t="s">
+        <v>265</v>
+      </c>
+      <c r="F304" t="s">
+        <v>7</v>
+      </c>
+      <c r="G304" t="s">
         <v>1200</v>
-      </c>
-      <c r="C304" t="s">
-        <v>31</v>
-      </c>
-      <c r="D304" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E304" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F304" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G304" t="s">
-        <v>1204</v>
       </c>
       <c r="H304" t="s">
         <v>10</v>
@@ -11644,22 +11599,22 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C305" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D305" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="E305" t="s">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="F305" t="s">
         <v>7</v>
       </c>
       <c r="G305" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="H305" t="s">
         <v>10</v>
@@ -11667,22 +11622,22 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C306" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="D306" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="E306" t="s">
-        <v>1210</v>
+        <v>85</v>
       </c>
       <c r="F306" t="s">
         <v>7</v>
       </c>
       <c r="G306" t="s">
-        <v>170</v>
+        <v>1204</v>
       </c>
       <c r="H306" t="s">
         <v>10</v>
@@ -11690,22 +11645,22 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C307" t="s">
         <v>279</v>
       </c>
       <c r="D307" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="E307" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F307" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="G307" t="s">
-        <v>76</v>
+        <v>1207</v>
       </c>
       <c r="H307" t="s">
         <v>10</v>
@@ -11713,22 +11668,22 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="C308" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="D308" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="E308" t="s">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="F308" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="G308" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="H308" t="s">
         <v>10</v>
@@ -11736,22 +11691,22 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="C309" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="D309" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="E309" t="s">
-        <v>265</v>
+        <v>1213</v>
       </c>
       <c r="F309" t="s">
         <v>7</v>
       </c>
       <c r="G309" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H309" t="s">
         <v>10</v>
@@ -11759,22 +11714,22 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C310" t="s">
+        <v>12</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G310" t="s">
         <v>1217</v>
-      </c>
-      <c r="C310" t="s">
-        <v>69</v>
-      </c>
-      <c r="D310" t="s">
-        <v>1218</v>
-      </c>
-      <c r="E310" t="s">
-        <v>85</v>
-      </c>
-      <c r="F310" t="s">
-        <v>7</v>
-      </c>
-      <c r="G310" t="s">
-        <v>1219</v>
       </c>
       <c r="H310" t="s">
         <v>10</v>
@@ -11782,19 +11737,19 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C311" t="s">
+        <v>21</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E311" t="s">
         <v>1220</v>
       </c>
-      <c r="C311" t="s">
-        <v>279</v>
-      </c>
-      <c r="D311" t="s">
+      <c r="F311" t="s">
         <v>1221</v>
-      </c>
-      <c r="E311" t="s">
-        <v>23</v>
-      </c>
-      <c r="F311" t="s">
-        <v>24</v>
       </c>
       <c r="G311" t="s">
         <v>1222</v>
@@ -11808,19 +11763,19 @@
         <v>1223</v>
       </c>
       <c r="C312" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="D312" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="E312" t="s">
-        <v>80</v>
+        <v>1220</v>
       </c>
       <c r="F312" t="s">
-        <v>81</v>
+        <v>1221</v>
       </c>
       <c r="G312" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="H312" t="s">
         <v>10</v>
@@ -11828,22 +11783,22 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C313" t="s">
+        <v>22</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E313" t="s">
         <v>1226</v>
-      </c>
-      <c r="C313" t="s">
-        <v>241</v>
-      </c>
-      <c r="D313" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E313" t="s">
-        <v>1228</v>
       </c>
       <c r="F313" t="s">
         <v>7</v>
       </c>
       <c r="G313" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="H313" t="s">
         <v>10</v>
@@ -11851,22 +11806,22 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C314" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D314" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="E314" t="s">
-        <v>1180</v>
+        <v>1226</v>
       </c>
       <c r="F314" t="s">
-        <v>1181</v>
+        <v>7</v>
       </c>
       <c r="G314" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="H314" t="s">
         <v>10</v>
@@ -11874,22 +11829,22 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="C315" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D315" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="E315" t="s">
-        <v>1235</v>
+        <v>1170</v>
       </c>
       <c r="F315" t="s">
-        <v>1236</v>
+        <v>7</v>
       </c>
       <c r="G315" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="H315" t="s">
         <v>10</v>
@@ -11897,22 +11852,22 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="C316" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D316" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E316" t="s">
+        <v>189</v>
+      </c>
+      <c r="F316" t="s">
+        <v>7</v>
+      </c>
+      <c r="G316" t="s">
         <v>1234</v>
-      </c>
-      <c r="E316" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F316" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G316" t="s">
-        <v>1237</v>
       </c>
       <c r="H316" t="s">
         <v>10</v>
@@ -11920,22 +11875,22 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="C317" t="s">
-        <v>22</v>
+        <v>255</v>
       </c>
       <c r="D317" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="E317" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="F317" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G317" t="s">
-        <v>1242</v>
+        <v>313</v>
       </c>
       <c r="H317" t="s">
         <v>10</v>
@@ -11943,22 +11898,22 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="C318" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D318" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E318" t="s">
-        <v>1241</v>
+        <v>191</v>
       </c>
       <c r="F318" t="s">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="G318" t="s">
-        <v>1242</v>
+        <v>103</v>
       </c>
       <c r="H318" t="s">
         <v>10</v>
@@ -11966,22 +11921,22 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C319" t="s">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="D319" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="E319" t="s">
-        <v>1185</v>
+        <v>117</v>
       </c>
       <c r="F319" t="s">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="G319" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="H319" t="s">
         <v>10</v>
@@ -11989,22 +11944,22 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C320" t="s">
+        <v>34</v>
+      </c>
+      <c r="D320" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E320" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F320" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G320" t="s">
         <v>1247</v>
-      </c>
-      <c r="C320" t="s">
-        <v>18</v>
-      </c>
-      <c r="D320" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E320" t="s">
-        <v>189</v>
-      </c>
-      <c r="F320" t="s">
-        <v>7</v>
-      </c>
-      <c r="G320" t="s">
-        <v>1249</v>
       </c>
       <c r="H320" t="s">
         <v>10</v>
@@ -12012,22 +11967,22 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C321" t="s">
+        <v>26</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E321" t="s">
         <v>1250</v>
       </c>
-      <c r="C321" t="s">
-        <v>255</v>
-      </c>
-      <c r="D321" t="s">
+      <c r="F321" t="s">
         <v>1251</v>
       </c>
-      <c r="E321" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F321" t="s">
-        <v>35</v>
-      </c>
       <c r="G321" t="s">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="H321" t="s">
         <v>10</v>
@@ -12035,22 +11990,22 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C322" t="s">
+        <v>34</v>
+      </c>
+      <c r="D322" t="s">
         <v>1253</v>
       </c>
-      <c r="C322" t="s">
-        <v>12</v>
-      </c>
-      <c r="D322" t="s">
+      <c r="E322" t="s">
         <v>1254</v>
       </c>
-      <c r="E322" t="s">
-        <v>191</v>
-      </c>
       <c r="F322" t="s">
-        <v>192</v>
+        <v>1255</v>
       </c>
       <c r="G322" t="s">
-        <v>103</v>
+        <v>1256</v>
       </c>
       <c r="H322" t="s">
         <v>10</v>
@@ -12058,22 +12013,22 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C323" t="s">
-        <v>279</v>
+        <v>12</v>
       </c>
       <c r="D323" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="E323" t="s">
-        <v>117</v>
+        <v>1259</v>
       </c>
       <c r="F323" t="s">
-        <v>118</v>
+        <v>7</v>
       </c>
       <c r="G323" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="H323" t="s">
         <v>10</v>
@@ -12081,22 +12036,22 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="C324" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D324" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="E324" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F324" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G324" t="s">
-        <v>1262</v>
+        <v>47</v>
       </c>
       <c r="H324" t="s">
         <v>10</v>
@@ -12104,22 +12059,22 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C325" t="s">
+        <v>43</v>
+      </c>
+      <c r="D325" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E325" t="s">
         <v>1263</v>
       </c>
-      <c r="C325" t="s">
-        <v>26</v>
-      </c>
-      <c r="D325" t="s">
+      <c r="F325" t="s">
         <v>1264</v>
       </c>
-      <c r="E325" t="s">
-        <v>1265</v>
-      </c>
-      <c r="F325" t="s">
-        <v>1266</v>
-      </c>
       <c r="G325" t="s">
-        <v>88</v>
+        <v>1267</v>
       </c>
       <c r="H325" t="s">
         <v>10</v>
@@ -12127,22 +12082,22 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C326" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D326" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E326" t="s">
-        <v>1269</v>
+        <v>14</v>
       </c>
       <c r="F326" t="s">
+        <v>15</v>
+      </c>
+      <c r="G326" t="s">
         <v>1270</v>
-      </c>
-      <c r="G326" t="s">
-        <v>1271</v>
       </c>
       <c r="H326" t="s">
         <v>10</v>
@@ -12150,22 +12105,22 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C327" t="s">
+        <v>241</v>
+      </c>
+      <c r="D327" t="s">
         <v>1272</v>
       </c>
-      <c r="C327" t="s">
-        <v>12</v>
-      </c>
-      <c r="D327" t="s">
-        <v>1273</v>
-      </c>
       <c r="E327" t="s">
-        <v>1274</v>
+        <v>83</v>
       </c>
       <c r="F327" t="s">
         <v>7</v>
       </c>
       <c r="G327" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="H327" t="s">
         <v>10</v>
@@ -12173,22 +12128,22 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C328" t="s">
+        <v>51</v>
+      </c>
+      <c r="D328" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E328" t="s">
+        <v>139</v>
+      </c>
+      <c r="F328" t="s">
+        <v>52</v>
+      </c>
+      <c r="G328" t="s">
         <v>1276</v>
-      </c>
-      <c r="C328" t="s">
-        <v>43</v>
-      </c>
-      <c r="D328" t="s">
-        <v>1277</v>
-      </c>
-      <c r="E328" t="s">
-        <v>1278</v>
-      </c>
-      <c r="F328" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G328" t="s">
-        <v>47</v>
       </c>
       <c r="H328" t="s">
         <v>10</v>
@@ -12196,22 +12151,22 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C329" t="s">
+        <v>119</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E329" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F329" t="s">
         <v>1280</v>
       </c>
-      <c r="C329" t="s">
-        <v>43</v>
-      </c>
-      <c r="D329" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E329" t="s">
-        <v>1278</v>
-      </c>
-      <c r="F329" t="s">
-        <v>1279</v>
-      </c>
       <c r="G329" t="s">
-        <v>1282</v>
+        <v>47</v>
       </c>
       <c r="H329" t="s">
         <v>10</v>
@@ -12219,19 +12174,19 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C330" t="s">
+        <v>145</v>
+      </c>
+      <c r="D330" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E330" t="s">
         <v>1283</v>
       </c>
-      <c r="C330" t="s">
-        <v>19</v>
-      </c>
-      <c r="D330" t="s">
+      <c r="F330" t="s">
         <v>1284</v>
-      </c>
-      <c r="E330" t="s">
-        <v>14</v>
-      </c>
-      <c r="F330" t="s">
-        <v>15</v>
       </c>
       <c r="G330" t="s">
         <v>1285</v>
@@ -12245,19 +12200,19 @@
         <v>1286</v>
       </c>
       <c r="C331" t="s">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="D331" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="E331" t="s">
-        <v>83</v>
+        <v>1283</v>
       </c>
       <c r="F331" t="s">
-        <v>7</v>
+        <v>1284</v>
       </c>
       <c r="G331" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H331" t="s">
         <v>10</v>
@@ -12265,19 +12220,19 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C332" t="s">
+        <v>56</v>
+      </c>
+      <c r="D332" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E332" t="s">
         <v>1289</v>
       </c>
-      <c r="C332" t="s">
-        <v>51</v>
-      </c>
-      <c r="D332" t="s">
+      <c r="F332" t="s">
         <v>1290</v>
-      </c>
-      <c r="E332" t="s">
-        <v>139</v>
-      </c>
-      <c r="F332" t="s">
-        <v>52</v>
       </c>
       <c r="G332" t="s">
         <v>1291</v>
@@ -12291,7 +12246,7 @@
         <v>1292</v>
       </c>
       <c r="C333" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="D333" t="s">
         <v>1293</v>
@@ -12300,10 +12255,10 @@
         <v>1294</v>
       </c>
       <c r="F333" t="s">
+        <v>7</v>
+      </c>
+      <c r="G333" t="s">
         <v>1295</v>
-      </c>
-      <c r="G333" t="s">
-        <v>47</v>
       </c>
       <c r="H333" t="s">
         <v>10</v>
@@ -12314,7 +12269,7 @@
         <v>1296</v>
       </c>
       <c r="C334" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="D334" t="s">
         <v>1297</v>
@@ -12329,7 +12284,7 @@
         <v>1300</v>
       </c>
       <c r="H334" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
@@ -12337,134 +12292,134 @@
         <v>1301</v>
       </c>
       <c r="C335" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="D335" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="E335" t="s">
-        <v>1298</v>
+        <v>142</v>
       </c>
       <c r="F335" t="s">
-        <v>1299</v>
+        <v>143</v>
       </c>
       <c r="G335" t="s">
-        <v>1300</v>
+        <v>144</v>
       </c>
       <c r="H335" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C336" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D336" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="E336" t="s">
-        <v>1304</v>
+        <v>82</v>
       </c>
       <c r="F336" t="s">
+        <v>7</v>
+      </c>
+      <c r="G336" t="s">
         <v>1305</v>
       </c>
-      <c r="G336" t="s">
-        <v>1306</v>
-      </c>
       <c r="H336" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C337" t="s">
+        <v>16</v>
+      </c>
+      <c r="D337" t="s">
         <v>1307</v>
       </c>
-      <c r="C337" t="s">
-        <v>65</v>
-      </c>
-      <c r="D337" t="s">
+      <c r="E337" t="s">
         <v>1308</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1309</v>
       </c>
       <c r="F337" t="s">
         <v>7</v>
       </c>
       <c r="G337" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H337" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C338" t="s">
+        <v>59</v>
+      </c>
+      <c r="D338" t="s">
         <v>1311</v>
       </c>
-      <c r="C338" t="s">
-        <v>39</v>
-      </c>
-      <c r="D338" t="s">
+      <c r="E338" t="s">
         <v>1312</v>
       </c>
-      <c r="E338" t="s">
+      <c r="F338" t="s">
         <v>1313</v>
       </c>
-      <c r="F338" t="s">
+      <c r="G338" t="s">
         <v>1314</v>
       </c>
-      <c r="G338" t="s">
-        <v>1315</v>
-      </c>
       <c r="H338" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C339" t="s">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
         <v>1316</v>
       </c>
-      <c r="C339" t="s">
-        <v>37</v>
-      </c>
-      <c r="D339" t="s">
+      <c r="E339" t="s">
         <v>1317</v>
       </c>
-      <c r="E339" t="s">
-        <v>142</v>
-      </c>
       <c r="F339" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="G339" t="s">
-        <v>144</v>
+        <v>1318</v>
       </c>
       <c r="H339" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C340" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D340" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E340" t="s">
-        <v>82</v>
+        <v>1321</v>
       </c>
       <c r="F340" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="G340" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="H340" t="s">
         <v>11</v>
@@ -12472,22 +12427,22 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C341" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D341" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="E341" t="s">
-        <v>1323</v>
+        <v>190</v>
       </c>
       <c r="F341" t="s">
         <v>7</v>
       </c>
       <c r="G341" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H341" t="s">
         <v>11</v>
@@ -12495,22 +12450,22 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C342" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="D342" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E342" t="s">
-        <v>1327</v>
+        <v>86</v>
       </c>
       <c r="F342" t="s">
+        <v>87</v>
+      </c>
+      <c r="G342" t="s">
         <v>1328</v>
-      </c>
-      <c r="G342" t="s">
-        <v>1329</v>
       </c>
       <c r="H342" t="s">
         <v>11</v>
@@ -12518,22 +12473,22 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C343" t="s">
+        <v>16</v>
+      </c>
+      <c r="D343" t="s">
         <v>1330</v>
       </c>
-      <c r="C343" t="s">
-        <v>50</v>
-      </c>
-      <c r="D343" t="s">
+      <c r="E343" t="s">
+        <v>86</v>
+      </c>
+      <c r="F343" t="s">
+        <v>87</v>
+      </c>
+      <c r="G343" t="s">
         <v>1331</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1332</v>
-      </c>
-      <c r="F343" t="s">
-        <v>35</v>
-      </c>
-      <c r="G343" t="s">
-        <v>1333</v>
       </c>
       <c r="H343" t="s">
         <v>11</v>
@@ -12541,22 +12496,22 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C344" t="s">
+        <v>26</v>
+      </c>
+      <c r="D344" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E344" t="s">
         <v>1334</v>
       </c>
-      <c r="C344" t="s">
-        <v>63</v>
-      </c>
-      <c r="D344" t="s">
+      <c r="F344" t="s">
         <v>1335</v>
       </c>
-      <c r="E344" t="s">
-        <v>1336</v>
-      </c>
-      <c r="F344" t="s">
-        <v>64</v>
-      </c>
       <c r="G344" t="s">
-        <v>1337</v>
+        <v>97</v>
       </c>
       <c r="H344" t="s">
         <v>11</v>
@@ -12564,22 +12519,22 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C345" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D345" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="E345" t="s">
-        <v>190</v>
+        <v>365</v>
       </c>
       <c r="F345" t="s">
-        <v>7</v>
+        <v>366</v>
       </c>
       <c r="G345" t="s">
-        <v>1340</v>
+        <v>475</v>
       </c>
       <c r="H345" t="s">
         <v>11</v>
@@ -12587,22 +12542,22 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="C346" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D346" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="E346" t="s">
-        <v>86</v>
+        <v>1126</v>
       </c>
       <c r="F346" t="s">
-        <v>87</v>
+        <v>1127</v>
       </c>
       <c r="G346" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="H346" t="s">
         <v>11</v>
@@ -12610,22 +12565,22 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C347" t="s">
+        <v>31</v>
+      </c>
+      <c r="D347" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F347" t="s">
+        <v>115</v>
+      </c>
+      <c r="G347" t="s">
         <v>1344</v>
-      </c>
-      <c r="C347" t="s">
-        <v>16</v>
-      </c>
-      <c r="D347" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E347" t="s">
-        <v>86</v>
-      </c>
-      <c r="F347" t="s">
-        <v>87</v>
-      </c>
-      <c r="G347" t="s">
-        <v>1346</v>
       </c>
       <c r="H347" t="s">
         <v>11</v>
@@ -12633,22 +12588,22 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C348" t="s">
+        <v>22</v>
+      </c>
+      <c r="D348" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E348" t="s">
         <v>1347</v>
       </c>
-      <c r="C348" t="s">
-        <v>26</v>
-      </c>
-      <c r="D348" t="s">
+      <c r="F348" t="s">
         <v>1348</v>
       </c>
-      <c r="E348" t="s">
+      <c r="G348" t="s">
         <v>1349</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G348" t="s">
-        <v>97</v>
       </c>
       <c r="H348" t="s">
         <v>11</v>
@@ -12656,22 +12611,22 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C349" t="s">
+        <v>48</v>
+      </c>
+      <c r="D349" t="s">
         <v>1351</v>
       </c>
-      <c r="C349" t="s">
-        <v>50</v>
-      </c>
-      <c r="D349" t="s">
+      <c r="E349" t="s">
+        <v>557</v>
+      </c>
+      <c r="F349" t="s">
+        <v>40</v>
+      </c>
+      <c r="G349" t="s">
         <v>1352</v>
-      </c>
-      <c r="E349" t="s">
-        <v>365</v>
-      </c>
-      <c r="F349" t="s">
-        <v>366</v>
-      </c>
-      <c r="G349" t="s">
-        <v>475</v>
       </c>
       <c r="H349" t="s">
         <v>11</v>
@@ -12682,19 +12637,19 @@
         <v>1353</v>
       </c>
       <c r="C350" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D350" t="s">
         <v>1354</v>
       </c>
       <c r="E350" t="s">
-        <v>1141</v>
+        <v>196</v>
       </c>
       <c r="F350" t="s">
-        <v>1142</v>
+        <v>197</v>
       </c>
       <c r="G350" t="s">
-        <v>1355</v>
+        <v>154</v>
       </c>
       <c r="H350" t="s">
         <v>11</v>
@@ -12702,22 +12657,22 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C351" t="s">
+        <v>53</v>
+      </c>
+      <c r="D351" t="s">
         <v>1356</v>
       </c>
-      <c r="C351" t="s">
-        <v>31</v>
-      </c>
-      <c r="D351" t="s">
+      <c r="E351" t="s">
         <v>1357</v>
       </c>
-      <c r="E351" t="s">
+      <c r="F351" t="s">
         <v>1358</v>
       </c>
-      <c r="F351" t="s">
-        <v>115</v>
-      </c>
       <c r="G351" t="s">
-        <v>1359</v>
+        <v>97</v>
       </c>
       <c r="H351" t="s">
         <v>11</v>
@@ -12725,22 +12680,22 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C352" t="s">
+        <v>408</v>
+      </c>
+      <c r="D352" t="s">
         <v>1360</v>
       </c>
-      <c r="C352" t="s">
-        <v>22</v>
-      </c>
-      <c r="D352" t="s">
+      <c r="E352" t="s">
         <v>1361</v>
       </c>
-      <c r="E352" t="s">
+      <c r="F352" t="s">
         <v>1362</v>
       </c>
-      <c r="F352" t="s">
-        <v>1363</v>
-      </c>
       <c r="G352" t="s">
-        <v>1364</v>
+        <v>97</v>
       </c>
       <c r="H352" t="s">
         <v>11</v>
@@ -12748,22 +12703,22 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C353" t="s">
+        <v>26</v>
+      </c>
+      <c r="D353" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E353" t="s">
         <v>1365</v>
       </c>
-      <c r="C353" t="s">
-        <v>48</v>
-      </c>
-      <c r="D353" t="s">
+      <c r="F353" t="s">
+        <v>7</v>
+      </c>
+      <c r="G353" t="s">
         <v>1366</v>
-      </c>
-      <c r="E353" t="s">
-        <v>557</v>
-      </c>
-      <c r="F353" t="s">
-        <v>40</v>
-      </c>
-      <c r="G353" t="s">
-        <v>1367</v>
       </c>
       <c r="H353" t="s">
         <v>11</v>
@@ -12771,22 +12726,22 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C354" t="s">
+        <v>37</v>
+      </c>
+      <c r="D354" t="s">
         <v>1368</v>
       </c>
-      <c r="C354" t="s">
-        <v>53</v>
-      </c>
-      <c r="D354" t="s">
+      <c r="E354" t="s">
+        <v>729</v>
+      </c>
+      <c r="F354" t="s">
+        <v>730</v>
+      </c>
+      <c r="G354" t="s">
         <v>1369</v>
-      </c>
-      <c r="E354" t="s">
-        <v>196</v>
-      </c>
-      <c r="F354" t="s">
-        <v>197</v>
-      </c>
-      <c r="G354" t="s">
-        <v>154</v>
       </c>
       <c r="H354" t="s">
         <v>11</v>
@@ -12797,7 +12752,7 @@
         <v>1370</v>
       </c>
       <c r="C355" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D355" t="s">
         <v>1371</v>
@@ -12809,7 +12764,7 @@
         <v>1373</v>
       </c>
       <c r="G355" t="s">
-        <v>97</v>
+        <v>1374</v>
       </c>
       <c r="H355" t="s">
         <v>11</v>
@@ -12817,22 +12772,22 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C356" t="s">
-        <v>408</v>
+        <v>50</v>
       </c>
       <c r="D356" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E356" t="s">
-        <v>1376</v>
+        <v>704</v>
       </c>
       <c r="F356" t="s">
+        <v>705</v>
+      </c>
+      <c r="G356" t="s">
         <v>1377</v>
-      </c>
-      <c r="G356" t="s">
-        <v>97</v>
       </c>
       <c r="H356" t="s">
         <v>11</v>
@@ -12843,7 +12798,7 @@
         <v>1378</v>
       </c>
       <c r="C357" t="s">
-        <v>26</v>
+        <v>408</v>
       </c>
       <c r="D357" t="s">
         <v>1379</v>
@@ -12852,36 +12807,36 @@
         <v>1380</v>
       </c>
       <c r="F357" t="s">
-        <v>7</v>
+        <v>1381</v>
       </c>
       <c r="G357" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H357" t="s">
-        <v>11</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C358" t="s">
+        <v>408</v>
+      </c>
+      <c r="D358" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E358" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F358" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G358" t="s">
         <v>1382</v>
       </c>
-      <c r="C358" t="s">
-        <v>37</v>
-      </c>
-      <c r="D358" t="s">
+      <c r="H358" t="s">
         <v>1383</v>
-      </c>
-      <c r="E358" t="s">
-        <v>733</v>
-      </c>
-      <c r="F358" t="s">
-        <v>734</v>
-      </c>
-      <c r="G358" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H358" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
@@ -12889,235 +12844,143 @@
         <v>1385</v>
       </c>
       <c r="C359" t="s">
-        <v>59</v>
+        <v>408</v>
       </c>
       <c r="D359" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="E359" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
       <c r="F359" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="G359" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="H359" t="s">
-        <v>11</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C360" t="s">
+        <v>119</v>
+      </c>
+      <c r="D360" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E360" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F360" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G360" t="s">
         <v>1390</v>
       </c>
-      <c r="C360" t="s">
-        <v>50</v>
-      </c>
-      <c r="D360" t="s">
+      <c r="H360" t="s">
         <v>1391</v>
-      </c>
-      <c r="E360" t="s">
-        <v>708</v>
-      </c>
-      <c r="F360" t="s">
-        <v>709</v>
-      </c>
-      <c r="G360" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H360" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C361" t="s">
+        <v>9</v>
+      </c>
+      <c r="D361" t="s">
         <v>1393</v>
       </c>
-      <c r="C361" t="s">
-        <v>408</v>
-      </c>
-      <c r="D361" t="s">
+      <c r="E361" t="s">
+        <v>106</v>
+      </c>
+      <c r="F361" t="s">
+        <v>107</v>
+      </c>
+      <c r="G361" t="s">
         <v>1394</v>
       </c>
-      <c r="E361" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F361" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G361" t="s">
-        <v>1397</v>
-      </c>
       <c r="H361" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C362" t="s">
-        <v>408</v>
+        <v>9</v>
       </c>
       <c r="D362" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E362" t="s">
+        <v>106</v>
+      </c>
+      <c r="F362" t="s">
+        <v>107</v>
+      </c>
+      <c r="G362" t="s">
         <v>1394</v>
       </c>
-      <c r="E362" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F362" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G362" t="s">
-        <v>1397</v>
-      </c>
       <c r="H362" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="C363" t="s">
-        <v>408</v>
+        <v>63</v>
       </c>
       <c r="D363" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="E363" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="F363" t="s">
-        <v>1396</v>
+        <v>64</v>
       </c>
       <c r="G363" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="H363" t="s">
-        <v>1398</v>
+        <v>91</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C364" t="s">
+        <v>45</v>
+      </c>
+      <c r="D364" t="s">
         <v>1401</v>
       </c>
-      <c r="C364" t="s">
-        <v>119</v>
-      </c>
-      <c r="D364" t="s">
+      <c r="E364" t="s">
+        <v>506</v>
+      </c>
+      <c r="F364" t="s">
+        <v>507</v>
+      </c>
+      <c r="G364" t="s">
         <v>1402</v>
       </c>
-      <c r="E364" t="s">
-        <v>1403</v>
-      </c>
-      <c r="F364" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G364" t="s">
-        <v>1405</v>
-      </c>
       <c r="H364" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>1407</v>
-      </c>
-      <c r="C365" t="s">
-        <v>9</v>
-      </c>
-      <c r="D365" t="s">
-        <v>1408</v>
-      </c>
-      <c r="E365" t="s">
-        <v>106</v>
-      </c>
-      <c r="F365" t="s">
-        <v>107</v>
-      </c>
-      <c r="G365" t="s">
-        <v>1409</v>
-      </c>
-      <c r="H365" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
-        <v>1410</v>
-      </c>
-      <c r="C366" t="s">
-        <v>9</v>
-      </c>
-      <c r="D366" t="s">
-        <v>1408</v>
-      </c>
-      <c r="E366" t="s">
-        <v>106</v>
-      </c>
-      <c r="F366" t="s">
-        <v>107</v>
-      </c>
-      <c r="G366" t="s">
-        <v>1409</v>
-      </c>
-      <c r="H366" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C367" t="s">
-        <v>63</v>
-      </c>
-      <c r="D367" t="s">
-        <v>1412</v>
-      </c>
-      <c r="E367" t="s">
-        <v>1413</v>
-      </c>
-      <c r="F367" t="s">
-        <v>64</v>
-      </c>
-      <c r="G367" t="s">
-        <v>1414</v>
-      </c>
-      <c r="H367" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C368" t="s">
-        <v>45</v>
-      </c>
-      <c r="D368" t="s">
-        <v>1416</v>
-      </c>
-      <c r="E368" t="s">
-        <v>506</v>
-      </c>
-      <c r="F368" t="s">
-        <v>507</v>
-      </c>
-      <c r="G368" t="s">
-        <v>1417</v>
-      </c>
-      <c r="H368" t="s">
         <v>213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:H381" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}">
-    <sortState ref="C65:H330">
-      <sortCondition ref="E1:E357"/>
+  <autoFilter ref="C1:H377" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}">
+    <sortState ref="C65:H326">
+      <sortCondition ref="E1:E353"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C7D2EC-1DC5-4944-92D1-555598781C7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE9D479-6DA8-4D36-BECE-15430107E7D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2390" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="1278">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -411,24 +411,9 @@
     <t>K-915</t>
   </si>
   <si>
-    <t>6ab6935b219e3d74bbe3e567</t>
-  </si>
-  <si>
     <t>K-9122</t>
   </si>
   <si>
-    <t>260922-F00014282</t>
-  </si>
-  <si>
-    <t>5400</t>
-  </si>
-  <si>
-    <t>MEZŐTÚR</t>
-  </si>
-  <si>
-    <t>Klapka tábornok utca</t>
-  </si>
-  <si>
     <t>5900</t>
   </si>
   <si>
@@ -444,15 +429,6 @@
     <t>K-973</t>
   </si>
   <si>
-    <t>6ab620b7219e3d74bbe3d237</t>
-  </si>
-  <si>
-    <t>260925-F00001172</t>
-  </si>
-  <si>
-    <t>Gagarin tér</t>
-  </si>
-  <si>
     <t>2941</t>
   </si>
   <si>
@@ -1861,15 +1837,6 @@
   </si>
   <si>
     <t>Kiss Ernő utca</t>
-  </si>
-  <si>
-    <t>6abbb40a219e3d74bbe432bc</t>
-  </si>
-  <si>
-    <t>260929-F00010020</t>
-  </si>
-  <si>
-    <t>Haszkovó utca</t>
   </si>
   <si>
     <t>6abbb40e219e3d74bbe432ed</t>
@@ -4248,7 +4215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H342"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -4285,13 +4252,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
         <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
@@ -4300,7 +4267,7 @@
         <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="H2" t="s">
         <v>117</v>
@@ -4308,22 +4275,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -4331,22 +4298,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -4400,13 +4367,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
         <v>90</v>
@@ -4415,7 +4382,7 @@
         <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
@@ -4423,22 +4390,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
@@ -4446,22 +4413,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -4469,13 +4436,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -4484,7 +4451,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -4492,22 +4459,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
@@ -4515,19 +4482,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E12" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F12" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G12" t="s">
         <v>41</v>
@@ -4538,22 +4505,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E13" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F13" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G13" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="H13" t="s">
         <v>10</v>
@@ -4561,13 +4528,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C14" t="s">
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E14" t="s">
         <v>84</v>
@@ -4576,7 +4543,7 @@
         <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="H14" t="s">
         <v>10</v>
@@ -4584,13 +4551,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
         <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E15" t="s">
         <v>84</v>
@@ -4599,7 +4566,7 @@
         <v>85</v>
       </c>
       <c r="G15" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="H15" t="s">
         <v>10</v>
@@ -4607,13 +4574,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C16" t="s">
         <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="E16" t="s">
         <v>53</v>
@@ -4622,7 +4589,7 @@
         <v>54</v>
       </c>
       <c r="G16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H16" t="s">
         <v>10</v>
@@ -4630,22 +4597,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E17" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="F17" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G17" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="H17" t="s">
         <v>10</v>
@@ -4653,22 +4620,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E18" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F18" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="G18" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="H18" t="s">
         <v>10</v>
@@ -4676,22 +4643,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E19" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F19" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="G19" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="H19" t="s">
         <v>10</v>
@@ -4699,22 +4666,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E20" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F20" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="G20" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H20" t="s">
         <v>10</v>
@@ -4722,22 +4689,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E21" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F21" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G21" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="H21" t="s">
         <v>10</v>
@@ -4745,22 +4712,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E22" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F22" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G22" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="H22" t="s">
         <v>10</v>
@@ -4768,22 +4735,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C23" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E23" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
       </c>
       <c r="G23" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="H23" t="s">
         <v>10</v>
@@ -4791,22 +4758,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C24" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
       </c>
       <c r="G24" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="H24" t="s">
         <v>10</v>
@@ -4814,19 +4781,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C25" t="s">
         <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="G25" t="s">
         <v>41</v>
@@ -4837,13 +4804,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C26" t="s">
         <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E26" t="s">
         <v>92</v>
@@ -4852,7 +4819,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H26" t="s">
         <v>10</v>
@@ -4860,22 +4827,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E27" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
       </c>
       <c r="G27" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H27" t="s">
         <v>10</v>
@@ -4883,22 +4850,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E28" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F28" t="s">
         <v>22</v>
       </c>
       <c r="G28" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H28" t="s">
         <v>10</v>
@@ -4906,19 +4873,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E29" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F29" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="G29" t="s">
         <v>37</v>
@@ -4929,19 +4896,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E30" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F30" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="G30" t="s">
         <v>17</v>
@@ -4952,19 +4919,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E31" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F31" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="G31" t="s">
         <v>17</v>
@@ -4975,19 +4942,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E32" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F32" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G32" t="s">
         <v>110</v>
@@ -4998,19 +4965,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C33" t="s">
         <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E33" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F33" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G33" t="s">
         <v>110</v>
@@ -5021,22 +4988,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C34" t="s">
         <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E34" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="H34" t="s">
         <v>10</v>
@@ -5044,22 +5011,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>312</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="F35" t="s">
-        <v>131</v>
+        <v>314</v>
       </c>
       <c r="G35" t="s">
-        <v>132</v>
+        <v>315</v>
       </c>
       <c r="H35" t="s">
         <v>10</v>
@@ -5067,22 +5034,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E36" t="s">
-        <v>321</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>322</v>
+        <v>129</v>
       </c>
       <c r="G36" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H36" t="s">
         <v>10</v>
@@ -5090,22 +5057,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E37" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F37" t="s">
-        <v>134</v>
+        <v>322</v>
       </c>
       <c r="G37" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H37" t="s">
         <v>10</v>
@@ -5113,22 +5080,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>324</v>
+      </c>
+      <c r="C38" t="s">
+        <v>325</v>
+      </c>
+      <c r="D38" t="s">
+        <v>326</v>
+      </c>
+      <c r="E38" t="s">
         <v>327</v>
       </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>328</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>329</v>
-      </c>
-      <c r="F38" t="s">
-        <v>330</v>
-      </c>
-      <c r="G38" t="s">
-        <v>331</v>
       </c>
       <c r="H38" t="s">
         <v>10</v>
@@ -5136,22 +5103,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>330</v>
+      </c>
+      <c r="C39" t="s">
+        <v>325</v>
+      </c>
+      <c r="D39" t="s">
+        <v>331</v>
+      </c>
+      <c r="E39" t="s">
+        <v>327</v>
+      </c>
+      <c r="F39" t="s">
+        <v>328</v>
+      </c>
+      <c r="G39" t="s">
         <v>332</v>
-      </c>
-      <c r="C39" t="s">
-        <v>333</v>
-      </c>
-      <c r="D39" t="s">
-        <v>334</v>
-      </c>
-      <c r="E39" t="s">
-        <v>335</v>
-      </c>
-      <c r="F39" t="s">
-        <v>336</v>
-      </c>
-      <c r="G39" t="s">
-        <v>337</v>
       </c>
       <c r="H39" t="s">
         <v>10</v>
@@ -5159,13 +5126,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C40" t="s">
-        <v>333</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E40" t="s">
         <v>335</v>
@@ -5174,7 +5141,7 @@
         <v>336</v>
       </c>
       <c r="G40" t="s">
-        <v>340</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
         <v>10</v>
@@ -5182,22 +5149,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
+        <v>338</v>
+      </c>
+      <c r="E41" t="s">
+        <v>339</v>
+      </c>
+      <c r="F41" t="s">
+        <v>340</v>
+      </c>
+      <c r="G41" t="s">
         <v>341</v>
-      </c>
-      <c r="C41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" t="s">
-        <v>342</v>
-      </c>
-      <c r="E41" t="s">
-        <v>343</v>
-      </c>
-      <c r="F41" t="s">
-        <v>344</v>
-      </c>
-      <c r="G41" t="s">
-        <v>18</v>
       </c>
       <c r="H41" t="s">
         <v>10</v>
@@ -5205,22 +5172,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>342</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" t="s">
+        <v>343</v>
+      </c>
+      <c r="E42" t="s">
+        <v>344</v>
+      </c>
+      <c r="F42" t="s">
         <v>345</v>
       </c>
-      <c r="C42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="G42" t="s">
         <v>346</v>
-      </c>
-      <c r="E42" t="s">
-        <v>347</v>
-      </c>
-      <c r="F42" t="s">
-        <v>348</v>
-      </c>
-      <c r="G42" t="s">
-        <v>349</v>
       </c>
       <c r="H42" t="s">
         <v>10</v>
@@ -5228,22 +5195,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>347</v>
+      </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
+        <v>348</v>
+      </c>
+      <c r="E43" t="s">
+        <v>349</v>
+      </c>
+      <c r="F43" t="s">
         <v>350</v>
       </c>
-      <c r="C43" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" t="s">
-        <v>351</v>
-      </c>
-      <c r="E43" t="s">
-        <v>352</v>
-      </c>
-      <c r="F43" t="s">
-        <v>353</v>
-      </c>
       <c r="G43" t="s">
-        <v>354</v>
+        <v>41</v>
       </c>
       <c r="H43" t="s">
         <v>10</v>
@@ -5251,22 +5218,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" t="s">
+        <v>353</v>
+      </c>
+      <c r="E44" t="s">
+        <v>354</v>
+      </c>
+      <c r="F44" t="s">
         <v>355</v>
       </c>
-      <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="G44" t="s">
         <v>356</v>
-      </c>
-      <c r="E44" t="s">
-        <v>357</v>
-      </c>
-      <c r="F44" t="s">
-        <v>358</v>
-      </c>
-      <c r="G44" t="s">
-        <v>41</v>
       </c>
       <c r="H44" t="s">
         <v>10</v>
@@ -5274,22 +5241,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>357</v>
       </c>
       <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>358</v>
+      </c>
+      <c r="E45" t="s">
         <v>359</v>
       </c>
-      <c r="D45" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" t="s">
-        <v>98</v>
-      </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>360</v>
       </c>
       <c r="G45" t="s">
-        <v>140</v>
+        <v>361</v>
       </c>
       <c r="H45" t="s">
         <v>10</v>
@@ -5297,22 +5264,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>363</v>
       </c>
       <c r="D46" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E46" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F46" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G46" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H46" t="s">
         <v>10</v>
@@ -5320,22 +5287,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="D47" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E47" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F47" t="s">
-        <v>368</v>
+        <v>7</v>
       </c>
       <c r="G47" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H47" t="s">
         <v>10</v>
@@ -5343,19 +5310,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C48" t="s">
-        <v>371</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E48" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F48" t="s">
-        <v>374</v>
+        <v>13</v>
       </c>
       <c r="G48" t="s">
         <v>375</v>
@@ -5369,7 +5336,7 @@
         <v>376</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
         <v>377</v>
@@ -5378,10 +5345,10 @@
         <v>378</v>
       </c>
       <c r="F49" t="s">
-        <v>7</v>
+        <v>379</v>
       </c>
       <c r="G49" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H49" t="s">
         <v>10</v>
@@ -5389,22 +5356,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>381</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>377</v>
+      </c>
+      <c r="E50" t="s">
+        <v>378</v>
+      </c>
+      <c r="F50" t="s">
+        <v>379</v>
+      </c>
+      <c r="G50" t="s">
         <v>380</v>
-      </c>
-      <c r="C50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" t="s">
-        <v>381</v>
-      </c>
-      <c r="E50" t="s">
-        <v>382</v>
-      </c>
-      <c r="F50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" t="s">
-        <v>383</v>
       </c>
       <c r="H50" t="s">
         <v>10</v>
@@ -5412,22 +5379,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>382</v>
+      </c>
+      <c r="C51" t="s">
+        <v>325</v>
+      </c>
+      <c r="D51" t="s">
+        <v>383</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" t="s">
         <v>384</v>
-      </c>
-      <c r="C51" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" t="s">
-        <v>385</v>
-      </c>
-      <c r="E51" t="s">
-        <v>386</v>
-      </c>
-      <c r="F51" t="s">
-        <v>387</v>
-      </c>
-      <c r="G51" t="s">
-        <v>388</v>
       </c>
       <c r="H51" t="s">
         <v>10</v>
@@ -5435,22 +5402,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="D52" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E52" t="s">
-        <v>386</v>
+        <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>387</v>
+        <v>43</v>
       </c>
       <c r="G52" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H52" t="s">
         <v>10</v>
@@ -5458,22 +5425,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C53" t="s">
-        <v>333</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>388</v>
       </c>
       <c r="F53" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G53" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H53" t="s">
         <v>10</v>
@@ -5481,22 +5448,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C54" t="s">
-        <v>333</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
         <v>391</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>392</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H54" t="s">
         <v>10</v>
@@ -5507,19 +5474,19 @@
         <v>394</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
         <v>395</v>
       </c>
       <c r="E55" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G55" t="s">
         <v>396</v>
-      </c>
-      <c r="F55" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" t="s">
-        <v>397</v>
       </c>
       <c r="H55" t="s">
         <v>10</v>
@@ -5527,22 +5494,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E56" t="s">
-        <v>400</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G56" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H56" t="s">
         <v>10</v>
@@ -5550,22 +5517,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E57" t="s">
-        <v>46</v>
+        <v>400</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G57" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H57" t="s">
         <v>10</v>
@@ -5573,19 +5540,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="D58" t="s">
         <v>403</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G58" t="s">
         <v>404</v>
@@ -5596,22 +5563,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C59" t="s">
         <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E59" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="F59" t="s">
         <v>22</v>
       </c>
       <c r="G59" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H59" t="s">
         <v>10</v>
@@ -5619,22 +5586,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C60" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>400</v>
       </c>
       <c r="F60" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G60" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H60" t="s">
         <v>10</v>
@@ -5642,22 +5609,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E61" t="s">
-        <v>408</v>
+        <v>75</v>
       </c>
       <c r="F61" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H61" t="s">
         <v>10</v>
@@ -5665,19 +5632,19 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D62" t="s">
+        <v>413</v>
+      </c>
+      <c r="E62" t="s">
         <v>414</v>
       </c>
-      <c r="E62" t="s">
-        <v>408</v>
-      </c>
       <c r="F62" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G62" t="s">
         <v>415</v>
@@ -5688,22 +5655,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D63" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E63" t="s">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
       </c>
       <c r="G63" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H63" t="s">
         <v>10</v>
@@ -5711,22 +5678,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>417</v>
+      </c>
+      <c r="C64" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" t="s">
+        <v>418</v>
+      </c>
+      <c r="E64" t="s">
+        <v>419</v>
+      </c>
+      <c r="F64" t="s">
         <v>420</v>
       </c>
-      <c r="C64" t="s">
-        <v>66</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="G64" t="s">
         <v>421</v>
-      </c>
-      <c r="E64" t="s">
-        <v>422</v>
-      </c>
-      <c r="F64" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" t="s">
-        <v>423</v>
       </c>
       <c r="H64" t="s">
         <v>10</v>
@@ -5734,22 +5701,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>422</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>423</v>
+      </c>
+      <c r="E65" t="s">
         <v>424</v>
       </c>
-      <c r="C65" t="s">
-        <v>66</v>
-      </c>
-      <c r="D65" t="s">
-        <v>421</v>
-      </c>
-      <c r="E65" t="s">
-        <v>422</v>
-      </c>
       <c r="F65" t="s">
-        <v>7</v>
+        <v>425</v>
       </c>
       <c r="G65" t="s">
-        <v>423</v>
+        <v>17</v>
       </c>
       <c r="H65" t="s">
         <v>10</v>
@@ -5757,22 +5724,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>426</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>423</v>
+      </c>
+      <c r="E66" t="s">
+        <v>424</v>
+      </c>
+      <c r="F66" t="s">
         <v>425</v>
       </c>
-      <c r="C66" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" t="s">
-        <v>426</v>
-      </c>
-      <c r="E66" t="s">
-        <v>427</v>
-      </c>
-      <c r="F66" t="s">
-        <v>428</v>
-      </c>
       <c r="G66" t="s">
-        <v>429</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
         <v>10</v>
@@ -5780,22 +5747,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C67" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="D67" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E67" t="s">
-        <v>432</v>
+        <v>182</v>
       </c>
       <c r="F67" t="s">
-        <v>433</v>
+        <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>429</v>
       </c>
       <c r="H67" t="s">
         <v>10</v>
@@ -5803,22 +5770,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="D68" t="s">
         <v>431</v>
       </c>
       <c r="E68" t="s">
+        <v>49</v>
+      </c>
+      <c r="F68" t="s">
+        <v>50</v>
+      </c>
+      <c r="G68" t="s">
         <v>432</v>
-      </c>
-      <c r="F68" t="s">
-        <v>433</v>
-      </c>
-      <c r="G68" t="s">
-        <v>17</v>
       </c>
       <c r="H68" t="s">
         <v>10</v>
@@ -5826,22 +5793,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>433</v>
+      </c>
+      <c r="C69" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" t="s">
+        <v>434</v>
+      </c>
+      <c r="E69" t="s">
         <v>435</v>
       </c>
-      <c r="C69" t="s">
-        <v>162</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" t="s">
         <v>436</v>
-      </c>
-      <c r="E69" t="s">
-        <v>190</v>
-      </c>
-      <c r="F69" t="s">
-        <v>7</v>
-      </c>
-      <c r="G69" t="s">
-        <v>437</v>
       </c>
       <c r="H69" t="s">
         <v>10</v>
@@ -5849,22 +5816,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>437</v>
+      </c>
+      <c r="C70" t="s">
+        <v>74</v>
+      </c>
+      <c r="D70" t="s">
         <v>438</v>
       </c>
-      <c r="C70" t="s">
-        <v>162</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F70" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" t="s">
         <v>439</v>
-      </c>
-      <c r="E70" t="s">
-        <v>49</v>
-      </c>
-      <c r="F70" t="s">
-        <v>50</v>
-      </c>
-      <c r="G70" t="s">
-        <v>440</v>
       </c>
       <c r="H70" t="s">
         <v>10</v>
@@ -5872,22 +5839,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>440</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
         <v>441</v>
       </c>
-      <c r="C71" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>442</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s">
         <v>443</v>
-      </c>
-      <c r="F71" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" t="s">
-        <v>444</v>
       </c>
       <c r="H71" t="s">
         <v>10</v>
@@ -5895,22 +5862,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>444</v>
+      </c>
+      <c r="C72" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
         <v>445</v>
       </c>
-      <c r="C72" t="s">
-        <v>74</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>446</v>
       </c>
-      <c r="E72" t="s">
-        <v>175</v>
-      </c>
       <c r="F72" t="s">
-        <v>7</v>
+        <v>447</v>
       </c>
       <c r="G72" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H72" t="s">
         <v>10</v>
@@ -5918,19 +5885,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C73" t="s">
-        <v>24</v>
+        <v>274</v>
       </c>
       <c r="D73" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E73" t="s">
-        <v>450</v>
+        <v>87</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G73" t="s">
         <v>451</v>
@@ -5944,7 +5911,7 @@
         <v>452</v>
       </c>
       <c r="C74" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D74" t="s">
         <v>453</v>
@@ -5967,19 +5934,19 @@
         <v>457</v>
       </c>
       <c r="C75" t="s">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="D75" t="s">
         <v>458</v>
       </c>
       <c r="E75" t="s">
-        <v>87</v>
+        <v>459</v>
       </c>
       <c r="F75" t="s">
-        <v>7</v>
+        <v>460</v>
       </c>
       <c r="G75" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H75" t="s">
         <v>10</v>
@@ -5987,22 +5954,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C76" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E76" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F76" t="s">
-        <v>463</v>
+        <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H76" t="s">
         <v>10</v>
@@ -6010,22 +5977,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D77" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E77" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F77" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G77" t="s">
-        <v>469</v>
+        <v>30</v>
       </c>
       <c r="H77" t="s">
         <v>10</v>
@@ -6036,7 +6003,7 @@
         <v>470</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s">
         <v>471</v>
@@ -6045,10 +6012,10 @@
         <v>472</v>
       </c>
       <c r="F78" t="s">
-        <v>7</v>
+        <v>473</v>
       </c>
       <c r="G78" t="s">
-        <v>473</v>
+        <v>41</v>
       </c>
       <c r="H78" t="s">
         <v>10</v>
@@ -6059,7 +6026,7 @@
         <v>474</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D79" t="s">
         <v>475</v>
@@ -6068,10 +6035,10 @@
         <v>476</v>
       </c>
       <c r="F79" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" t="s">
         <v>477</v>
-      </c>
-      <c r="G79" t="s">
-        <v>30</v>
       </c>
       <c r="H79" t="s">
         <v>10</v>
@@ -6082,19 +6049,19 @@
         <v>478</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
         <v>479</v>
       </c>
       <c r="E80" t="s">
+        <v>435</v>
+      </c>
+      <c r="F80" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" t="s">
         <v>480</v>
-      </c>
-      <c r="F80" t="s">
-        <v>481</v>
-      </c>
-      <c r="G80" t="s">
-        <v>41</v>
       </c>
       <c r="H80" t="s">
         <v>10</v>
@@ -6102,22 +6069,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E81" t="s">
-        <v>484</v>
+        <v>435</v>
       </c>
       <c r="F81" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G81" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="H81" t="s">
         <v>10</v>
@@ -6125,22 +6092,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E82" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="F82" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G82" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H82" t="s">
         <v>10</v>
@@ -6148,22 +6115,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
         <v>487</v>
       </c>
       <c r="E83" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="F83" t="s">
-        <v>22</v>
+        <v>489</v>
       </c>
       <c r="G83" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H83" t="s">
         <v>10</v>
@@ -6171,22 +6138,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="D84" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E84" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F84" t="s">
-        <v>7</v>
+        <v>494</v>
       </c>
       <c r="G84" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="H84" t="s">
         <v>10</v>
@@ -6194,22 +6161,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>495</v>
+      </c>
+      <c r="C85" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" t="s">
+        <v>492</v>
+      </c>
+      <c r="E85" t="s">
+        <v>493</v>
+      </c>
+      <c r="F85" t="s">
         <v>494</v>
       </c>
-      <c r="C85" t="s">
-        <v>137</v>
-      </c>
-      <c r="D85" t="s">
-        <v>495</v>
-      </c>
-      <c r="E85" t="s">
-        <v>496</v>
-      </c>
-      <c r="F85" t="s">
-        <v>497</v>
-      </c>
       <c r="G85" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="H85" t="s">
         <v>10</v>
@@ -6217,22 +6184,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>496</v>
+      </c>
+      <c r="C86" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" t="s">
+        <v>497</v>
+      </c>
+      <c r="E86" t="s">
+        <v>498</v>
+      </c>
+      <c r="F86" t="s">
         <v>499</v>
       </c>
-      <c r="C86" t="s">
-        <v>77</v>
-      </c>
-      <c r="D86" t="s">
-        <v>500</v>
-      </c>
-      <c r="E86" t="s">
-        <v>501</v>
-      </c>
-      <c r="F86" t="s">
-        <v>502</v>
-      </c>
       <c r="G86" t="s">
-        <v>493</v>
+        <v>65</v>
       </c>
       <c r="H86" t="s">
         <v>10</v>
@@ -6240,22 +6207,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C87" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E87" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F87" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G87" t="s">
-        <v>493</v>
+        <v>65</v>
       </c>
       <c r="H87" t="s">
         <v>10</v>
@@ -6263,22 +6230,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>501</v>
+      </c>
+      <c r="C88" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88" t="s">
+        <v>502</v>
+      </c>
+      <c r="E88" t="s">
+        <v>503</v>
+      </c>
+      <c r="F88" t="s">
         <v>504</v>
       </c>
-      <c r="C88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="G88" t="s">
         <v>505</v>
-      </c>
-      <c r="E88" t="s">
-        <v>506</v>
-      </c>
-      <c r="F88" t="s">
-        <v>507</v>
-      </c>
-      <c r="G88" t="s">
-        <v>65</v>
       </c>
       <c r="H88" t="s">
         <v>10</v>
@@ -6286,22 +6253,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>506</v>
+      </c>
+      <c r="C89" t="s">
+        <v>66</v>
+      </c>
+      <c r="D89" t="s">
+        <v>507</v>
+      </c>
+      <c r="E89" t="s">
         <v>508</v>
       </c>
-      <c r="C89" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" t="s">
-        <v>505</v>
-      </c>
-      <c r="E89" t="s">
-        <v>506</v>
-      </c>
       <c r="F89" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G89" t="s">
-        <v>65</v>
+        <v>510</v>
       </c>
       <c r="H89" t="s">
         <v>10</v>
@@ -6309,22 +6276,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E90" t="s">
-        <v>511</v>
+        <v>157</v>
       </c>
       <c r="F90" t="s">
-        <v>512</v>
+        <v>158</v>
       </c>
       <c r="G90" t="s">
-        <v>513</v>
+        <v>37</v>
       </c>
       <c r="H90" t="s">
         <v>10</v>
@@ -6332,22 +6299,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>513</v>
+      </c>
+      <c r="C91" t="s">
+        <v>274</v>
+      </c>
+      <c r="D91" t="s">
         <v>514</v>
       </c>
-      <c r="C91" t="s">
-        <v>66</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>515</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>516</v>
       </c>
-      <c r="F91" t="s">
-        <v>517</v>
-      </c>
       <c r="G91" t="s">
-        <v>518</v>
+        <v>169</v>
       </c>
       <c r="H91" t="s">
         <v>10</v>
@@ -6355,22 +6322,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C92" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E92" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="F92" t="s">
-        <v>166</v>
+        <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="H92" t="s">
         <v>10</v>
@@ -6378,22 +6345,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>519</v>
+      </c>
+      <c r="C93" t="s">
+        <v>20</v>
+      </c>
+      <c r="D93" t="s">
+        <v>520</v>
+      </c>
+      <c r="E93" t="s">
         <v>521</v>
       </c>
-      <c r="C93" t="s">
-        <v>282</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
         <v>522</v>
       </c>
-      <c r="E93" t="s">
-        <v>523</v>
-      </c>
-      <c r="F93" t="s">
-        <v>524</v>
-      </c>
       <c r="G93" t="s">
-        <v>177</v>
+        <v>31</v>
       </c>
       <c r="H93" t="s">
         <v>10</v>
@@ -6401,22 +6368,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>523</v>
+      </c>
+      <c r="C94" t="s">
+        <v>66</v>
+      </c>
+      <c r="D94" t="s">
+        <v>524</v>
+      </c>
+      <c r="E94" t="s">
+        <v>84</v>
+      </c>
+      <c r="F94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G94" t="s">
         <v>525</v>
-      </c>
-      <c r="C94" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" t="s">
-        <v>526</v>
-      </c>
-      <c r="E94" t="s">
-        <v>109</v>
-      </c>
-      <c r="F94" t="s">
-        <v>7</v>
-      </c>
-      <c r="G94" t="s">
-        <v>110</v>
       </c>
       <c r="H94" t="s">
         <v>10</v>
@@ -6424,22 +6391,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>526</v>
+      </c>
+      <c r="C95" t="s">
+        <v>105</v>
+      </c>
+      <c r="D95" t="s">
         <v>527</v>
       </c>
-      <c r="C95" t="s">
-        <v>20</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>528</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>529</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>530</v>
-      </c>
-      <c r="G95" t="s">
-        <v>31</v>
       </c>
       <c r="H95" t="s">
         <v>10</v>
@@ -6450,19 +6417,19 @@
         <v>531</v>
       </c>
       <c r="C96" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D96" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E96" t="s">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="F96" t="s">
-        <v>85</v>
+        <v>529</v>
       </c>
       <c r="G96" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H96" t="s">
         <v>10</v>
@@ -6470,22 +6437,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C97" t="s">
         <v>105</v>
       </c>
       <c r="D97" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E97" t="s">
-        <v>536</v>
+        <v>162</v>
       </c>
       <c r="F97" t="s">
-        <v>537</v>
+        <v>163</v>
       </c>
       <c r="G97" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="H97" t="s">
         <v>10</v>
@@ -6493,22 +6460,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C98" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D98" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E98" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F98" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G98" t="s">
-        <v>538</v>
+        <v>37</v>
       </c>
       <c r="H98" t="s">
         <v>10</v>
@@ -6516,22 +6483,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>539</v>
+      </c>
+      <c r="C99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D99" t="s">
         <v>540</v>
       </c>
-      <c r="C99" t="s">
-        <v>105</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>541</v>
       </c>
-      <c r="E99" t="s">
-        <v>170</v>
-      </c>
       <c r="F99" t="s">
-        <v>171</v>
+        <v>542</v>
       </c>
       <c r="G99" t="s">
-        <v>542</v>
+        <v>18</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -6542,7 +6509,7 @@
         <v>543</v>
       </c>
       <c r="C100" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D100" t="s">
         <v>544</v>
@@ -6554,7 +6521,7 @@
         <v>546</v>
       </c>
       <c r="G100" t="s">
-        <v>37</v>
+        <v>547</v>
       </c>
       <c r="H100" t="s">
         <v>10</v>
@@ -6562,22 +6529,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>325</v>
       </c>
       <c r="D101" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E101" t="s">
-        <v>549</v>
+        <v>103</v>
       </c>
       <c r="F101" t="s">
+        <v>104</v>
+      </c>
+      <c r="G101" t="s">
         <v>550</v>
-      </c>
-      <c r="G101" t="s">
-        <v>18</v>
       </c>
       <c r="H101" t="s">
         <v>10</v>
@@ -6588,19 +6555,19 @@
         <v>551</v>
       </c>
       <c r="C102" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D102" t="s">
         <v>552</v>
       </c>
       <c r="E102" t="s">
+        <v>184</v>
+      </c>
+      <c r="F102" t="s">
+        <v>168</v>
+      </c>
+      <c r="G102" t="s">
         <v>553</v>
-      </c>
-      <c r="F102" t="s">
-        <v>554</v>
-      </c>
-      <c r="G102" t="s">
-        <v>555</v>
       </c>
       <c r="H102" t="s">
         <v>10</v>
@@ -6608,19 +6575,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>554</v>
+      </c>
+      <c r="C103" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" t="s">
+        <v>555</v>
+      </c>
+      <c r="E103" t="s">
         <v>556</v>
       </c>
-      <c r="C103" t="s">
-        <v>333</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="F103" t="s">
         <v>557</v>
-      </c>
-      <c r="E103" t="s">
-        <v>103</v>
-      </c>
-      <c r="F103" t="s">
-        <v>104</v>
       </c>
       <c r="G103" t="s">
         <v>558</v>
@@ -6634,19 +6601,19 @@
         <v>559</v>
       </c>
       <c r="C104" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E104" t="s">
-        <v>192</v>
+        <v>556</v>
       </c>
       <c r="F104" t="s">
-        <v>176</v>
+        <v>557</v>
       </c>
       <c r="G104" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H104" t="s">
         <v>10</v>
@@ -6654,22 +6621,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>560</v>
+      </c>
+      <c r="C105" t="s">
+        <v>94</v>
+      </c>
+      <c r="D105" t="s">
+        <v>561</v>
+      </c>
+      <c r="E105" t="s">
+        <v>92</v>
+      </c>
+      <c r="F105" t="s">
+        <v>93</v>
+      </c>
+      <c r="G105" t="s">
         <v>562</v>
-      </c>
-      <c r="C105" t="s">
-        <v>25</v>
-      </c>
-      <c r="D105" t="s">
-        <v>563</v>
-      </c>
-      <c r="E105" t="s">
-        <v>564</v>
-      </c>
-      <c r="F105" t="s">
-        <v>565</v>
-      </c>
-      <c r="G105" t="s">
-        <v>566</v>
       </c>
       <c r="H105" t="s">
         <v>10</v>
@@ -6677,22 +6644,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D106" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E106" t="s">
-        <v>564</v>
+        <v>138</v>
       </c>
       <c r="F106" t="s">
-        <v>565</v>
+        <v>139</v>
       </c>
       <c r="G106" t="s">
-        <v>566</v>
+        <v>177</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -6700,22 +6667,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>565</v>
+      </c>
+      <c r="C107" t="s">
+        <v>132</v>
+      </c>
+      <c r="D107" t="s">
+        <v>566</v>
+      </c>
+      <c r="E107" t="s">
+        <v>567</v>
+      </c>
+      <c r="F107" t="s">
         <v>568</v>
       </c>
-      <c r="C107" t="s">
-        <v>94</v>
-      </c>
-      <c r="D107" t="s">
-        <v>569</v>
-      </c>
-      <c r="E107" t="s">
-        <v>92</v>
-      </c>
-      <c r="F107" t="s">
-        <v>93</v>
-      </c>
       <c r="G107" t="s">
-        <v>570</v>
+        <v>37</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -6723,22 +6690,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>569</v>
+      </c>
+      <c r="C108" t="s">
+        <v>39</v>
+      </c>
+      <c r="D108" t="s">
+        <v>570</v>
+      </c>
+      <c r="E108" t="s">
+        <v>112</v>
+      </c>
+      <c r="F108" t="s">
+        <v>113</v>
+      </c>
+      <c r="G108" t="s">
         <v>571</v>
-      </c>
-      <c r="C108" t="s">
-        <v>56</v>
-      </c>
-      <c r="D108" t="s">
-        <v>572</v>
-      </c>
-      <c r="E108" t="s">
-        <v>146</v>
-      </c>
-      <c r="F108" t="s">
-        <v>147</v>
-      </c>
-      <c r="G108" t="s">
-        <v>185</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -6746,22 +6713,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>572</v>
+      </c>
+      <c r="C109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109" t="s">
         <v>573</v>
       </c>
-      <c r="C109" t="s">
-        <v>137</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
+        <v>148</v>
+      </c>
+      <c r="F109" t="s">
+        <v>149</v>
+      </c>
+      <c r="G109" t="s">
         <v>574</v>
-      </c>
-      <c r="E109" t="s">
-        <v>575</v>
-      </c>
-      <c r="F109" t="s">
-        <v>576</v>
-      </c>
-      <c r="G109" t="s">
-        <v>37</v>
       </c>
       <c r="H109" t="s">
         <v>10</v>
@@ -6769,22 +6736,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>575</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" t="s">
+        <v>576</v>
+      </c>
+      <c r="E110" t="s">
+        <v>253</v>
+      </c>
+      <c r="F110" t="s">
+        <v>254</v>
+      </c>
+      <c r="G110" t="s">
         <v>577</v>
-      </c>
-      <c r="C110" t="s">
-        <v>39</v>
-      </c>
-      <c r="D110" t="s">
-        <v>578</v>
-      </c>
-      <c r="E110" t="s">
-        <v>112</v>
-      </c>
-      <c r="F110" t="s">
-        <v>113</v>
-      </c>
-      <c r="G110" t="s">
-        <v>579</v>
       </c>
       <c r="H110" t="s">
         <v>10</v>
@@ -6792,22 +6759,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E111" t="s">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="F111" t="s">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="G111" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="H111" t="s">
         <v>10</v>
@@ -6815,22 +6782,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D112" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E112" t="s">
-        <v>261</v>
+        <v>86</v>
       </c>
       <c r="F112" t="s">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="H112" t="s">
         <v>10</v>
@@ -6838,22 +6805,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D113" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E113" t="s">
-        <v>261</v>
+        <v>86</v>
       </c>
       <c r="F113" t="s">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="H113" t="s">
         <v>10</v>
@@ -6861,13 +6828,13 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C114" t="s">
         <v>35</v>
       </c>
       <c r="D114" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="E114" t="s">
         <v>86</v>
@@ -6876,7 +6843,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="H114" t="s">
         <v>10</v>
@@ -6884,22 +6851,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C115" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D115" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E115" t="s">
-        <v>86</v>
+        <v>508</v>
       </c>
       <c r="F115" t="s">
-        <v>80</v>
+        <v>509</v>
       </c>
       <c r="G115" t="s">
-        <v>589</v>
+        <v>135</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -6907,22 +6874,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C116" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D116" t="s">
+        <v>587</v>
+      </c>
+      <c r="E116" t="s">
         <v>588</v>
       </c>
-      <c r="E116" t="s">
-        <v>86</v>
-      </c>
       <c r="F116" t="s">
-        <v>80</v>
+        <v>589</v>
       </c>
       <c r="G116" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
@@ -6930,22 +6897,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>591</v>
+      </c>
+      <c r="C117" t="s">
+        <v>325</v>
+      </c>
+      <c r="D117" t="s">
         <v>592</v>
       </c>
-      <c r="C117" t="s">
-        <v>66</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>593</v>
       </c>
-      <c r="E117" t="s">
-        <v>516</v>
-      </c>
       <c r="F117" t="s">
-        <v>517</v>
+        <v>594</v>
       </c>
       <c r="G117" t="s">
-        <v>143</v>
+        <v>595</v>
       </c>
       <c r="H117" t="s">
         <v>10</v>
@@ -6953,22 +6920,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C118" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="D118" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E118" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F118" t="s">
-        <v>597</v>
+        <v>27</v>
       </c>
       <c r="G118" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H118" t="s">
         <v>10</v>
@@ -6976,22 +6943,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C119" t="s">
-        <v>333</v>
+        <v>127</v>
       </c>
       <c r="D119" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E119" t="s">
-        <v>601</v>
+        <v>173</v>
       </c>
       <c r="F119" t="s">
+        <v>174</v>
+      </c>
+      <c r="G119" t="s">
         <v>602</v>
-      </c>
-      <c r="G119" t="s">
-        <v>603</v>
       </c>
       <c r="H119" t="s">
         <v>10</v>
@@ -6999,19 +6966,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>603</v>
+      </c>
+      <c r="C120" t="s">
+        <v>126</v>
+      </c>
+      <c r="D120" t="s">
         <v>604</v>
       </c>
-      <c r="C120" t="s">
-        <v>29</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>605</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>606</v>
-      </c>
-      <c r="F120" t="s">
-        <v>27</v>
       </c>
       <c r="G120" t="s">
         <v>607</v>
@@ -7025,16 +6992,16 @@
         <v>608</v>
       </c>
       <c r="C121" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="D121" t="s">
         <v>609</v>
       </c>
       <c r="E121" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="F121" t="s">
-        <v>182</v>
+        <v>7</v>
       </c>
       <c r="G121" t="s">
         <v>610</v>
@@ -7048,19 +7015,19 @@
         <v>611</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D122" t="s">
         <v>612</v>
       </c>
       <c r="E122" t="s">
-        <v>144</v>
+        <v>613</v>
       </c>
       <c r="F122" t="s">
-        <v>145</v>
+        <v>614</v>
       </c>
       <c r="G122" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H122" t="s">
         <v>10</v>
@@ -7068,22 +7035,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C123" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="D123" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E123" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F123" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="G123" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H123" t="s">
         <v>10</v>
@@ -7091,22 +7058,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C124" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D124" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E124" t="s">
-        <v>106</v>
+        <v>623</v>
       </c>
       <c r="F124" t="s">
-        <v>7</v>
+        <v>624</v>
       </c>
       <c r="G124" t="s">
-        <v>621</v>
+        <v>15</v>
       </c>
       <c r="H124" t="s">
         <v>10</v>
@@ -7114,22 +7081,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>625</v>
+      </c>
+      <c r="C125" t="s">
+        <v>72</v>
+      </c>
+      <c r="D125" t="s">
         <v>622</v>
       </c>
-      <c r="C125" t="s">
-        <v>77</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>623</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>624</v>
       </c>
-      <c r="F125" t="s">
-        <v>625</v>
-      </c>
       <c r="G125" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="H125" t="s">
         <v>10</v>
@@ -7137,22 +7104,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C126" t="s">
         <v>72</v>
       </c>
       <c r="D126" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E126" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="F126" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="G126" t="s">
-        <v>631</v>
+        <v>15</v>
       </c>
       <c r="H126" t="s">
         <v>10</v>
@@ -7160,22 +7127,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="C127" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D127" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="E127" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="F127" t="s">
-        <v>635</v>
+        <v>27</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>630</v>
       </c>
       <c r="H127" t="s">
         <v>10</v>
@@ -7183,22 +7150,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C128" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="D128" t="s">
+        <v>632</v>
+      </c>
+      <c r="E128" t="s">
+        <v>155</v>
+      </c>
+      <c r="F128" t="s">
+        <v>156</v>
+      </c>
+      <c r="G128" t="s">
         <v>633</v>
-      </c>
-      <c r="E128" t="s">
-        <v>634</v>
-      </c>
-      <c r="F128" t="s">
-        <v>635</v>
-      </c>
-      <c r="G128" t="s">
-        <v>15</v>
       </c>
       <c r="H128" t="s">
         <v>10</v>
@@ -7206,22 +7173,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>634</v>
+      </c>
+      <c r="C129" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" t="s">
+        <v>635</v>
+      </c>
+      <c r="E129" t="s">
+        <v>636</v>
+      </c>
+      <c r="F129" t="s">
         <v>637</v>
       </c>
-      <c r="C129" t="s">
-        <v>72</v>
-      </c>
-      <c r="D129" t="s">
-        <v>633</v>
-      </c>
-      <c r="E129" t="s">
-        <v>634</v>
-      </c>
-      <c r="F129" t="s">
-        <v>635</v>
-      </c>
       <c r="G129" t="s">
-        <v>15</v>
+        <v>610</v>
       </c>
       <c r="H129" t="s">
         <v>10</v>
@@ -7232,19 +7199,19 @@
         <v>638</v>
       </c>
       <c r="C130" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D130" t="s">
         <v>639</v>
       </c>
       <c r="E130" t="s">
-        <v>640</v>
+        <v>144</v>
       </c>
       <c r="F130" t="s">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="G130" t="s">
-        <v>641</v>
+        <v>97</v>
       </c>
       <c r="H130" t="s">
         <v>10</v>
@@ -7252,22 +7219,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C131" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D131" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E131" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="F131" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="G131" t="s">
-        <v>644</v>
+        <v>97</v>
       </c>
       <c r="H131" t="s">
         <v>10</v>
@@ -7275,22 +7242,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C132" t="s">
-        <v>19</v>
+        <v>325</v>
       </c>
       <c r="D132" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E132" t="s">
-        <v>647</v>
+        <v>51</v>
       </c>
       <c r="F132" t="s">
-        <v>648</v>
+        <v>52</v>
       </c>
       <c r="G132" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="H132" t="s">
         <v>10</v>
@@ -7298,22 +7265,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C133" t="s">
-        <v>35</v>
+        <v>325</v>
       </c>
       <c r="D133" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E133" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="F133" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G133" t="s">
-        <v>97</v>
+        <v>643</v>
       </c>
       <c r="H133" t="s">
         <v>10</v>
@@ -7321,22 +7288,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C134" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E134" t="s">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="F134" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="G134" t="s">
-        <v>97</v>
+        <v>647</v>
       </c>
       <c r="H134" t="s">
         <v>10</v>
@@ -7344,22 +7311,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C135" t="s">
-        <v>333</v>
+        <v>33</v>
       </c>
       <c r="D135" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E135" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="F135" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="G135" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="H135" t="s">
         <v>10</v>
@@ -7367,22 +7334,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C136" t="s">
-        <v>333</v>
+        <v>11</v>
       </c>
       <c r="D136" t="s">
+        <v>652</v>
+      </c>
+      <c r="E136" t="s">
         <v>653</v>
       </c>
-      <c r="E136" t="s">
-        <v>51</v>
-      </c>
       <c r="F136" t="s">
-        <v>52</v>
+        <v>654</v>
       </c>
       <c r="G136" t="s">
-        <v>654</v>
+        <v>79</v>
       </c>
       <c r="H136" t="s">
         <v>10</v>
@@ -7390,22 +7357,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>655</v>
+      </c>
+      <c r="C137" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137" t="s">
         <v>656</v>
       </c>
-      <c r="C137" t="s">
-        <v>25</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>657</v>
       </c>
-      <c r="E137" t="s">
-        <v>46</v>
-      </c>
       <c r="F137" t="s">
-        <v>47</v>
+        <v>658</v>
       </c>
       <c r="G137" t="s">
-        <v>658</v>
+        <v>59</v>
       </c>
       <c r="H137" t="s">
         <v>10</v>
@@ -7416,19 +7383,19 @@
         <v>659</v>
       </c>
       <c r="C138" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D138" t="s">
         <v>660</v>
       </c>
       <c r="E138" t="s">
-        <v>192</v>
+        <v>661</v>
       </c>
       <c r="F138" t="s">
-        <v>176</v>
+        <v>662</v>
       </c>
       <c r="G138" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H138" t="s">
         <v>10</v>
@@ -7436,22 +7403,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C139" t="s">
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E139" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F139" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G139" t="s">
-        <v>79</v>
+        <v>668</v>
       </c>
       <c r="H139" t="s">
         <v>10</v>
@@ -7459,22 +7426,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>669</v>
+      </c>
+      <c r="C140" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" t="s">
+        <v>665</v>
+      </c>
+      <c r="E140" t="s">
         <v>666</v>
       </c>
-      <c r="C140" t="s">
-        <v>14</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="F140" t="s">
         <v>667</v>
       </c>
-      <c r="E140" t="s">
+      <c r="G140" t="s">
         <v>668</v>
-      </c>
-      <c r="F140" t="s">
-        <v>669</v>
-      </c>
-      <c r="G140" t="s">
-        <v>59</v>
       </c>
       <c r="H140" t="s">
         <v>10</v>
@@ -7485,7 +7452,7 @@
         <v>670</v>
       </c>
       <c r="C141" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D141" t="s">
         <v>671</v>
@@ -7508,7 +7475,7 @@
         <v>675</v>
       </c>
       <c r="C142" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="D142" t="s">
         <v>676</v>
@@ -7520,7 +7487,7 @@
         <v>678</v>
       </c>
       <c r="G142" t="s">
-        <v>679</v>
+        <v>152</v>
       </c>
       <c r="H142" t="s">
         <v>10</v>
@@ -7528,10 +7495,10 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C143" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="D143" t="s">
         <v>676</v>
@@ -7543,7 +7510,7 @@
         <v>678</v>
       </c>
       <c r="G143" t="s">
-        <v>679</v>
+        <v>152</v>
       </c>
       <c r="H143" t="s">
         <v>10</v>
@@ -7551,22 +7518,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>680</v>
+      </c>
+      <c r="C144" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" t="s">
         <v>681</v>
       </c>
-      <c r="C144" t="s">
-        <v>38</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
+        <v>241</v>
+      </c>
+      <c r="F144" t="s">
+        <v>242</v>
+      </c>
+      <c r="G144" t="s">
         <v>682</v>
-      </c>
-      <c r="E144" t="s">
-        <v>683</v>
-      </c>
-      <c r="F144" t="s">
-        <v>684</v>
-      </c>
-      <c r="G144" t="s">
-        <v>685</v>
       </c>
       <c r="H144" t="s">
         <v>10</v>
@@ -7574,22 +7541,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>683</v>
+      </c>
+      <c r="C145" t="s">
+        <v>72</v>
+      </c>
+      <c r="D145" t="s">
+        <v>684</v>
+      </c>
+      <c r="E145" t="s">
+        <v>685</v>
+      </c>
+      <c r="F145" t="s">
         <v>686</v>
       </c>
-      <c r="C145" t="s">
-        <v>137</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="G145" t="s">
         <v>687</v>
-      </c>
-      <c r="E145" t="s">
-        <v>688</v>
-      </c>
-      <c r="F145" t="s">
-        <v>689</v>
-      </c>
-      <c r="G145" t="s">
-        <v>160</v>
       </c>
       <c r="H145" t="s">
         <v>10</v>
@@ -7597,22 +7564,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>688</v>
+      </c>
+      <c r="C146" t="s">
+        <v>127</v>
+      </c>
+      <c r="D146" t="s">
+        <v>689</v>
+      </c>
+      <c r="E146" t="s">
+        <v>53</v>
+      </c>
+      <c r="F146" t="s">
+        <v>54</v>
+      </c>
+      <c r="G146" t="s">
         <v>690</v>
-      </c>
-      <c r="C146" t="s">
-        <v>137</v>
-      </c>
-      <c r="D146" t="s">
-        <v>687</v>
-      </c>
-      <c r="E146" t="s">
-        <v>688</v>
-      </c>
-      <c r="F146" t="s">
-        <v>689</v>
-      </c>
-      <c r="G146" t="s">
-        <v>160</v>
       </c>
       <c r="H146" t="s">
         <v>10</v>
@@ -7623,19 +7590,19 @@
         <v>691</v>
       </c>
       <c r="C147" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D147" t="s">
         <v>692</v>
       </c>
       <c r="E147" t="s">
-        <v>249</v>
+        <v>693</v>
       </c>
       <c r="F147" t="s">
-        <v>250</v>
+        <v>694</v>
       </c>
       <c r="G147" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H147" t="s">
         <v>10</v>
@@ -7643,22 +7610,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C148" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="D148" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E148" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F148" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G148" t="s">
-        <v>698</v>
+        <v>79</v>
       </c>
       <c r="H148" t="s">
         <v>10</v>
@@ -7666,22 +7633,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C149" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="D149" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E149" t="s">
-        <v>53</v>
+        <v>702</v>
       </c>
       <c r="F149" t="s">
-        <v>54</v>
+        <v>703</v>
       </c>
       <c r="G149" t="s">
-        <v>701</v>
+        <v>610</v>
       </c>
       <c r="H149" t="s">
         <v>10</v>
@@ -7689,22 +7656,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D150" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E150" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F150" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="G150" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H150" t="s">
         <v>10</v>
@@ -7712,22 +7679,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C151" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E151" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F151" t="s">
-        <v>710</v>
+        <v>7</v>
       </c>
       <c r="G151" t="s">
-        <v>79</v>
+        <v>712</v>
       </c>
       <c r="H151" t="s">
         <v>10</v>
@@ -7735,22 +7702,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C152" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="D152" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E152" t="s">
-        <v>713</v>
+        <v>181</v>
       </c>
       <c r="F152" t="s">
-        <v>714</v>
+        <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>621</v>
+        <v>715</v>
       </c>
       <c r="H152" t="s">
         <v>10</v>
@@ -7758,22 +7725,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C153" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E153" t="s">
-        <v>717</v>
+        <v>151</v>
       </c>
       <c r="F153" t="s">
+        <v>7</v>
+      </c>
+      <c r="G153" t="s">
         <v>718</v>
-      </c>
-      <c r="G153" t="s">
-        <v>719</v>
       </c>
       <c r="H153" t="s">
         <v>10</v>
@@ -7781,22 +7748,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>719</v>
+      </c>
+      <c r="C154" t="s">
+        <v>124</v>
+      </c>
+      <c r="D154" t="s">
         <v>720</v>
       </c>
-      <c r="C154" t="s">
-        <v>16</v>
-      </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
+        <v>44</v>
+      </c>
+      <c r="F154" t="s">
+        <v>45</v>
+      </c>
+      <c r="G154" t="s">
         <v>721</v>
-      </c>
-      <c r="E154" t="s">
-        <v>722</v>
-      </c>
-      <c r="F154" t="s">
-        <v>7</v>
-      </c>
-      <c r="G154" t="s">
-        <v>723</v>
       </c>
       <c r="H154" t="s">
         <v>10</v>
@@ -7804,19 +7771,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>722</v>
+      </c>
+      <c r="C155" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" t="s">
+        <v>723</v>
+      </c>
+      <c r="E155" t="s">
         <v>724</v>
       </c>
-      <c r="C155" t="s">
-        <v>135</v>
-      </c>
-      <c r="D155" t="s">
+      <c r="F155" t="s">
         <v>725</v>
-      </c>
-      <c r="E155" t="s">
-        <v>189</v>
-      </c>
-      <c r="F155" t="s">
-        <v>7</v>
       </c>
       <c r="G155" t="s">
         <v>726</v>
@@ -7830,19 +7797,19 @@
         <v>727</v>
       </c>
       <c r="C156" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D156" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E156" t="s">
-        <v>159</v>
+        <v>724</v>
       </c>
       <c r="F156" t="s">
-        <v>7</v>
+        <v>725</v>
       </c>
       <c r="G156" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="H156" t="s">
         <v>10</v>
@@ -7850,22 +7817,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C157" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="D157" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E157" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F157" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="G157" t="s">
-        <v>732</v>
+        <v>153</v>
       </c>
       <c r="H157" t="s">
         <v>10</v>
@@ -7873,22 +7840,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>730</v>
+      </c>
+      <c r="C158" t="s">
+        <v>124</v>
+      </c>
+      <c r="D158" t="s">
+        <v>731</v>
+      </c>
+      <c r="E158" t="s">
+        <v>732</v>
+      </c>
+      <c r="F158" t="s">
         <v>733</v>
       </c>
-      <c r="C158" t="s">
-        <v>12</v>
-      </c>
-      <c r="D158" t="s">
+      <c r="G158" t="s">
         <v>734</v>
-      </c>
-      <c r="E158" t="s">
-        <v>735</v>
-      </c>
-      <c r="F158" t="s">
-        <v>736</v>
-      </c>
-      <c r="G158" t="s">
-        <v>737</v>
       </c>
       <c r="H158" t="s">
         <v>10</v>
@@ -7896,22 +7863,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>735</v>
+      </c>
+      <c r="C159" t="s">
+        <v>127</v>
+      </c>
+      <c r="D159" t="s">
+        <v>736</v>
+      </c>
+      <c r="E159" t="s">
+        <v>737</v>
+      </c>
+      <c r="F159" t="s">
         <v>738</v>
       </c>
-      <c r="C159" t="s">
-        <v>12</v>
-      </c>
-      <c r="D159" t="s">
-        <v>734</v>
-      </c>
-      <c r="E159" t="s">
-        <v>735</v>
-      </c>
-      <c r="F159" t="s">
-        <v>736</v>
-      </c>
       <c r="G159" t="s">
-        <v>737</v>
+        <v>79</v>
       </c>
       <c r="H159" t="s">
         <v>10</v>
@@ -7922,19 +7889,19 @@
         <v>739</v>
       </c>
       <c r="C160" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="D160" t="s">
         <v>740</v>
       </c>
       <c r="E160" t="s">
-        <v>95</v>
+        <v>741</v>
       </c>
       <c r="F160" t="s">
-        <v>96</v>
+        <v>742</v>
       </c>
       <c r="G160" t="s">
-        <v>161</v>
+        <v>743</v>
       </c>
       <c r="H160" t="s">
         <v>10</v>
@@ -7942,22 +7909,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C161" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="D161" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E161" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="F161" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="G161" t="s">
-        <v>745</v>
+        <v>34</v>
       </c>
       <c r="H161" t="s">
         <v>10</v>
@@ -7965,22 +7932,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>748</v>
+      </c>
+      <c r="C162" t="s">
+        <v>19</v>
+      </c>
+      <c r="D162" t="s">
+        <v>745</v>
+      </c>
+      <c r="E162" t="s">
         <v>746</v>
       </c>
-      <c r="C162" t="s">
-        <v>128</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
         <v>747</v>
       </c>
-      <c r="E162" t="s">
-        <v>748</v>
-      </c>
-      <c r="F162" t="s">
-        <v>749</v>
-      </c>
       <c r="G162" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="H162" t="s">
         <v>10</v>
@@ -7988,22 +7955,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>749</v>
+      </c>
+      <c r="C163" t="s">
+        <v>38</v>
+      </c>
+      <c r="D163" t="s">
         <v>750</v>
       </c>
-      <c r="C163" t="s">
-        <v>128</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>751</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>752</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>753</v>
-      </c>
-      <c r="G163" t="s">
-        <v>754</v>
       </c>
       <c r="H163" t="s">
         <v>10</v>
@@ -8011,22 +7978,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>754</v>
+      </c>
+      <c r="C164" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" t="s">
         <v>755</v>
       </c>
-      <c r="C164" t="s">
-        <v>19</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>756</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>757</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>758</v>
-      </c>
-      <c r="G164" t="s">
-        <v>34</v>
       </c>
       <c r="H164" t="s">
         <v>10</v>
@@ -8037,19 +8004,19 @@
         <v>759</v>
       </c>
       <c r="C165" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D165" t="s">
+        <v>755</v>
+      </c>
+      <c r="E165" t="s">
         <v>756</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>757</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>758</v>
-      </c>
-      <c r="G165" t="s">
-        <v>34</v>
       </c>
       <c r="H165" t="s">
         <v>10</v>
@@ -8060,7 +8027,7 @@
         <v>760</v>
       </c>
       <c r="C166" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="D166" t="s">
         <v>761</v>
@@ -8083,7 +8050,7 @@
         <v>765</v>
       </c>
       <c r="C167" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D167" t="s">
         <v>766</v>
@@ -8095,7 +8062,7 @@
         <v>768</v>
       </c>
       <c r="G167" t="s">
-        <v>769</v>
+        <v>34</v>
       </c>
       <c r="H167" t="s">
         <v>10</v>
@@ -8103,10 +8070,10 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C168" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D168" t="s">
         <v>766</v>
@@ -8118,7 +8085,7 @@
         <v>768</v>
       </c>
       <c r="G168" t="s">
-        <v>769</v>
+        <v>34</v>
       </c>
       <c r="H168" t="s">
         <v>10</v>
@@ -8126,22 +8093,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>770</v>
+      </c>
+      <c r="C169" t="s">
+        <v>66</v>
+      </c>
+      <c r="D169" t="s">
         <v>771</v>
       </c>
-      <c r="C169" t="s">
-        <v>128</v>
-      </c>
-      <c r="D169" t="s">
-        <v>772</v>
-      </c>
       <c r="E169" t="s">
-        <v>773</v>
+        <v>414</v>
       </c>
       <c r="F169" t="s">
-        <v>774</v>
+        <v>7</v>
       </c>
       <c r="G169" t="s">
-        <v>775</v>
+        <v>415</v>
       </c>
       <c r="H169" t="s">
         <v>10</v>
@@ -8149,22 +8116,22 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C170" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D170" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="E170" t="s">
-        <v>778</v>
+        <v>414</v>
       </c>
       <c r="F170" t="s">
-        <v>779</v>
+        <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>34</v>
+        <v>415</v>
       </c>
       <c r="H170" t="s">
         <v>10</v>
@@ -8172,22 +8139,22 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="C171" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D171" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E171" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="F171" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="G171" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="H171" t="s">
         <v>10</v>
@@ -8195,22 +8162,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C172" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D172" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E172" t="s">
-        <v>422</v>
+        <v>111</v>
       </c>
       <c r="F172" t="s">
         <v>7</v>
       </c>
       <c r="G172" t="s">
-        <v>423</v>
+        <v>186</v>
       </c>
       <c r="H172" t="s">
         <v>10</v>
@@ -8218,22 +8185,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>779</v>
+      </c>
+      <c r="C173" t="s">
+        <v>126</v>
+      </c>
+      <c r="D173" t="s">
+        <v>780</v>
+      </c>
+      <c r="E173" t="s">
+        <v>781</v>
+      </c>
+      <c r="F173" t="s">
+        <v>782</v>
+      </c>
+      <c r="G173" t="s">
         <v>783</v>
-      </c>
-      <c r="C173" t="s">
-        <v>66</v>
-      </c>
-      <c r="D173" t="s">
-        <v>782</v>
-      </c>
-      <c r="E173" t="s">
-        <v>422</v>
-      </c>
-      <c r="F173" t="s">
-        <v>7</v>
-      </c>
-      <c r="G173" t="s">
-        <v>423</v>
       </c>
       <c r="H173" t="s">
         <v>10</v>
@@ -8244,7 +8211,7 @@
         <v>784</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="D174" t="s">
         <v>785</v>
@@ -8256,7 +8223,7 @@
         <v>787</v>
       </c>
       <c r="G174" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H174" t="s">
         <v>10</v>
@@ -8267,19 +8234,19 @@
         <v>788</v>
       </c>
       <c r="C175" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="D175" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E175" t="s">
-        <v>111</v>
+        <v>786</v>
       </c>
       <c r="F175" t="s">
-        <v>7</v>
+        <v>787</v>
       </c>
       <c r="G175" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="H175" t="s">
         <v>10</v>
@@ -8287,22 +8254,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>789</v>
+      </c>
+      <c r="C176" t="s">
+        <v>28</v>
+      </c>
+      <c r="D176" t="s">
         <v>790</v>
       </c>
-      <c r="C176" t="s">
-        <v>126</v>
-      </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>791</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>792</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>793</v>
-      </c>
-      <c r="G176" t="s">
-        <v>794</v>
       </c>
       <c r="H176" t="s">
         <v>10</v>
@@ -8310,22 +8277,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>794</v>
+      </c>
+      <c r="C177" t="s">
+        <v>74</v>
+      </c>
+      <c r="D177" t="s">
         <v>795</v>
       </c>
-      <c r="C177" t="s">
-        <v>81</v>
-      </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
+        <v>106</v>
+      </c>
+      <c r="F177" t="s">
+        <v>7</v>
+      </c>
+      <c r="G177" t="s">
         <v>796</v>
-      </c>
-      <c r="E177" t="s">
-        <v>797</v>
-      </c>
-      <c r="F177" t="s">
-        <v>798</v>
-      </c>
-      <c r="G177" t="s">
-        <v>172</v>
       </c>
       <c r="H177" t="s">
         <v>10</v>
@@ -8333,22 +8300,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C178" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D178" t="s">
+        <v>795</v>
+      </c>
+      <c r="E178" t="s">
+        <v>106</v>
+      </c>
+      <c r="F178" t="s">
+        <v>7</v>
+      </c>
+      <c r="G178" t="s">
         <v>796</v>
-      </c>
-      <c r="E178" t="s">
-        <v>797</v>
-      </c>
-      <c r="F178" t="s">
-        <v>798</v>
-      </c>
-      <c r="G178" t="s">
-        <v>172</v>
       </c>
       <c r="H178" t="s">
         <v>10</v>
@@ -8356,22 +8323,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>798</v>
+      </c>
+      <c r="C179" t="s">
+        <v>363</v>
+      </c>
+      <c r="D179" t="s">
+        <v>799</v>
+      </c>
+      <c r="E179" t="s">
         <v>800</v>
       </c>
-      <c r="C179" t="s">
-        <v>28</v>
-      </c>
-      <c r="D179" t="s">
+      <c r="F179" t="s">
         <v>801</v>
       </c>
-      <c r="E179" t="s">
-        <v>802</v>
-      </c>
-      <c r="F179" t="s">
-        <v>803</v>
-      </c>
       <c r="G179" t="s">
-        <v>804</v>
+        <v>743</v>
       </c>
       <c r="H179" t="s">
         <v>10</v>
@@ -8379,22 +8346,22 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C180" t="s">
-        <v>74</v>
+        <v>363</v>
       </c>
       <c r="D180" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="E180" t="s">
-        <v>106</v>
+        <v>800</v>
       </c>
       <c r="F180" t="s">
-        <v>7</v>
+        <v>801</v>
       </c>
       <c r="G180" t="s">
-        <v>807</v>
+        <v>743</v>
       </c>
       <c r="H180" t="s">
         <v>10</v>
@@ -8402,19 +8369,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C181" t="s">
-        <v>74</v>
+        <v>351</v>
       </c>
       <c r="D181" t="s">
+        <v>804</v>
+      </c>
+      <c r="E181" t="s">
+        <v>805</v>
+      </c>
+      <c r="F181" t="s">
         <v>806</v>
-      </c>
-      <c r="E181" t="s">
-        <v>106</v>
-      </c>
-      <c r="F181" t="s">
-        <v>7</v>
       </c>
       <c r="G181" t="s">
         <v>807</v>
@@ -8425,22 +8392,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>808</v>
+      </c>
+      <c r="C182" t="s">
+        <v>48</v>
+      </c>
+      <c r="D182" t="s">
         <v>809</v>
       </c>
-      <c r="C182" t="s">
-        <v>371</v>
-      </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
+        <v>57</v>
+      </c>
+      <c r="F182" t="s">
+        <v>7</v>
+      </c>
+      <c r="G182" t="s">
         <v>810</v>
-      </c>
-      <c r="E182" t="s">
-        <v>811</v>
-      </c>
-      <c r="F182" t="s">
-        <v>812</v>
-      </c>
-      <c r="G182" t="s">
-        <v>754</v>
       </c>
       <c r="H182" t="s">
         <v>10</v>
@@ -8448,22 +8415,22 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C183" t="s">
-        <v>371</v>
+        <v>48</v>
       </c>
       <c r="D183" t="s">
+        <v>809</v>
+      </c>
+      <c r="E183" t="s">
+        <v>57</v>
+      </c>
+      <c r="F183" t="s">
+        <v>7</v>
+      </c>
+      <c r="G183" t="s">
         <v>810</v>
-      </c>
-      <c r="E183" t="s">
-        <v>811</v>
-      </c>
-      <c r="F183" t="s">
-        <v>812</v>
-      </c>
-      <c r="G183" t="s">
-        <v>754</v>
       </c>
       <c r="H183" t="s">
         <v>10</v>
@@ -8471,22 +8438,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>812</v>
+      </c>
+      <c r="C184" t="s">
+        <v>105</v>
+      </c>
+      <c r="D184" t="s">
+        <v>813</v>
+      </c>
+      <c r="E184" t="s">
+        <v>309</v>
+      </c>
+      <c r="F184" t="s">
+        <v>7</v>
+      </c>
+      <c r="G184" t="s">
         <v>814</v>
-      </c>
-      <c r="C184" t="s">
-        <v>359</v>
-      </c>
-      <c r="D184" t="s">
-        <v>815</v>
-      </c>
-      <c r="E184" t="s">
-        <v>816</v>
-      </c>
-      <c r="F184" t="s">
-        <v>817</v>
-      </c>
-      <c r="G184" t="s">
-        <v>818</v>
       </c>
       <c r="H184" t="s">
         <v>10</v>
@@ -8494,22 +8461,22 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C185" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D185" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E185" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="F185" t="s">
-        <v>7</v>
+        <v>203</v>
       </c>
       <c r="G185" t="s">
-        <v>821</v>
+        <v>152</v>
       </c>
       <c r="H185" t="s">
         <v>10</v>
@@ -8517,22 +8484,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C186" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D186" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E186" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="F186" t="s">
-        <v>7</v>
+        <v>203</v>
       </c>
       <c r="G186" t="s">
-        <v>821</v>
+        <v>152</v>
       </c>
       <c r="H186" t="s">
         <v>10</v>
@@ -8540,22 +8507,22 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C187" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D187" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="E187" t="s">
-        <v>317</v>
+        <v>198</v>
       </c>
       <c r="F187" t="s">
-        <v>7</v>
+        <v>199</v>
       </c>
       <c r="G187" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="H187" t="s">
         <v>10</v>
@@ -8563,22 +8530,22 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C188" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="D188" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="E188" t="s">
-        <v>210</v>
+        <v>823</v>
       </c>
       <c r="F188" t="s">
-        <v>211</v>
+        <v>824</v>
       </c>
       <c r="G188" t="s">
-        <v>160</v>
+        <v>825</v>
       </c>
       <c r="H188" t="s">
         <v>10</v>
@@ -8586,22 +8553,22 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C189" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D189" t="s">
         <v>827</v>
       </c>
       <c r="E189" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="F189" t="s">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="G189" t="s">
-        <v>160</v>
+        <v>828</v>
       </c>
       <c r="H189" t="s">
         <v>10</v>
@@ -8612,16 +8579,16 @@
         <v>829</v>
       </c>
       <c r="C190" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D190" t="s">
         <v>830</v>
       </c>
       <c r="E190" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="F190" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="G190" t="s">
         <v>831</v>
@@ -8635,7 +8602,7 @@
         <v>832</v>
       </c>
       <c r="C191" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="D191" t="s">
         <v>833</v>
@@ -8658,19 +8625,19 @@
         <v>837</v>
       </c>
       <c r="C192" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D192" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="E192" t="s">
-        <v>144</v>
+        <v>834</v>
       </c>
       <c r="F192" t="s">
-        <v>145</v>
+        <v>835</v>
       </c>
       <c r="G192" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="H192" t="s">
         <v>10</v>
@@ -8678,56 +8645,56 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>838</v>
+      </c>
+      <c r="C193" t="s">
+        <v>26</v>
+      </c>
+      <c r="D193" t="s">
+        <v>839</v>
+      </c>
+      <c r="E193" t="s">
+        <v>142</v>
+      </c>
+      <c r="F193" t="s">
+        <v>143</v>
+      </c>
+      <c r="G193" t="s">
         <v>840</v>
       </c>
-      <c r="C193" t="s">
-        <v>77</v>
-      </c>
-      <c r="D193" t="s">
-        <v>841</v>
-      </c>
-      <c r="E193" t="s">
-        <v>141</v>
-      </c>
-      <c r="F193" t="s">
-        <v>142</v>
-      </c>
-      <c r="G193" t="s">
-        <v>842</v>
-      </c>
       <c r="H193" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C194" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="D194" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E194" t="s">
-        <v>845</v>
+        <v>175</v>
       </c>
       <c r="F194" t="s">
-        <v>846</v>
+        <v>7</v>
       </c>
       <c r="G194" t="s">
-        <v>847</v>
+        <v>188</v>
       </c>
       <c r="H194" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C195" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D195" t="s">
         <v>844</v>
@@ -8742,24 +8709,24 @@
         <v>847</v>
       </c>
       <c r="H195" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>848</v>
+      </c>
+      <c r="C196" t="s">
+        <v>74</v>
+      </c>
+      <c r="D196" t="s">
         <v>849</v>
       </c>
-      <c r="C196" t="s">
-        <v>26</v>
-      </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>850</v>
       </c>
-      <c r="E196" t="s">
-        <v>150</v>
-      </c>
       <c r="F196" t="s">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="G196" t="s">
         <v>851</v>
@@ -8773,19 +8740,19 @@
         <v>852</v>
       </c>
       <c r="C197" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D197" t="s">
         <v>853</v>
       </c>
       <c r="E197" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="F197" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="G197" t="s">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="H197" t="s">
         <v>55</v>
@@ -8796,7 +8763,7 @@
         <v>854</v>
       </c>
       <c r="C198" t="s">
-        <v>14</v>
+        <v>325</v>
       </c>
       <c r="D198" t="s">
         <v>855</v>
@@ -8819,7 +8786,7 @@
         <v>859</v>
       </c>
       <c r="C199" t="s">
-        <v>74</v>
+        <v>363</v>
       </c>
       <c r="D199" t="s">
         <v>860</v>
@@ -8828,10 +8795,10 @@
         <v>861</v>
       </c>
       <c r="F199" t="s">
-        <v>7</v>
+        <v>862</v>
       </c>
       <c r="G199" t="s">
-        <v>862</v>
+        <v>89</v>
       </c>
       <c r="H199" t="s">
         <v>55</v>
@@ -8842,19 +8809,19 @@
         <v>863</v>
       </c>
       <c r="C200" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D200" t="s">
         <v>864</v>
       </c>
       <c r="E200" t="s">
-        <v>112</v>
+        <v>865</v>
       </c>
       <c r="F200" t="s">
-        <v>113</v>
+        <v>866</v>
       </c>
       <c r="G200" t="s">
-        <v>114</v>
+        <v>867</v>
       </c>
       <c r="H200" t="s">
         <v>55</v>
@@ -8862,22 +8829,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C201" t="s">
-        <v>333</v>
+        <v>26</v>
       </c>
       <c r="D201" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E201" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="F201" t="s">
-        <v>868</v>
+        <v>27</v>
       </c>
       <c r="G201" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="H201" t="s">
         <v>55</v>
@@ -8885,22 +8852,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C202" t="s">
-        <v>371</v>
+        <v>26</v>
       </c>
       <c r="D202" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E202" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F202" t="s">
-        <v>873</v>
+        <v>27</v>
       </c>
       <c r="G202" t="s">
-        <v>89</v>
+        <v>875</v>
       </c>
       <c r="H202" t="s">
         <v>55</v>
@@ -8908,22 +8875,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>876</v>
+      </c>
+      <c r="C203" t="s">
+        <v>26</v>
+      </c>
+      <c r="D203" t="s">
+        <v>873</v>
+      </c>
+      <c r="E203" t="s">
         <v>874</v>
       </c>
-      <c r="C203" t="s">
-        <v>14</v>
-      </c>
-      <c r="D203" t="s">
+      <c r="F203" t="s">
+        <v>27</v>
+      </c>
+      <c r="G203" t="s">
         <v>875</v>
-      </c>
-      <c r="E203" t="s">
-        <v>876</v>
-      </c>
-      <c r="F203" t="s">
-        <v>877</v>
-      </c>
-      <c r="G203" t="s">
-        <v>878</v>
       </c>
       <c r="H203" t="s">
         <v>55</v>
@@ -8931,22 +8898,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>877</v>
+      </c>
+      <c r="C204" t="s">
+        <v>132</v>
+      </c>
+      <c r="D204" t="s">
+        <v>878</v>
+      </c>
+      <c r="E204" t="s">
+        <v>677</v>
+      </c>
+      <c r="F204" t="s">
+        <v>678</v>
+      </c>
+      <c r="G204" t="s">
         <v>879</v>
-      </c>
-      <c r="C204" t="s">
-        <v>26</v>
-      </c>
-      <c r="D204" t="s">
-        <v>880</v>
-      </c>
-      <c r="E204" t="s">
-        <v>881</v>
-      </c>
-      <c r="F204" t="s">
-        <v>27</v>
-      </c>
-      <c r="G204" t="s">
-        <v>882</v>
       </c>
       <c r="H204" t="s">
         <v>55</v>
@@ -8954,22 +8921,22 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="C205" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D205" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="E205" t="s">
-        <v>885</v>
+        <v>508</v>
       </c>
       <c r="F205" t="s">
-        <v>27</v>
+        <v>509</v>
       </c>
       <c r="G205" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="H205" t="s">
         <v>55</v>
@@ -8977,10 +8944,10 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C206" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D206" t="s">
         <v>884</v>
@@ -8989,36 +8956,36 @@
         <v>885</v>
       </c>
       <c r="F206" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G206" t="s">
         <v>886</v>
       </c>
       <c r="H206" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>887</v>
+      </c>
+      <c r="C207" t="s">
+        <v>105</v>
+      </c>
+      <c r="D207" t="s">
         <v>888</v>
       </c>
-      <c r="C207" t="s">
-        <v>137</v>
-      </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>889</v>
       </c>
-      <c r="E207" t="s">
-        <v>688</v>
-      </c>
       <c r="F207" t="s">
-        <v>689</v>
+        <v>7</v>
       </c>
       <c r="G207" t="s">
         <v>890</v>
       </c>
       <c r="H207" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
@@ -9032,36 +8999,36 @@
         <v>892</v>
       </c>
       <c r="E208" t="s">
-        <v>516</v>
+        <v>893</v>
       </c>
       <c r="F208" t="s">
-        <v>517</v>
+        <v>7</v>
       </c>
       <c r="G208" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H208" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C209" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D209" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="E209" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="F209" t="s">
         <v>7</v>
       </c>
       <c r="G209" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -9069,22 +9036,22 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C210" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="D210" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="E210" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="F210" t="s">
         <v>7</v>
       </c>
       <c r="G210" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -9092,22 +9059,22 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="C211" t="s">
-        <v>66</v>
+        <v>325</v>
       </c>
       <c r="D211" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="E211" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="F211" t="s">
-        <v>7</v>
+        <v>900</v>
       </c>
       <c r="G211" t="s">
-        <v>905</v>
+        <v>17</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -9115,22 +9082,22 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C212" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="D212" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E212" t="s">
-        <v>904</v>
+        <v>69</v>
       </c>
       <c r="F212" t="s">
         <v>7</v>
       </c>
       <c r="G212" t="s">
-        <v>905</v>
+        <v>180</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -9138,22 +9105,22 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C213" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="D213" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E213" t="s">
-        <v>904</v>
+        <v>69</v>
       </c>
       <c r="F213" t="s">
         <v>7</v>
       </c>
       <c r="G213" t="s">
-        <v>905</v>
+        <v>180</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -9161,22 +9128,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="C214" t="s">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="D214" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E214" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="F214" t="s">
-        <v>911</v>
+        <v>73</v>
       </c>
       <c r="G214" t="s">
-        <v>17</v>
+        <v>907</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -9184,22 +9151,22 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C215" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D215" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E215" t="s">
-        <v>69</v>
+        <v>287</v>
       </c>
       <c r="F215" t="s">
         <v>7</v>
       </c>
       <c r="G215" t="s">
-        <v>188</v>
+        <v>910</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -9207,22 +9174,22 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C216" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D216" t="s">
+        <v>912</v>
+      </c>
+      <c r="E216" t="s">
         <v>913</v>
-      </c>
-      <c r="E216" t="s">
-        <v>69</v>
       </c>
       <c r="F216" t="s">
         <v>7</v>
       </c>
       <c r="G216" t="s">
-        <v>188</v>
+        <v>914</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -9233,19 +9200,19 @@
         <v>915</v>
       </c>
       <c r="C217" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="D217" t="s">
         <v>916</v>
       </c>
       <c r="E217" t="s">
+        <v>464</v>
+      </c>
+      <c r="F217" t="s">
+        <v>7</v>
+      </c>
+      <c r="G217" t="s">
         <v>917</v>
-      </c>
-      <c r="F217" t="s">
-        <v>73</v>
-      </c>
-      <c r="G217" t="s">
-        <v>918</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -9253,22 +9220,22 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C218" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="D218" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E218" t="s">
-        <v>295</v>
+        <v>464</v>
       </c>
       <c r="F218" t="s">
         <v>7</v>
       </c>
       <c r="G218" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -9276,22 +9243,22 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C219" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="D219" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="E219" t="s">
-        <v>924</v>
+        <v>464</v>
       </c>
       <c r="F219" t="s">
         <v>7</v>
       </c>
       <c r="G219" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -9299,22 +9266,22 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C220" t="s">
         <v>16</v>
       </c>
       <c r="D220" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="E220" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="F220" t="s">
         <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -9322,22 +9289,22 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="C221" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D221" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="E221" t="s">
-        <v>472</v>
+        <v>925</v>
       </c>
       <c r="F221" t="s">
         <v>7</v>
       </c>
       <c r="G221" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -9345,22 +9312,22 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>927</v>
+      </c>
+      <c r="C222" t="s">
+        <v>39</v>
+      </c>
+      <c r="D222" t="s">
+        <v>928</v>
+      </c>
+      <c r="E222" t="s">
+        <v>929</v>
+      </c>
+      <c r="F222" t="s">
         <v>930</v>
       </c>
-      <c r="C222" t="s">
-        <v>16</v>
-      </c>
-      <c r="D222" t="s">
+      <c r="G222" t="s">
         <v>931</v>
-      </c>
-      <c r="E222" t="s">
-        <v>472</v>
-      </c>
-      <c r="F222" t="s">
-        <v>7</v>
-      </c>
-      <c r="G222" t="s">
-        <v>932</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -9368,22 +9335,22 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C223" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D223" t="s">
+        <v>928</v>
+      </c>
+      <c r="E223" t="s">
+        <v>929</v>
+      </c>
+      <c r="F223" t="s">
+        <v>930</v>
+      </c>
+      <c r="G223" t="s">
         <v>931</v>
-      </c>
-      <c r="E223" t="s">
-        <v>472</v>
-      </c>
-      <c r="F223" t="s">
-        <v>7</v>
-      </c>
-      <c r="G223" t="s">
-        <v>932</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -9391,22 +9358,22 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
+        <v>933</v>
+      </c>
+      <c r="C224" t="s">
+        <v>274</v>
+      </c>
+      <c r="D224" t="s">
         <v>934</v>
       </c>
-      <c r="C224" t="s">
-        <v>66</v>
-      </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
+        <v>192</v>
+      </c>
+      <c r="F224" t="s">
+        <v>193</v>
+      </c>
+      <c r="G224" t="s">
         <v>935</v>
-      </c>
-      <c r="E224" t="s">
-        <v>936</v>
-      </c>
-      <c r="F224" t="s">
-        <v>7</v>
-      </c>
-      <c r="G224" t="s">
-        <v>937</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -9414,22 +9381,22 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C225" t="s">
-        <v>39</v>
+        <v>274</v>
       </c>
       <c r="D225" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E225" t="s">
-        <v>940</v>
+        <v>192</v>
       </c>
       <c r="F225" t="s">
-        <v>941</v>
+        <v>193</v>
       </c>
       <c r="G225" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -9437,22 +9404,22 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="C226" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D226" t="s">
+        <v>938</v>
+      </c>
+      <c r="E226" t="s">
         <v>939</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>940</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>941</v>
-      </c>
-      <c r="G226" t="s">
-        <v>942</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -9460,22 +9427,22 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C227" t="s">
-        <v>282</v>
+        <v>56</v>
       </c>
       <c r="D227" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E227" t="s">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F227" t="s">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="G227" t="s">
-        <v>946</v>
+        <v>807</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -9483,19 +9450,19 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C228" t="s">
-        <v>282</v>
+        <v>64</v>
       </c>
       <c r="D228" t="s">
         <v>945</v>
       </c>
       <c r="E228" t="s">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="F228" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="G228" t="s">
         <v>946</v>
@@ -9506,22 +9473,22 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C229" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D229" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="E229" t="s">
-        <v>950</v>
+        <v>287</v>
       </c>
       <c r="F229" t="s">
-        <v>951</v>
+        <v>7</v>
       </c>
       <c r="G229" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -9529,22 +9496,22 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C230" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D230" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="E230" t="s">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="F230" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="G230" t="s">
-        <v>818</v>
+        <v>951</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -9552,22 +9519,22 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C231" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D231" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="E231" t="s">
-        <v>295</v>
+        <v>954</v>
       </c>
       <c r="F231" t="s">
         <v>7</v>
       </c>
       <c r="G231" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -9575,22 +9542,22 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C232" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D232" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="E232" t="s">
-        <v>295</v>
+        <v>954</v>
       </c>
       <c r="F232" t="s">
         <v>7</v>
       </c>
       <c r="G232" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -9598,22 +9565,22 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
+        <v>957</v>
+      </c>
+      <c r="C233" t="s">
+        <v>39</v>
+      </c>
+      <c r="D233" t="s">
+        <v>958</v>
+      </c>
+      <c r="E233" t="s">
         <v>959</v>
       </c>
-      <c r="C233" t="s">
-        <v>78</v>
-      </c>
-      <c r="D233" t="s">
+      <c r="F233" t="s">
         <v>960</v>
       </c>
-      <c r="E233" t="s">
+      <c r="G233" t="s">
         <v>961</v>
-      </c>
-      <c r="F233" t="s">
-        <v>7</v>
-      </c>
-      <c r="G233" t="s">
-        <v>962</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -9621,22 +9588,22 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
+        <v>962</v>
+      </c>
+      <c r="C234" t="s">
+        <v>64</v>
+      </c>
+      <c r="D234" t="s">
         <v>963</v>
       </c>
-      <c r="C234" t="s">
-        <v>78</v>
-      </c>
-      <c r="D234" t="s">
-        <v>964</v>
-      </c>
       <c r="E234" t="s">
-        <v>965</v>
+        <v>115</v>
       </c>
       <c r="F234" t="s">
         <v>7</v>
       </c>
       <c r="G234" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -9644,22 +9611,22 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C235" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D235" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E235" t="s">
-        <v>965</v>
+        <v>115</v>
       </c>
       <c r="F235" t="s">
         <v>7</v>
       </c>
       <c r="G235" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -9667,22 +9634,22 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C236" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D236" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="E236" t="s">
-        <v>970</v>
+        <v>115</v>
       </c>
       <c r="F236" t="s">
-        <v>971</v>
+        <v>7</v>
       </c>
       <c r="G236" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -9690,22 +9657,22 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="C237" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="D237" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="E237" t="s">
-        <v>115</v>
+        <v>969</v>
       </c>
       <c r="F237" t="s">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="G237" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -9713,19 +9680,19 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C238" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="D238" t="s">
+        <v>973</v>
+      </c>
+      <c r="E238" t="s">
         <v>974</v>
       </c>
-      <c r="E238" t="s">
-        <v>115</v>
-      </c>
       <c r="F238" t="s">
-        <v>7</v>
+        <v>161</v>
       </c>
       <c r="G238" t="s">
         <v>975</v>
@@ -9736,22 +9703,22 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
+        <v>976</v>
+      </c>
+      <c r="C239" t="s">
+        <v>74</v>
+      </c>
+      <c r="D239" t="s">
         <v>977</v>
       </c>
-      <c r="C239" t="s">
-        <v>64</v>
-      </c>
-      <c r="D239" t="s">
-        <v>974</v>
-      </c>
       <c r="E239" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="F239" t="s">
         <v>7</v>
       </c>
       <c r="G239" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -9759,19 +9726,19 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C240" t="s">
-        <v>162</v>
+        <v>274</v>
       </c>
       <c r="D240" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E240" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F240" t="s">
-        <v>981</v>
+        <v>7</v>
       </c>
       <c r="G240" t="s">
         <v>982</v>
@@ -9785,19 +9752,19 @@
         <v>983</v>
       </c>
       <c r="C241" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D241" t="s">
         <v>984</v>
       </c>
       <c r="E241" t="s">
+        <v>287</v>
+      </c>
+      <c r="F241" t="s">
+        <v>7</v>
+      </c>
+      <c r="G241" t="s">
         <v>985</v>
-      </c>
-      <c r="F241" t="s">
-        <v>169</v>
-      </c>
-      <c r="G241" t="s">
-        <v>986</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -9805,22 +9772,22 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C242" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D242" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="E242" t="s">
-        <v>175</v>
+        <v>287</v>
       </c>
       <c r="F242" t="s">
         <v>7</v>
       </c>
       <c r="G242" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -9828,22 +9795,22 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="C243" t="s">
-        <v>282</v>
+        <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="E243" t="s">
-        <v>992</v>
+        <v>165</v>
       </c>
       <c r="F243" t="s">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="G243" t="s">
-        <v>993</v>
+        <v>30</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -9851,22 +9818,22 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C244" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="E244" t="s">
-        <v>295</v>
+        <v>165</v>
       </c>
       <c r="F244" t="s">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="G244" t="s">
-        <v>996</v>
+        <v>30</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -9874,22 +9841,22 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="C245" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D245" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="E245" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="F245" t="s">
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -9897,22 +9864,22 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="C246" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D246" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="E246" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F246" t="s">
-        <v>174</v>
+        <v>7</v>
       </c>
       <c r="G246" t="s">
-        <v>30</v>
+        <v>992</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -9920,22 +9887,22 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C247" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D247" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="E247" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F247" t="s">
-        <v>174</v>
+        <v>7</v>
       </c>
       <c r="G247" t="s">
-        <v>30</v>
+        <v>992</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -9943,22 +9910,22 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="C248" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D248" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="E248" t="s">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="F248" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="G248" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -9966,22 +9933,22 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C249" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D249" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E249" t="s">
-        <v>204</v>
+        <v>929</v>
       </c>
       <c r="F249" t="s">
-        <v>7</v>
+        <v>930</v>
       </c>
       <c r="G249" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -9989,16 +9956,16 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C250" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="D250" t="s">
         <v>1002</v>
       </c>
       <c r="E250" t="s">
-        <v>204</v>
+        <v>464</v>
       </c>
       <c r="F250" t="s">
         <v>7</v>
@@ -10012,22 +9979,22 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C251" t="s">
+        <v>74</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E251" t="s">
+        <v>167</v>
+      </c>
+      <c r="F251" t="s">
+        <v>7</v>
+      </c>
+      <c r="G251" t="s">
         <v>1006</v>
-      </c>
-      <c r="C251" t="s">
-        <v>39</v>
-      </c>
-      <c r="D251" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E251" t="s">
-        <v>112</v>
-      </c>
-      <c r="F251" t="s">
-        <v>113</v>
-      </c>
-      <c r="G251" t="s">
-        <v>1008</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -10035,22 +10002,22 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C252" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D252" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="E252" t="s">
-        <v>940</v>
+        <v>167</v>
       </c>
       <c r="F252" t="s">
-        <v>941</v>
+        <v>7</v>
       </c>
       <c r="G252" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -10058,22 +10025,22 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C253" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D253" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="E253" t="s">
-        <v>472</v>
+        <v>1010</v>
       </c>
       <c r="F253" t="s">
-        <v>7</v>
+        <v>1011</v>
       </c>
       <c r="G253" t="s">
-        <v>1014</v>
+        <v>32</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -10081,22 +10048,22 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="C254" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="D254" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="E254" t="s">
-        <v>175</v>
+        <v>1010</v>
       </c>
       <c r="F254" t="s">
-        <v>7</v>
+        <v>1011</v>
       </c>
       <c r="G254" t="s">
-        <v>1017</v>
+        <v>32</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -10104,19 +10071,19 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="C255" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D255" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E255" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F255" t="s">
         <v>1016</v>
-      </c>
-      <c r="E255" t="s">
-        <v>175</v>
-      </c>
-      <c r="F255" t="s">
-        <v>7</v>
       </c>
       <c r="G255" t="s">
         <v>1017</v>
@@ -10127,22 +10094,22 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C256" t="s">
         <v>11</v>
       </c>
       <c r="D256" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G256" t="s">
         <v>1020</v>
-      </c>
-      <c r="E256" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F256" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G256" t="s">
-        <v>32</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -10150,22 +10117,22 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C257" t="s">
+        <v>72</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E257" t="s">
         <v>1023</v>
       </c>
-      <c r="C257" t="s">
-        <v>11</v>
-      </c>
-      <c r="D257" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E257" t="s">
-        <v>1021</v>
-      </c>
       <c r="F257" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="G257" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -10173,22 +10140,22 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C258" t="s">
+        <v>72</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E258" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F258" t="s">
         <v>1024</v>
       </c>
-      <c r="C258" t="s">
-        <v>28</v>
-      </c>
-      <c r="D258" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E258" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F258" t="s">
-        <v>1027</v>
-      </c>
       <c r="G258" t="s">
-        <v>1028</v>
+        <v>41</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -10196,22 +10163,22 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C259" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="D259" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="E259" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="F259" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="G259" t="s">
-        <v>1031</v>
+        <v>41</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -10219,22 +10186,22 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="C260" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="D260" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="E260" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="F260" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G260" t="s">
-        <v>41</v>
+        <v>1031</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -10242,22 +10209,22 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F261" t="s">
+        <v>7</v>
+      </c>
+      <c r="G261" t="s">
         <v>1036</v>
-      </c>
-      <c r="C261" t="s">
-        <v>72</v>
-      </c>
-      <c r="D261" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E261" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F261" t="s">
-        <v>1035</v>
-      </c>
-      <c r="G261" t="s">
-        <v>41</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -10268,19 +10235,19 @@
         <v>1037</v>
       </c>
       <c r="C262" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D262" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="E262" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="F262" t="s">
-        <v>1035</v>
+        <v>7</v>
       </c>
       <c r="G262" t="s">
-        <v>41</v>
+        <v>1040</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -10288,22 +10255,22 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C263" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="D263" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="E263" t="s">
-        <v>1040</v>
+        <v>60</v>
       </c>
       <c r="F263" t="s">
-        <v>1041</v>
+        <v>61</v>
       </c>
       <c r="G263" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -10311,22 +10278,22 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C264" t="s">
-        <v>1044</v>
+        <v>9</v>
       </c>
       <c r="D264" t="s">
         <v>1045</v>
       </c>
       <c r="E264" t="s">
-        <v>1046</v>
+        <v>102</v>
       </c>
       <c r="F264" t="s">
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -10334,22 +10301,22 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D265" t="s">
         <v>1048</v>
       </c>
-      <c r="C265" t="s">
-        <v>64</v>
-      </c>
-      <c r="D265" t="s">
-        <v>1049</v>
-      </c>
       <c r="E265" t="s">
-        <v>1050</v>
+        <v>102</v>
       </c>
       <c r="F265" t="s">
         <v>7</v>
       </c>
       <c r="G265" t="s">
-        <v>1051</v>
+        <v>187</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -10357,22 +10324,22 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C266" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="D266" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E266" t="s">
-        <v>60</v>
+        <v>929</v>
       </c>
       <c r="F266" t="s">
-        <v>61</v>
+        <v>930</v>
       </c>
       <c r="G266" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -10380,22 +10347,22 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C267" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="E267" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="F267" t="s">
-        <v>7</v>
+        <v>171</v>
       </c>
       <c r="G267" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -10403,22 +10370,22 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="C268" t="s">
-        <v>1044</v>
+        <v>56</v>
       </c>
       <c r="D268" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E268" t="s">
-        <v>102</v>
+        <v>1057</v>
       </c>
       <c r="F268" t="s">
         <v>7</v>
       </c>
       <c r="G268" t="s">
-        <v>195</v>
+        <v>1058</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -10426,19 +10393,19 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C269" t="s">
+        <v>9</v>
+      </c>
+      <c r="D269" t="s">
         <v>1060</v>
       </c>
-      <c r="C269" t="s">
-        <v>39</v>
-      </c>
-      <c r="D269" t="s">
+      <c r="E269" t="s">
         <v>1061</v>
       </c>
-      <c r="E269" t="s">
-        <v>940</v>
-      </c>
       <c r="F269" t="s">
-        <v>941</v>
+        <v>7</v>
       </c>
       <c r="G269" t="s">
         <v>1062</v>
@@ -10452,19 +10419,19 @@
         <v>1063</v>
       </c>
       <c r="C270" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="D270" t="s">
         <v>1064</v>
       </c>
       <c r="E270" t="s">
-        <v>178</v>
+        <v>1065</v>
       </c>
       <c r="F270" t="s">
-        <v>179</v>
+        <v>1066</v>
       </c>
       <c r="G270" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -10472,22 +10439,22 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C271" t="s">
+        <v>124</v>
+      </c>
+      <c r="D271" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E271" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F271" t="s">
         <v>1066</v>
       </c>
-      <c r="C271" t="s">
-        <v>56</v>
-      </c>
-      <c r="D271" t="s">
+      <c r="G271" t="s">
         <v>1067</v>
-      </c>
-      <c r="E271" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F271" t="s">
-        <v>7</v>
-      </c>
-      <c r="G271" t="s">
-        <v>1069</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -10495,22 +10462,22 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
         <v>1070</v>
       </c>
-      <c r="C272" t="s">
-        <v>9</v>
-      </c>
-      <c r="D272" t="s">
+      <c r="E272" t="s">
         <v>1071</v>
-      </c>
-      <c r="E272" t="s">
-        <v>1072</v>
       </c>
       <c r="F272" t="s">
         <v>7</v>
       </c>
       <c r="G272" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -10518,22 +10485,22 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C273" t="s">
+        <v>56</v>
+      </c>
+      <c r="D273" t="s">
         <v>1074</v>
       </c>
-      <c r="C273" t="s">
-        <v>124</v>
-      </c>
-      <c r="D273" t="s">
+      <c r="E273" t="s">
         <v>1075</v>
       </c>
-      <c r="E273" t="s">
-        <v>1076</v>
-      </c>
       <c r="F273" t="s">
-        <v>1077</v>
+        <v>7</v>
       </c>
       <c r="G273" t="s">
-        <v>1078</v>
+        <v>176</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -10541,22 +10508,22 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C274" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="D274" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E274" t="s">
         <v>1075</v>
       </c>
-      <c r="E274" t="s">
-        <v>1076</v>
-      </c>
       <c r="F274" t="s">
-        <v>1077</v>
+        <v>7</v>
       </c>
       <c r="G274" t="s">
-        <v>1078</v>
+        <v>176</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -10564,22 +10531,22 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C275" t="s">
+        <v>14</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E275" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F275" t="s">
         <v>1080</v>
       </c>
-      <c r="C275" t="s">
-        <v>68</v>
-      </c>
-      <c r="D275" t="s">
+      <c r="G275" t="s">
         <v>1081</v>
-      </c>
-      <c r="E275" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F275" t="s">
-        <v>7</v>
-      </c>
-      <c r="G275" t="s">
-        <v>1083</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -10587,22 +10554,22 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C276" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E276" t="s">
         <v>1084</v>
-      </c>
-      <c r="C276" t="s">
-        <v>56</v>
-      </c>
-      <c r="D276" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E276" t="s">
-        <v>1086</v>
       </c>
       <c r="F276" t="s">
         <v>7</v>
       </c>
       <c r="G276" t="s">
-        <v>184</v>
+        <v>1085</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -10610,22 +10577,22 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C277" t="s">
+        <v>325</v>
+      </c>
+      <c r="D277" t="s">
         <v>1087</v>
       </c>
-      <c r="C277" t="s">
-        <v>56</v>
-      </c>
-      <c r="D277" t="s">
-        <v>1085</v>
-      </c>
       <c r="E277" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F277" t="s">
-        <v>7</v>
+        <v>1089</v>
       </c>
       <c r="G277" t="s">
-        <v>184</v>
+        <v>1090</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -10633,22 +10600,22 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C278" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D278" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="E278" t="s">
-        <v>1090</v>
+        <v>106</v>
       </c>
       <c r="F278" t="s">
-        <v>1091</v>
+        <v>7</v>
       </c>
       <c r="G278" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -10656,19 +10623,19 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C279" t="s">
-        <v>1044</v>
+        <v>351</v>
       </c>
       <c r="D279" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E279" t="s">
-        <v>1095</v>
+        <v>98</v>
       </c>
       <c r="F279" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="G279" t="s">
         <v>1096</v>
@@ -10682,19 +10649,19 @@
         <v>1097</v>
       </c>
       <c r="C280" t="s">
-        <v>333</v>
+        <v>14</v>
       </c>
       <c r="D280" t="s">
         <v>1098</v>
       </c>
       <c r="E280" t="s">
+        <v>136</v>
+      </c>
+      <c r="F280" t="s">
+        <v>137</v>
+      </c>
+      <c r="G280" t="s">
         <v>1099</v>
-      </c>
-      <c r="F280" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G280" t="s">
-        <v>1101</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -10702,19 +10669,19 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C281" t="s">
+        <v>325</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E281" t="s">
         <v>1102</v>
       </c>
-      <c r="C281" t="s">
-        <v>74</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
         <v>1103</v>
-      </c>
-      <c r="E281" t="s">
-        <v>106</v>
-      </c>
-      <c r="F281" t="s">
-        <v>7</v>
       </c>
       <c r="G281" t="s">
         <v>1104</v>
@@ -10728,19 +10695,19 @@
         <v>1105</v>
       </c>
       <c r="C282" t="s">
-        <v>359</v>
+        <v>1033</v>
       </c>
       <c r="D282" t="s">
         <v>1106</v>
       </c>
       <c r="E282" t="s">
-        <v>98</v>
+        <v>1107</v>
       </c>
       <c r="F282" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="G282" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -10748,22 +10715,22 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C283" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="D283" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E283" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F283" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="G283" t="s">
-        <v>1110</v>
+        <v>1062</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -10774,19 +10741,19 @@
         <v>1111</v>
       </c>
       <c r="C284" t="s">
-        <v>333</v>
+        <v>23</v>
       </c>
       <c r="D284" t="s">
         <v>1112</v>
       </c>
       <c r="E284" t="s">
+        <v>146</v>
+      </c>
+      <c r="F284" t="s">
+        <v>147</v>
+      </c>
+      <c r="G284" t="s">
         <v>1113</v>
-      </c>
-      <c r="F284" t="s">
-        <v>1114</v>
-      </c>
-      <c r="G284" t="s">
-        <v>1115</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -10794,22 +10761,22 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C285" t="s">
+        <v>130</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E285" t="s">
         <v>1116</v>
-      </c>
-      <c r="C285" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D285" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1118</v>
       </c>
       <c r="F285" t="s">
         <v>7</v>
       </c>
       <c r="G285" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -10817,22 +10784,22 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="C286" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D286" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="E286" t="s">
-        <v>167</v>
+        <v>1116</v>
       </c>
       <c r="F286" t="s">
-        <v>168</v>
+        <v>7</v>
       </c>
       <c r="G286" t="s">
-        <v>1073</v>
+        <v>1117</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -10840,22 +10807,22 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="C287" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="D287" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="E287" t="s">
-        <v>154</v>
+        <v>1116</v>
       </c>
       <c r="F287" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="G287" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -10863,22 +10830,22 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="C288" t="s">
-        <v>135</v>
+        <v>351</v>
       </c>
       <c r="D288" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="E288" t="s">
-        <v>1127</v>
+        <v>98</v>
       </c>
       <c r="F288" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="G288" t="s">
-        <v>1128</v>
+        <v>88</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -10886,22 +10853,22 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="C289" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D289" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F289" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G289" t="s">
         <v>1126</v>
-      </c>
-      <c r="E289" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F289" t="s">
-        <v>7</v>
-      </c>
-      <c r="G289" t="s">
-        <v>1128</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -10909,22 +10876,22 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C290" t="s">
+        <v>38</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E290" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F290" t="s">
         <v>1130</v>
       </c>
-      <c r="C290" t="s">
-        <v>135</v>
-      </c>
-      <c r="D290" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E290" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F290" t="s">
-        <v>7</v>
-      </c>
       <c r="G290" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -10932,22 +10899,22 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C291" t="s">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="D291" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E291" t="s">
-        <v>98</v>
+        <v>1134</v>
       </c>
       <c r="F291" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="G291" t="s">
-        <v>88</v>
+        <v>1135</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -10955,22 +10922,22 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="C292" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="D292" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="E292" t="s">
-        <v>1135</v>
+        <v>184</v>
       </c>
       <c r="F292" t="s">
-        <v>1136</v>
+        <v>168</v>
       </c>
       <c r="G292" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -10978,19 +10945,19 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C293" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D293" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E293" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F293" t="s">
-        <v>1141</v>
+        <v>36</v>
       </c>
       <c r="G293" t="s">
         <v>1142</v>
@@ -11004,7 +10971,7 @@
         <v>1143</v>
       </c>
       <c r="C294" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D294" t="s">
         <v>1144</v>
@@ -11013,10 +10980,10 @@
         <v>1145</v>
       </c>
       <c r="F294" t="s">
-        <v>73</v>
+        <v>1146</v>
       </c>
       <c r="G294" t="s">
-        <v>1146</v>
+        <v>32</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -11027,16 +10994,16 @@
         <v>1147</v>
       </c>
       <c r="C295" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D295" t="s">
         <v>1148</v>
       </c>
       <c r="E295" t="s">
-        <v>192</v>
+        <v>392</v>
       </c>
       <c r="F295" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="G295" t="s">
         <v>1149</v>
@@ -11050,19 +11017,19 @@
         <v>1150</v>
       </c>
       <c r="C296" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="D296" t="s">
         <v>1151</v>
       </c>
       <c r="E296" t="s">
+        <v>148</v>
+      </c>
+      <c r="F296" t="s">
+        <v>149</v>
+      </c>
+      <c r="G296" t="s">
         <v>1152</v>
-      </c>
-      <c r="F296" t="s">
-        <v>36</v>
-      </c>
-      <c r="G296" t="s">
-        <v>1153</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -11070,22 +11037,22 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C297" t="s">
+        <v>23</v>
+      </c>
+      <c r="D297" t="s">
         <v>1154</v>
       </c>
-      <c r="C297" t="s">
-        <v>14</v>
-      </c>
-      <c r="D297" t="s">
+      <c r="E297" t="s">
+        <v>140</v>
+      </c>
+      <c r="F297" t="s">
+        <v>141</v>
+      </c>
+      <c r="G297" t="s">
         <v>1155</v>
-      </c>
-      <c r="E297" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F297" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G297" t="s">
-        <v>32</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -11093,22 +11060,22 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C298" t="s">
+        <v>74</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E298" t="s">
         <v>1158</v>
       </c>
-      <c r="C298" t="s">
-        <v>29</v>
-      </c>
-      <c r="D298" t="s">
+      <c r="F298" t="s">
+        <v>7</v>
+      </c>
+      <c r="G298" t="s">
         <v>1159</v>
-      </c>
-      <c r="E298" t="s">
-        <v>400</v>
-      </c>
-      <c r="F298" t="s">
-        <v>27</v>
-      </c>
-      <c r="G298" t="s">
-        <v>1160</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -11116,22 +11083,22 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C299" t="s">
+        <v>62</v>
+      </c>
+      <c r="D299" t="s">
         <v>1161</v>
       </c>
-      <c r="C299" t="s">
-        <v>124</v>
-      </c>
-      <c r="D299" t="s">
+      <c r="E299" t="s">
         <v>1162</v>
       </c>
-      <c r="E299" t="s">
-        <v>156</v>
-      </c>
       <c r="F299" t="s">
-        <v>157</v>
+        <v>1163</v>
       </c>
       <c r="G299" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -11139,22 +11106,22 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C300" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E300" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="F300" t="s">
-        <v>149</v>
+        <v>7</v>
       </c>
       <c r="G300" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -11162,22 +11129,22 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C301" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="E301" t="s">
-        <v>1169</v>
+        <v>179</v>
       </c>
       <c r="F301" t="s">
         <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -11185,22 +11152,22 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C302" t="s">
+        <v>78</v>
+      </c>
+      <c r="D302" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E302" t="s">
         <v>1171</v>
       </c>
-      <c r="C302" t="s">
-        <v>62</v>
-      </c>
-      <c r="D302" t="s">
+      <c r="F302" t="s">
+        <v>7</v>
+      </c>
+      <c r="G302" t="s">
         <v>1172</v>
-      </c>
-      <c r="E302" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F302" t="s">
-        <v>1174</v>
-      </c>
-      <c r="G302" t="s">
-        <v>1175</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -11208,22 +11175,22 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="C303" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D303" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="E303" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F303" t="s">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="G303" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -11231,22 +11198,22 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="C304" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="D304" t="s">
         <v>1177</v>
       </c>
       <c r="E304" t="s">
-        <v>187</v>
+        <v>1178</v>
       </c>
       <c r="F304" t="s">
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -11257,7 +11224,7 @@
         <v>1180</v>
       </c>
       <c r="C305" t="s">
-        <v>78</v>
+        <v>363</v>
       </c>
       <c r="D305" t="s">
         <v>1181</v>
@@ -11266,10 +11233,10 @@
         <v>1182</v>
       </c>
       <c r="F305" t="s">
-        <v>7</v>
+        <v>1183</v>
       </c>
       <c r="G305" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -11277,25 +11244,25 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C306" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D306" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E306" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="F306" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="G306" t="s">
-        <v>1186</v>
+        <v>183</v>
       </c>
       <c r="H306" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
@@ -11303,7 +11270,7 @@
         <v>1187</v>
       </c>
       <c r="C307" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D307" t="s">
         <v>1188</v>
@@ -11312,56 +11279,56 @@
         <v>1189</v>
       </c>
       <c r="F307" t="s">
-        <v>7</v>
+        <v>1190</v>
       </c>
       <c r="G307" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H307" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C308" t="s">
-        <v>371</v>
+        <v>28</v>
       </c>
       <c r="D308" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E308" t="s">
-        <v>1193</v>
+        <v>189</v>
       </c>
       <c r="F308" t="s">
-        <v>1194</v>
+        <v>190</v>
       </c>
       <c r="G308" t="s">
-        <v>1195</v>
+        <v>191</v>
       </c>
       <c r="H308" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C309" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D309" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E309" t="s">
-        <v>232</v>
+        <v>67</v>
       </c>
       <c r="F309" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G309" t="s">
-        <v>191</v>
+        <v>810</v>
       </c>
       <c r="H309" t="s">
         <v>63</v>
@@ -11369,22 +11336,22 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C310" t="s">
+        <v>105</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E310" t="s">
         <v>1198</v>
       </c>
-      <c r="C310" t="s">
-        <v>135</v>
-      </c>
-      <c r="D310" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E310" t="s">
-        <v>1200</v>
-      </c>
       <c r="F310" t="s">
-        <v>1201</v>
+        <v>7</v>
       </c>
       <c r="G310" t="s">
-        <v>1202</v>
+        <v>1062</v>
       </c>
       <c r="H310" t="s">
         <v>63</v>
@@ -11392,22 +11359,22 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="C311" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="D311" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="E311" t="s">
-        <v>197</v>
+        <v>49</v>
       </c>
       <c r="F311" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="G311" t="s">
-        <v>199</v>
+        <v>1201</v>
       </c>
       <c r="H311" t="s">
         <v>63</v>
@@ -11415,22 +11382,22 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C312" t="s">
+        <v>274</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E312" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F312" t="s">
         <v>1205</v>
       </c>
-      <c r="C312" t="s">
-        <v>48</v>
-      </c>
-      <c r="D312" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E312" t="s">
-        <v>67</v>
-      </c>
-      <c r="F312" t="s">
-        <v>7</v>
-      </c>
       <c r="G312" t="s">
-        <v>821</v>
+        <v>31</v>
       </c>
       <c r="H312" t="s">
         <v>63</v>
@@ -11438,22 +11405,22 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C313" t="s">
+        <v>78</v>
+      </c>
+      <c r="D313" t="s">
         <v>1207</v>
       </c>
-      <c r="C313" t="s">
-        <v>105</v>
-      </c>
-      <c r="D313" t="s">
-        <v>1208</v>
-      </c>
       <c r="E313" t="s">
-        <v>1209</v>
+        <v>954</v>
       </c>
       <c r="F313" t="s">
         <v>7</v>
       </c>
       <c r="G313" t="s">
-        <v>1073</v>
+        <v>131</v>
       </c>
       <c r="H313" t="s">
         <v>63</v>
@@ -11461,22 +11428,22 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C314" t="s">
+        <v>48</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E314" t="s">
         <v>1210</v>
       </c>
-      <c r="C314" t="s">
-        <v>162</v>
-      </c>
-      <c r="D314" t="s">
+      <c r="F314" t="s">
+        <v>7</v>
+      </c>
+      <c r="G314" t="s">
         <v>1211</v>
-      </c>
-      <c r="E314" t="s">
-        <v>49</v>
-      </c>
-      <c r="F314" t="s">
-        <v>50</v>
-      </c>
-      <c r="G314" t="s">
-        <v>1212</v>
       </c>
       <c r="H314" t="s">
         <v>63</v>
@@ -11484,22 +11451,22 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C315" t="s">
+        <v>154</v>
+      </c>
+      <c r="D315" t="s">
         <v>1213</v>
       </c>
-      <c r="C315" t="s">
-        <v>282</v>
-      </c>
-      <c r="D315" t="s">
+      <c r="E315" t="s">
         <v>1214</v>
       </c>
-      <c r="E315" t="s">
+      <c r="F315" t="s">
+        <v>7</v>
+      </c>
+      <c r="G315" t="s">
         <v>1215</v>
-      </c>
-      <c r="F315" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G315" t="s">
-        <v>31</v>
       </c>
       <c r="H315" t="s">
         <v>63</v>
@@ -11507,22 +11474,22 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C316" t="s">
+        <v>28</v>
+      </c>
+      <c r="D316" t="s">
         <v>1217</v>
       </c>
-      <c r="C316" t="s">
-        <v>78</v>
-      </c>
-      <c r="D316" t="s">
+      <c r="E316" t="s">
         <v>1218</v>
       </c>
-      <c r="E316" t="s">
-        <v>965</v>
-      </c>
       <c r="F316" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="G316" t="s">
-        <v>136</v>
+        <v>1220</v>
       </c>
       <c r="H316" t="s">
         <v>63</v>
@@ -11530,22 +11497,22 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C317" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D317" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E317" t="s">
-        <v>1221</v>
+        <v>194</v>
       </c>
       <c r="F317" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="G317" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H317" t="s">
         <v>63</v>
@@ -11553,22 +11520,22 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C318" t="s">
-        <v>162</v>
+        <v>28</v>
       </c>
       <c r="D318" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E318" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F318" t="s">
-        <v>7</v>
+        <v>1227</v>
       </c>
       <c r="G318" t="s">
-        <v>1226</v>
+        <v>125</v>
       </c>
       <c r="H318" t="s">
         <v>63</v>
@@ -11576,19 +11543,19 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C319" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D319" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E319" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F319" t="s">
-        <v>1230</v>
+        <v>13</v>
       </c>
       <c r="G319" t="s">
         <v>1231</v>
@@ -11602,19 +11569,19 @@
         <v>1232</v>
       </c>
       <c r="C320" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D320" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="E320" t="s">
-        <v>202</v>
+        <v>1230</v>
       </c>
       <c r="F320" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="G320" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="H320" t="s">
         <v>63</v>
@@ -11622,22 +11589,22 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C321" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D321" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="E321" t="s">
-        <v>1237</v>
+        <v>313</v>
       </c>
       <c r="F321" t="s">
-        <v>1238</v>
+        <v>314</v>
       </c>
       <c r="G321" t="s">
-        <v>125</v>
+        <v>323</v>
       </c>
       <c r="H321" t="s">
         <v>63</v>
@@ -11645,22 +11612,22 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="C322" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="D322" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="E322" t="s">
-        <v>1241</v>
+        <v>370</v>
       </c>
       <c r="F322" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G322" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="H322" t="s">
         <v>63</v>
@@ -11668,22 +11635,22 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="C323" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D323" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E323" t="s">
         <v>1240</v>
       </c>
-      <c r="E323" t="s">
+      <c r="F323" t="s">
         <v>1241</v>
       </c>
-      <c r="F323" t="s">
-        <v>13</v>
-      </c>
       <c r="G323" t="s">
-        <v>1242</v>
+        <v>185</v>
       </c>
       <c r="H323" t="s">
         <v>63</v>
@@ -11691,22 +11658,22 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C324" t="s">
+        <v>29</v>
+      </c>
+      <c r="D324" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E324" t="s">
+        <v>629</v>
+      </c>
+      <c r="F324" t="s">
+        <v>27</v>
+      </c>
+      <c r="G324" t="s">
         <v>1244</v>
-      </c>
-      <c r="C324" t="s">
-        <v>26</v>
-      </c>
-      <c r="D324" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E324" t="s">
-        <v>321</v>
-      </c>
-      <c r="F324" t="s">
-        <v>322</v>
-      </c>
-      <c r="G324" t="s">
-        <v>331</v>
       </c>
       <c r="H324" t="s">
         <v>63</v>
@@ -11714,22 +11681,22 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C325" t="s">
+        <v>154</v>
+      </c>
+      <c r="D325" t="s">
         <v>1246</v>
       </c>
-      <c r="C325" t="s">
-        <v>76</v>
-      </c>
-      <c r="D325" t="s">
+      <c r="E325" t="s">
+        <v>107</v>
+      </c>
+      <c r="F325" t="s">
+        <v>108</v>
+      </c>
+      <c r="G325" t="s">
         <v>1247</v>
-      </c>
-      <c r="E325" t="s">
-        <v>378</v>
-      </c>
-      <c r="F325" t="s">
-        <v>7</v>
-      </c>
-      <c r="G325" t="s">
-        <v>1248</v>
       </c>
       <c r="H325" t="s">
         <v>63</v>
@@ -11737,22 +11704,22 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C326" t="s">
+        <v>20</v>
+      </c>
+      <c r="D326" t="s">
         <v>1249</v>
       </c>
-      <c r="C326" t="s">
-        <v>25</v>
-      </c>
-      <c r="D326" t="s">
+      <c r="E326" t="s">
+        <v>253</v>
+      </c>
+      <c r="F326" t="s">
+        <v>254</v>
+      </c>
+      <c r="G326" t="s">
         <v>1250</v>
-      </c>
-      <c r="E326" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F326" t="s">
-        <v>1252</v>
-      </c>
-      <c r="G326" t="s">
-        <v>193</v>
       </c>
       <c r="H326" t="s">
         <v>63</v>
@@ -11760,272 +11727,272 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C327" t="s">
+        <v>325</v>
+      </c>
+      <c r="D327" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E327" t="s">
         <v>1253</v>
       </c>
-      <c r="C327" t="s">
-        <v>29</v>
-      </c>
-      <c r="D327" t="s">
+      <c r="F327" t="s">
         <v>1254</v>
       </c>
-      <c r="E327" t="s">
-        <v>640</v>
-      </c>
-      <c r="F327" t="s">
-        <v>27</v>
-      </c>
-      <c r="G327" t="s">
-        <v>1255</v>
-      </c>
       <c r="H327" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C328" t="s">
+        <v>20</v>
+      </c>
+      <c r="D328" t="s">
         <v>1256</v>
       </c>
-      <c r="C328" t="s">
-        <v>162</v>
-      </c>
-      <c r="D328" t="s">
+      <c r="E328" t="s">
         <v>1257</v>
       </c>
-      <c r="E328" t="s">
-        <v>107</v>
-      </c>
       <c r="F328" t="s">
-        <v>108</v>
+        <v>1258</v>
       </c>
       <c r="G328" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H328" t="s">
-        <v>63</v>
+        <v>197</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>1259</v>
+        <v>200</v>
       </c>
       <c r="C329" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D329" t="s">
-        <v>1260</v>
+        <v>201</v>
       </c>
       <c r="E329" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="F329" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="G329" t="s">
-        <v>1261</v>
+        <v>204</v>
       </c>
       <c r="H329" t="s">
-        <v>63</v>
+        <v>197</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>1262</v>
+        <v>205</v>
       </c>
       <c r="C330" t="s">
-        <v>333</v>
+        <v>26</v>
       </c>
       <c r="D330" t="s">
-        <v>1263</v>
+        <v>201</v>
       </c>
       <c r="E330" t="s">
-        <v>1264</v>
+        <v>202</v>
       </c>
       <c r="F330" t="s">
-        <v>1265</v>
+        <v>203</v>
+      </c>
+      <c r="G330" t="s">
+        <v>204</v>
       </c>
       <c r="H330" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="C331" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D331" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="E331" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="F331" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="G331" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="H331" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>208</v>
+        <v>1265</v>
       </c>
       <c r="C332" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D332" t="s">
-        <v>209</v>
+        <v>1261</v>
       </c>
       <c r="E332" t="s">
-        <v>210</v>
+        <v>1262</v>
       </c>
       <c r="F332" t="s">
-        <v>211</v>
+        <v>1263</v>
       </c>
       <c r="G332" t="s">
-        <v>212</v>
+        <v>1264</v>
       </c>
       <c r="H332" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>213</v>
+        <v>1266</v>
       </c>
       <c r="C333" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D333" t="s">
-        <v>209</v>
+        <v>1261</v>
       </c>
       <c r="E333" t="s">
-        <v>210</v>
+        <v>1262</v>
       </c>
       <c r="F333" t="s">
-        <v>211</v>
+        <v>1263</v>
       </c>
       <c r="G333" t="s">
-        <v>212</v>
+        <v>1264</v>
       </c>
       <c r="H333" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="C334" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D334" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="E334" t="s">
-        <v>1273</v>
+        <v>82</v>
       </c>
       <c r="F334" t="s">
-        <v>1274</v>
+        <v>83</v>
       </c>
       <c r="G334" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="H334" t="s">
-        <v>205</v>
+        <v>117</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="C335" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="D335" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E335" t="s">
+        <v>446</v>
+      </c>
+      <c r="F335" t="s">
+        <v>447</v>
+      </c>
+      <c r="G335" t="s">
         <v>1272</v>
       </c>
-      <c r="E335" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G335" t="s">
-        <v>1275</v>
-      </c>
       <c r="H335" t="s">
-        <v>205</v>
+        <v>116</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="C336" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="D336" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E336" t="s">
+        <v>446</v>
+      </c>
+      <c r="F336" t="s">
+        <v>447</v>
+      </c>
+      <c r="G336" t="s">
         <v>1272</v>
       </c>
-      <c r="E336" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G336" t="s">
-        <v>1275</v>
-      </c>
       <c r="H336" t="s">
-        <v>205</v>
+        <v>116</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C337" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D337" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="E337" t="s">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="F337" t="s">
-        <v>83</v>
+        <v>447</v>
       </c>
       <c r="G337" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="H337" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="C338" t="s">
         <v>11</v>
       </c>
       <c r="D338" t="s">
-        <v>1282</v>
+        <v>1271</v>
       </c>
       <c r="E338" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F338" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="G338" t="s">
-        <v>1283</v>
+        <v>1272</v>
       </c>
       <c r="H338" t="s">
         <v>116</v>
@@ -12033,85 +12000,16 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="C339" t="s">
-        <v>11</v>
+        <v>351</v>
       </c>
       <c r="D339" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E339" t="s">
-        <v>454</v>
-      </c>
-      <c r="F339" t="s">
-        <v>455</v>
-      </c>
-      <c r="G339" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="H339" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C340" t="s">
-        <v>11</v>
-      </c>
-      <c r="D340" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E340" t="s">
-        <v>454</v>
-      </c>
-      <c r="F340" t="s">
-        <v>455</v>
-      </c>
-      <c r="G340" t="s">
-        <v>1283</v>
-      </c>
-      <c r="H340" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A341" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C341" t="s">
-        <v>11</v>
-      </c>
-      <c r="D341" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E341" t="s">
-        <v>454</v>
-      </c>
-      <c r="F341" t="s">
-        <v>455</v>
-      </c>
-      <c r="G341" t="s">
-        <v>1283</v>
-      </c>
-      <c r="H341" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C342" t="s">
-        <v>359</v>
-      </c>
-      <c r="D342" t="s">
-        <v>1287</v>
-      </c>
-      <c r="H342" t="s">
-        <v>1288</v>
+        <v>1277</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF8812E-25F2-45D7-ACE2-0904BEE4065E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B6DCFE-008A-4E2D-9A8C-DC0E28F8CDD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1112">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -1164,18 +1164,6 @@
     <t>6aba77aa219e3d74bbe41976</t>
   </si>
   <si>
-    <t>6aba155c219e3d74bbe405d3</t>
-  </si>
-  <si>
-    <t>260928-W00002297</t>
-  </si>
-  <si>
-    <t>9245</t>
-  </si>
-  <si>
-    <t>MOSONSZOLNOK</t>
-  </si>
-  <si>
     <t>6aba259c219e3d74bbe4091a</t>
   </si>
   <si>
@@ -1513,18 +1501,6 @@
   </si>
   <si>
     <t>260930-F00007800</t>
-  </si>
-  <si>
-    <t>6abcebe1219e3d74bbe44f7d</t>
-  </si>
-  <si>
-    <t>260930-F00007808</t>
-  </si>
-  <si>
-    <t>4523</t>
-  </si>
-  <si>
-    <t>PÁTROHA</t>
   </si>
   <si>
     <t>6abc7a18219e3d74bbe440b3</t>
@@ -3741,7 +3717,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -5184,7 +5160,7 @@
         <v>378</v>
       </c>
       <c r="C63" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="D63" t="s">
         <v>379</v>
@@ -5193,10 +5169,10 @@
         <v>380</v>
       </c>
       <c r="F63" t="s">
-        <v>381</v>
+        <v>74</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="H63" t="s">
         <v>10</v>
@@ -5204,22 +5180,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>381</v>
+      </c>
+      <c r="C64" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" t="s">
         <v>382</v>
       </c>
-      <c r="C64" t="s">
-        <v>128</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
+        <v>86</v>
+      </c>
+      <c r="F64" t="s">
+        <v>87</v>
+      </c>
+      <c r="G64" t="s">
         <v>383</v>
-      </c>
-      <c r="E64" t="s">
-        <v>384</v>
-      </c>
-      <c r="F64" t="s">
-        <v>74</v>
-      </c>
-      <c r="G64" t="s">
-        <v>118</v>
       </c>
       <c r="H64" t="s">
         <v>10</v>
@@ -5227,22 +5203,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>384</v>
+      </c>
+      <c r="C65" t="s">
         <v>385</v>
-      </c>
-      <c r="C65" t="s">
-        <v>88</v>
       </c>
       <c r="D65" t="s">
         <v>386</v>
       </c>
       <c r="E65" t="s">
-        <v>86</v>
+        <v>387</v>
       </c>
       <c r="F65" t="s">
-        <v>87</v>
+        <v>388</v>
       </c>
       <c r="G65" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H65" t="s">
         <v>10</v>
@@ -5250,22 +5226,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C66" t="s">
-        <v>389</v>
+        <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E66" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F66" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G66" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H66" t="s">
         <v>10</v>
@@ -5273,22 +5249,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C67" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E67" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F67" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G67" t="s">
-        <v>398</v>
+        <v>75</v>
       </c>
       <c r="H67" t="s">
         <v>10</v>
@@ -5302,13 +5278,13 @@
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E68" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F68" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G68" t="s">
         <v>75</v>
@@ -5319,22 +5295,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>400</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>401</v>
+      </c>
+      <c r="E69" t="s">
+        <v>402</v>
+      </c>
+      <c r="F69" t="s">
         <v>403</v>
       </c>
-      <c r="C69" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" t="s">
-        <v>400</v>
-      </c>
-      <c r="E69" t="s">
-        <v>401</v>
-      </c>
-      <c r="F69" t="s">
-        <v>402</v>
-      </c>
       <c r="G69" t="s">
-        <v>75</v>
+        <v>404</v>
       </c>
       <c r="H69" t="s">
         <v>10</v>
@@ -5342,22 +5318,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C70" t="s">
-        <v>9</v>
+        <v>358</v>
       </c>
       <c r="D70" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E70" t="s">
-        <v>406</v>
+        <v>93</v>
       </c>
       <c r="F70" t="s">
+        <v>94</v>
+      </c>
+      <c r="G70" t="s">
         <v>407</v>
-      </c>
-      <c r="G70" t="s">
-        <v>408</v>
       </c>
       <c r="H70" t="s">
         <v>10</v>
@@ -5365,22 +5341,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>408</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
         <v>409</v>
       </c>
-      <c r="C71" t="s">
-        <v>358</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>410</v>
       </c>
-      <c r="E71" t="s">
-        <v>93</v>
-      </c>
       <c r="F71" t="s">
-        <v>94</v>
+        <v>411</v>
       </c>
       <c r="G71" t="s">
-        <v>411</v>
+        <v>16</v>
       </c>
       <c r="H71" t="s">
         <v>10</v>
@@ -5394,13 +5370,13 @@
         <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E72" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F72" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
@@ -5411,22 +5387,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>413</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
+        <v>414</v>
+      </c>
+      <c r="E73" t="s">
+        <v>415</v>
+      </c>
+      <c r="F73" t="s">
         <v>416</v>
       </c>
-      <c r="C73" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" t="s">
-        <v>413</v>
-      </c>
-      <c r="E73" t="s">
-        <v>414</v>
-      </c>
-      <c r="F73" t="s">
-        <v>415</v>
-      </c>
       <c r="G73" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="H73" t="s">
         <v>10</v>
@@ -5443,13 +5419,13 @@
         <v>418</v>
       </c>
       <c r="E74" t="s">
-        <v>419</v>
+        <v>165</v>
       </c>
       <c r="F74" t="s">
-        <v>420</v>
+        <v>166</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="H74" t="s">
         <v>10</v>
@@ -5457,13 +5433,13 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E75" t="s">
         <v>165</v>
@@ -5480,22 +5456,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>420</v>
+      </c>
+      <c r="C76" t="s">
+        <v>349</v>
+      </c>
+      <c r="D76" t="s">
+        <v>421</v>
+      </c>
+      <c r="E76" t="s">
+        <v>422</v>
+      </c>
+      <c r="F76" t="s">
         <v>423</v>
       </c>
-      <c r="C76" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" t="s">
-        <v>422</v>
-      </c>
-      <c r="E76" t="s">
-        <v>165</v>
-      </c>
-      <c r="F76" t="s">
-        <v>166</v>
-      </c>
       <c r="G76" t="s">
-        <v>31</v>
+        <v>424</v>
       </c>
       <c r="H76" t="s">
         <v>10</v>
@@ -5503,22 +5479,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C77" t="s">
-        <v>349</v>
+        <v>61</v>
       </c>
       <c r="D77" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E77" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F77" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G77" t="s">
-        <v>428</v>
+        <v>70</v>
       </c>
       <c r="H77" t="s">
         <v>10</v>
@@ -5532,13 +5508,13 @@
         <v>61</v>
       </c>
       <c r="D78" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E78" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F78" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="G78" t="s">
         <v>70</v>
@@ -5549,22 +5525,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E79" t="s">
-        <v>431</v>
+        <v>117</v>
       </c>
       <c r="F79" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" t="s">
         <v>432</v>
-      </c>
-      <c r="G79" t="s">
-        <v>70</v>
       </c>
       <c r="H79" t="s">
         <v>10</v>
@@ -5572,22 +5548,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>433</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" t="s">
         <v>434</v>
       </c>
-      <c r="C80" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" t="s">
-        <v>435</v>
-      </c>
       <c r="E80" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="F80" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="G80" t="s">
-        <v>436</v>
+        <v>164</v>
       </c>
       <c r="H80" t="s">
         <v>10</v>
@@ -5595,22 +5571,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>435</v>
+      </c>
+      <c r="C81" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81" t="s">
+        <v>436</v>
+      </c>
+      <c r="E81" t="s">
+        <v>78</v>
+      </c>
+      <c r="F81" t="s">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s">
         <v>437</v>
-      </c>
-      <c r="C81" t="s">
-        <v>32</v>
-      </c>
-      <c r="D81" t="s">
-        <v>438</v>
-      </c>
-      <c r="E81" t="s">
-        <v>90</v>
-      </c>
-      <c r="F81" t="s">
-        <v>91</v>
-      </c>
-      <c r="G81" t="s">
-        <v>164</v>
       </c>
       <c r="H81" t="s">
         <v>10</v>
@@ -5618,13 +5594,13 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C82" t="s">
         <v>61</v>
       </c>
       <c r="D82" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E82" t="s">
         <v>78</v>
@@ -5633,7 +5609,7 @@
         <v>79</v>
       </c>
       <c r="G82" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H82" t="s">
         <v>10</v>
@@ -5641,19 +5617,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C83" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D83" t="s">
         <v>440</v>
       </c>
       <c r="E83" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F83" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G83" t="s">
         <v>441</v>
@@ -5664,22 +5640,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>442</v>
+      </c>
+      <c r="C84" t="s">
+        <v>61</v>
+      </c>
+      <c r="D84" t="s">
         <v>443</v>
       </c>
-      <c r="C84" t="s">
-        <v>104</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>444</v>
       </c>
-      <c r="E84" t="s">
-        <v>66</v>
-      </c>
       <c r="F84" t="s">
-        <v>67</v>
+        <v>445</v>
       </c>
       <c r="G84" t="s">
-        <v>445</v>
+        <v>36</v>
       </c>
       <c r="H84" t="s">
         <v>10</v>
@@ -5690,19 +5666,19 @@
         <v>446</v>
       </c>
       <c r="C85" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
         <v>447</v>
       </c>
       <c r="E85" t="s">
+        <v>145</v>
+      </c>
+      <c r="F85" t="s">
+        <v>146</v>
+      </c>
+      <c r="G85" t="s">
         <v>448</v>
-      </c>
-      <c r="F85" t="s">
-        <v>449</v>
-      </c>
-      <c r="G85" t="s">
-        <v>36</v>
       </c>
       <c r="H85" t="s">
         <v>10</v>
@@ -5710,22 +5686,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>449</v>
+      </c>
+      <c r="C86" t="s">
+        <v>236</v>
+      </c>
+      <c r="D86" t="s">
         <v>450</v>
       </c>
-      <c r="C86" t="s">
-        <v>34</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>451</v>
       </c>
-      <c r="E86" t="s">
-        <v>145</v>
-      </c>
       <c r="F86" t="s">
-        <v>146</v>
+        <v>452</v>
       </c>
       <c r="G86" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H86" t="s">
         <v>10</v>
@@ -5733,22 +5709,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C87" t="s">
         <v>236</v>
       </c>
       <c r="D87" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E87" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F87" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G87" t="s">
-        <v>457</v>
+        <v>36</v>
       </c>
       <c r="H87" t="s">
         <v>10</v>
@@ -5759,19 +5735,19 @@
         <v>458</v>
       </c>
       <c r="C88" t="s">
-        <v>236</v>
+        <v>26</v>
       </c>
       <c r="D88" t="s">
         <v>459</v>
       </c>
       <c r="E88" t="s">
+        <v>112</v>
+      </c>
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" t="s">
         <v>460</v>
-      </c>
-      <c r="F88" t="s">
-        <v>461</v>
-      </c>
-      <c r="G88" t="s">
-        <v>36</v>
       </c>
       <c r="H88" t="s">
         <v>10</v>
@@ -5779,22 +5755,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>461</v>
+      </c>
+      <c r="C89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" t="s">
         <v>462</v>
       </c>
-      <c r="C89" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>463</v>
       </c>
-      <c r="E89" t="s">
-        <v>112</v>
-      </c>
       <c r="F89" t="s">
-        <v>12</v>
+        <v>464</v>
       </c>
       <c r="G89" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H89" t="s">
         <v>10</v>
@@ -5802,22 +5778,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C90" t="s">
         <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E90" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F90" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G90" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H90" t="s">
         <v>10</v>
@@ -5825,19 +5801,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D91" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E91" t="s">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="F91" t="s">
-        <v>468</v>
+        <v>110</v>
       </c>
       <c r="G91" t="s">
         <v>469</v>
@@ -5848,22 +5824,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>470</v>
+      </c>
+      <c r="C92" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" t="s">
         <v>471</v>
       </c>
-      <c r="C92" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" t="s">
-        <v>472</v>
-      </c>
       <c r="E92" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F92" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>473</v>
+        <v>179</v>
       </c>
       <c r="H92" t="s">
         <v>10</v>
@@ -5871,22 +5847,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>472</v>
+      </c>
+      <c r="C93" t="s">
+        <v>88</v>
+      </c>
+      <c r="D93" t="s">
+        <v>473</v>
+      </c>
+      <c r="E93" t="s">
         <v>474</v>
       </c>
-      <c r="C93" t="s">
-        <v>19</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
         <v>475</v>
       </c>
-      <c r="E93" t="s">
-        <v>127</v>
-      </c>
-      <c r="F93" t="s">
-        <v>20</v>
-      </c>
       <c r="G93" t="s">
-        <v>179</v>
+        <v>476</v>
       </c>
       <c r="H93" t="s">
         <v>10</v>
@@ -5894,22 +5870,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C94" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E94" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F94" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G94" t="s">
-        <v>480</v>
+        <v>31</v>
       </c>
       <c r="H94" t="s">
         <v>10</v>
@@ -5920,7 +5896,7 @@
         <v>481</v>
       </c>
       <c r="C95" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D95" t="s">
         <v>482</v>
@@ -5929,10 +5905,10 @@
         <v>483</v>
       </c>
       <c r="F95" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" t="s">
         <v>484</v>
-      </c>
-      <c r="G95" t="s">
-        <v>31</v>
       </c>
       <c r="H95" t="s">
         <v>10</v>
@@ -5946,16 +5922,16 @@
         <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E96" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F96" t="s">
         <v>20</v>
       </c>
       <c r="G96" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H96" t="s">
         <v>10</v>
@@ -5963,19 +5939,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C97" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E97" t="s">
-        <v>487</v>
+        <v>136</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="G97" t="s">
         <v>488</v>
@@ -5986,22 +5962,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>489</v>
+      </c>
+      <c r="C98" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" t="s">
         <v>490</v>
       </c>
-      <c r="C98" t="s">
-        <v>23</v>
-      </c>
-      <c r="D98" t="s">
-        <v>491</v>
-      </c>
       <c r="E98" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="F98" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="G98" t="s">
-        <v>492</v>
+        <v>62</v>
       </c>
       <c r="H98" t="s">
         <v>10</v>
@@ -6009,22 +5985,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>354</v>
       </c>
       <c r="D99" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E99" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F99" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -6032,22 +6008,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>493</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>494</v>
+      </c>
+      <c r="E100" t="s">
+        <v>205</v>
+      </c>
+      <c r="F100" t="s">
+        <v>206</v>
+      </c>
+      <c r="G100" t="s">
         <v>495</v>
-      </c>
-      <c r="C100" t="s">
-        <v>30</v>
-      </c>
-      <c r="D100" t="s">
-        <v>496</v>
-      </c>
-      <c r="E100" t="s">
-        <v>497</v>
-      </c>
-      <c r="F100" t="s">
-        <v>498</v>
-      </c>
-      <c r="G100" t="s">
-        <v>116</v>
       </c>
       <c r="H100" t="s">
         <v>10</v>
@@ -6055,22 +6031,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>496</v>
+      </c>
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="s">
+        <v>497</v>
+      </c>
+      <c r="E101" t="s">
+        <v>498</v>
+      </c>
+      <c r="F101" t="s">
         <v>499</v>
       </c>
-      <c r="C101" t="s">
-        <v>354</v>
-      </c>
-      <c r="D101" t="s">
-        <v>500</v>
-      </c>
-      <c r="E101" t="s">
-        <v>121</v>
-      </c>
-      <c r="F101" t="s">
-        <v>122</v>
-      </c>
       <c r="G101" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="H101" t="s">
         <v>10</v>
@@ -6078,22 +6054,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>500</v>
+      </c>
+      <c r="C102" t="s">
+        <v>354</v>
+      </c>
+      <c r="D102" t="s">
         <v>501</v>
       </c>
-      <c r="C102" t="s">
-        <v>24</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>502</v>
       </c>
-      <c r="E102" t="s">
-        <v>205</v>
-      </c>
       <c r="F102" t="s">
-        <v>206</v>
+        <v>503</v>
       </c>
       <c r="G102" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H102" t="s">
         <v>10</v>
@@ -6101,22 +6077,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>504</v>
+        <v>147</v>
       </c>
       <c r="C103" t="s">
-        <v>11</v>
+        <v>385</v>
       </c>
       <c r="D103" t="s">
-        <v>505</v>
+        <v>148</v>
       </c>
       <c r="E103" t="s">
-        <v>506</v>
+        <v>149</v>
       </c>
       <c r="F103" t="s">
-        <v>507</v>
+        <v>150</v>
       </c>
       <c r="G103" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="H103" t="s">
         <v>10</v>
@@ -6124,22 +6100,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>508</v>
+        <v>151</v>
       </c>
       <c r="C104" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="D104" t="s">
-        <v>509</v>
+        <v>148</v>
       </c>
       <c r="E104" t="s">
-        <v>510</v>
+        <v>149</v>
       </c>
       <c r="F104" t="s">
-        <v>511</v>
+        <v>150</v>
       </c>
       <c r="G104" t="s">
-        <v>512</v>
+        <v>144</v>
       </c>
       <c r="H104" t="s">
         <v>10</v>
@@ -6147,22 +6123,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>505</v>
       </c>
       <c r="C105" t="s">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="D105" t="s">
-        <v>148</v>
+        <v>506</v>
       </c>
       <c r="E105" t="s">
-        <v>149</v>
+        <v>507</v>
       </c>
       <c r="F105" t="s">
-        <v>150</v>
+        <v>508</v>
       </c>
       <c r="G105" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="H105" t="s">
         <v>10</v>
@@ -6170,22 +6146,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>151</v>
+        <v>509</v>
       </c>
       <c r="C106" t="s">
-        <v>389</v>
+        <v>32</v>
       </c>
       <c r="D106" t="s">
-        <v>148</v>
+        <v>510</v>
       </c>
       <c r="E106" t="s">
-        <v>149</v>
+        <v>511</v>
       </c>
       <c r="F106" t="s">
-        <v>150</v>
+        <v>512</v>
       </c>
       <c r="G106" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -6196,19 +6172,19 @@
         <v>513</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D107" t="s">
         <v>514</v>
       </c>
       <c r="E107" t="s">
+        <v>184</v>
+      </c>
+      <c r="F107" t="s">
+        <v>185</v>
+      </c>
+      <c r="G107" t="s">
         <v>515</v>
-      </c>
-      <c r="F107" t="s">
-        <v>516</v>
-      </c>
-      <c r="G107" t="s">
-        <v>28</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -6216,22 +6192,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>516</v>
+      </c>
+      <c r="C108" t="s">
+        <v>49</v>
+      </c>
+      <c r="D108" t="s">
         <v>517</v>
       </c>
-      <c r="C108" t="s">
-        <v>32</v>
-      </c>
-      <c r="D108" t="s">
-        <v>518</v>
-      </c>
       <c r="E108" t="s">
-        <v>519</v>
+        <v>105</v>
       </c>
       <c r="F108" t="s">
-        <v>520</v>
+        <v>106</v>
       </c>
       <c r="G108" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -6239,22 +6215,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>518</v>
+      </c>
+      <c r="C109" t="s">
+        <v>32</v>
+      </c>
+      <c r="D109" t="s">
+        <v>519</v>
+      </c>
+      <c r="E109" t="s">
+        <v>520</v>
+      </c>
+      <c r="F109" t="s">
         <v>521</v>
       </c>
-      <c r="C109" t="s">
-        <v>61</v>
-      </c>
-      <c r="D109" t="s">
-        <v>522</v>
-      </c>
-      <c r="E109" t="s">
-        <v>184</v>
-      </c>
-      <c r="F109" t="s">
-        <v>185</v>
-      </c>
       <c r="G109" t="s">
-        <v>523</v>
+        <v>178</v>
       </c>
       <c r="H109" t="s">
         <v>10</v>
@@ -6262,22 +6238,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C110" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D110" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="E110" t="s">
-        <v>105</v>
+        <v>520</v>
       </c>
       <c r="F110" t="s">
-        <v>106</v>
+        <v>521</v>
       </c>
       <c r="G110" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
       <c r="H110" t="s">
         <v>10</v>
@@ -6285,22 +6261,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>523</v>
+      </c>
+      <c r="C111" t="s">
+        <v>43</v>
+      </c>
+      <c r="D111" t="s">
+        <v>524</v>
+      </c>
+      <c r="E111" t="s">
+        <v>525</v>
+      </c>
+      <c r="F111" t="s">
+        <v>7</v>
+      </c>
+      <c r="G111" t="s">
         <v>526</v>
-      </c>
-      <c r="C111" t="s">
-        <v>32</v>
-      </c>
-      <c r="D111" t="s">
-        <v>527</v>
-      </c>
-      <c r="E111" t="s">
-        <v>528</v>
-      </c>
-      <c r="F111" t="s">
-        <v>529</v>
-      </c>
-      <c r="G111" t="s">
-        <v>178</v>
       </c>
       <c r="H111" t="s">
         <v>10</v>
@@ -6308,22 +6284,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>527</v>
+      </c>
+      <c r="C112" t="s">
+        <v>88</v>
+      </c>
+      <c r="D112" t="s">
+        <v>528</v>
+      </c>
+      <c r="E112" t="s">
+        <v>529</v>
+      </c>
+      <c r="F112" t="s">
         <v>530</v>
       </c>
-      <c r="C112" t="s">
-        <v>32</v>
-      </c>
-      <c r="D112" t="s">
-        <v>527</v>
-      </c>
-      <c r="E112" t="s">
-        <v>528</v>
-      </c>
-      <c r="F112" t="s">
-        <v>529</v>
-      </c>
       <c r="G112" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
       <c r="H112" t="s">
         <v>10</v>
@@ -6334,7 +6310,7 @@
         <v>531</v>
       </c>
       <c r="C113" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="D113" t="s">
         <v>532</v>
@@ -6343,10 +6319,10 @@
         <v>533</v>
       </c>
       <c r="F113" t="s">
-        <v>7</v>
+        <v>534</v>
       </c>
       <c r="G113" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H113" t="s">
         <v>10</v>
@@ -6354,22 +6330,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C114" t="s">
-        <v>88</v>
+        <v>537</v>
       </c>
       <c r="D114" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E114" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F114" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G114" t="s">
-        <v>28</v>
+        <v>541</v>
       </c>
       <c r="H114" t="s">
         <v>10</v>
@@ -6377,22 +6353,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="D115" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E115" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F115" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="G115" t="s">
-        <v>543</v>
+        <v>31</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -6400,25 +6376,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C116" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D116" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E116" t="s">
-        <v>547</v>
+        <v>55</v>
       </c>
       <c r="F116" t="s">
-        <v>548</v>
+        <v>56</v>
       </c>
       <c r="G116" t="s">
         <v>549</v>
       </c>
       <c r="H116" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
@@ -6426,7 +6402,7 @@
         <v>550</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D117" t="s">
         <v>551</v>
@@ -6438,30 +6414,30 @@
         <v>553</v>
       </c>
       <c r="G117" t="s">
-        <v>31</v>
+        <v>554</v>
       </c>
       <c r="H117" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C118" t="s">
-        <v>555</v>
+        <v>22</v>
       </c>
       <c r="D118" t="s">
         <v>556</v>
       </c>
       <c r="E118" t="s">
-        <v>55</v>
+        <v>557</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="G118" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H118" t="s">
         <v>48</v>
@@ -6469,22 +6445,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C119" t="s">
-        <v>9</v>
+        <v>349</v>
       </c>
       <c r="D119" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E119" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F119" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G119" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H119" t="s">
         <v>48</v>
@@ -6492,22 +6468,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C120" t="s">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="D120" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E120" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F120" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G120" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H120" t="s">
         <v>48</v>
@@ -6515,19 +6491,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C121" t="s">
-        <v>349</v>
+        <v>23</v>
       </c>
       <c r="D121" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E121" t="s">
-        <v>570</v>
+        <v>109</v>
       </c>
       <c r="F121" t="s">
-        <v>571</v>
+        <v>110</v>
       </c>
       <c r="G121" t="s">
         <v>572</v>
@@ -6541,7 +6517,7 @@
         <v>573</v>
       </c>
       <c r="C122" t="s">
-        <v>349</v>
+        <v>32</v>
       </c>
       <c r="D122" t="s">
         <v>574</v>
@@ -6564,19 +6540,19 @@
         <v>578</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E123" t="s">
-        <v>109</v>
+        <v>575</v>
       </c>
       <c r="F123" t="s">
-        <v>110</v>
+        <v>576</v>
       </c>
       <c r="G123" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H123" t="s">
         <v>48</v>
@@ -6584,22 +6560,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C124" t="s">
         <v>32</v>
       </c>
       <c r="D124" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E124" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F124" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="G124" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="H124" t="s">
         <v>48</v>
@@ -6607,22 +6583,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C125" t="s">
         <v>32</v>
       </c>
       <c r="D125" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E125" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F125" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="G125" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="H125" t="s">
         <v>48</v>
@@ -6630,22 +6606,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C126" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D126" t="s">
         <v>582</v>
       </c>
       <c r="E126" t="s">
+        <v>78</v>
+      </c>
+      <c r="F126" t="s">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s">
         <v>583</v>
-      </c>
-      <c r="F126" t="s">
-        <v>584</v>
-      </c>
-      <c r="G126" t="s">
-        <v>585</v>
       </c>
       <c r="H126" t="s">
         <v>48</v>
@@ -6653,71 +6629,71 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>584</v>
+      </c>
+      <c r="C127" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" t="s">
+        <v>585</v>
+      </c>
+      <c r="E127" t="s">
+        <v>586</v>
+      </c>
+      <c r="F127" t="s">
+        <v>587</v>
+      </c>
+      <c r="G127" t="s">
         <v>588</v>
       </c>
-      <c r="C127" t="s">
-        <v>32</v>
-      </c>
-      <c r="D127" t="s">
-        <v>582</v>
-      </c>
-      <c r="E127" t="s">
-        <v>583</v>
-      </c>
-      <c r="F127" t="s">
-        <v>584</v>
-      </c>
-      <c r="G127" t="s">
-        <v>585</v>
-      </c>
       <c r="H127" t="s">
-        <v>48</v>
+        <v>589</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>590</v>
+      </c>
+      <c r="C128" t="s">
+        <v>349</v>
+      </c>
+      <c r="D128" t="s">
+        <v>591</v>
+      </c>
+      <c r="E128" t="s">
+        <v>142</v>
+      </c>
+      <c r="F128" t="s">
+        <v>143</v>
+      </c>
+      <c r="G128" t="s">
+        <v>592</v>
+      </c>
+      <c r="H128" t="s">
         <v>589</v>
-      </c>
-      <c r="C128" t="s">
-        <v>61</v>
-      </c>
-      <c r="D128" t="s">
-        <v>590</v>
-      </c>
-      <c r="E128" t="s">
-        <v>78</v>
-      </c>
-      <c r="F128" t="s">
-        <v>79</v>
-      </c>
-      <c r="G128" t="s">
-        <v>591</v>
-      </c>
-      <c r="H128" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C129" t="s">
-        <v>22</v>
+        <v>358</v>
       </c>
       <c r="D129" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E129" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F129" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G129" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H129" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
@@ -6725,22 +6701,22 @@
         <v>598</v>
       </c>
       <c r="C130" t="s">
-        <v>349</v>
+        <v>54</v>
       </c>
       <c r="D130" t="s">
         <v>599</v>
       </c>
       <c r="E130" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="F130" t="s">
-        <v>143</v>
+        <v>7</v>
       </c>
       <c r="G130" t="s">
         <v>600</v>
       </c>
       <c r="H130" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
@@ -6748,56 +6724,56 @@
         <v>601</v>
       </c>
       <c r="C131" t="s">
-        <v>358</v>
+        <v>537</v>
       </c>
       <c r="D131" t="s">
         <v>602</v>
       </c>
       <c r="E131" t="s">
-        <v>603</v>
+        <v>134</v>
       </c>
       <c r="F131" t="s">
-        <v>604</v>
-      </c>
-      <c r="G131" t="s">
-        <v>605</v>
+        <v>135</v>
+      </c>
+      <c r="G131" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="H131" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C132" t="s">
-        <v>54</v>
+        <v>537</v>
       </c>
       <c r="D132" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E132" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="F132" t="s">
-        <v>7</v>
-      </c>
-      <c r="G132" t="s">
-        <v>608</v>
+        <v>135</v>
+      </c>
+      <c r="G132" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="H132" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C133" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D133" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="E133" t="s">
         <v>134</v>
@@ -6809,53 +6785,53 @@
         <v>#NUM!</v>
       </c>
       <c r="H133" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C134" t="s">
-        <v>545</v>
+        <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E134" t="s">
-        <v>134</v>
+        <v>607</v>
       </c>
       <c r="F134" t="s">
-        <v>135</v>
-      </c>
-      <c r="G134" t="e">
-        <v>#NUM!</v>
+        <v>7</v>
+      </c>
+      <c r="G134" t="s">
+        <v>608</v>
       </c>
       <c r="H134" t="s">
-        <v>597</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C135" t="s">
-        <v>545</v>
+        <v>385</v>
       </c>
       <c r="D135" t="s">
         <v>610</v>
       </c>
       <c r="E135" t="s">
-        <v>134</v>
+        <v>611</v>
       </c>
       <c r="F135" t="s">
-        <v>135</v>
-      </c>
-      <c r="G135" t="e">
-        <v>#NUM!</v>
+        <v>612</v>
+      </c>
+      <c r="G135" t="s">
+        <v>172</v>
       </c>
       <c r="H135" t="s">
-        <v>597</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
@@ -6863,19 +6839,19 @@
         <v>613</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>385</v>
       </c>
       <c r="D136" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E136" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F136" t="s">
-        <v>7</v>
+        <v>612</v>
       </c>
       <c r="G136" t="s">
-        <v>616</v>
+        <v>172</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -6883,22 +6859,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C137" t="s">
-        <v>389</v>
+        <v>92</v>
       </c>
       <c r="D137" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E137" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F137" t="s">
-        <v>620</v>
+        <v>180</v>
       </c>
       <c r="G137" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -6906,22 +6882,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C138" t="s">
-        <v>389</v>
+        <v>92</v>
       </c>
       <c r="D138" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E138" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F138" t="s">
-        <v>620</v>
+        <v>180</v>
       </c>
       <c r="G138" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -6929,16 +6905,16 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C139" t="s">
         <v>92</v>
       </c>
       <c r="D139" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E139" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F139" t="s">
         <v>180</v>
@@ -6952,22 +6928,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C140" t="s">
-        <v>92</v>
+        <v>358</v>
       </c>
       <c r="D140" t="s">
+        <v>620</v>
+      </c>
+      <c r="E140" t="s">
+        <v>621</v>
+      </c>
+      <c r="F140" t="s">
+        <v>622</v>
+      </c>
+      <c r="G140" t="s">
         <v>623</v>
-      </c>
-      <c r="E140" t="s">
-        <v>624</v>
-      </c>
-      <c r="F140" t="s">
-        <v>180</v>
-      </c>
-      <c r="G140" t="s">
-        <v>249</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -6975,22 +6951,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>624</v>
+      </c>
+      <c r="C141" t="s">
+        <v>537</v>
+      </c>
+      <c r="D141" t="s">
+        <v>625</v>
+      </c>
+      <c r="E141" t="s">
         <v>626</v>
       </c>
-      <c r="C141" t="s">
-        <v>92</v>
-      </c>
-      <c r="D141" t="s">
-        <v>623</v>
-      </c>
-      <c r="E141" t="s">
-        <v>624</v>
-      </c>
       <c r="F141" t="s">
-        <v>180</v>
+        <v>627</v>
       </c>
       <c r="G141" t="s">
-        <v>249</v>
+        <v>130</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -6998,19 +6974,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C142" t="s">
-        <v>358</v>
+        <v>27</v>
       </c>
       <c r="D142" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E142" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F142" t="s">
-        <v>630</v>
+        <v>25</v>
       </c>
       <c r="G142" t="s">
         <v>631</v>
@@ -7024,19 +7000,19 @@
         <v>632</v>
       </c>
       <c r="C143" t="s">
-        <v>545</v>
+        <v>43</v>
       </c>
       <c r="D143" t="s">
         <v>633</v>
       </c>
       <c r="E143" t="s">
+        <v>525</v>
+      </c>
+      <c r="F143" t="s">
+        <v>7</v>
+      </c>
+      <c r="G143" t="s">
         <v>634</v>
-      </c>
-      <c r="F143" t="s">
-        <v>635</v>
-      </c>
-      <c r="G143" t="s">
-        <v>130</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -7044,22 +7020,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>635</v>
+      </c>
+      <c r="C144" t="s">
+        <v>35</v>
+      </c>
+      <c r="D144" t="s">
         <v>636</v>
       </c>
-      <c r="C144" t="s">
-        <v>27</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
+        <v>82</v>
+      </c>
+      <c r="F144" t="s">
+        <v>83</v>
+      </c>
+      <c r="G144" t="s">
         <v>637</v>
-      </c>
-      <c r="E144" t="s">
-        <v>638</v>
-      </c>
-      <c r="F144" t="s">
-        <v>25</v>
-      </c>
-      <c r="G144" t="s">
-        <v>639</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -7067,16 +7043,16 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>638</v>
+      </c>
+      <c r="C145" t="s">
+        <v>639</v>
+      </c>
+      <c r="D145" t="s">
         <v>640</v>
       </c>
-      <c r="C145" t="s">
-        <v>43</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>641</v>
-      </c>
-      <c r="E145" t="s">
-        <v>533</v>
       </c>
       <c r="F145" t="s">
         <v>7</v>
@@ -7093,19 +7069,19 @@
         <v>643</v>
       </c>
       <c r="C146" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D146" t="s">
         <v>644</v>
       </c>
       <c r="E146" t="s">
-        <v>82</v>
+        <v>645</v>
       </c>
       <c r="F146" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="G146" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -7113,16 +7089,16 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C147" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D147" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E147" t="s">
-        <v>649</v>
+        <v>113</v>
       </c>
       <c r="F147" t="s">
         <v>7</v>
@@ -7139,7 +7115,7 @@
         <v>651</v>
       </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D148" t="s">
         <v>652</v>
@@ -7162,19 +7138,19 @@
         <v>655</v>
       </c>
       <c r="C149" t="s">
+        <v>120</v>
+      </c>
+      <c r="D149" t="s">
         <v>656</v>
       </c>
-      <c r="D149" t="s">
-        <v>657</v>
-      </c>
       <c r="E149" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F149" t="s">
         <v>7</v>
       </c>
       <c r="G149" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -7182,22 +7158,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>658</v>
+      </c>
+      <c r="C150" t="s">
+        <v>104</v>
+      </c>
+      <c r="D150" t="s">
         <v>659</v>
       </c>
-      <c r="C150" t="s">
-        <v>9</v>
-      </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
         <v>660</v>
-      </c>
-      <c r="E150" t="s">
-        <v>661</v>
       </c>
       <c r="F150" t="s">
         <v>7</v>
       </c>
       <c r="G150" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -7205,22 +7181,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C151" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D151" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="E151" t="s">
-        <v>131</v>
+        <v>660</v>
       </c>
       <c r="F151" t="s">
         <v>7</v>
       </c>
       <c r="G151" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -7228,22 +7204,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C152" t="s">
         <v>104</v>
       </c>
       <c r="D152" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E152" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="F152" t="s">
         <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -7251,22 +7227,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C153" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="D153" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E153" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F153" t="s">
         <v>7</v>
       </c>
       <c r="G153" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -7274,22 +7250,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>668</v>
+      </c>
+      <c r="C154" t="s">
+        <v>18</v>
+      </c>
+      <c r="D154" t="s">
+        <v>669</v>
+      </c>
+      <c r="E154" t="s">
+        <v>670</v>
+      </c>
+      <c r="F154" t="s">
         <v>671</v>
       </c>
-      <c r="C154" t="s">
-        <v>104</v>
-      </c>
-      <c r="D154" t="s">
-        <v>667</v>
-      </c>
-      <c r="E154" t="s">
-        <v>668</v>
-      </c>
-      <c r="F154" t="s">
-        <v>7</v>
-      </c>
       <c r="G154" t="s">
-        <v>669</v>
+        <v>71</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -7300,19 +7276,19 @@
         <v>672</v>
       </c>
       <c r="C155" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="E155" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="F155" t="s">
-        <v>7</v>
+        <v>671</v>
       </c>
       <c r="G155" t="s">
-        <v>675</v>
+        <v>71</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -7320,19 +7296,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C156" t="s">
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E156" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F156" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="G156" t="s">
         <v>71</v>
@@ -7343,22 +7319,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
+        <v>547</v>
       </c>
       <c r="D157" t="s">
+        <v>675</v>
+      </c>
+      <c r="E157" t="s">
+        <v>676</v>
+      </c>
+      <c r="F157" t="s">
         <v>677</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>678</v>
-      </c>
-      <c r="F157" t="s">
-        <v>679</v>
-      </c>
-      <c r="G157" t="s">
-        <v>71</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -7366,22 +7342,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>679</v>
+      </c>
+      <c r="C158" t="s">
+        <v>537</v>
+      </c>
+      <c r="D158" t="s">
+        <v>680</v>
+      </c>
+      <c r="E158" t="s">
+        <v>69</v>
+      </c>
+      <c r="F158" t="s">
+        <v>7</v>
+      </c>
+      <c r="G158" t="s">
         <v>681</v>
-      </c>
-      <c r="C158" t="s">
-        <v>18</v>
-      </c>
-      <c r="D158" t="s">
-        <v>677</v>
-      </c>
-      <c r="E158" t="s">
-        <v>678</v>
-      </c>
-      <c r="F158" t="s">
-        <v>679</v>
-      </c>
-      <c r="G158" t="s">
-        <v>71</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -7392,7 +7368,7 @@
         <v>682</v>
       </c>
       <c r="C159" t="s">
-        <v>555</v>
+        <v>53</v>
       </c>
       <c r="D159" t="s">
         <v>683</v>
@@ -7401,10 +7377,10 @@
         <v>684</v>
       </c>
       <c r="F159" t="s">
+        <v>7</v>
+      </c>
+      <c r="G159" t="s">
         <v>685</v>
-      </c>
-      <c r="G159" t="s">
-        <v>686</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -7412,16 +7388,16 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>686</v>
+      </c>
+      <c r="C160" t="s">
+        <v>53</v>
+      </c>
+      <c r="D160" t="s">
         <v>687</v>
       </c>
-      <c r="C160" t="s">
-        <v>545</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>688</v>
-      </c>
-      <c r="E160" t="s">
-        <v>69</v>
       </c>
       <c r="F160" t="s">
         <v>7</v>
@@ -7438,7 +7414,7 @@
         <v>690</v>
       </c>
       <c r="C161" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D161" t="s">
         <v>691</v>
@@ -7461,19 +7437,19 @@
         <v>694</v>
       </c>
       <c r="C162" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D162" t="s">
         <v>695</v>
       </c>
       <c r="E162" t="s">
-        <v>696</v>
+        <v>129</v>
       </c>
       <c r="F162" t="s">
         <v>7</v>
       </c>
       <c r="G162" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -7481,22 +7457,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>697</v>
+      </c>
+      <c r="C163" t="s">
+        <v>537</v>
+      </c>
+      <c r="D163" t="s">
         <v>698</v>
       </c>
-      <c r="C163" t="s">
-        <v>35</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
+        <v>626</v>
+      </c>
+      <c r="F163" t="s">
+        <v>627</v>
+      </c>
+      <c r="G163" t="s">
         <v>699</v>
-      </c>
-      <c r="E163" t="s">
-        <v>700</v>
-      </c>
-      <c r="F163" t="s">
-        <v>7</v>
-      </c>
-      <c r="G163" t="s">
-        <v>701</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -7504,22 +7480,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>700</v>
+      </c>
+      <c r="C164" t="s">
+        <v>639</v>
+      </c>
+      <c r="D164" t="s">
+        <v>701</v>
+      </c>
+      <c r="E164" t="s">
         <v>702</v>
-      </c>
-      <c r="C164" t="s">
-        <v>60</v>
-      </c>
-      <c r="D164" t="s">
-        <v>703</v>
-      </c>
-      <c r="E164" t="s">
-        <v>129</v>
       </c>
       <c r="F164" t="s">
         <v>7</v>
       </c>
       <c r="G164" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -7527,19 +7503,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>704</v>
+      </c>
+      <c r="C165" t="s">
+        <v>92</v>
+      </c>
+      <c r="D165" t="s">
         <v>705</v>
       </c>
-      <c r="C165" t="s">
-        <v>545</v>
-      </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>706</v>
       </c>
-      <c r="E165" t="s">
-        <v>634</v>
-      </c>
       <c r="F165" t="s">
-        <v>635</v>
+        <v>7</v>
       </c>
       <c r="G165" t="s">
         <v>707</v>
@@ -7553,19 +7529,19 @@
         <v>708</v>
       </c>
       <c r="C166" t="s">
-        <v>647</v>
+        <v>92</v>
       </c>
       <c r="D166" t="s">
         <v>709</v>
       </c>
       <c r="E166" t="s">
-        <v>710</v>
+        <v>163</v>
       </c>
       <c r="F166" t="s">
         <v>7</v>
       </c>
       <c r="G166" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -7573,22 +7549,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C167" t="s">
         <v>92</v>
       </c>
       <c r="D167" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E167" t="s">
-        <v>714</v>
+        <v>163</v>
       </c>
       <c r="F167" t="s">
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -7596,22 +7572,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C168" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D168" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="E168" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="F168" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G168" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -7619,22 +7595,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>715</v>
+      </c>
+      <c r="C169" t="s">
+        <v>104</v>
+      </c>
+      <c r="D169" t="s">
+        <v>716</v>
+      </c>
+      <c r="E169" t="s">
+        <v>717</v>
+      </c>
+      <c r="F169" t="s">
+        <v>718</v>
+      </c>
+      <c r="G169" t="s">
         <v>719</v>
-      </c>
-      <c r="C169" t="s">
-        <v>92</v>
-      </c>
-      <c r="D169" t="s">
-        <v>717</v>
-      </c>
-      <c r="E169" t="s">
-        <v>163</v>
-      </c>
-      <c r="F169" t="s">
-        <v>7</v>
-      </c>
-      <c r="G169" t="s">
-        <v>718</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -7645,19 +7621,19 @@
         <v>720</v>
       </c>
       <c r="C170" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D170" t="s">
         <v>721</v>
       </c>
       <c r="E170" t="s">
-        <v>41</v>
+        <v>722</v>
       </c>
       <c r="F170" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -7665,19 +7641,19 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C171" t="s">
-        <v>104</v>
+        <v>639</v>
       </c>
       <c r="D171" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E171" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F171" t="s">
-        <v>726</v>
+        <v>7</v>
       </c>
       <c r="G171" t="s">
         <v>727</v>
@@ -7691,19 +7667,19 @@
         <v>728</v>
       </c>
       <c r="C172" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="D172" t="s">
         <v>729</v>
       </c>
       <c r="E172" t="s">
-        <v>730</v>
+        <v>173</v>
       </c>
       <c r="F172" t="s">
         <v>7</v>
       </c>
       <c r="G172" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -7711,22 +7687,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>731</v>
+      </c>
+      <c r="C173" t="s">
+        <v>648</v>
+      </c>
+      <c r="D173" t="s">
         <v>732</v>
       </c>
-      <c r="C173" t="s">
-        <v>647</v>
-      </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>733</v>
-      </c>
-      <c r="E173" t="s">
-        <v>734</v>
       </c>
       <c r="F173" t="s">
         <v>7</v>
       </c>
       <c r="G173" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -7734,22 +7710,22 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>735</v>
+      </c>
+      <c r="C174" t="s">
+        <v>537</v>
+      </c>
+      <c r="D174" t="s">
         <v>736</v>
       </c>
-      <c r="C174" t="s">
-        <v>92</v>
-      </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>737</v>
       </c>
-      <c r="E174" t="s">
-        <v>173</v>
-      </c>
       <c r="F174" t="s">
-        <v>7</v>
+        <v>738</v>
       </c>
       <c r="G174" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -7757,16 +7733,16 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C175" t="s">
-        <v>656</v>
+        <v>537</v>
       </c>
       <c r="D175" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E175" t="s">
-        <v>741</v>
+        <v>69</v>
       </c>
       <c r="F175" t="s">
         <v>7</v>
@@ -7783,7 +7759,7 @@
         <v>743</v>
       </c>
       <c r="C176" t="s">
-        <v>545</v>
+        <v>92</v>
       </c>
       <c r="D176" t="s">
         <v>744</v>
@@ -7792,10 +7768,10 @@
         <v>745</v>
       </c>
       <c r="F176" t="s">
+        <v>7</v>
+      </c>
+      <c r="G176" t="s">
         <v>746</v>
-      </c>
-      <c r="G176" t="s">
-        <v>747</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -7803,22 +7779,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>747</v>
+      </c>
+      <c r="C177" t="s">
+        <v>60</v>
+      </c>
+      <c r="D177" t="s">
         <v>748</v>
       </c>
-      <c r="C177" t="s">
-        <v>545</v>
-      </c>
-      <c r="D177" t="s">
-        <v>749</v>
-      </c>
       <c r="E177" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="F177" t="s">
         <v>7</v>
       </c>
       <c r="G177" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -7826,22 +7802,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>750</v>
+      </c>
+      <c r="C178" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" t="s">
         <v>751</v>
       </c>
-      <c r="C178" t="s">
-        <v>92</v>
-      </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
+        <v>95</v>
+      </c>
+      <c r="F178" t="s">
+        <v>96</v>
+      </c>
+      <c r="G178" t="s">
         <v>752</v>
-      </c>
-      <c r="E178" t="s">
-        <v>753</v>
-      </c>
-      <c r="F178" t="s">
-        <v>7</v>
-      </c>
-      <c r="G178" t="s">
-        <v>754</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -7849,22 +7825,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>753</v>
+      </c>
+      <c r="C179" t="s">
+        <v>53</v>
+      </c>
+      <c r="D179" t="s">
+        <v>754</v>
+      </c>
+      <c r="E179" t="s">
         <v>755</v>
-      </c>
-      <c r="C179" t="s">
-        <v>60</v>
-      </c>
-      <c r="D179" t="s">
-        <v>756</v>
-      </c>
-      <c r="E179" t="s">
-        <v>161</v>
       </c>
       <c r="F179" t="s">
         <v>7</v>
       </c>
       <c r="G179" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -7872,19 +7848,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>757</v>
+      </c>
+      <c r="C180" t="s">
+        <v>58</v>
+      </c>
+      <c r="D180" t="s">
         <v>758</v>
       </c>
-      <c r="C180" t="s">
-        <v>14</v>
-      </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>759</v>
       </c>
-      <c r="E180" t="s">
-        <v>95</v>
-      </c>
       <c r="F180" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="G180" t="s">
         <v>760</v>
@@ -7898,7 +7874,7 @@
         <v>761</v>
       </c>
       <c r="C181" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="D181" t="s">
         <v>762</v>
@@ -7921,7 +7897,7 @@
         <v>765</v>
       </c>
       <c r="C182" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D182" t="s">
         <v>766</v>
@@ -7930,7 +7906,7 @@
         <v>767</v>
       </c>
       <c r="F182" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G182" t="s">
         <v>768</v>
@@ -7944,19 +7920,19 @@
         <v>769</v>
       </c>
       <c r="C183" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="D183" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="E183" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="F183" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G183" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -7964,22 +7940,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C184" t="s">
         <v>26</v>
       </c>
       <c r="D184" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="E184" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="F184" t="s">
         <v>12</v>
       </c>
       <c r="G184" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -7987,22 +7963,22 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C185" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D185" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E185" t="s">
-        <v>775</v>
+        <v>126</v>
       </c>
       <c r="F185" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G185" t="s">
-        <v>776</v>
+        <v>160</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -8010,22 +7986,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C186" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D186" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E186" t="s">
-        <v>775</v>
+        <v>126</v>
       </c>
       <c r="F186" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G186" t="s">
-        <v>776</v>
+        <v>160</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -8033,22 +8009,22 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C187" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="E187" t="s">
-        <v>126</v>
+        <v>607</v>
       </c>
       <c r="F187" t="s">
         <v>7</v>
       </c>
       <c r="G187" t="s">
-        <v>160</v>
+        <v>776</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -8056,22 +8032,22 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C188" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D188" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="E188" t="s">
-        <v>126</v>
+        <v>607</v>
       </c>
       <c r="F188" t="s">
         <v>7</v>
       </c>
       <c r="G188" t="s">
-        <v>160</v>
+        <v>776</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -8079,22 +8055,22 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C189" t="s">
         <v>14</v>
       </c>
       <c r="D189" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="E189" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="F189" t="s">
         <v>7</v>
       </c>
       <c r="G189" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -8102,22 +8078,22 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="C190" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D190" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E190" t="s">
-        <v>615</v>
+        <v>781</v>
       </c>
       <c r="F190" t="s">
-        <v>7</v>
+        <v>782</v>
       </c>
       <c r="G190" t="s">
-        <v>784</v>
+        <v>84</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -8125,22 +8101,22 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>783</v>
+      </c>
+      <c r="C191" t="s">
+        <v>35</v>
+      </c>
+      <c r="D191" t="s">
+        <v>784</v>
+      </c>
+      <c r="E191" t="s">
+        <v>785</v>
+      </c>
+      <c r="F191" t="s">
         <v>786</v>
       </c>
-      <c r="C191" t="s">
-        <v>14</v>
-      </c>
-      <c r="D191" t="s">
-        <v>783</v>
-      </c>
-      <c r="E191" t="s">
-        <v>615</v>
-      </c>
-      <c r="F191" t="s">
-        <v>7</v>
-      </c>
       <c r="G191" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -8148,22 +8124,22 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C192" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="D192" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E192" t="s">
-        <v>789</v>
+        <v>162</v>
       </c>
       <c r="F192" t="s">
+        <v>7</v>
+      </c>
+      <c r="G192" t="s">
         <v>790</v>
-      </c>
-      <c r="G192" t="s">
-        <v>84</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -8174,19 +8150,19 @@
         <v>791</v>
       </c>
       <c r="C193" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D193" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E193" t="s">
-        <v>793</v>
+        <v>162</v>
       </c>
       <c r="F193" t="s">
-        <v>794</v>
+        <v>7</v>
       </c>
       <c r="G193" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -8194,22 +8170,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C194" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="E194" t="s">
-        <v>162</v>
+        <v>670</v>
       </c>
       <c r="F194" t="s">
-        <v>7</v>
+        <v>671</v>
       </c>
       <c r="G194" t="s">
-        <v>798</v>
+        <v>71</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -8217,22 +8193,22 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C195" t="s">
-        <v>53</v>
+        <v>639</v>
       </c>
       <c r="D195" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E195" t="s">
-        <v>162</v>
+        <v>796</v>
       </c>
       <c r="F195" t="s">
         <v>7</v>
       </c>
       <c r="G195" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -8240,22 +8216,22 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C196" t="s">
-        <v>18</v>
+        <v>639</v>
       </c>
       <c r="D196" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="E196" t="s">
-        <v>678</v>
+        <v>796</v>
       </c>
       <c r="F196" t="s">
-        <v>679</v>
+        <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>71</v>
+        <v>797</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -8263,22 +8239,22 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C197" t="s">
-        <v>647</v>
+        <v>35</v>
       </c>
       <c r="D197" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="E197" t="s">
-        <v>804</v>
+        <v>82</v>
       </c>
       <c r="F197" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="G197" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -8286,22 +8262,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C198" t="s">
-        <v>647</v>
+        <v>61</v>
       </c>
       <c r="D198" t="s">
         <v>803</v>
       </c>
       <c r="E198" t="s">
+        <v>78</v>
+      </c>
+      <c r="F198" t="s">
+        <v>79</v>
+      </c>
+      <c r="G198" t="s">
         <v>804</v>
-      </c>
-      <c r="F198" t="s">
-        <v>7</v>
-      </c>
-      <c r="G198" t="s">
-        <v>805</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -8309,22 +8285,22 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C199" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D199" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="E199" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F199" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G199" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -8332,22 +8308,22 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C200" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D200" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E200" t="s">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="F200" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="G200" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -8355,19 +8331,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C201" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="D201" t="s">
+        <v>810</v>
+      </c>
+      <c r="E201" t="s">
         <v>811</v>
       </c>
-      <c r="E201" t="s">
-        <v>78</v>
-      </c>
       <c r="F201" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="G201" t="s">
         <v>812</v>
@@ -8378,22 +8354,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C202" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="D202" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="E202" t="s">
-        <v>158</v>
+        <v>811</v>
       </c>
       <c r="F202" t="s">
         <v>7</v>
       </c>
       <c r="G202" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -8401,22 +8377,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>814</v>
+      </c>
+      <c r="C203" t="s">
+        <v>49</v>
+      </c>
+      <c r="D203" t="s">
+        <v>815</v>
+      </c>
+      <c r="E203" t="s">
+        <v>816</v>
+      </c>
+      <c r="F203" t="s">
         <v>817</v>
       </c>
-      <c r="C203" t="s">
-        <v>120</v>
-      </c>
-      <c r="D203" t="s">
+      <c r="G203" t="s">
         <v>818</v>
-      </c>
-      <c r="E203" t="s">
-        <v>819</v>
-      </c>
-      <c r="F203" t="s">
-        <v>7</v>
-      </c>
-      <c r="G203" t="s">
-        <v>820</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -8424,22 +8400,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C204" t="s">
-        <v>120</v>
+        <v>547</v>
       </c>
       <c r="D204" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E204" t="s">
-        <v>819</v>
+        <v>55</v>
       </c>
       <c r="F204" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="G204" t="s">
-        <v>820</v>
+        <v>138</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -8447,22 +8423,22 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C205" t="s">
-        <v>49</v>
+        <v>547</v>
       </c>
       <c r="D205" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E205" t="s">
-        <v>824</v>
+        <v>55</v>
       </c>
       <c r="F205" t="s">
-        <v>825</v>
+        <v>56</v>
       </c>
       <c r="G205" t="s">
-        <v>826</v>
+        <v>138</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -8470,13 +8446,13 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C206" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="D206" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="E206" t="s">
         <v>55</v>
@@ -8493,22 +8469,22 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="C207" t="s">
-        <v>555</v>
+        <v>43</v>
       </c>
       <c r="D207" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E207" t="s">
-        <v>55</v>
+        <v>825</v>
       </c>
       <c r="F207" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -8516,22 +8492,22 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
+        <v>826</v>
+      </c>
+      <c r="C208" t="s">
+        <v>104</v>
+      </c>
+      <c r="D208" t="s">
+        <v>827</v>
+      </c>
+      <c r="E208" t="s">
+        <v>828</v>
+      </c>
+      <c r="F208" t="s">
+        <v>829</v>
+      </c>
+      <c r="G208" t="s">
         <v>830</v>
-      </c>
-      <c r="C208" t="s">
-        <v>555</v>
-      </c>
-      <c r="D208" t="s">
-        <v>828</v>
-      </c>
-      <c r="E208" t="s">
-        <v>55</v>
-      </c>
-      <c r="F208" t="s">
-        <v>56</v>
-      </c>
-      <c r="G208" t="s">
-        <v>138</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -8542,19 +8518,19 @@
         <v>831</v>
       </c>
       <c r="C209" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D209" t="s">
         <v>832</v>
       </c>
       <c r="E209" t="s">
+        <v>46</v>
+      </c>
+      <c r="F209" t="s">
+        <v>47</v>
+      </c>
+      <c r="G209" t="s">
         <v>833</v>
-      </c>
-      <c r="F209" t="s">
-        <v>7</v>
-      </c>
-      <c r="G209" t="s">
-        <v>152</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -8565,19 +8541,19 @@
         <v>834</v>
       </c>
       <c r="C210" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="D210" t="s">
         <v>835</v>
       </c>
       <c r="E210" t="s">
+        <v>181</v>
+      </c>
+      <c r="F210" t="s">
+        <v>7</v>
+      </c>
+      <c r="G210" t="s">
         <v>836</v>
-      </c>
-      <c r="F210" t="s">
-        <v>837</v>
-      </c>
-      <c r="G210" t="s">
-        <v>838</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -8585,22 +8561,22 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
+        <v>837</v>
+      </c>
+      <c r="C211" t="s">
+        <v>60</v>
+      </c>
+      <c r="D211" t="s">
+        <v>838</v>
+      </c>
+      <c r="E211" t="s">
+        <v>169</v>
+      </c>
+      <c r="F211" t="s">
+        <v>7</v>
+      </c>
+      <c r="G211" t="s">
         <v>839</v>
-      </c>
-      <c r="C211" t="s">
-        <v>61</v>
-      </c>
-      <c r="D211" t="s">
-        <v>840</v>
-      </c>
-      <c r="E211" t="s">
-        <v>46</v>
-      </c>
-      <c r="F211" t="s">
-        <v>47</v>
-      </c>
-      <c r="G211" t="s">
-        <v>841</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -8608,22 +8584,22 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
+        <v>840</v>
+      </c>
+      <c r="C212" t="s">
+        <v>35</v>
+      </c>
+      <c r="D212" t="s">
+        <v>841</v>
+      </c>
+      <c r="E212" t="s">
+        <v>82</v>
+      </c>
+      <c r="F212" t="s">
+        <v>83</v>
+      </c>
+      <c r="G212" t="s">
         <v>842</v>
-      </c>
-      <c r="C212" t="s">
-        <v>23</v>
-      </c>
-      <c r="D212" t="s">
-        <v>843</v>
-      </c>
-      <c r="E212" t="s">
-        <v>181</v>
-      </c>
-      <c r="F212" t="s">
-        <v>7</v>
-      </c>
-      <c r="G212" t="s">
-        <v>844</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -8631,22 +8607,22 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C213" t="s">
         <v>60</v>
       </c>
       <c r="D213" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E213" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="F213" t="s">
         <v>7</v>
       </c>
       <c r="G213" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -8654,22 +8630,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C214" t="s">
         <v>35</v>
       </c>
       <c r="D214" t="s">
+        <v>847</v>
+      </c>
+      <c r="E214" t="s">
+        <v>848</v>
+      </c>
+      <c r="F214" t="s">
         <v>849</v>
       </c>
-      <c r="E214" t="s">
-        <v>82</v>
-      </c>
-      <c r="F214" t="s">
-        <v>83</v>
-      </c>
       <c r="G214" t="s">
-        <v>850</v>
+        <v>15</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -8677,22 +8653,22 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
+        <v>850</v>
+      </c>
+      <c r="C215" t="s">
+        <v>537</v>
+      </c>
+      <c r="D215" t="s">
         <v>851</v>
       </c>
-      <c r="C215" t="s">
-        <v>60</v>
-      </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>852</v>
       </c>
-      <c r="E215" t="s">
-        <v>59</v>
-      </c>
       <c r="F215" t="s">
-        <v>7</v>
+        <v>853</v>
       </c>
       <c r="G215" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -8700,22 +8676,22 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C216" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D216" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E216" t="s">
-        <v>856</v>
+        <v>41</v>
       </c>
       <c r="F216" t="s">
+        <v>42</v>
+      </c>
+      <c r="G216" t="s">
         <v>857</v>
-      </c>
-      <c r="G216" t="s">
-        <v>15</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -8726,7 +8702,7 @@
         <v>858</v>
       </c>
       <c r="C217" t="s">
-        <v>545</v>
+        <v>9</v>
       </c>
       <c r="D217" t="s">
         <v>859</v>
@@ -8749,19 +8725,19 @@
         <v>863</v>
       </c>
       <c r="C218" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D218" t="s">
         <v>864</v>
       </c>
       <c r="E218" t="s">
-        <v>41</v>
+        <v>865</v>
       </c>
       <c r="F218" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G218" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -8769,22 +8745,22 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>867</v>
+      </c>
+      <c r="C219" t="s">
+        <v>54</v>
+      </c>
+      <c r="D219" t="s">
+        <v>864</v>
+      </c>
+      <c r="E219" t="s">
+        <v>865</v>
+      </c>
+      <c r="F219" t="s">
+        <v>7</v>
+      </c>
+      <c r="G219" t="s">
         <v>866</v>
-      </c>
-      <c r="C219" t="s">
-        <v>9</v>
-      </c>
-      <c r="D219" t="s">
-        <v>867</v>
-      </c>
-      <c r="E219" t="s">
-        <v>868</v>
-      </c>
-      <c r="F219" t="s">
-        <v>869</v>
-      </c>
-      <c r="G219" t="s">
-        <v>870</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -8792,22 +8768,22 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="C220" t="s">
-        <v>54</v>
+        <v>639</v>
       </c>
       <c r="D220" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="E220" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F220" t="s">
         <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -8815,22 +8791,22 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C221" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E221" t="s">
-        <v>873</v>
+        <v>402</v>
       </c>
       <c r="F221" t="s">
-        <v>7</v>
+        <v>403</v>
       </c>
       <c r="G221" t="s">
-        <v>874</v>
+        <v>13</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -8838,22 +8814,22 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C222" t="s">
-        <v>647</v>
+        <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="E222" t="s">
-        <v>878</v>
+        <v>402</v>
       </c>
       <c r="F222" t="s">
-        <v>7</v>
+        <v>403</v>
       </c>
       <c r="G222" t="s">
-        <v>879</v>
+        <v>13</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -8861,22 +8837,22 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C223" t="s">
-        <v>9</v>
+        <v>876</v>
       </c>
       <c r="D223" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="E223" t="s">
-        <v>406</v>
+        <v>76</v>
       </c>
       <c r="F223" t="s">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="G223" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -8884,22 +8860,22 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C224" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D224" t="s">
+        <v>879</v>
+      </c>
+      <c r="E224" t="s">
+        <v>880</v>
+      </c>
+      <c r="F224" t="s">
+        <v>7</v>
+      </c>
+      <c r="G224" t="s">
         <v>881</v>
-      </c>
-      <c r="E224" t="s">
-        <v>406</v>
-      </c>
-      <c r="F224" t="s">
-        <v>407</v>
-      </c>
-      <c r="G224" t="s">
-        <v>13</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -8907,22 +8883,22 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
+        <v>882</v>
+      </c>
+      <c r="C225" t="s">
+        <v>639</v>
+      </c>
+      <c r="D225" t="s">
         <v>883</v>
       </c>
-      <c r="C225" t="s">
+      <c r="E225" t="s">
+        <v>81</v>
+      </c>
+      <c r="F225" t="s">
+        <v>7</v>
+      </c>
+      <c r="G225" t="s">
         <v>884</v>
-      </c>
-      <c r="D225" t="s">
-        <v>885</v>
-      </c>
-      <c r="E225" t="s">
-        <v>76</v>
-      </c>
-      <c r="F225" t="s">
-        <v>77</v>
-      </c>
-      <c r="G225" t="s">
-        <v>33</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -8930,22 +8906,22 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>886</v>
+        <v>174</v>
       </c>
       <c r="C226" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="D226" t="s">
-        <v>887</v>
+        <v>175</v>
       </c>
       <c r="E226" t="s">
-        <v>888</v>
+        <v>176</v>
       </c>
       <c r="F226" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="G226" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -8953,22 +8929,22 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="C227" t="s">
-        <v>647</v>
+        <v>35</v>
       </c>
       <c r="D227" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="E227" t="s">
-        <v>81</v>
+        <v>887</v>
       </c>
       <c r="F227" t="s">
         <v>7</v>
       </c>
       <c r="G227" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -8976,22 +8952,22 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>174</v>
+        <v>889</v>
       </c>
       <c r="C228" t="s">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="D228" t="s">
-        <v>175</v>
+        <v>890</v>
       </c>
       <c r="E228" t="s">
-        <v>176</v>
+        <v>891</v>
       </c>
       <c r="F228" t="s">
-        <v>177</v>
+        <v>892</v>
       </c>
       <c r="G228" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -9002,7 +8978,7 @@
         <v>893</v>
       </c>
       <c r="C229" t="s">
-        <v>35</v>
+        <v>537</v>
       </c>
       <c r="D229" t="s">
         <v>894</v>
@@ -9011,10 +8987,10 @@
         <v>895</v>
       </c>
       <c r="F229" t="s">
-        <v>7</v>
+        <v>896</v>
       </c>
       <c r="G229" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -9022,22 +8998,22 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C230" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="D230" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E230" t="s">
-        <v>899</v>
+        <v>132</v>
       </c>
       <c r="F230" t="s">
+        <v>133</v>
+      </c>
+      <c r="G230" t="s">
         <v>900</v>
-      </c>
-      <c r="G230" t="s">
-        <v>119</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -9048,19 +9024,19 @@
         <v>901</v>
       </c>
       <c r="C231" t="s">
-        <v>545</v>
+        <v>104</v>
       </c>
       <c r="D231" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="E231" t="s">
-        <v>903</v>
+        <v>132</v>
       </c>
       <c r="F231" t="s">
-        <v>904</v>
+        <v>133</v>
       </c>
       <c r="G231" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -9068,22 +9044,22 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C232" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="D232" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E232" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="F232" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="G232" t="s">
-        <v>908</v>
+        <v>62</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -9091,22 +9067,22 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="C233" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D233" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E233" t="s">
-        <v>132</v>
+        <v>339</v>
       </c>
       <c r="F233" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="G233" t="s">
-        <v>908</v>
+        <v>164</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -9114,22 +9090,22 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C234" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D234" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E234" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="F234" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="G234" t="s">
-        <v>62</v>
+        <v>908</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -9137,22 +9113,22 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
+        <v>909</v>
+      </c>
+      <c r="C235" t="s">
+        <v>23</v>
+      </c>
+      <c r="D235" t="s">
+        <v>910</v>
+      </c>
+      <c r="E235" t="s">
+        <v>911</v>
+      </c>
+      <c r="F235" t="s">
+        <v>7</v>
+      </c>
+      <c r="G235" t="s">
         <v>912</v>
-      </c>
-      <c r="C235" t="s">
-        <v>89</v>
-      </c>
-      <c r="D235" t="s">
-        <v>913</v>
-      </c>
-      <c r="E235" t="s">
-        <v>339</v>
-      </c>
-      <c r="F235" t="s">
-        <v>57</v>
-      </c>
-      <c r="G235" t="s">
-        <v>164</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -9160,22 +9136,22 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
+        <v>913</v>
+      </c>
+      <c r="C236" t="s">
+        <v>61</v>
+      </c>
+      <c r="D236" t="s">
         <v>914</v>
       </c>
-      <c r="C236" t="s">
-        <v>32</v>
-      </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
+        <v>111</v>
+      </c>
+      <c r="F236" t="s">
+        <v>7</v>
+      </c>
+      <c r="G236" t="s">
         <v>915</v>
-      </c>
-      <c r="E236" t="s">
-        <v>101</v>
-      </c>
-      <c r="F236" t="s">
-        <v>102</v>
-      </c>
-      <c r="G236" t="s">
-        <v>916</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -9183,22 +9159,22 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
+        <v>916</v>
+      </c>
+      <c r="C237" t="s">
+        <v>61</v>
+      </c>
+      <c r="D237" t="s">
         <v>917</v>
       </c>
-      <c r="C237" t="s">
-        <v>23</v>
-      </c>
-      <c r="D237" t="s">
-        <v>918</v>
-      </c>
       <c r="E237" t="s">
-        <v>919</v>
+        <v>37</v>
       </c>
       <c r="F237" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G237" t="s">
-        <v>920</v>
+        <v>29</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -9206,22 +9182,22 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="C238" t="s">
         <v>61</v>
       </c>
       <c r="D238" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="E238" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="F238" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G238" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -9229,22 +9205,22 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C239" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="D239" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="E239" t="s">
-        <v>37</v>
+        <v>483</v>
       </c>
       <c r="F239" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G239" t="s">
-        <v>29</v>
+        <v>923</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -9252,22 +9228,22 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>924</v>
+      </c>
+      <c r="C240" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" t="s">
+        <v>925</v>
+      </c>
+      <c r="E240" t="s">
+        <v>170</v>
+      </c>
+      <c r="F240" t="s">
+        <v>7</v>
+      </c>
+      <c r="G240" t="s">
         <v>926</v>
-      </c>
-      <c r="C240" t="s">
-        <v>61</v>
-      </c>
-      <c r="D240" t="s">
-        <v>927</v>
-      </c>
-      <c r="E240" t="s">
-        <v>46</v>
-      </c>
-      <c r="F240" t="s">
-        <v>47</v>
-      </c>
-      <c r="G240" t="s">
-        <v>928</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -9275,19 +9251,19 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
+        <v>927</v>
+      </c>
+      <c r="C241" t="s">
+        <v>354</v>
+      </c>
+      <c r="D241" t="s">
+        <v>928</v>
+      </c>
+      <c r="E241" t="s">
         <v>929</v>
       </c>
-      <c r="C241" t="s">
-        <v>19</v>
-      </c>
-      <c r="D241" t="s">
+      <c r="F241" t="s">
         <v>930</v>
-      </c>
-      <c r="E241" t="s">
-        <v>487</v>
-      </c>
-      <c r="F241" t="s">
-        <v>20</v>
       </c>
       <c r="G241" t="s">
         <v>931</v>
@@ -9301,13 +9277,13 @@
         <v>932</v>
       </c>
       <c r="C242" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D242" t="s">
         <v>933</v>
       </c>
       <c r="E242" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="F242" t="s">
         <v>7</v>
@@ -9324,19 +9300,19 @@
         <v>935</v>
       </c>
       <c r="C243" t="s">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="D243" t="s">
         <v>936</v>
       </c>
       <c r="E243" t="s">
+        <v>763</v>
+      </c>
+      <c r="F243" t="s">
+        <v>7</v>
+      </c>
+      <c r="G243" t="s">
         <v>937</v>
-      </c>
-      <c r="F243" t="s">
-        <v>938</v>
-      </c>
-      <c r="G243" t="s">
-        <v>939</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -9344,22 +9320,22 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C244" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D244" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="E244" t="s">
-        <v>126</v>
+        <v>763</v>
       </c>
       <c r="F244" t="s">
         <v>7</v>
       </c>
       <c r="G244" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -9367,22 +9343,22 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C245" t="s">
-        <v>120</v>
+        <v>876</v>
       </c>
       <c r="D245" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="E245" t="s">
-        <v>771</v>
+        <v>941</v>
       </c>
       <c r="F245" t="s">
-        <v>7</v>
+        <v>942</v>
       </c>
       <c r="G245" t="s">
-        <v>945</v>
+        <v>268</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -9390,22 +9366,22 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C246" t="s">
-        <v>120</v>
+        <v>358</v>
       </c>
       <c r="D246" t="s">
         <v>944</v>
       </c>
       <c r="E246" t="s">
-        <v>771</v>
+        <v>945</v>
       </c>
       <c r="F246" t="s">
-        <v>7</v>
+        <v>946</v>
       </c>
       <c r="G246" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -9413,22 +9389,22 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C247" t="s">
-        <v>884</v>
+        <v>21</v>
       </c>
       <c r="D247" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E247" t="s">
-        <v>949</v>
+        <v>97</v>
       </c>
       <c r="F247" t="s">
+        <v>98</v>
+      </c>
+      <c r="G247" t="s">
         <v>950</v>
-      </c>
-      <c r="G247" t="s">
-        <v>268</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -9439,19 +9415,19 @@
         <v>951</v>
       </c>
       <c r="C248" t="s">
-        <v>358</v>
+        <v>128</v>
       </c>
       <c r="D248" t="s">
         <v>952</v>
       </c>
       <c r="E248" t="s">
+        <v>39</v>
+      </c>
+      <c r="F248" t="s">
+        <v>40</v>
+      </c>
+      <c r="G248" t="s">
         <v>953</v>
-      </c>
-      <c r="F248" t="s">
-        <v>954</v>
-      </c>
-      <c r="G248" t="s">
-        <v>955</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -9459,22 +9435,22 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C249" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="D249" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="E249" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="F249" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="G249" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -9482,22 +9458,22 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C250" t="s">
-        <v>128</v>
+        <v>639</v>
       </c>
       <c r="D250" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E250" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="F250" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G250" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -9505,22 +9481,22 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C251" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="D251" t="s">
+        <v>959</v>
+      </c>
+      <c r="E251" t="s">
+        <v>887</v>
+      </c>
+      <c r="F251" t="s">
+        <v>7</v>
+      </c>
+      <c r="G251" t="s">
         <v>960</v>
-      </c>
-      <c r="E251" t="s">
-        <v>39</v>
-      </c>
-      <c r="F251" t="s">
-        <v>40</v>
-      </c>
-      <c r="G251" t="s">
-        <v>961</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -9528,22 +9504,22 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C252" t="s">
-        <v>647</v>
+        <v>92</v>
       </c>
       <c r="D252" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E252" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F252" t="s">
         <v>7</v>
       </c>
       <c r="G252" t="s">
-        <v>965</v>
+        <v>730</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -9551,22 +9527,22 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C253" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D253" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="E253" t="s">
-        <v>895</v>
+        <v>525</v>
       </c>
       <c r="F253" t="s">
         <v>7</v>
       </c>
       <c r="G253" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -9574,22 +9550,22 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C254" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="D254" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="E254" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="F254" t="s">
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>738</v>
+        <v>968</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -9597,22 +9573,22 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
+        <v>969</v>
+      </c>
+      <c r="C255" t="s">
+        <v>24</v>
+      </c>
+      <c r="D255" t="s">
+        <v>970</v>
+      </c>
+      <c r="E255" t="s">
+        <v>139</v>
+      </c>
+      <c r="F255" t="s">
+        <v>25</v>
+      </c>
+      <c r="G255" t="s">
         <v>971</v>
-      </c>
-      <c r="C255" t="s">
-        <v>43</v>
-      </c>
-      <c r="D255" t="s">
-        <v>972</v>
-      </c>
-      <c r="E255" t="s">
-        <v>533</v>
-      </c>
-      <c r="F255" t="s">
-        <v>7</v>
-      </c>
-      <c r="G255" t="s">
-        <v>973</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -9620,19 +9596,19 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
+        <v>972</v>
+      </c>
+      <c r="C256" t="s">
+        <v>34</v>
+      </c>
+      <c r="D256" t="s">
+        <v>973</v>
+      </c>
+      <c r="E256" t="s">
         <v>974</v>
       </c>
-      <c r="C256" t="s">
-        <v>60</v>
-      </c>
-      <c r="D256" t="s">
+      <c r="F256" t="s">
         <v>975</v>
-      </c>
-      <c r="E256" t="s">
-        <v>115</v>
-      </c>
-      <c r="F256" t="s">
-        <v>7</v>
       </c>
       <c r="G256" t="s">
         <v>976</v>
@@ -9646,19 +9622,19 @@
         <v>977</v>
       </c>
       <c r="C257" t="s">
-        <v>24</v>
+        <v>385</v>
       </c>
       <c r="D257" t="s">
         <v>978</v>
       </c>
       <c r="E257" t="s">
-        <v>139</v>
+        <v>979</v>
       </c>
       <c r="F257" t="s">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="G257" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -9666,19 +9642,19 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C258" t="s">
-        <v>34</v>
+        <v>639</v>
       </c>
       <c r="D258" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="E258" t="s">
-        <v>982</v>
+        <v>81</v>
       </c>
       <c r="F258" t="s">
-        <v>983</v>
+        <v>7</v>
       </c>
       <c r="G258" t="s">
         <v>984</v>
@@ -9692,7 +9668,7 @@
         <v>985</v>
       </c>
       <c r="C259" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D259" t="s">
         <v>986</v>
@@ -9715,19 +9691,19 @@
         <v>990</v>
       </c>
       <c r="C260" t="s">
-        <v>647</v>
+        <v>385</v>
       </c>
       <c r="D260" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="E260" t="s">
-        <v>81</v>
+        <v>987</v>
       </c>
       <c r="F260" t="s">
-        <v>7</v>
+        <v>988</v>
       </c>
       <c r="G260" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -9735,22 +9711,22 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C261" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D261" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="E261" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="F261" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="G261" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -9758,22 +9734,22 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C262" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D262" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="E262" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="F262" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="G262" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -9781,22 +9757,22 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="C263" t="s">
-        <v>389</v>
+        <v>17</v>
       </c>
       <c r="D263" t="s">
         <v>994</v>
       </c>
       <c r="E263" t="s">
+        <v>329</v>
+      </c>
+      <c r="F263" t="s">
+        <v>330</v>
+      </c>
+      <c r="G263" t="s">
         <v>995</v>
-      </c>
-      <c r="F263" t="s">
-        <v>996</v>
-      </c>
-      <c r="G263" t="s">
-        <v>997</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -9804,68 +9780,68 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C264" t="s">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="D264" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E264" t="s">
-        <v>995</v>
+        <v>183</v>
       </c>
       <c r="F264" t="s">
-        <v>996</v>
+        <v>12</v>
       </c>
       <c r="G264" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H264" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
+        <v>999</v>
+      </c>
+      <c r="C265" t="s">
+        <v>354</v>
+      </c>
+      <c r="D265" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E265" t="s">
+        <v>107</v>
+      </c>
+      <c r="F265" t="s">
+        <v>108</v>
+      </c>
+      <c r="G265" t="s">
         <v>1001</v>
       </c>
-      <c r="C265" t="s">
-        <v>17</v>
-      </c>
-      <c r="D265" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E265" t="s">
-        <v>329</v>
-      </c>
-      <c r="F265" t="s">
-        <v>330</v>
-      </c>
-      <c r="G265" t="s">
-        <v>1003</v>
-      </c>
       <c r="H265" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C266" t="s">
-        <v>349</v>
+        <v>35</v>
       </c>
       <c r="D266" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E266" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="F266" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G266" t="s">
-        <v>1006</v>
+        <v>453</v>
       </c>
       <c r="H266" t="s">
         <v>51</v>
@@ -9873,22 +9849,22 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="C267" t="s">
         <v>354</v>
       </c>
       <c r="D267" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E267" t="s">
-        <v>107</v>
+        <v>929</v>
       </c>
       <c r="F267" t="s">
-        <v>108</v>
+        <v>930</v>
       </c>
       <c r="G267" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="H267" t="s">
         <v>51</v>
@@ -9896,22 +9872,22 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C268" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D268" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E268" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="F268" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="G268" t="s">
-        <v>457</v>
+        <v>1009</v>
       </c>
       <c r="H268" t="s">
         <v>51</v>
@@ -9919,22 +9895,22 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C269" t="s">
         <v>354</v>
       </c>
       <c r="D269" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="E269" t="s">
-        <v>937</v>
+        <v>107</v>
       </c>
       <c r="F269" t="s">
-        <v>938</v>
+        <v>108</v>
       </c>
       <c r="G269" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="H269" t="s">
         <v>51</v>
@@ -9942,22 +9918,22 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C270" t="s">
+        <v>49</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E270" t="s">
         <v>1015</v>
       </c>
-      <c r="C270" t="s">
-        <v>24</v>
-      </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
         <v>1016</v>
       </c>
-      <c r="E270" t="s">
-        <v>139</v>
-      </c>
-      <c r="F270" t="s">
-        <v>25</v>
-      </c>
       <c r="G270" t="s">
-        <v>1017</v>
+        <v>116</v>
       </c>
       <c r="H270" t="s">
         <v>51</v>
@@ -9965,19 +9941,19 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C271" t="s">
         <v>354</v>
       </c>
       <c r="D271" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E271" t="s">
         <v>1019</v>
       </c>
-      <c r="E271" t="s">
-        <v>107</v>
-      </c>
       <c r="F271" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="G271" t="s">
         <v>1020</v>
@@ -9991,7 +9967,7 @@
         <v>1021</v>
       </c>
       <c r="C272" t="s">
-        <v>49</v>
+        <v>354</v>
       </c>
       <c r="D272" t="s">
         <v>1022</v>
@@ -10000,10 +9976,10 @@
         <v>1023</v>
       </c>
       <c r="F272" t="s">
+        <v>7</v>
+      </c>
+      <c r="G272" t="s">
         <v>1024</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
       </c>
       <c r="H272" t="s">
         <v>51</v>
@@ -10017,16 +9993,16 @@
         <v>354</v>
       </c>
       <c r="D273" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="E273" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F273" t="s">
         <v>7</v>
       </c>
       <c r="G273" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="H273" t="s">
         <v>51</v>
@@ -10034,22 +10010,22 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C274" t="s">
-        <v>354</v>
+        <v>58</v>
       </c>
       <c r="D274" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E274" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="F274" t="s">
         <v>7</v>
       </c>
       <c r="G274" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="H274" t="s">
         <v>51</v>
@@ -10057,22 +10033,22 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C275" t="s">
+        <v>24</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E275" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F275" t="s">
+        <v>25</v>
+      </c>
+      <c r="G275" t="s">
         <v>1033</v>
-      </c>
-      <c r="C275" t="s">
-        <v>354</v>
-      </c>
-      <c r="D275" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E275" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F275" t="s">
-        <v>7</v>
-      </c>
-      <c r="G275" t="s">
-        <v>1032</v>
       </c>
       <c r="H275" t="s">
         <v>51</v>
@@ -10083,7 +10059,7 @@
         <v>1034</v>
       </c>
       <c r="C276" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D276" t="s">
         <v>1035</v>
@@ -10092,10 +10068,10 @@
         <v>1036</v>
       </c>
       <c r="F276" t="s">
-        <v>7</v>
+        <v>1037</v>
       </c>
       <c r="G276" t="s">
-        <v>1037</v>
+        <v>31</v>
       </c>
       <c r="H276" t="s">
         <v>51</v>
@@ -10106,19 +10082,19 @@
         <v>1038</v>
       </c>
       <c r="C277" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D277" t="s">
         <v>1039</v>
       </c>
       <c r="E277" t="s">
+        <v>767</v>
+      </c>
+      <c r="F277" t="s">
+        <v>12</v>
+      </c>
+      <c r="G277" t="s">
         <v>1040</v>
-      </c>
-      <c r="F277" t="s">
-        <v>25</v>
-      </c>
-      <c r="G277" t="s">
-        <v>1041</v>
       </c>
       <c r="H277" t="s">
         <v>51</v>
@@ -10126,22 +10102,22 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C278" t="s">
+        <v>23</v>
+      </c>
+      <c r="D278" t="s">
         <v>1042</v>
       </c>
-      <c r="C278" t="s">
-        <v>21</v>
-      </c>
-      <c r="D278" t="s">
+      <c r="E278" t="s">
+        <v>109</v>
+      </c>
+      <c r="F278" t="s">
+        <v>110</v>
+      </c>
+      <c r="G278" t="s">
         <v>1043</v>
-      </c>
-      <c r="E278" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F278" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G278" t="s">
-        <v>31</v>
       </c>
       <c r="H278" t="s">
         <v>51</v>
@@ -10149,22 +10125,22 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C279" t="s">
+        <v>537</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E279" t="s">
+        <v>895</v>
+      </c>
+      <c r="F279" t="s">
+        <v>896</v>
+      </c>
+      <c r="G279" t="s">
         <v>1046</v>
-      </c>
-      <c r="C279" t="s">
-        <v>26</v>
-      </c>
-      <c r="D279" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E279" t="s">
-        <v>775</v>
-      </c>
-      <c r="F279" t="s">
-        <v>12</v>
-      </c>
-      <c r="G279" t="s">
-        <v>1048</v>
       </c>
       <c r="H279" t="s">
         <v>51</v>
@@ -10172,22 +10148,22 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C280" t="s">
+        <v>26</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E280" t="s">
         <v>1049</v>
       </c>
-      <c r="C280" t="s">
-        <v>23</v>
-      </c>
-      <c r="D280" t="s">
+      <c r="F280" t="s">
+        <v>12</v>
+      </c>
+      <c r="G280" t="s">
         <v>1050</v>
-      </c>
-      <c r="E280" t="s">
-        <v>109</v>
-      </c>
-      <c r="F280" t="s">
-        <v>110</v>
-      </c>
-      <c r="G280" t="s">
-        <v>1051</v>
       </c>
       <c r="H280" t="s">
         <v>51</v>
@@ -10195,22 +10171,22 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C281" t="s">
+        <v>24</v>
+      </c>
+      <c r="D281" t="s">
         <v>1052</v>
       </c>
-      <c r="C281" t="s">
-        <v>545</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="E281" t="s">
+        <v>99</v>
+      </c>
+      <c r="F281" t="s">
+        <v>100</v>
+      </c>
+      <c r="G281" t="s">
         <v>1053</v>
-      </c>
-      <c r="E281" t="s">
-        <v>903</v>
-      </c>
-      <c r="F281" t="s">
-        <v>904</v>
-      </c>
-      <c r="G281" t="s">
-        <v>1054</v>
       </c>
       <c r="H281" t="s">
         <v>51</v>
@@ -10218,22 +10194,22 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C282" t="s">
+        <v>35</v>
+      </c>
+      <c r="D282" t="s">
         <v>1055</v>
       </c>
-      <c r="C282" t="s">
-        <v>26</v>
-      </c>
-      <c r="D282" t="s">
+      <c r="E282" t="s">
+        <v>82</v>
+      </c>
+      <c r="F282" t="s">
+        <v>83</v>
+      </c>
+      <c r="G282" t="s">
         <v>1056</v>
-      </c>
-      <c r="E282" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F282" t="s">
-        <v>12</v>
-      </c>
-      <c r="G282" t="s">
-        <v>1058</v>
       </c>
       <c r="H282" t="s">
         <v>51</v>
@@ -10241,22 +10217,22 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C283" t="s">
+        <v>9</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E283" t="s">
+        <v>103</v>
+      </c>
+      <c r="F283" t="s">
+        <v>7</v>
+      </c>
+      <c r="G283" t="s">
         <v>1059</v>
-      </c>
-      <c r="C283" t="s">
-        <v>24</v>
-      </c>
-      <c r="D283" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E283" t="s">
-        <v>99</v>
-      </c>
-      <c r="F283" t="s">
-        <v>100</v>
-      </c>
-      <c r="G283" t="s">
-        <v>1061</v>
       </c>
       <c r="H283" t="s">
         <v>51</v>
@@ -10264,22 +10240,22 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C284" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D284" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="E284" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="F284" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="G284" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="H284" t="s">
         <v>51</v>
@@ -10287,22 +10263,22 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C285" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D285" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="E285" t="s">
-        <v>103</v>
+        <v>1063</v>
       </c>
       <c r="F285" t="s">
         <v>7</v>
       </c>
       <c r="G285" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H285" t="s">
         <v>51</v>
@@ -10310,19 +10286,19 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C286" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D286" t="s">
         <v>1066</v>
       </c>
       <c r="E286" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F286" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="G286" t="s">
         <v>1067</v>
@@ -10333,19 +10309,19 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C287" t="s">
+        <v>21</v>
+      </c>
+      <c r="D287" t="s">
         <v>1069</v>
       </c>
-      <c r="C287" t="s">
-        <v>14</v>
-      </c>
-      <c r="D287" t="s">
+      <c r="E287" t="s">
         <v>1070</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>1071</v>
-      </c>
-      <c r="F287" t="s">
-        <v>7</v>
       </c>
       <c r="G287" t="s">
         <v>1072</v>
@@ -10359,19 +10335,19 @@
         <v>1073</v>
       </c>
       <c r="C288" t="s">
-        <v>14</v>
+        <v>639</v>
       </c>
       <c r="D288" t="s">
         <v>1074</v>
       </c>
       <c r="E288" t="s">
-        <v>95</v>
+        <v>1075</v>
       </c>
       <c r="F288" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="G288" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H288" t="s">
         <v>51</v>
@@ -10379,22 +10355,22 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C289" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D289" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E289" t="s">
-        <v>1078</v>
+        <v>80</v>
       </c>
       <c r="F289" t="s">
-        <v>1079</v>
+        <v>7</v>
       </c>
       <c r="G289" t="s">
-        <v>1080</v>
+        <v>141</v>
       </c>
       <c r="H289" t="s">
         <v>51</v>
@@ -10402,22 +10378,22 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C290" t="s">
+        <v>9</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E290" t="s">
         <v>1081</v>
-      </c>
-      <c r="C290" t="s">
-        <v>647</v>
-      </c>
-      <c r="D290" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E290" t="s">
-        <v>1083</v>
       </c>
       <c r="F290" t="s">
         <v>7</v>
       </c>
       <c r="G290" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H290" t="s">
         <v>51</v>
@@ -10425,22 +10401,22 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C291" t="s">
+        <v>104</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E291" t="s">
+        <v>66</v>
+      </c>
+      <c r="F291" t="s">
+        <v>67</v>
+      </c>
+      <c r="G291" t="s">
         <v>1085</v>
-      </c>
-      <c r="C291" t="s">
-        <v>61</v>
-      </c>
-      <c r="D291" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E291" t="s">
-        <v>80</v>
-      </c>
-      <c r="F291" t="s">
-        <v>7</v>
-      </c>
-      <c r="G291" t="s">
-        <v>141</v>
       </c>
       <c r="H291" t="s">
         <v>51</v>
@@ -10448,91 +10424,91 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C292" t="s">
+        <v>358</v>
+      </c>
+      <c r="D292" t="s">
         <v>1087</v>
       </c>
-      <c r="C292" t="s">
-        <v>9</v>
-      </c>
-      <c r="D292" t="s">
+      <c r="E292" t="s">
+        <v>156</v>
+      </c>
+      <c r="F292" t="s">
+        <v>157</v>
+      </c>
+      <c r="G292" t="s">
+        <v>389</v>
+      </c>
+      <c r="H292" t="s">
         <v>1088</v>
-      </c>
-      <c r="E292" t="s">
-        <v>1089</v>
-      </c>
-      <c r="F292" t="s">
-        <v>7</v>
-      </c>
-      <c r="G292" t="s">
-        <v>1090</v>
-      </c>
-      <c r="H292" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C293" t="s">
+        <v>236</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E293" t="s">
         <v>1091</v>
       </c>
-      <c r="C293" t="s">
-        <v>104</v>
-      </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>1092</v>
       </c>
-      <c r="E293" t="s">
-        <v>66</v>
-      </c>
-      <c r="F293" t="s">
-        <v>67</v>
-      </c>
       <c r="G293" t="s">
-        <v>1093</v>
+        <v>186</v>
       </c>
       <c r="H293" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C294" t="s">
-        <v>358</v>
+        <v>236</v>
       </c>
       <c r="D294" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="E294" t="s">
-        <v>156</v>
+        <v>1091</v>
       </c>
       <c r="F294" t="s">
-        <v>157</v>
+        <v>1092</v>
       </c>
       <c r="G294" t="s">
-        <v>393</v>
+        <v>186</v>
       </c>
       <c r="H294" t="s">
-        <v>1096</v>
+        <v>85</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C295" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="D295" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="E295" t="s">
-        <v>1099</v>
+        <v>66</v>
       </c>
       <c r="F295" t="s">
-        <v>1100</v>
+        <v>67</v>
       </c>
       <c r="G295" t="s">
-        <v>186</v>
+        <v>1096</v>
       </c>
       <c r="H295" t="s">
         <v>85</v>
@@ -10540,22 +10516,22 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="C296" t="s">
-        <v>236</v>
+        <v>92</v>
       </c>
       <c r="D296" t="s">
         <v>1098</v>
       </c>
       <c r="E296" t="s">
+        <v>113</v>
+      </c>
+      <c r="F296" t="s">
+        <v>7</v>
+      </c>
+      <c r="G296" t="s">
         <v>1099</v>
-      </c>
-      <c r="F296" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G296" t="s">
-        <v>186</v>
       </c>
       <c r="H296" t="s">
         <v>85</v>
@@ -10563,136 +10539,90 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C297" t="s">
+        <v>19</v>
+      </c>
+      <c r="D297" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E297" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F297" t="s">
+        <v>20</v>
+      </c>
+      <c r="G297" t="s">
         <v>1102</v>
       </c>
-      <c r="C297" t="s">
-        <v>104</v>
-      </c>
-      <c r="D297" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E297" t="s">
-        <v>66</v>
-      </c>
-      <c r="F297" t="s">
-        <v>67</v>
-      </c>
-      <c r="G297" t="s">
-        <v>1104</v>
-      </c>
       <c r="H297" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C298" t="s">
+        <v>19</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E298" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F298" t="s">
+        <v>20</v>
+      </c>
+      <c r="G298" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H298" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C299" t="s">
+        <v>9</v>
+      </c>
+      <c r="D299" t="s">
         <v>1105</v>
       </c>
-      <c r="C298" t="s">
-        <v>92</v>
-      </c>
-      <c r="D298" t="s">
+      <c r="E299" t="s">
         <v>1106</v>
       </c>
-      <c r="E298" t="s">
-        <v>113</v>
-      </c>
-      <c r="F298" t="s">
-        <v>7</v>
-      </c>
-      <c r="G298" t="s">
+      <c r="F299" t="s">
         <v>1107</v>
       </c>
-      <c r="H298" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
+      <c r="G299" t="s">
         <v>1108</v>
       </c>
-      <c r="C299" t="s">
-        <v>19</v>
-      </c>
-      <c r="D299" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E299" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F299" t="s">
-        <v>20</v>
-      </c>
-      <c r="G299" t="s">
-        <v>1110</v>
-      </c>
       <c r="H299" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C300" t="s">
+        <v>89</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E300" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F300" t="s">
+        <v>57</v>
+      </c>
+      <c r="G300" t="s">
         <v>1111</v>
       </c>
-      <c r="C300" t="s">
-        <v>19</v>
-      </c>
-      <c r="D300" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E300" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F300" t="s">
-        <v>20</v>
-      </c>
-      <c r="G300" t="s">
-        <v>1112</v>
-      </c>
       <c r="H300" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C301" t="s">
-        <v>9</v>
-      </c>
-      <c r="D301" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E301" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F301" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G301" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H301" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C302" t="s">
-        <v>89</v>
-      </c>
-      <c r="D302" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E302" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F302" t="s">
-        <v>57</v>
-      </c>
-      <c r="G302" t="s">
-        <v>1119</v>
-      </c>
-      <c r="H302" t="s">
         <v>8</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EDA1EC-C534-4331-BACF-E857F5249EBA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FB4393-03D8-4DEE-B7C9-58FBAA3A5644}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="600">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -396,24 +396,15 @@
     <t>Kelemen Béla utca</t>
   </si>
   <si>
-    <t>6ab6935b219e3d74bbe3e567</t>
-  </si>
-  <si>
     <t>K-9121</t>
   </si>
   <si>
-    <t>260922-F00014282</t>
-  </si>
-  <si>
     <t>5400</t>
   </si>
   <si>
     <t>MEZŐTÚR</t>
   </si>
   <si>
-    <t>Klapka tábornok utca</t>
-  </si>
-  <si>
     <t>6aba5b84219e3d74bbe413de</t>
   </si>
   <si>
@@ -1786,24 +1777,6 @@
   </si>
   <si>
     <t>Makó utca</t>
-  </si>
-  <si>
-    <t>159995579544811822</t>
-  </si>
-  <si>
-    <t>R437887</t>
-  </si>
-  <si>
-    <t>4731</t>
-  </si>
-  <si>
-    <t>TUNYOGMATOLCS</t>
-  </si>
-  <si>
-    <t>Bocskai u</t>
-  </si>
-  <si>
-    <t>159995579544811839</t>
   </si>
   <si>
     <t>159995579544811723</t>
@@ -2208,7 +2181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -2383,22 +2356,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
         <v>122</v>
       </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
@@ -2406,22 +2379,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" t="s">
         <v>128</v>
       </c>
-      <c r="C9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="G9" t="s">
         <v>129</v>
-      </c>
-      <c r="E9" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" t="s">
-        <v>132</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -2429,22 +2402,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" t="s">
         <v>133</v>
       </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" t="s">
-        <v>129</v>
-      </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -2452,22 +2425,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
         <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="F11" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
@@ -2475,22 +2448,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="G12" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>10</v>
@@ -2498,45 +2471,45 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H14" t="s">
         <v>32</v>
@@ -2544,22 +2517,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G15" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
         <v>32</v>
@@ -2567,22 +2540,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -2590,22 +2563,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="H17" t="s">
         <v>32</v>
@@ -2613,25 +2586,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" t="s">
         <v>123</v>
       </c>
-      <c r="D18" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" t="s">
-        <v>169</v>
-      </c>
       <c r="F18" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
         <v>171</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -2639,19 +2612,19 @@
         <v>172</v>
       </c>
       <c r="C19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" t="s">
-        <v>173</v>
-      </c>
-      <c r="E19" t="s">
-        <v>125</v>
-      </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -2659,22 +2632,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" t="s">
         <v>123</v>
       </c>
-      <c r="D20" t="s">
-        <v>173</v>
-      </c>
-      <c r="E20" t="s">
-        <v>125</v>
-      </c>
       <c r="F20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -2682,22 +2655,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" t="s">
         <v>176</v>
-      </c>
-      <c r="C21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" t="s">
-        <v>174</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -2711,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E22" t="s">
         <v>61</v>
@@ -2720,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -2728,22 +2701,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" t="s">
         <v>180</v>
       </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" t="s">
-        <v>178</v>
-      </c>
-      <c r="E23" t="s">
-        <v>61</v>
-      </c>
       <c r="F23" t="s">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="G23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -2751,22 +2724,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
         <v>56</v>
       </c>
       <c r="D24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" t="s">
         <v>182</v>
-      </c>
-      <c r="E24" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" t="s">
-        <v>184</v>
-      </c>
-      <c r="G24" t="s">
-        <v>185</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -2774,22 +2747,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" t="s">
         <v>186</v>
       </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" t="s">
-        <v>182</v>
-      </c>
       <c r="E25" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F25" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -2797,19 +2770,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" t="s">
         <v>187</v>
       </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
         <v>188</v>
-      </c>
-      <c r="D26" t="s">
-        <v>189</v>
-      </c>
-      <c r="E26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F26" t="s">
-        <v>191</v>
       </c>
       <c r="G26" t="s">
         <v>70</v>
@@ -2820,22 +2793,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" t="s">
         <v>192</v>
-      </c>
-      <c r="C27" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" t="s">
-        <v>189</v>
-      </c>
-      <c r="E27" t="s">
-        <v>190</v>
-      </c>
-      <c r="F27" t="s">
-        <v>191</v>
-      </c>
-      <c r="G27" t="s">
-        <v>70</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -2849,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
         <v>60</v>
@@ -2858,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -2866,13 +2839,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E29" t="s">
         <v>60</v>
@@ -2881,7 +2854,7 @@
         <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -2889,22 +2862,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" t="s">
         <v>197</v>
-      </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" t="s">
-        <v>194</v>
-      </c>
-      <c r="E30" t="s">
-        <v>60</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
       </c>
       <c r="G30" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -2912,22 +2885,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="D31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E31" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>203</v>
       </c>
       <c r="G31" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -2935,22 +2908,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" t="s">
         <v>202</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>203</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" t="s">
         <v>204</v>
-      </c>
-      <c r="E32" t="s">
-        <v>205</v>
-      </c>
-      <c r="F32" t="s">
-        <v>206</v>
-      </c>
-      <c r="G32" t="s">
-        <v>207</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -2958,22 +2931,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" t="s">
         <v>208</v>
       </c>
-      <c r="C33" t="s">
-        <v>203</v>
-      </c>
-      <c r="D33" t="s">
-        <v>204</v>
-      </c>
-      <c r="E33" t="s">
-        <v>205</v>
-      </c>
       <c r="F33" t="s">
-        <v>206</v>
+        <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -2981,22 +2954,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="D34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -3004,22 +2977,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -3027,22 +3000,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E36" t="s">
         <v>217</v>
-      </c>
-      <c r="C36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" t="s">
-        <v>214</v>
-      </c>
-      <c r="E36" t="s">
-        <v>215</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -3050,16 +3023,16 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E37" t="s">
-        <v>220</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -3076,19 +3049,19 @@
         <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
         <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="G38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -3096,22 +3069,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C39" t="s">
         <v>28</v>
       </c>
       <c r="D39" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" t="s">
+        <v>224</v>
+      </c>
+      <c r="F39" t="s">
+        <v>225</v>
+      </c>
+      <c r="G39" t="s">
         <v>226</v>
-      </c>
-      <c r="E39" t="s">
-        <v>227</v>
-      </c>
-      <c r="F39" t="s">
-        <v>228</v>
-      </c>
-      <c r="G39" t="s">
-        <v>229</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -3119,22 +3092,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" t="s">
         <v>230</v>
       </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>226</v>
-      </c>
-      <c r="E40" t="s">
-        <v>227</v>
-      </c>
       <c r="F40" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -3142,22 +3115,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -3165,22 +3138,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
         <v>20</v>
       </c>
       <c r="D42" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" t="s">
+        <v>236</v>
+      </c>
+      <c r="G42" t="s">
         <v>237</v>
-      </c>
-      <c r="E42" t="s">
-        <v>238</v>
-      </c>
-      <c r="F42" t="s">
-        <v>239</v>
-      </c>
-      <c r="G42" t="s">
-        <v>240</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -3188,22 +3161,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" t="s">
-        <v>237</v>
-      </c>
       <c r="E43" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F43" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G43" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -3211,22 +3184,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>109</v>
       </c>
       <c r="D44" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F44" t="s">
-        <v>246</v>
+        <v>7</v>
       </c>
       <c r="G44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -3234,22 +3207,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C45" t="s">
         <v>109</v>
       </c>
       <c r="D45" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
       </c>
       <c r="G45" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -3257,22 +3230,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>250</v>
+      </c>
+      <c r="C46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" t="s">
+        <v>251</v>
+      </c>
+      <c r="E46" t="s">
         <v>252</v>
       </c>
-      <c r="C46" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" t="s">
-        <v>249</v>
-      </c>
-      <c r="E46" t="s">
-        <v>250</v>
-      </c>
       <c r="F46" t="s">
-        <v>7</v>
+        <v>253</v>
       </c>
       <c r="G46" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -3280,22 +3253,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C47" t="s">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="D47" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E47" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F47" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -3303,22 +3276,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" t="s">
+        <v>200</v>
+      </c>
+      <c r="D48" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" t="s">
+        <v>257</v>
+      </c>
+      <c r="F48" t="s">
         <v>258</v>
       </c>
-      <c r="C48" t="s">
-        <v>203</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="G48" t="s">
         <v>259</v>
-      </c>
-      <c r="E48" t="s">
-        <v>260</v>
-      </c>
-      <c r="F48" t="s">
-        <v>261</v>
-      </c>
-      <c r="G48" t="s">
-        <v>262</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -3326,22 +3299,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" t="s">
+        <v>99</v>
+      </c>
+      <c r="F49" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" t="s">
         <v>263</v>
-      </c>
-      <c r="C49" t="s">
-        <v>203</v>
-      </c>
-      <c r="D49" t="s">
-        <v>259</v>
-      </c>
-      <c r="E49" t="s">
-        <v>260</v>
-      </c>
-      <c r="F49" t="s">
-        <v>261</v>
-      </c>
-      <c r="G49" t="s">
-        <v>262</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -3355,7 +3328,7 @@
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E50" t="s">
         <v>99</v>
@@ -3364,7 +3337,7 @@
         <v>22</v>
       </c>
       <c r="G50" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -3372,22 +3345,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>265</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>266</v>
+      </c>
+      <c r="E51" t="s">
         <v>267</v>
       </c>
-      <c r="C51" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" t="s">
-        <v>265</v>
-      </c>
-      <c r="E51" t="s">
-        <v>99</v>
-      </c>
       <c r="F51" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G51" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -3395,16 +3368,16 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E52" t="s">
-        <v>270</v>
+        <v>98</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -3421,19 +3394,19 @@
         <v>272</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D53" t="s">
         <v>273</v>
       </c>
       <c r="E53" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="F53" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="G53" t="s">
-        <v>274</v>
+        <v>43</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -3441,22 +3414,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>275</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>96</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G54" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -3464,22 +3437,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>274</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="D55" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>276</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
       </c>
       <c r="G55" t="s">
-        <v>85</v>
+        <v>277</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -3487,22 +3460,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F56" t="s">
-        <v>7</v>
+        <v>281</v>
       </c>
       <c r="G56" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -3510,22 +3483,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E57" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F57" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -3533,16 +3506,16 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E58" t="s">
-        <v>288</v>
+        <v>84</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -3559,19 +3532,19 @@
         <v>290</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
         <v>291</v>
       </c>
       <c r="E59" t="s">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="F59" t="s">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="G59" t="s">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -3579,22 +3552,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="D60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E60" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F60" t="s">
-        <v>296</v>
+        <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>38</v>
+        <v>297</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -3602,22 +3575,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C61" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E61" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>301</v>
       </c>
       <c r="G61" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -3625,22 +3598,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E62" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F62" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G62" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -3648,22 +3621,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>308</v>
+      </c>
+      <c r="C63" t="s">
+        <v>122</v>
+      </c>
+      <c r="D63" t="s">
+        <v>304</v>
+      </c>
+      <c r="E63" t="s">
+        <v>305</v>
+      </c>
+      <c r="F63" t="s">
         <v>306</v>
       </c>
-      <c r="C63" t="s">
-        <v>123</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="G63" t="s">
         <v>307</v>
-      </c>
-      <c r="E63" t="s">
-        <v>308</v>
-      </c>
-      <c r="F63" t="s">
-        <v>309</v>
-      </c>
-      <c r="G63" t="s">
-        <v>310</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -3671,22 +3644,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>309</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" t="s">
+        <v>310</v>
+      </c>
+      <c r="E64" t="s">
+        <v>65</v>
+      </c>
+      <c r="F64" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" t="s">
         <v>311</v>
-      </c>
-      <c r="C64" t="s">
-        <v>123</v>
-      </c>
-      <c r="D64" t="s">
-        <v>307</v>
-      </c>
-      <c r="E64" t="s">
-        <v>308</v>
-      </c>
-      <c r="F64" t="s">
-        <v>309</v>
-      </c>
-      <c r="G64" t="s">
-        <v>310</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -3697,16 +3670,16 @@
         <v>312</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D65" t="s">
         <v>313</v>
       </c>
       <c r="E65" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="F65" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G65" t="s">
         <v>314</v>
@@ -3720,19 +3693,19 @@
         <v>315</v>
       </c>
       <c r="C66" t="s">
-        <v>75</v>
+        <v>316</v>
       </c>
       <c r="D66" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>318</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="G66" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -3740,22 +3713,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C67" t="s">
-        <v>319</v>
+        <v>16</v>
       </c>
       <c r="D67" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E67" t="s">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="F67" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G67" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -3763,22 +3736,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="F68" t="s">
-        <v>326</v>
+        <v>22</v>
       </c>
       <c r="G68" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -3786,22 +3759,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E69" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>332</v>
       </c>
       <c r="G69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -3809,22 +3782,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F70" t="s">
-        <v>335</v>
+        <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -3832,22 +3805,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C71" t="s">
         <v>74</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E71" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
       </c>
       <c r="G71" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -3855,22 +3828,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C72" t="s">
         <v>74</v>
       </c>
       <c r="D72" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E72" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
       </c>
       <c r="G72" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -3878,22 +3851,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>340</v>
+      </c>
+      <c r="C73" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73" t="s">
+        <v>341</v>
+      </c>
+      <c r="E73" t="s">
+        <v>123</v>
+      </c>
+      <c r="F73" t="s">
+        <v>124</v>
+      </c>
+      <c r="G73" t="s">
         <v>342</v>
-      </c>
-      <c r="C73" t="s">
-        <v>74</v>
-      </c>
-      <c r="D73" t="s">
-        <v>338</v>
-      </c>
-      <c r="E73" t="s">
-        <v>339</v>
-      </c>
-      <c r="F73" t="s">
-        <v>7</v>
-      </c>
-      <c r="G73" t="s">
-        <v>340</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -3904,19 +3877,19 @@
         <v>343</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="D74" t="s">
         <v>344</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>345</v>
       </c>
       <c r="F74" t="s">
-        <v>126</v>
+        <v>346</v>
       </c>
       <c r="G74" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -3924,22 +3897,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C75" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E75" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F75" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G75" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -3947,22 +3920,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E76" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F76" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G76" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -3970,22 +3943,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
       </c>
       <c r="D77" t="s">
+        <v>354</v>
+      </c>
+      <c r="E77" t="s">
+        <v>355</v>
+      </c>
+      <c r="F77" t="s">
+        <v>356</v>
+      </c>
+      <c r="G77" t="s">
         <v>357</v>
-      </c>
-      <c r="E77" t="s">
-        <v>358</v>
-      </c>
-      <c r="F77" t="s">
-        <v>359</v>
-      </c>
-      <c r="G77" t="s">
-        <v>360</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -3993,22 +3966,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>359</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>360</v>
+      </c>
+      <c r="E78" t="s">
         <v>361</v>
       </c>
-      <c r="C78" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" t="s">
-        <v>357</v>
-      </c>
-      <c r="E78" t="s">
-        <v>358</v>
-      </c>
       <c r="F78" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G78" t="s">
-        <v>360</v>
+        <v>29</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -4016,22 +3989,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C79" t="s">
-        <v>15</v>
+        <v>364</v>
       </c>
       <c r="D79" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E79" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F79" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G79" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -4039,22 +4012,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C80" t="s">
-        <v>367</v>
+        <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E80" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F80" t="s">
-        <v>370</v>
+        <v>7</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>371</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -4062,22 +4035,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C81" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="D81" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E81" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F81" t="s">
-        <v>7</v>
+        <v>375</v>
       </c>
       <c r="G81" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -4085,22 +4058,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>377</v>
+      </c>
+      <c r="C82" t="s">
+        <v>156</v>
+      </c>
+      <c r="D82" t="s">
+        <v>373</v>
+      </c>
+      <c r="E82" t="s">
+        <v>374</v>
+      </c>
+      <c r="F82" t="s">
         <v>375</v>
       </c>
-      <c r="C82" t="s">
-        <v>159</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="G82" t="s">
         <v>376</v>
-      </c>
-      <c r="E82" t="s">
-        <v>377</v>
-      </c>
-      <c r="F82" t="s">
-        <v>378</v>
-      </c>
-      <c r="G82" t="s">
-        <v>379</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -4108,22 +4081,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>378</v>
+      </c>
+      <c r="C83" t="s">
+        <v>185</v>
+      </c>
+      <c r="D83" t="s">
+        <v>379</v>
+      </c>
+      <c r="E83" t="s">
         <v>380</v>
       </c>
-      <c r="C83" t="s">
-        <v>159</v>
-      </c>
-      <c r="D83" t="s">
-        <v>376</v>
-      </c>
-      <c r="E83" t="s">
-        <v>377</v>
-      </c>
       <c r="F83" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G83" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -4131,22 +4104,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
+        <v>19</v>
       </c>
       <c r="D84" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E84" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F84" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G84" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -4154,22 +4127,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="D85" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E85" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F85" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G85" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -4177,22 +4150,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E86" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F86" t="s">
-        <v>394</v>
+        <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -4203,19 +4176,19 @@
         <v>396</v>
       </c>
       <c r="C87" t="s">
-        <v>73</v>
+        <v>397</v>
       </c>
       <c r="D87" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E87" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F87" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="G87" t="s">
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -4223,19 +4196,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C88" t="s">
-        <v>400</v>
+        <v>56</v>
       </c>
       <c r="D88" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E88" t="s">
-        <v>402</v>
+        <v>180</v>
       </c>
       <c r="F88" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="G88" t="s">
         <v>403</v>
@@ -4252,16 +4225,16 @@
         <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E89" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F89" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G89" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -4269,22 +4242,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>405</v>
+      </c>
+      <c r="C90" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" t="s">
+        <v>406</v>
+      </c>
+      <c r="E90" t="s">
+        <v>276</v>
+      </c>
+      <c r="F90" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" t="s">
         <v>407</v>
-      </c>
-      <c r="C90" t="s">
-        <v>56</v>
-      </c>
-      <c r="D90" t="s">
-        <v>405</v>
-      </c>
-      <c r="E90" t="s">
-        <v>183</v>
-      </c>
-      <c r="F90" t="s">
-        <v>184</v>
-      </c>
-      <c r="G90" t="s">
-        <v>406</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -4295,16 +4268,16 @@
         <v>408</v>
       </c>
       <c r="C91" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D91" t="s">
         <v>409</v>
       </c>
       <c r="E91" t="s">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="F91" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G91" t="s">
         <v>410</v>
@@ -4318,19 +4291,19 @@
         <v>411</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="D92" t="s">
         <v>412</v>
       </c>
       <c r="E92" t="s">
-        <v>103</v>
+        <v>413</v>
       </c>
       <c r="F92" t="s">
-        <v>36</v>
+        <v>414</v>
       </c>
       <c r="G92" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -4338,19 +4311,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C93" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D93" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E93" t="s">
-        <v>416</v>
+        <v>34</v>
       </c>
       <c r="F93" t="s">
-        <v>417</v>
+        <v>35</v>
       </c>
       <c r="G93" t="s">
         <v>418</v>
@@ -4364,16 +4337,16 @@
         <v>419</v>
       </c>
       <c r="C94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D94" t="s">
         <v>420</v>
       </c>
       <c r="E94" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F94" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G94" t="s">
         <v>421</v>
@@ -4387,13 +4360,13 @@
         <v>422</v>
       </c>
       <c r="C95" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D95" t="s">
         <v>423</v>
       </c>
       <c r="E95" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F95" t="s">
         <v>7</v>
@@ -4410,16 +4383,16 @@
         <v>425</v>
       </c>
       <c r="C96" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="D96" t="s">
         <v>426</v>
       </c>
       <c r="E96" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="F96" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="G96" t="s">
         <v>427</v>
@@ -4433,16 +4406,16 @@
         <v>428</v>
       </c>
       <c r="C97" t="s">
-        <v>243</v>
+        <v>109</v>
       </c>
       <c r="D97" t="s">
         <v>429</v>
       </c>
       <c r="E97" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F97" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="G97" t="s">
         <v>430</v>
@@ -4456,16 +4429,16 @@
         <v>431</v>
       </c>
       <c r="C98" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="D98" t="s">
         <v>432</v>
       </c>
       <c r="E98" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F98" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G98" t="s">
         <v>433</v>
@@ -4479,16 +4452,16 @@
         <v>434</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
         <v>435</v>
       </c>
       <c r="E99" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="F99" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G99" t="s">
         <v>436</v>
@@ -4505,7 +4478,7 @@
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E100" t="s">
         <v>91</v>
@@ -4514,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -4522,22 +4495,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>438</v>
+      </c>
+      <c r="C101" t="s">
+        <v>73</v>
+      </c>
+      <c r="D101" t="s">
+        <v>439</v>
+      </c>
+      <c r="E101" t="s">
+        <v>53</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
         <v>440</v>
-      </c>
-      <c r="C101" t="s">
-        <v>20</v>
-      </c>
-      <c r="D101" t="s">
-        <v>438</v>
-      </c>
-      <c r="E101" t="s">
-        <v>91</v>
-      </c>
-      <c r="F101" t="s">
-        <v>7</v>
-      </c>
-      <c r="G101" t="s">
-        <v>439</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -4548,19 +4521,19 @@
         <v>441</v>
       </c>
       <c r="C102" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
         <v>442</v>
       </c>
       <c r="E102" t="s">
-        <v>53</v>
+        <v>443</v>
       </c>
       <c r="F102" t="s">
-        <v>12</v>
+        <v>444</v>
       </c>
       <c r="G102" t="s">
-        <v>443</v>
+        <v>39</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -4568,19 +4541,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C103" t="s">
         <v>28</v>
       </c>
       <c r="D103" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E103" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F103" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G103" t="s">
         <v>39</v>
@@ -4591,22 +4564,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>446</v>
+      </c>
+      <c r="C104" t="s">
+        <v>447</v>
+      </c>
+      <c r="D104" t="s">
         <v>448</v>
       </c>
-      <c r="C104" t="s">
-        <v>28</v>
-      </c>
-      <c r="D104" t="s">
-        <v>445</v>
-      </c>
       <c r="E104" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F104" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G104" t="s">
-        <v>39</v>
+        <v>451</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -4614,19 +4587,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C105" t="s">
-        <v>450</v>
+        <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E105" t="s">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="F105" t="s">
-        <v>453</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
         <v>454</v>
@@ -4640,16 +4613,16 @@
         <v>455</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D106" t="s">
         <v>456</v>
       </c>
       <c r="E106" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F106" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G106" t="s">
         <v>457</v>
@@ -4663,19 +4636,19 @@
         <v>458</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
         <v>459</v>
       </c>
       <c r="E107" t="s">
-        <v>67</v>
+        <v>460</v>
       </c>
       <c r="F107" t="s">
-        <v>68</v>
+        <v>461</v>
       </c>
       <c r="G107" t="s">
-        <v>460</v>
+        <v>97</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -4683,22 +4656,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E108" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F108" t="s">
-        <v>464</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>97</v>
+        <v>465</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -4706,22 +4679,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E109" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F109" t="s">
-        <v>18</v>
+        <v>469</v>
       </c>
       <c r="G109" t="s">
-        <v>468</v>
+        <v>347</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -4729,22 +4702,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D110" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E110" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F110" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G110" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -4752,22 +4725,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D111" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E111" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F111" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G111" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -4775,19 +4748,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C112" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D112" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E112" t="s">
-        <v>480</v>
+        <v>88</v>
       </c>
       <c r="F112" t="s">
-        <v>481</v>
+        <v>7</v>
       </c>
       <c r="G112" t="s">
         <v>482</v>
@@ -4801,19 +4774,19 @@
         <v>483</v>
       </c>
       <c r="C113" t="s">
-        <v>87</v>
+        <v>316</v>
       </c>
       <c r="D113" t="s">
         <v>484</v>
       </c>
       <c r="E113" t="s">
-        <v>88</v>
+        <v>485</v>
       </c>
       <c r="F113" t="s">
-        <v>7</v>
+        <v>486</v>
       </c>
       <c r="G113" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -4821,19 +4794,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C114" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="D114" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E114" t="s">
-        <v>488</v>
+        <v>51</v>
       </c>
       <c r="F114" t="s">
-        <v>489</v>
+        <v>52</v>
       </c>
       <c r="G114" t="s">
         <v>490</v>
@@ -4847,19 +4820,19 @@
         <v>491</v>
       </c>
       <c r="C115" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D115" t="s">
         <v>492</v>
       </c>
       <c r="E115" t="s">
-        <v>51</v>
+        <v>493</v>
       </c>
       <c r="F115" t="s">
-        <v>52</v>
+        <v>461</v>
       </c>
       <c r="G115" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -4867,22 +4840,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D116" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E116" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F116" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="G116" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -4890,22 +4863,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C117" t="s">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="D117" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E117" t="s">
-        <v>500</v>
+        <v>93</v>
       </c>
       <c r="F117" t="s">
-        <v>501</v>
+        <v>94</v>
       </c>
       <c r="G117" t="s">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -4913,22 +4886,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>502</v>
+      </c>
+      <c r="C118" t="s">
+        <v>109</v>
+      </c>
+      <c r="D118" t="s">
         <v>503</v>
       </c>
-      <c r="C118" t="s">
-        <v>243</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
+        <v>79</v>
+      </c>
+      <c r="F118" t="s">
+        <v>7</v>
+      </c>
+      <c r="G118" t="s">
         <v>504</v>
-      </c>
-      <c r="E118" t="s">
-        <v>93</v>
-      </c>
-      <c r="F118" t="s">
-        <v>94</v>
-      </c>
-      <c r="G118" t="s">
-        <v>77</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -4939,19 +4912,19 @@
         <v>505</v>
       </c>
       <c r="C119" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="D119" t="s">
         <v>506</v>
       </c>
       <c r="E119" t="s">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="F119" t="s">
         <v>7</v>
       </c>
       <c r="G119" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -4959,19 +4932,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C120" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E120" t="s">
-        <v>510</v>
+        <v>71</v>
       </c>
       <c r="F120" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G120" t="s">
         <v>511</v>
@@ -4985,19 +4958,19 @@
         <v>512</v>
       </c>
       <c r="C121" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D121" t="s">
         <v>513</v>
       </c>
       <c r="E121" t="s">
-        <v>71</v>
+        <v>514</v>
       </c>
       <c r="F121" t="s">
-        <v>72</v>
+        <v>515</v>
       </c>
       <c r="G121" t="s">
-        <v>514</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -5005,22 +4978,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C122" t="s">
-        <v>16</v>
+        <v>316</v>
       </c>
       <c r="D122" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E122" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F122" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G122" t="s">
-        <v>92</v>
+        <v>520</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -5028,22 +5001,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>521</v>
+      </c>
+      <c r="C123" t="s">
+        <v>316</v>
+      </c>
+      <c r="D123" t="s">
+        <v>517</v>
+      </c>
+      <c r="E123" t="s">
+        <v>518</v>
+      </c>
+      <c r="F123" t="s">
         <v>519</v>
       </c>
-      <c r="C123" t="s">
-        <v>319</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="G123" t="s">
         <v>520</v>
-      </c>
-      <c r="E123" t="s">
-        <v>521</v>
-      </c>
-      <c r="F123" t="s">
-        <v>522</v>
-      </c>
-      <c r="G123" t="s">
-        <v>523</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -5051,22 +5024,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C124" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D124" t="s">
+        <v>517</v>
+      </c>
+      <c r="E124" t="s">
+        <v>518</v>
+      </c>
+      <c r="F124" t="s">
+        <v>519</v>
+      </c>
+      <c r="G124" t="s">
         <v>520</v>
-      </c>
-      <c r="E124" t="s">
-        <v>521</v>
-      </c>
-      <c r="F124" t="s">
-        <v>522</v>
-      </c>
-      <c r="G124" t="s">
-        <v>523</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -5074,22 +5047,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>523</v>
+      </c>
+      <c r="C125" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" t="s">
+        <v>524</v>
+      </c>
+      <c r="E125" t="s">
         <v>525</v>
       </c>
-      <c r="C125" t="s">
-        <v>319</v>
-      </c>
-      <c r="D125" t="s">
-        <v>520</v>
-      </c>
-      <c r="E125" t="s">
-        <v>521</v>
-      </c>
       <c r="F125" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G125" t="s">
-        <v>523</v>
+        <v>14</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -5097,22 +5070,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C126" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="D126" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E126" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F126" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G126" t="s">
-        <v>14</v>
+        <v>531</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -5120,19 +5093,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C127" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="D127" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E127" t="s">
-        <v>532</v>
+        <v>276</v>
       </c>
       <c r="F127" t="s">
-        <v>533</v>
+        <v>7</v>
       </c>
       <c r="G127" t="s">
         <v>534</v>
@@ -5146,42 +5119,42 @@
         <v>535</v>
       </c>
       <c r="C128" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="D128" t="s">
         <v>536</v>
       </c>
       <c r="E128" t="s">
-        <v>279</v>
+        <v>537</v>
       </c>
       <c r="F128" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G128" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H128" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C129" t="s">
         <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E129" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F129" t="s">
         <v>22</v>
       </c>
       <c r="G129" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H129" t="s">
         <v>33</v>
@@ -5189,22 +5162,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C130" t="s">
         <v>21</v>
       </c>
       <c r="D130" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E130" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F130" t="s">
         <v>22</v>
       </c>
       <c r="G130" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H130" t="s">
         <v>33</v>
@@ -5212,22 +5185,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C131" t="s">
         <v>21</v>
       </c>
       <c r="D131" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E131" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F131" t="s">
         <v>22</v>
       </c>
       <c r="G131" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H131" t="s">
         <v>33</v>
@@ -5235,22 +5208,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C132" t="s">
         <v>21</v>
       </c>
       <c r="D132" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E132" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F132" t="s">
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H132" t="s">
         <v>33</v>
@@ -5258,22 +5231,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>543</v>
+      </c>
+      <c r="C133" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" t="s">
+        <v>544</v>
+      </c>
+      <c r="E133" t="s">
+        <v>63</v>
+      </c>
+      <c r="F133" t="s">
+        <v>7</v>
+      </c>
+      <c r="G133" t="s">
         <v>545</v>
-      </c>
-      <c r="C133" t="s">
-        <v>21</v>
-      </c>
-      <c r="D133" t="s">
-        <v>539</v>
-      </c>
-      <c r="E133" t="s">
-        <v>540</v>
-      </c>
-      <c r="F133" t="s">
-        <v>22</v>
-      </c>
-      <c r="G133" t="s">
-        <v>541</v>
       </c>
       <c r="H133" t="s">
         <v>33</v>
@@ -5284,19 +5257,19 @@
         <v>546</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D134" t="s">
         <v>547</v>
       </c>
       <c r="E134" t="s">
-        <v>63</v>
+        <v>548</v>
       </c>
       <c r="F134" t="s">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="G134" t="s">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s">
         <v>33</v>
@@ -5304,22 +5277,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C135" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D135" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E135" t="s">
-        <v>551</v>
+        <v>83</v>
       </c>
       <c r="F135" t="s">
+        <v>7</v>
+      </c>
+      <c r="G135" t="s">
         <v>552</v>
-      </c>
-      <c r="G135" t="s">
-        <v>81</v>
       </c>
       <c r="H135" t="s">
         <v>33</v>
@@ -5330,19 +5303,19 @@
         <v>553</v>
       </c>
       <c r="C136" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D136" t="s">
         <v>554</v>
       </c>
       <c r="E136" t="s">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="F136" t="s">
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H136" t="s">
         <v>33</v>
@@ -5350,22 +5323,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>556</v>
+        <v>100</v>
       </c>
       <c r="C137" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="D137" t="s">
-        <v>557</v>
+        <v>101</v>
       </c>
       <c r="E137" t="s">
-        <v>558</v>
+        <v>89</v>
       </c>
       <c r="F137" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="G137" t="s">
-        <v>559</v>
+        <v>102</v>
       </c>
       <c r="H137" t="s">
         <v>33</v>
@@ -5373,22 +5346,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>100</v>
+        <v>557</v>
       </c>
       <c r="C138" t="s">
         <v>13</v>
       </c>
       <c r="D138" t="s">
-        <v>101</v>
+        <v>558</v>
       </c>
       <c r="E138" t="s">
-        <v>89</v>
+        <v>559</v>
       </c>
       <c r="F138" t="s">
-        <v>90</v>
+        <v>560</v>
       </c>
       <c r="G138" t="s">
-        <v>102</v>
+        <v>561</v>
       </c>
       <c r="H138" t="s">
         <v>33</v>
@@ -5396,22 +5369,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C139" t="s">
         <v>13</v>
       </c>
       <c r="D139" t="s">
+        <v>558</v>
+      </c>
+      <c r="E139" t="s">
+        <v>559</v>
+      </c>
+      <c r="F139" t="s">
+        <v>560</v>
+      </c>
+      <c r="G139" t="s">
         <v>561</v>
-      </c>
-      <c r="E139" t="s">
-        <v>562</v>
-      </c>
-      <c r="F139" t="s">
-        <v>563</v>
-      </c>
-      <c r="G139" t="s">
-        <v>564</v>
       </c>
       <c r="H139" t="s">
         <v>33</v>
@@ -5419,22 +5392,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>563</v>
+      </c>
+      <c r="C140" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" t="s">
+        <v>564</v>
+      </c>
+      <c r="E140" t="s">
+        <v>49</v>
+      </c>
+      <c r="F140" t="s">
+        <v>7</v>
+      </c>
+      <c r="G140" t="s">
         <v>565</v>
-      </c>
-      <c r="C140" t="s">
-        <v>13</v>
-      </c>
-      <c r="D140" t="s">
-        <v>561</v>
-      </c>
-      <c r="E140" t="s">
-        <v>562</v>
-      </c>
-      <c r="F140" t="s">
-        <v>563</v>
-      </c>
-      <c r="G140" t="s">
-        <v>564</v>
       </c>
       <c r="H140" t="s">
         <v>33</v>
@@ -5445,42 +5418,42 @@
         <v>566</v>
       </c>
       <c r="C141" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D141" t="s">
         <v>567</v>
       </c>
       <c r="E141" t="s">
-        <v>49</v>
+        <v>568</v>
       </c>
       <c r="F141" t="s">
-        <v>7</v>
+        <v>461</v>
       </c>
       <c r="G141" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H141" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C142" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D142" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E142" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F142" t="s">
-        <v>464</v>
+        <v>573</v>
       </c>
       <c r="G142" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H142" t="s">
         <v>44</v>
@@ -5488,19 +5461,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E143" t="s">
-        <v>575</v>
+        <v>47</v>
       </c>
       <c r="F143" t="s">
-        <v>576</v>
+        <v>48</v>
       </c>
       <c r="G143" t="s">
         <v>577</v>
@@ -5517,7 +5490,7 @@
         <v>16</v>
       </c>
       <c r="D144" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E144" t="s">
         <v>47</v>
@@ -5526,7 +5499,7 @@
         <v>48</v>
       </c>
       <c r="G144" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H144" t="s">
         <v>44</v>
@@ -5534,13 +5507,13 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E145" t="s">
         <v>47</v>
@@ -5549,7 +5522,7 @@
         <v>48</v>
       </c>
       <c r="G145" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H145" t="s">
         <v>44</v>
@@ -5557,22 +5530,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>580</v>
+      </c>
+      <c r="C146" t="s">
+        <v>80</v>
+      </c>
+      <c r="D146" t="s">
+        <v>581</v>
+      </c>
+      <c r="E146" t="s">
+        <v>497</v>
+      </c>
+      <c r="F146" t="s">
+        <v>498</v>
+      </c>
+      <c r="G146" t="s">
         <v>582</v>
-      </c>
-      <c r="C146" t="s">
-        <v>16</v>
-      </c>
-      <c r="D146" t="s">
-        <v>579</v>
-      </c>
-      <c r="E146" t="s">
-        <v>47</v>
-      </c>
-      <c r="F146" t="s">
-        <v>48</v>
-      </c>
-      <c r="G146" t="s">
-        <v>580</v>
       </c>
       <c r="H146" t="s">
         <v>44</v>
@@ -5583,19 +5556,19 @@
         <v>583</v>
       </c>
       <c r="C147" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="D147" t="s">
         <v>584</v>
       </c>
       <c r="E147" t="s">
-        <v>500</v>
+        <v>585</v>
       </c>
       <c r="F147" t="s">
-        <v>501</v>
+        <v>586</v>
       </c>
       <c r="G147" t="s">
-        <v>585</v>
+        <v>55</v>
       </c>
       <c r="H147" t="s">
         <v>44</v>
@@ -5603,22 +5576,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>587</v>
+      </c>
+      <c r="C148" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" t="s">
+        <v>584</v>
+      </c>
+      <c r="E148" t="s">
+        <v>585</v>
+      </c>
+      <c r="F148" t="s">
         <v>586</v>
       </c>
-      <c r="C148" t="s">
-        <v>11</v>
-      </c>
-      <c r="D148" t="s">
-        <v>587</v>
-      </c>
-      <c r="E148" t="s">
-        <v>588</v>
-      </c>
-      <c r="F148" t="s">
-        <v>589</v>
-      </c>
       <c r="G148" t="s">
-        <v>590</v>
+        <v>55</v>
       </c>
       <c r="H148" t="s">
         <v>44</v>
@@ -5626,22 +5599,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C149" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D149" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E149" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F149" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G149" t="s">
-        <v>590</v>
+        <v>55</v>
       </c>
       <c r="H149" t="s">
         <v>44</v>
@@ -5649,19 +5622,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C150" t="s">
         <v>19</v>
       </c>
       <c r="D150" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E150" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="F150" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="G150" t="s">
         <v>55</v>
@@ -5672,19 +5645,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C151" t="s">
         <v>19</v>
       </c>
       <c r="D151" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E151" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="F151" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="G151" t="s">
         <v>55</v>
@@ -5695,22 +5668,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C152" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="D152" t="s">
+        <v>592</v>
+      </c>
+      <c r="E152" t="s">
         <v>593</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" t="s">
         <v>594</v>
-      </c>
-      <c r="F152" t="s">
-        <v>595</v>
-      </c>
-      <c r="G152" t="s">
-        <v>55</v>
       </c>
       <c r="H152" t="s">
         <v>44</v>
@@ -5718,25 +5691,25 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>595</v>
+      </c>
+      <c r="C153" t="s">
+        <v>28</v>
+      </c>
+      <c r="D153" t="s">
+        <v>596</v>
+      </c>
+      <c r="E153" t="s">
+        <v>331</v>
+      </c>
+      <c r="F153" t="s">
+        <v>332</v>
+      </c>
+      <c r="G153" t="s">
+        <v>597</v>
+      </c>
+      <c r="H153" t="s">
         <v>598</v>
-      </c>
-      <c r="C153" t="s">
-        <v>19</v>
-      </c>
-      <c r="D153" t="s">
-        <v>593</v>
-      </c>
-      <c r="E153" t="s">
-        <v>594</v>
-      </c>
-      <c r="F153" t="s">
-        <v>595</v>
-      </c>
-      <c r="G153" t="s">
-        <v>55</v>
-      </c>
-      <c r="H153" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
@@ -5744,95 +5717,26 @@
         <v>599</v>
       </c>
       <c r="C154" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D154" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E154" t="s">
-        <v>594</v>
+        <v>331</v>
       </c>
       <c r="F154" t="s">
-        <v>595</v>
+        <v>332</v>
       </c>
       <c r="G154" t="s">
-        <v>55</v>
+        <v>597</v>
       </c>
       <c r="H154" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>600</v>
-      </c>
-      <c r="C155" t="s">
-        <v>73</v>
-      </c>
-      <c r="D155" t="s">
-        <v>601</v>
-      </c>
-      <c r="E155" t="s">
-        <v>602</v>
-      </c>
-      <c r="F155" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" t="s">
-        <v>603</v>
-      </c>
-      <c r="H155" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>604</v>
-      </c>
-      <c r="C156" t="s">
-        <v>28</v>
-      </c>
-      <c r="D156" t="s">
-        <v>605</v>
-      </c>
-      <c r="E156" t="s">
-        <v>334</v>
-      </c>
-      <c r="F156" t="s">
-        <v>335</v>
-      </c>
-      <c r="G156" t="s">
-        <v>606</v>
-      </c>
-      <c r="H156" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>608</v>
-      </c>
-      <c r="C157" t="s">
-        <v>28</v>
-      </c>
-      <c r="D157" t="s">
-        <v>605</v>
-      </c>
-      <c r="E157" t="s">
-        <v>334</v>
-      </c>
-      <c r="F157" t="s">
-        <v>335</v>
-      </c>
-      <c r="G157" t="s">
-        <v>606</v>
-      </c>
-      <c r="H157" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:H9" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
+  <autoFilter ref="C1:H8" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FB4393-03D8-4DEE-B7C9-58FBAA3A5644}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB828A12-9766-4C0A-9073-A125B258BDAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="604">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -63,60 +63,15 @@
     <t>TELEKOM</t>
   </si>
   <si>
-    <t>K-983</t>
-  </si>
-  <si>
-    <t>MISKOLC</t>
-  </si>
-  <si>
-    <t>SZ-803</t>
-  </si>
-  <si>
     <t>Petőfi Sándor utca</t>
   </si>
   <si>
-    <t>K-951</t>
-  </si>
-  <si>
-    <t>K-931</t>
-  </si>
-  <si>
-    <t>K-941</t>
-  </si>
-  <si>
-    <t>SZEGED</t>
-  </si>
-  <si>
-    <t>K-942</t>
-  </si>
-  <si>
     <t>SZ-822</t>
   </si>
   <si>
-    <t>K-982</t>
-  </si>
-  <si>
-    <t>DEBRECEN</t>
-  </si>
-  <si>
-    <t>K-998</t>
-  </si>
-  <si>
     <t>József Attila utca</t>
   </si>
   <si>
-    <t>K-981</t>
-  </si>
-  <si>
-    <t>Kossuth utca</t>
-  </si>
-  <si>
-    <t>K-943</t>
-  </si>
-  <si>
-    <t>K-952</t>
-  </si>
-  <si>
     <t>Kossuth Lajos utca</t>
   </si>
   <si>
@@ -132,72 +87,18 @@
     <t>AUCHAN</t>
   </si>
   <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>SZÉKESFEHÉRVÁR</t>
-  </si>
-  <si>
-    <t>GYŐR</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>Dózsa György utca</t>
-  </si>
-  <si>
-    <t>Deák Ferenc utca</t>
-  </si>
-  <si>
-    <t>2085</t>
-  </si>
-  <si>
-    <t>PILISVÖRÖSVÁR</t>
-  </si>
-  <si>
     <t>1094</t>
   </si>
   <si>
-    <t>Határ utca</t>
-  </si>
-  <si>
     <t>INSPORT</t>
   </si>
   <si>
-    <t>K-915</t>
-  </si>
-  <si>
     <t>SZ-854</t>
   </si>
   <si>
-    <t>8200</t>
-  </si>
-  <si>
-    <t>VESZPRÉM</t>
-  </si>
-  <si>
     <t>1039</t>
   </si>
   <si>
-    <t>SZ-805</t>
-  </si>
-  <si>
-    <t>2360</t>
-  </si>
-  <si>
-    <t>GYÁL</t>
-  </si>
-  <si>
-    <t>3532</t>
-  </si>
-  <si>
-    <t>Széchenyi utca</t>
-  </si>
-  <si>
-    <t>Bartók Béla utca</t>
-  </si>
-  <si>
     <t>SZ-809</t>
   </si>
   <si>
@@ -213,90 +114,30 @@
     <t>1035</t>
   </si>
   <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
     <t>1222</t>
   </si>
   <si>
     <t>SZ-848</t>
   </si>
   <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>DRENCO</t>
-  </si>
-  <si>
-    <t>4244</t>
-  </si>
-  <si>
-    <t>ÚJFEHÉRTÓ</t>
-  </si>
-  <si>
-    <t>K-902</t>
-  </si>
-  <si>
     <t>Béke utca</t>
   </si>
   <si>
-    <t>7633</t>
-  </si>
-  <si>
-    <t>PÉCS</t>
-  </si>
-  <si>
-    <t>K-964</t>
-  </si>
-  <si>
     <t>SZ-823</t>
   </si>
   <si>
-    <t>K-918</t>
-  </si>
-  <si>
     <t>Béke út</t>
   </si>
   <si>
-    <t>Szamos utca</t>
-  </si>
-  <si>
-    <t>6723</t>
-  </si>
-  <si>
     <t>1112</t>
   </si>
   <si>
-    <t>K-910</t>
-  </si>
-  <si>
-    <t>Ady Endre út</t>
-  </si>
-  <si>
-    <t>2484</t>
-  </si>
-  <si>
     <t>1047</t>
   </si>
   <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>Sörgyár utca</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
     <t>SZ-819</t>
   </si>
   <si>
-    <t>1046</t>
-  </si>
-  <si>
     <t>2119</t>
   </si>
   <si>
@@ -306,1032 +147,54 @@
     <t>1225</t>
   </si>
   <si>
-    <t>Honvéd utca</t>
-  </si>
-  <si>
-    <t>2094</t>
-  </si>
-  <si>
-    <t>NAGYKOVÁCSI</t>
-  </si>
-  <si>
-    <t>330795256/1</t>
-  </si>
-  <si>
-    <t>330795256</t>
-  </si>
-  <si>
-    <t>Pacsirta utca</t>
-  </si>
-  <si>
     <t>1204</t>
   </si>
   <si>
-    <t>4025</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-S6J2/1</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-S6J2</t>
-  </si>
-  <si>
-    <t>Ond vezér utca</t>
-  </si>
-  <si>
-    <t>9027</t>
-  </si>
-  <si>
-    <t>159995579544624507</t>
-  </si>
-  <si>
-    <t>2026/13179</t>
-  </si>
-  <si>
-    <t>Kisvasút utca</t>
-  </si>
-  <si>
-    <t>159995579544624514</t>
-  </si>
-  <si>
-    <t>248747537/1</t>
-  </si>
-  <si>
     <t>SZ-832</t>
   </si>
   <si>
-    <t>248747537</t>
-  </si>
-  <si>
     <t>1119</t>
   </si>
   <si>
-    <t>Bártfai utca</t>
-  </si>
-  <si>
-    <t>6aa272342235a0231b9b28b6</t>
-  </si>
-  <si>
-    <t>260908-W00003013</t>
-  </si>
-  <si>
-    <t>7514</t>
-  </si>
-  <si>
-    <t>TARANY</t>
-  </si>
-  <si>
     <t>Csokonai utca</t>
   </si>
   <si>
-    <t>6aa272342235a0231b9b28b7</t>
-  </si>
-  <si>
-    <t>6ab2728e73749ba5fc07d967</t>
-  </si>
-  <si>
-    <t>260922-F00009838-1</t>
-  </si>
-  <si>
-    <t>Kelemen Béla utca</t>
-  </si>
-  <si>
-    <t>K-9121</t>
-  </si>
-  <si>
-    <t>5400</t>
-  </si>
-  <si>
-    <t>MEZŐTÚR</t>
-  </si>
-  <si>
-    <t>6aba5b84219e3d74bbe413de</t>
-  </si>
-  <si>
-    <t>260928-F00009843</t>
-  </si>
-  <si>
-    <t>5321</t>
-  </si>
-  <si>
-    <t>KUNMADARAS</t>
-  </si>
-  <si>
-    <t>Nagy Imre utca</t>
-  </si>
-  <si>
-    <t>6aba5b84219e3d74bbe413df</t>
-  </si>
-  <si>
-    <t>6aba8363219e3d74bbe41baa</t>
-  </si>
-  <si>
     <t>SZ-838</t>
   </si>
   <si>
-    <t>260928-F00014397</t>
-  </si>
-  <si>
-    <t>Viola utca</t>
-  </si>
-  <si>
-    <t>6abcb131219e3d74bbe4425a</t>
-  </si>
-  <si>
-    <t>260930-F00000674</t>
-  </si>
-  <si>
-    <t>6725</t>
-  </si>
-  <si>
-    <t>Petőfi Sándor sugárút</t>
-  </si>
-  <si>
-    <t>6abcebe1219e3d74bbe44f7d</t>
-  </si>
-  <si>
-    <t>260930-F00007808</t>
-  </si>
-  <si>
-    <t>4523</t>
-  </si>
-  <si>
-    <t>PÁTROHA</t>
-  </si>
-  <si>
-    <t>1449-289813</t>
-  </si>
-  <si>
     <t>SZ-820</t>
   </si>
   <si>
-    <t>267013875</t>
-  </si>
-  <si>
     <t>2721</t>
   </si>
   <si>
     <t>PILIS</t>
   </si>
   <si>
-    <t>Deák Ferenc u</t>
-  </si>
-  <si>
-    <t>1449-507549</t>
-  </si>
-  <si>
-    <t>K-971</t>
-  </si>
-  <si>
-    <t>267013997</t>
-  </si>
-  <si>
-    <t>2840</t>
-  </si>
-  <si>
-    <t>OROSZLÁNY</t>
-  </si>
-  <si>
-    <t>Bokodi út</t>
-  </si>
-  <si>
-    <t>1449-259083</t>
-  </si>
-  <si>
-    <t>K-961</t>
-  </si>
-  <si>
-    <t>267014088</t>
-  </si>
-  <si>
-    <t>3998</t>
-  </si>
-  <si>
-    <t>NYÍRI</t>
-  </si>
-  <si>
-    <t>1449-110326</t>
-  </si>
-  <si>
-    <t>267014093</t>
-  </si>
-  <si>
-    <t>7012</t>
-  </si>
-  <si>
-    <t>ALSÓSZENTIVÁN</t>
-  </si>
-  <si>
-    <t>1449-522600_2</t>
-  </si>
-  <si>
-    <t>267014153</t>
-  </si>
-  <si>
-    <t>5420</t>
-  </si>
-  <si>
-    <t>TÚRKEVE</t>
-  </si>
-  <si>
-    <t>Bélakirály utca</t>
-  </si>
-  <si>
-    <t>328225386/1</t>
-  </si>
-  <si>
-    <t>328225386</t>
-  </si>
-  <si>
-    <t>Táncsics Mihály Utca</t>
-  </si>
-  <si>
-    <t>328225386/2</t>
-  </si>
-  <si>
-    <t>328225386/3</t>
-  </si>
-  <si>
-    <t>329205290/1</t>
-  </si>
-  <si>
-    <t>329205290</t>
-  </si>
-  <si>
-    <t>Hollós Korvin Lajos Utca</t>
-  </si>
-  <si>
-    <t>329205290/2</t>
-  </si>
-  <si>
-    <t>329738914/1</t>
-  </si>
-  <si>
-    <t>329738914</t>
-  </si>
-  <si>
-    <t>2330</t>
-  </si>
-  <si>
-    <t>DUNAHARASZTI</t>
-  </si>
-  <si>
-    <t>Templom Utca</t>
-  </si>
-  <si>
-    <t>329738914/2</t>
-  </si>
-  <si>
-    <t>329841762/1</t>
-  </si>
-  <si>
-    <t>K-999</t>
-  </si>
-  <si>
-    <t>329841762</t>
-  </si>
-  <si>
-    <t>5537</t>
-  </si>
-  <si>
-    <t>ZSADÁNY</t>
-  </si>
-  <si>
-    <t>329841762/2</t>
-  </si>
-  <si>
-    <t>329892180/1</t>
-  </si>
-  <si>
-    <t>329892180</t>
-  </si>
-  <si>
     <t>Szél utca</t>
   </si>
   <si>
-    <t>329892180/2</t>
-  </si>
-  <si>
-    <t>329892180/3</t>
-  </si>
-  <si>
-    <t>329939235/1</t>
-  </si>
-  <si>
-    <t>329939235</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>Békési utca</t>
-  </si>
-  <si>
-    <t>330231156/1</t>
-  </si>
-  <si>
-    <t>K-921</t>
-  </si>
-  <si>
-    <t>330231156</t>
-  </si>
-  <si>
-    <t>2060</t>
-  </si>
-  <si>
-    <t>BICSKE</t>
-  </si>
-  <si>
-    <t>Csákvári út</t>
-  </si>
-  <si>
-    <t>330231156/2</t>
-  </si>
-  <si>
-    <t>330231762/1</t>
-  </si>
-  <si>
-    <t>330231762</t>
-  </si>
-  <si>
     <t>1172</t>
   </si>
   <si>
-    <t>Alsópetény utca</t>
-  </si>
-  <si>
-    <t>330328981/1</t>
-  </si>
-  <si>
-    <t>330328981</t>
-  </si>
-  <si>
     <t>1181</t>
   </si>
   <si>
-    <t>Vikár Béla Utca</t>
-  </si>
-  <si>
-    <t>330328981/2</t>
-  </si>
-  <si>
-    <t>330382530/1</t>
-  </si>
-  <si>
-    <t>330382530</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>Úri utca</t>
-  </si>
-  <si>
-    <t>330382980/1</t>
-  </si>
-  <si>
-    <t>330382980</t>
-  </si>
-  <si>
-    <t>Hungária körút</t>
-  </si>
-  <si>
-    <t>330441274/1</t>
-  </si>
-  <si>
-    <t>330441274</t>
-  </si>
-  <si>
-    <t>7763</t>
-  </si>
-  <si>
-    <t>SZEMELY</t>
-  </si>
-  <si>
-    <t>Zrínyi köz</t>
-  </si>
-  <si>
-    <t>330441274/2</t>
-  </si>
-  <si>
-    <t>330497610/1</t>
-  </si>
-  <si>
-    <t>330497610</t>
-  </si>
-  <si>
-    <t>6600</t>
-  </si>
-  <si>
-    <t>SZENTES</t>
-  </si>
-  <si>
-    <t>Kossuth tér</t>
-  </si>
-  <si>
-    <t>330557871/1</t>
-  </si>
-  <si>
-    <t>330557871</t>
-  </si>
-  <si>
-    <t>2039</t>
-  </si>
-  <si>
-    <t>PUSZTAZÁMOR</t>
-  </si>
-  <si>
-    <t>Park utca</t>
-  </si>
-  <si>
-    <t>330557871/2</t>
-  </si>
-  <si>
-    <t>330558030/1</t>
-  </si>
-  <si>
     <t>SZ-830</t>
   </si>
   <si>
-    <t>330558030</t>
-  </si>
-  <si>
-    <t>2081</t>
-  </si>
-  <si>
-    <t>PILISCSABA</t>
-  </si>
-  <si>
-    <t>Nádas utca</t>
-  </si>
-  <si>
-    <t>330558114/1</t>
-  </si>
-  <si>
-    <t>330558114</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>Kovászna utca</t>
-  </si>
-  <si>
-    <t>330558114/2</t>
-  </si>
-  <si>
-    <t>330613192/1</t>
-  </si>
-  <si>
-    <t>330613192</t>
-  </si>
-  <si>
     <t>2100</t>
   </si>
   <si>
     <t>GÖDÖLLŐ</t>
   </si>
   <si>
-    <t>Pattantyús Ábrahám körút</t>
-  </si>
-  <si>
-    <t>330613273/1</t>
-  </si>
-  <si>
-    <t>330613273</t>
-  </si>
-  <si>
-    <t>2500</t>
-  </si>
-  <si>
-    <t>ESZTERGOM</t>
-  </si>
-  <si>
-    <t>Sugár út</t>
-  </si>
-  <si>
-    <t>330613273/2</t>
-  </si>
-  <si>
-    <t>330613634/1</t>
-  </si>
-  <si>
-    <t>330613634</t>
-  </si>
-  <si>
-    <t>Boldogfalva utca</t>
-  </si>
-  <si>
-    <t>330613634/2</t>
-  </si>
-  <si>
-    <t>330669933/1</t>
-  </si>
-  <si>
-    <t>330669933</t>
-  </si>
-  <si>
-    <t>1173</t>
-  </si>
-  <si>
-    <t>Vanília utca</t>
-  </si>
-  <si>
-    <t>330670308/1</t>
-  </si>
-  <si>
-    <t>330670308</t>
-  </si>
-  <si>
-    <t>Előd utca</t>
-  </si>
-  <si>
-    <t>330795144/1</t>
-  </si>
-  <si>
-    <t>330795144</t>
-  </si>
-  <si>
-    <t>330795294/1</t>
-  </si>
-  <si>
-    <t>330795294</t>
-  </si>
-  <si>
     <t>1086</t>
   </si>
   <si>
-    <t>Teleki László tér</t>
-  </si>
-  <si>
-    <t>330795301/1</t>
-  </si>
-  <si>
-    <t>330795301</t>
-  </si>
-  <si>
-    <t>5501</t>
-  </si>
-  <si>
-    <t>GYOMAENDRŐD</t>
-  </si>
-  <si>
-    <t>Mirhóháti Utca</t>
-  </si>
-  <si>
-    <t>330795318/1</t>
-  </si>
-  <si>
-    <t>330795318</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>Várfok utca</t>
-  </si>
-  <si>
-    <t>330795624/1</t>
-  </si>
-  <si>
-    <t>330795624</t>
-  </si>
-  <si>
-    <t>Bársonyos utca</t>
-  </si>
-  <si>
-    <t>330795674/1</t>
-  </si>
-  <si>
-    <t>330795674</t>
-  </si>
-  <si>
-    <t>4060</t>
-  </si>
-  <si>
-    <t>BALMAZÚJVÁROS</t>
-  </si>
-  <si>
-    <t>330795767/1</t>
-  </si>
-  <si>
-    <t>330795767</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>Albert utca</t>
-  </si>
-  <si>
-    <t>330795862/1</t>
-  </si>
-  <si>
-    <t>330795862</t>
-  </si>
-  <si>
-    <t>2370</t>
-  </si>
-  <si>
-    <t>DABAS</t>
-  </si>
-  <si>
-    <t>Gólya utca</t>
-  </si>
-  <si>
-    <t>330795878/1</t>
-  </si>
-  <si>
-    <t>330795878</t>
-  </si>
-  <si>
-    <t>5085</t>
-  </si>
-  <si>
-    <t>RÁKÓCZIFALVA</t>
-  </si>
-  <si>
-    <t>Kossuth Lajos Út</t>
-  </si>
-  <si>
-    <t>330795878/2</t>
-  </si>
-  <si>
-    <t>330795978/1</t>
-  </si>
-  <si>
-    <t>330795978</t>
-  </si>
-  <si>
-    <t>Nyáry Pál</t>
-  </si>
-  <si>
-    <t>330909222/1</t>
-  </si>
-  <si>
-    <t>330909222</t>
-  </si>
-  <si>
-    <t>Sziget Utca utca</t>
-  </si>
-  <si>
-    <t>330909272/1</t>
-  </si>
-  <si>
-    <t>K-903</t>
-  </si>
-  <si>
-    <t>330909272</t>
-  </si>
-  <si>
-    <t>7090</t>
-  </si>
-  <si>
-    <t>TAMÁSI</t>
-  </si>
-  <si>
-    <t>Kishenye utca</t>
-  </si>
-  <si>
-    <t>330909349/1</t>
-  </si>
-  <si>
-    <t>330909349</t>
-  </si>
-  <si>
-    <t>GÁRDONY</t>
-  </si>
-  <si>
-    <t>Vénusz tér</t>
-  </si>
-  <si>
-    <t>330909415/1</t>
-  </si>
-  <si>
-    <t>330909415</t>
-  </si>
-  <si>
-    <t>4032</t>
-  </si>
-  <si>
-    <t>Egyetem tér</t>
-  </si>
-  <si>
-    <t>330909448/1</t>
-  </si>
-  <si>
-    <t>330909448</t>
-  </si>
-  <si>
-    <t>7700</t>
-  </si>
-  <si>
-    <t>MOHÁCS</t>
-  </si>
-  <si>
-    <t>Duna utca</t>
-  </si>
-  <si>
-    <t>330909530/1</t>
-  </si>
-  <si>
-    <t>330909530</t>
-  </si>
-  <si>
-    <t>1053</t>
-  </si>
-  <si>
-    <t>Veres Pálné utca</t>
-  </si>
-  <si>
-    <t>330909530/2</t>
-  </si>
-  <si>
-    <t>330909530/3</t>
-  </si>
-  <si>
-    <t>331022089/1</t>
-  </si>
-  <si>
-    <t>331022089</t>
-  </si>
-  <si>
-    <t>Pétery Károly utca</t>
-  </si>
-  <si>
-    <t>331022265/1</t>
-  </si>
-  <si>
-    <t>331022265</t>
-  </si>
-  <si>
-    <t>2523</t>
-  </si>
-  <si>
-    <t>SÁRISÁP</t>
-  </si>
-  <si>
     <t>Arany János utca</t>
   </si>
   <si>
-    <t>331022286/1</t>
-  </si>
-  <si>
-    <t>331022286</t>
-  </si>
-  <si>
-    <t>4064</t>
-  </si>
-  <si>
-    <t>NAGYHEGYES</t>
-  </si>
-  <si>
-    <t>Nyugati utca</t>
-  </si>
-  <si>
-    <t>331022459/1</t>
-  </si>
-  <si>
-    <t>331022459</t>
-  </si>
-  <si>
-    <t>8151</t>
-  </si>
-  <si>
-    <t>SZABADBATTYÁN</t>
-  </si>
-  <si>
-    <t>Kölcsey utca</t>
-  </si>
-  <si>
-    <t>331022459/2</t>
-  </si>
-  <si>
-    <t>331022488/1</t>
-  </si>
-  <si>
-    <t>331022488</t>
-  </si>
-  <si>
-    <t>7300</t>
-  </si>
-  <si>
-    <t>KOMLÓ</t>
-  </si>
-  <si>
-    <t>331022502/1</t>
-  </si>
-  <si>
-    <t>K-973</t>
-  </si>
-  <si>
-    <t>331022502</t>
-  </si>
-  <si>
-    <t>9723</t>
-  </si>
-  <si>
-    <t>GYÖNGYÖSFALU</t>
-  </si>
-  <si>
-    <t>331022537/1</t>
-  </si>
-  <si>
-    <t>331022537</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>Szabó Ilonka utca</t>
-  </si>
-  <si>
-    <t>331022632/1</t>
-  </si>
-  <si>
-    <t>331022632</t>
-  </si>
-  <si>
-    <t>3989</t>
-  </si>
-  <si>
-    <t>MIKÓHÁZA</t>
-  </si>
-  <si>
-    <t>Radnóti Miklós utca,</t>
-  </si>
-  <si>
-    <t>331022632/2</t>
-  </si>
-  <si>
-    <t>331022704/1</t>
-  </si>
-  <si>
-    <t>331022704</t>
-  </si>
-  <si>
-    <t>4130</t>
-  </si>
-  <si>
-    <t>DERECSKE</t>
-  </si>
-  <si>
-    <t>Nyúl utca</t>
-  </si>
-  <si>
-    <t>331022810/1</t>
-  </si>
-  <si>
-    <t>331022810</t>
-  </si>
-  <si>
-    <t>6800</t>
-  </si>
-  <si>
-    <t>HÓDMEZŐVÁSÁRHELY</t>
-  </si>
-  <si>
-    <t>Medgyesi utca</t>
-  </si>
-  <si>
-    <t>331022848/1</t>
-  </si>
-  <si>
-    <t>331022848</t>
-  </si>
-  <si>
-    <t>5462</t>
-  </si>
-  <si>
-    <t>CIBAKHÁZA</t>
-  </si>
-  <si>
-    <t>Zrínyi Utca</t>
-  </si>
-  <si>
-    <t>331182320/1</t>
-  </si>
-  <si>
-    <t>331182320</t>
-  </si>
-  <si>
-    <t>3527</t>
-  </si>
-  <si>
-    <t>331182329/1</t>
-  </si>
-  <si>
-    <t>K-953</t>
-  </si>
-  <si>
-    <t>331182329</t>
-  </si>
-  <si>
-    <t>7629</t>
-  </si>
-  <si>
-    <t>Corvin utca</t>
-  </si>
-  <si>
-    <t>331182339/1</t>
-  </si>
-  <si>
-    <t>331182339</t>
-  </si>
-  <si>
-    <t>Munkácsy Mihály utca</t>
-  </si>
-  <si>
-    <t>331182339/2</t>
-  </si>
-  <si>
-    <t>331182437/1</t>
-  </si>
-  <si>
-    <t>331182437</t>
-  </si>
-  <si>
-    <t>Bauer Sándor</t>
-  </si>
-  <si>
-    <t>331182547/1</t>
-  </si>
-  <si>
-    <t>331182547</t>
-  </si>
-  <si>
-    <t>Budai út</t>
-  </si>
-  <si>
-    <t>331182590/1</t>
-  </si>
-  <si>
-    <t>331182590</t>
-  </si>
-  <si>
-    <t>2316</t>
-  </si>
-  <si>
-    <t>TÖKÖL</t>
-  </si>
-  <si>
-    <t>Ibolya utca</t>
-  </si>
-  <si>
-    <t>331182609/1</t>
-  </si>
-  <si>
-    <t>331182609</t>
-  </si>
-  <si>
-    <t>Nagybányai utca</t>
-  </si>
-  <si>
-    <t>331182845/1</t>
-  </si>
-  <si>
-    <t>331182845</t>
-  </si>
-  <si>
-    <t>Alkotmány utca</t>
-  </si>
-  <si>
-    <t>331183054/1</t>
-  </si>
-  <si>
-    <t>331183054</t>
-  </si>
-  <si>
-    <t>Pozsonyi utca</t>
-  </si>
-  <si>
-    <t>331183131/1</t>
-  </si>
-  <si>
-    <t>331183131</t>
-  </si>
-  <si>
-    <t>Őzike utca</t>
-  </si>
-  <si>
-    <t>331183207/1</t>
-  </si>
-  <si>
-    <t>331183207</t>
-  </si>
-  <si>
-    <t>Rupphegyi út</t>
-  </si>
-  <si>
-    <t>331183245/1</t>
-  </si>
-  <si>
-    <t>331183245</t>
-  </si>
-  <si>
-    <t>Gárdonyi utca</t>
-  </si>
-  <si>
     <t>331183263/1</t>
   </si>
   <si>
@@ -1344,490 +207,1639 @@
     <t>331183263/2</t>
   </si>
   <si>
-    <t>331183270/1</t>
-  </si>
-  <si>
-    <t>331183270</t>
-  </si>
-  <si>
-    <t>Zoltán utca</t>
-  </si>
-  <si>
-    <t>331280445/1</t>
-  </si>
-  <si>
-    <t>331280445</t>
-  </si>
-  <si>
-    <t>7122</t>
-  </si>
-  <si>
-    <t>KAKASD</t>
-  </si>
-  <si>
-    <t>331280445/2</t>
-  </si>
-  <si>
-    <t>331280487/1</t>
-  </si>
-  <si>
-    <t>K-991</t>
-  </si>
-  <si>
-    <t>331280487</t>
-  </si>
-  <si>
-    <t>6453</t>
-  </si>
-  <si>
-    <t>BÁCSBOKOD</t>
-  </si>
-  <si>
-    <t>Ménes utca</t>
-  </si>
-  <si>
-    <t>331280527/1</t>
-  </si>
-  <si>
-    <t>331280527</t>
-  </si>
-  <si>
-    <t>Római körút</t>
-  </si>
-  <si>
-    <t>331280687/1</t>
-  </si>
-  <si>
-    <t>331280687</t>
-  </si>
-  <si>
-    <t>Kürt Utca</t>
-  </si>
-  <si>
-    <t>331280928/1</t>
-  </si>
-  <si>
-    <t>331280928</t>
-  </si>
-  <si>
-    <t>4400</t>
-  </si>
-  <si>
-    <t>NYÍREGYHÁZA</t>
-  </si>
-  <si>
-    <t>331280931/1</t>
-  </si>
-  <si>
-    <t>331280931</t>
-  </si>
-  <si>
-    <t>6771</t>
-  </si>
-  <si>
-    <t>Szerb utca</t>
-  </si>
-  <si>
-    <t>331281014/1</t>
-  </si>
-  <si>
-    <t>331281014</t>
-  </si>
-  <si>
-    <t>7570</t>
-  </si>
-  <si>
-    <t>BARCS</t>
-  </si>
-  <si>
-    <t>331281065/1</t>
-  </si>
-  <si>
-    <t>331281065</t>
-  </si>
-  <si>
-    <t>4080</t>
-  </si>
-  <si>
-    <t>HAJDÚNÁNÁS</t>
-  </si>
-  <si>
-    <t>Bocskai Út</t>
-  </si>
-  <si>
-    <t>331281128/1</t>
-  </si>
-  <si>
-    <t>331281128</t>
-  </si>
-  <si>
-    <t>9245</t>
-  </si>
-  <si>
-    <t>MOSONSZOLNOK</t>
-  </si>
-  <si>
-    <t>Akácfa utca</t>
-  </si>
-  <si>
-    <t>331281150/1</t>
-  </si>
-  <si>
-    <t>331281150</t>
-  </si>
-  <si>
-    <t>Erdősor út</t>
-  </si>
-  <si>
-    <t>331281255/1</t>
-  </si>
-  <si>
-    <t>331281255</t>
-  </si>
-  <si>
-    <t>2457</t>
-  </si>
-  <si>
-    <t>ADONY</t>
-  </si>
-  <si>
     <t>Ady Endre utca</t>
   </si>
   <si>
-    <t>331281339/1</t>
-  </si>
-  <si>
-    <t>331281339</t>
-  </si>
-  <si>
-    <t>Kosztolányi Dezső utca</t>
-  </si>
-  <si>
-    <t>331281370/1</t>
-  </si>
-  <si>
-    <t>331281370</t>
-  </si>
-  <si>
-    <t>4551</t>
-  </si>
-  <si>
-    <t>Szilvavölgy sétány</t>
-  </si>
-  <si>
-    <t>331365340/1</t>
-  </si>
-  <si>
-    <t>331365340</t>
-  </si>
-  <si>
-    <t>9400</t>
-  </si>
-  <si>
-    <t>SOPRON</t>
-  </si>
-  <si>
-    <t>SZENT MIHÁLY utca</t>
-  </si>
-  <si>
-    <t>331365467/1</t>
-  </si>
-  <si>
-    <t>331365467</t>
-  </si>
-  <si>
-    <t>331366091/1</t>
-  </si>
-  <si>
-    <t>331366091</t>
-  </si>
-  <si>
-    <t>Kánai út</t>
-  </si>
-  <si>
-    <t>331366180/1</t>
-  </si>
-  <si>
-    <t>331366180</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>Attila út</t>
-  </si>
-  <si>
-    <t>331366197/1</t>
-  </si>
-  <si>
-    <t>331366197</t>
-  </si>
-  <si>
-    <t>Magyar Lajos utca</t>
-  </si>
-  <si>
-    <t>331366249/1</t>
-  </si>
-  <si>
-    <t>331366249</t>
-  </si>
-  <si>
-    <t>8100</t>
-  </si>
-  <si>
-    <t>VÁRPALOTA</t>
-  </si>
-  <si>
-    <t>331430734/1</t>
-  </si>
-  <si>
-    <t>331430734</t>
-  </si>
-  <si>
-    <t>2400</t>
-  </si>
-  <si>
-    <t>DUNAÚJVÁROS</t>
-  </si>
-  <si>
-    <t>Apáczai Csere János út</t>
-  </si>
-  <si>
-    <t>331430734/2</t>
-  </si>
-  <si>
-    <t>331430734/3</t>
-  </si>
-  <si>
-    <t>331430973/1</t>
-  </si>
-  <si>
-    <t>331430973</t>
-  </si>
-  <si>
-    <t>4355</t>
-  </si>
-  <si>
-    <t>NAGYECSED</t>
-  </si>
-  <si>
-    <t>99003403/1</t>
-  </si>
-  <si>
-    <t>99003403</t>
-  </si>
-  <si>
     <t>2628</t>
   </si>
   <si>
     <t>SZOB</t>
   </si>
   <si>
-    <t>Préskert utca</t>
-  </si>
-  <si>
-    <t>99003422/1</t>
-  </si>
-  <si>
-    <t>99003422</t>
-  </si>
-  <si>
-    <t>Szeszgyár utca</t>
-  </si>
-  <si>
-    <t>202609232601985201</t>
-  </si>
-  <si>
-    <t>NFD6-09-22-9XU7</t>
-  </si>
-  <si>
-    <t>4225</t>
-  </si>
-  <si>
-    <t>Tokaji utca</t>
-  </si>
-  <si>
-    <t>202609232601985202</t>
-  </si>
-  <si>
-    <t>202609232601985203</t>
-  </si>
-  <si>
-    <t>202609232601985204</t>
-  </si>
-  <si>
-    <t>202609232601985205</t>
-  </si>
-  <si>
-    <t>202609302602018601</t>
-  </si>
-  <si>
-    <t>NFD6-09-29-V5GV</t>
-  </si>
-  <si>
-    <t>Franciska utca</t>
-  </si>
-  <si>
-    <t>202610022602025001</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-CHPH</t>
-  </si>
-  <si>
-    <t>5061</t>
-  </si>
-  <si>
-    <t>TISZASÜLY</t>
-  </si>
-  <si>
-    <t>202610022602027701</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-LYHG</t>
-  </si>
-  <si>
-    <t>Perényi Zsigmond utca</t>
-  </si>
-  <si>
-    <t>202610022602029201</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-ND9X</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>Bukarest utca</t>
-  </si>
-  <si>
-    <t>202610022602024701</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-V7HM</t>
-  </si>
-  <si>
     <t>2234</t>
   </si>
   <si>
     <t>MAGLÓD</t>
   </si>
   <si>
-    <t>Sallai utca</t>
-  </si>
-  <si>
-    <t>202610022602024702</t>
-  </si>
-  <si>
-    <t>202610022602029101</t>
-  </si>
-  <si>
-    <t>NFD6-10-01-ZD6S</t>
-  </si>
-  <si>
-    <t>Bebo Károly utca</t>
-  </si>
-  <si>
-    <t>159995579544811914</t>
-  </si>
-  <si>
-    <t>R437481</t>
-  </si>
-  <si>
-    <t>4431</t>
-  </si>
-  <si>
-    <t>Állomás utca</t>
-  </si>
-  <si>
-    <t>159995579544748579</t>
-  </si>
-  <si>
-    <t>R437649</t>
-  </si>
-  <si>
-    <t>7054</t>
-  </si>
-  <si>
-    <t>TENGELIC</t>
-  </si>
-  <si>
-    <t>Rákóczi F</t>
-  </si>
-  <si>
-    <t>159995579544748654</t>
-  </si>
-  <si>
-    <t>R437754</t>
-  </si>
-  <si>
-    <t>Ívelő sétány</t>
-  </si>
-  <si>
-    <t>159995579544748661</t>
-  </si>
-  <si>
-    <t>159995579544748678</t>
-  </si>
-  <si>
-    <t>159995579544748487</t>
-  </si>
-  <si>
-    <t>R437885</t>
-  </si>
-  <si>
-    <t>Makó utca</t>
-  </si>
-  <si>
-    <t>159995579544811723</t>
-  </si>
-  <si>
-    <t>R438006</t>
-  </si>
-  <si>
-    <t>6781</t>
-  </si>
-  <si>
-    <t>DOMASZÉK</t>
-  </si>
-  <si>
-    <t>159995579544811730</t>
-  </si>
-  <si>
-    <t>159995579544811747</t>
-  </si>
-  <si>
-    <t>159995579544811754</t>
-  </si>
-  <si>
-    <t>159995579544811761</t>
-  </si>
-  <si>
-    <t>159995579544812010</t>
-  </si>
-  <si>
-    <t>R438243</t>
-  </si>
-  <si>
-    <t>3534</t>
-  </si>
-  <si>
-    <t>Bertalan utca</t>
-  </si>
-  <si>
-    <t>159995579544750916</t>
-  </si>
-  <si>
-    <t>SA26/H006979</t>
-  </si>
-  <si>
     <t>Baross utca</t>
   </si>
   <si>
-    <t>PICIGURMAN</t>
-  </si>
-  <si>
-    <t>159995579544750923</t>
+    <t>6abe6490219e3d74bbe46f04</t>
+  </si>
+  <si>
+    <t>260830-W00009571</t>
+  </si>
+  <si>
+    <t>Báthory utca</t>
+  </si>
+  <si>
+    <t>6abfa761219e3d74bbe482ab</t>
+  </si>
+  <si>
+    <t>260911-F00009205</t>
+  </si>
+  <si>
+    <t>Ezerfürtű utca</t>
+  </si>
+  <si>
+    <t>6abba415219e3d74bbe42f5d</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>260921-F00011312</t>
+  </si>
+  <si>
+    <t>1138</t>
+  </si>
+  <si>
+    <t>Népfürdő utca</t>
+  </si>
+  <si>
+    <t>6abf9419219e3d74bbe4800d</t>
+  </si>
+  <si>
+    <t>260923-F00005473</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>Alsómalom utca</t>
+  </si>
+  <si>
+    <t>6abcf6d1219e3d74bbe451a8</t>
+  </si>
+  <si>
+    <t>260924-F00007201</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>II. Rákóczi Ferenc út</t>
+  </si>
+  <si>
+    <t>6abfb376219e3d74bbe48486</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>260924-F00008209-1</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>Ónodi utca</t>
+  </si>
+  <si>
+    <t>6abe23fb219e3d74bbe46520</t>
+  </si>
+  <si>
+    <t>260925-F00006702</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Kőér köz</t>
+  </si>
+  <si>
+    <t>6ab66f3e219e3d74bbe3df5f</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>260925-F00009844-1</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>Szántóföld utca</t>
+  </si>
+  <si>
+    <t>6abf7dfa219e3d74bbe47c7e</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>260926-F00002405</t>
+  </si>
+  <si>
+    <t>Háros utca</t>
+  </si>
+  <si>
+    <t>6ab7cb40219e3d74bbe3f616</t>
+  </si>
+  <si>
+    <t>260926-F00004957</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>Gladiátor utca</t>
+  </si>
+  <si>
+    <t>6abe24dd219e3d74bbe4654f</t>
+  </si>
+  <si>
+    <t>260926-F00006440</t>
+  </si>
+  <si>
+    <t>Oltvány árok</t>
+  </si>
+  <si>
+    <t>6abe1ee3219e3d74bbe46439</t>
+  </si>
+  <si>
+    <t>260926-W00009064</t>
+  </si>
+  <si>
+    <t>Háromdobos utca</t>
+  </si>
+  <si>
+    <t>6abe1ee3219e3d74bbe4643a</t>
+  </si>
+  <si>
+    <t>6abe6ed9219e3d74bbe47066</t>
+  </si>
+  <si>
+    <t>260927-F00003963</t>
+  </si>
+  <si>
+    <t>Balázs Béla utca</t>
+  </si>
+  <si>
+    <t>6abe6ed9219e3d74bbe47068</t>
+  </si>
+  <si>
+    <t>6abf7a2a219e3d74bbe47bea</t>
+  </si>
+  <si>
+    <t>260928-F00007732</t>
+  </si>
+  <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>Erzsébet királyné útja</t>
+  </si>
+  <si>
+    <t>6ac38201219e3d74bbe4ac8c</t>
+  </si>
+  <si>
+    <t>260928-F00015356</t>
+  </si>
+  <si>
+    <t>Etele út</t>
+  </si>
+  <si>
+    <t>6ac3825d219e3d74bbe4acb9</t>
+  </si>
+  <si>
+    <t>260928-W00010286</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>Akác köz</t>
+  </si>
+  <si>
+    <t>6abb9b6f219e3d74bbe42d71</t>
+  </si>
+  <si>
+    <t>260929-W00005487</t>
+  </si>
+  <si>
+    <t>1165</t>
+  </si>
+  <si>
+    <t>Dóra tér</t>
+  </si>
+  <si>
+    <t>6abd2e8b219e3d74bbe45b1e</t>
+  </si>
+  <si>
+    <t>260930-F00014200-3</t>
+  </si>
+  <si>
+    <t>Déli-bekötő út</t>
+  </si>
+  <si>
+    <t>6abd07e5219e3d74bbe45536</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>260930-W00007710</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>6abd07e5219e3d74bbe45537</t>
+  </si>
+  <si>
+    <t>6abd1d01219e3d74bbe458b9</t>
+  </si>
+  <si>
+    <t>260930-W00009094</t>
+  </si>
+  <si>
+    <t>Szabadkai utca</t>
+  </si>
+  <si>
+    <t>6abe2705219e3d74bbe465bf</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>261001-F00004400</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Kőrózsa utca</t>
+  </si>
+  <si>
+    <t>6abe2a86219e3d74bbe46641</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>261001-F00004944</t>
+  </si>
+  <si>
+    <t>Koszorú utca</t>
+  </si>
+  <si>
+    <t>6abe36b5219e3d74bbe46865</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>261001-F00006188</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>Tarkő utca</t>
+  </si>
+  <si>
+    <t>6abe36b5219e3d74bbe46866</t>
+  </si>
+  <si>
+    <t>6abe54c2219e3d74bbe46cb2</t>
+  </si>
+  <si>
+    <t>261001-F00009041</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>Pasaréti út</t>
+  </si>
+  <si>
+    <t>6ac360d5219e3d74bbe4a66d</t>
+  </si>
+  <si>
+    <t>261001-F00009268</t>
+  </si>
+  <si>
+    <t>Attila utca</t>
+  </si>
+  <si>
+    <t>6abe7456219e3d74bbe47117</t>
+  </si>
+  <si>
+    <t>261001-F00011556</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>Regős utca</t>
+  </si>
+  <si>
+    <t>6abe02b1219e3d74bbe45fdb</t>
+  </si>
+  <si>
+    <t>261001-W00001793</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>Szigetcsép utca</t>
+  </si>
+  <si>
+    <t>6ac37cd3219e3d74bbe4abde</t>
+  </si>
+  <si>
+    <t>261001-W00003605</t>
+  </si>
+  <si>
+    <t>Szentendrei út</t>
+  </si>
+  <si>
+    <t>6abe2703219e3d74bbe4659f</t>
+  </si>
+  <si>
+    <t>261001-W00003955</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>Mécsvirág utca</t>
+  </si>
+  <si>
+    <t>6abe7a37219e3d74bbe471b8</t>
+  </si>
+  <si>
+    <t>261001-W00008917</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>Gyulai Pál utca</t>
+  </si>
+  <si>
+    <t>6abe7a37219e3d74bbe471ba</t>
+  </si>
+  <si>
+    <t>6abe7ee8219e3d74bbe4721d</t>
+  </si>
+  <si>
+    <t>261001-W00009109</t>
+  </si>
+  <si>
+    <t>Királyok útja</t>
+  </si>
+  <si>
+    <t>6abe7ee8219e3d74bbe4721e</t>
+  </si>
+  <si>
+    <t>6abe800b219e3d74bbe4722b</t>
+  </si>
+  <si>
+    <t>SZ-826</t>
+  </si>
+  <si>
+    <t>261001-W00009316</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>Nefelejcs utca</t>
+  </si>
+  <si>
+    <t>6abe800b219e3d74bbe4722c</t>
+  </si>
+  <si>
+    <t>6abe813e219e3d74bbe47249</t>
+  </si>
+  <si>
+    <t>261001-W00009355</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Váci út</t>
+  </si>
+  <si>
+    <t>6abf95e0219e3d74bbe4804f</t>
+  </si>
+  <si>
+    <t>261002-F00007700</t>
+  </si>
+  <si>
+    <t>Mátyás király út</t>
+  </si>
+  <si>
+    <t>6abf95e0219e3d74bbe48051</t>
+  </si>
+  <si>
+    <t>6abf73db219e3d74bbe47add</t>
+  </si>
+  <si>
+    <t>261002-W00003106</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>Bercsényi utca</t>
+  </si>
+  <si>
+    <t>6abf73db219e3d74bbe47ade</t>
+  </si>
+  <si>
+    <t>6abfaf96219e3d74bbe483fd</t>
+  </si>
+  <si>
+    <t>261002-W00007674</t>
+  </si>
+  <si>
+    <t>Reviczky utca</t>
+  </si>
+  <si>
+    <t>6abfb8f7219e3d74bbe48529</t>
+  </si>
+  <si>
+    <t>261002-W00007937</t>
+  </si>
+  <si>
+    <t>Szőlőliget utca</t>
+  </si>
+  <si>
+    <t>1449-495404</t>
+  </si>
+  <si>
+    <t>267014118</t>
+  </si>
+  <si>
+    <t>2337</t>
+  </si>
+  <si>
+    <t>DÉLEGYHÁZA</t>
+  </si>
+  <si>
+    <t>Faház sor</t>
+  </si>
+  <si>
+    <t>329320160/1</t>
+  </si>
+  <si>
+    <t>329320160</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>Vezseny utca</t>
+  </si>
+  <si>
+    <t>329431545/1</t>
+  </si>
+  <si>
+    <t>329431545</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Tárogató út</t>
+  </si>
+  <si>
+    <t>329431545/2</t>
+  </si>
+  <si>
+    <t>330183706/1</t>
+  </si>
+  <si>
+    <t>330183706</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>Szigeti József Utca</t>
+  </si>
+  <si>
+    <t>330441004/1</t>
+  </si>
+  <si>
+    <t>330441004</t>
+  </si>
+  <si>
+    <t>2131</t>
+  </si>
+  <si>
+    <t>GÖD</t>
+  </si>
+  <si>
+    <t>330441013/1</t>
+  </si>
+  <si>
+    <t>330441013</t>
+  </si>
+  <si>
+    <t>2162</t>
+  </si>
+  <si>
+    <t>ŐRBOTTYÁN</t>
+  </si>
+  <si>
+    <t>Rákóczi Ferenc utca</t>
+  </si>
+  <si>
+    <t>330613095/1</t>
+  </si>
+  <si>
+    <t>330613095</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>ERDŐKERTES</t>
+  </si>
+  <si>
+    <t>Dobó utca</t>
+  </si>
+  <si>
+    <t>330669727/1</t>
+  </si>
+  <si>
+    <t>330669727</t>
+  </si>
+  <si>
+    <t>1061</t>
+  </si>
+  <si>
+    <t>Paulay Ede utca</t>
+  </si>
+  <si>
+    <t>330670112/1</t>
+  </si>
+  <si>
+    <t>330670112</t>
+  </si>
+  <si>
+    <t>Rudolf Utca</t>
+  </si>
+  <si>
+    <t>330670517/1</t>
+  </si>
+  <si>
+    <t>330670517</t>
+  </si>
+  <si>
+    <t>2235</t>
+  </si>
+  <si>
+    <t>MENDE</t>
+  </si>
+  <si>
+    <t>330795351/1</t>
+  </si>
+  <si>
+    <t>330795351</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>Adria sétány</t>
+  </si>
+  <si>
+    <t>330795351/2</t>
+  </si>
+  <si>
+    <t>330795351/3</t>
+  </si>
+  <si>
+    <t>330795967/1</t>
+  </si>
+  <si>
+    <t>330795967</t>
+  </si>
+  <si>
+    <t>Dagálysétány utca</t>
+  </si>
+  <si>
+    <t>330909292/1</t>
+  </si>
+  <si>
+    <t>330909292</t>
+  </si>
+  <si>
+    <t>330909492/1</t>
+  </si>
+  <si>
+    <t>330909492</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>Böszörményi út</t>
+  </si>
+  <si>
+    <t>330909492/2</t>
+  </si>
+  <si>
+    <t>330909566/1</t>
+  </si>
+  <si>
+    <t>330909566</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>Haller utca</t>
+  </si>
+  <si>
+    <t>330909689/1</t>
+  </si>
+  <si>
+    <t>330909689</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>Dugonics utca</t>
+  </si>
+  <si>
+    <t>330909837/1</t>
+  </si>
+  <si>
+    <t>330909837</t>
+  </si>
+  <si>
+    <t>Nyáregyházi út</t>
+  </si>
+  <si>
+    <t>330909872/1</t>
+  </si>
+  <si>
+    <t>330909872</t>
+  </si>
+  <si>
+    <t>2730</t>
+  </si>
+  <si>
+    <t>ALBERTIRSA</t>
+  </si>
+  <si>
+    <t>Politzer Ádám utca</t>
+  </si>
+  <si>
+    <t>330910020/1</t>
+  </si>
+  <si>
+    <t>330910020</t>
+  </si>
+  <si>
+    <t>2225</t>
+  </si>
+  <si>
+    <t>ÜLLŐ</t>
+  </si>
+  <si>
+    <t>Árvácska utca</t>
+  </si>
+  <si>
+    <t>330910104/1</t>
+  </si>
+  <si>
+    <t>330910104</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>Telepes Utca</t>
+  </si>
+  <si>
+    <t>330910192/1</t>
+  </si>
+  <si>
+    <t>330910192</t>
+  </si>
+  <si>
+    <t>Columbus utca</t>
+  </si>
+  <si>
+    <t>331021957/1</t>
+  </si>
+  <si>
+    <t>331021957</t>
+  </si>
+  <si>
+    <t>Fehéregyházi út</t>
+  </si>
+  <si>
+    <t>331022067/1</t>
+  </si>
+  <si>
+    <t>331022067</t>
+  </si>
+  <si>
+    <t>Hárshegyi út</t>
+  </si>
+  <si>
+    <t>331022067/2</t>
+  </si>
+  <si>
+    <t>331022085/1</t>
+  </si>
+  <si>
+    <t>331022085</t>
+  </si>
+  <si>
+    <t>Zsolnay Vilmos utca</t>
+  </si>
+  <si>
+    <t>331022213/1</t>
+  </si>
+  <si>
+    <t>331022213</t>
+  </si>
+  <si>
+    <t>2144</t>
+  </si>
+  <si>
+    <t>KEREPES</t>
+  </si>
+  <si>
+    <t>Szőlő utca</t>
+  </si>
+  <si>
+    <t>331022252/1</t>
+  </si>
+  <si>
+    <t>331022252</t>
+  </si>
+  <si>
+    <t>2750</t>
+  </si>
+  <si>
+    <t>NAGYKŐRÖS</t>
+  </si>
+  <si>
+    <t>Sarkantyú utca</t>
+  </si>
+  <si>
+    <t>331022310/1</t>
+  </si>
+  <si>
+    <t>331022310</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>Madarász Viktor utca</t>
+  </si>
+  <si>
+    <t>331022310/2</t>
+  </si>
+  <si>
+    <t>331022393/1</t>
+  </si>
+  <si>
+    <t>331022393</t>
+  </si>
+  <si>
+    <t>Fehérvári Út út</t>
+  </si>
+  <si>
+    <t>331022428/1</t>
+  </si>
+  <si>
+    <t>331022428</t>
+  </si>
+  <si>
+    <t>Maléter Pál</t>
+  </si>
+  <si>
+    <t>331022428/2</t>
+  </si>
+  <si>
+    <t>331022560/1</t>
+  </si>
+  <si>
+    <t>331022560</t>
+  </si>
+  <si>
+    <t>331022586/1</t>
+  </si>
+  <si>
+    <t>331022586</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>Székely Bertalan utca</t>
+  </si>
+  <si>
+    <t>331022657/1</t>
+  </si>
+  <si>
+    <t>331022657</t>
+  </si>
+  <si>
+    <t>Budafoki út</t>
+  </si>
+  <si>
+    <t>331022817/1</t>
+  </si>
+  <si>
+    <t>331022817</t>
+  </si>
+  <si>
+    <t>Erdőszél utca</t>
+  </si>
+  <si>
+    <t>331022843/1</t>
+  </si>
+  <si>
+    <t>331022843</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>Külső Szilágyi út</t>
+  </si>
+  <si>
+    <t>331022843/2</t>
+  </si>
+  <si>
+    <t>331022843/3</t>
+  </si>
+  <si>
+    <t>331182317/1</t>
+  </si>
+  <si>
+    <t>331182317</t>
+  </si>
+  <si>
+    <t>Nagykikinda utca</t>
+  </si>
+  <si>
+    <t>331182456/1</t>
+  </si>
+  <si>
+    <t>331182456</t>
+  </si>
+  <si>
+    <t>2254</t>
+  </si>
+  <si>
+    <t>SZENTMÁRTONKÁTA</t>
+  </si>
+  <si>
+    <t>Bacsó Béla Út</t>
+  </si>
+  <si>
+    <t>331182570/1</t>
+  </si>
+  <si>
+    <t>331182570</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>Klapka Utca utca</t>
+  </si>
+  <si>
+    <t>331182600/1</t>
+  </si>
+  <si>
+    <t>331182600</t>
+  </si>
+  <si>
+    <t>Wekerle Utca</t>
+  </si>
+  <si>
+    <t>331182637/1</t>
+  </si>
+  <si>
+    <t>331182637</t>
+  </si>
+  <si>
+    <t>2170</t>
+  </si>
+  <si>
+    <t>ASZÓD</t>
+  </si>
+  <si>
+    <t>331182748/1</t>
+  </si>
+  <si>
+    <t>331182748</t>
+  </si>
+  <si>
+    <t>Március utca</t>
+  </si>
+  <si>
+    <t>331183016/1</t>
+  </si>
+  <si>
+    <t>331183016</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>331183154/1</t>
+  </si>
+  <si>
+    <t>331183154</t>
+  </si>
+  <si>
+    <t>2700</t>
+  </si>
+  <si>
+    <t>CEGLÉD</t>
+  </si>
+  <si>
+    <t>Örkényi út</t>
+  </si>
+  <si>
+    <t>331280551/1</t>
+  </si>
+  <si>
+    <t>331280551</t>
+  </si>
+  <si>
+    <t>2768</t>
+  </si>
+  <si>
+    <t>ÚJSZILVÁS</t>
+  </si>
+  <si>
+    <t>331280666/1</t>
+  </si>
+  <si>
+    <t>331280666</t>
+  </si>
+  <si>
+    <t>Kasza utca</t>
+  </si>
+  <si>
+    <t>331280666/2</t>
+  </si>
+  <si>
+    <t>331280753/1</t>
+  </si>
+  <si>
+    <t>331280753</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>Hajnóczy József utca</t>
+  </si>
+  <si>
+    <t>331280823/1</t>
+  </si>
+  <si>
+    <t>331280823</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>Kárpát utca</t>
+  </si>
+  <si>
+    <t>331280834/1</t>
+  </si>
+  <si>
+    <t>331280834</t>
+  </si>
+  <si>
+    <t>Nyírfa utca</t>
+  </si>
+  <si>
+    <t>331281131/1</t>
+  </si>
+  <si>
+    <t>331281131</t>
+  </si>
+  <si>
+    <t>Fogarasi út</t>
+  </si>
+  <si>
+    <t>331281131/2</t>
+  </si>
+  <si>
+    <t>331281215/1</t>
+  </si>
+  <si>
+    <t>331281215</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>Almássy tér</t>
+  </si>
+  <si>
+    <t>331365349/1</t>
+  </si>
+  <si>
+    <t>331365349</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Kiskorona utca</t>
+  </si>
+  <si>
+    <t>331365377/1</t>
+  </si>
+  <si>
+    <t>331365377</t>
+  </si>
+  <si>
+    <t>331365717/1</t>
+  </si>
+  <si>
+    <t>331365717</t>
+  </si>
+  <si>
+    <t>2760</t>
+  </si>
+  <si>
+    <t>NAGYKÁTA</t>
+  </si>
+  <si>
+    <t>Rózsavölgyi Márk utca</t>
+  </si>
+  <si>
+    <t>331365792/1</t>
+  </si>
+  <si>
+    <t>331365792</t>
+  </si>
+  <si>
+    <t>Muhar utca</t>
+  </si>
+  <si>
+    <t>331365844/1</t>
+  </si>
+  <si>
+    <t>331365844</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>Füredi utca</t>
+  </si>
+  <si>
+    <t>331365915/1</t>
+  </si>
+  <si>
+    <t>331365915</t>
+  </si>
+  <si>
+    <t>Bőszénfa utca</t>
+  </si>
+  <si>
+    <t>331365979/1</t>
+  </si>
+  <si>
+    <t>331365979</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>Nemes utca</t>
+  </si>
+  <si>
+    <t>331365979/2</t>
+  </si>
+  <si>
+    <t>331366002/1</t>
+  </si>
+  <si>
+    <t>331366002</t>
+  </si>
+  <si>
+    <t>MADARÁSZ VIKTOR UTCA</t>
+  </si>
+  <si>
+    <t>331366036/1</t>
+  </si>
+  <si>
+    <t>331366036</t>
+  </si>
+  <si>
+    <t>Delej utca</t>
+  </si>
+  <si>
+    <t>331366036/2</t>
+  </si>
+  <si>
+    <t>331366106/1</t>
+  </si>
+  <si>
+    <t>331366106</t>
+  </si>
+  <si>
+    <t>Podhorszky utca</t>
+  </si>
+  <si>
+    <t>331366237/1</t>
+  </si>
+  <si>
+    <t>331366237</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>Epreserdő utca</t>
+  </si>
+  <si>
+    <t>331366237/2</t>
+  </si>
+  <si>
+    <t>331430779/1</t>
+  </si>
+  <si>
+    <t>331430779</t>
+  </si>
+  <si>
+    <t>331430868/1</t>
+  </si>
+  <si>
+    <t>331430868</t>
+  </si>
+  <si>
+    <t>2377</t>
+  </si>
+  <si>
+    <t>ÖRKÉNY</t>
+  </si>
+  <si>
+    <t>202610052602031601</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-2Z55</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>Tűzliliom utca</t>
+  </si>
+  <si>
+    <t>202610052602031401</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-C6YW</t>
+  </si>
+  <si>
+    <t>2040</t>
+  </si>
+  <si>
+    <t>BUDAÖRS</t>
+  </si>
+  <si>
+    <t>Árpád utca</t>
+  </si>
+  <si>
+    <t>202610052602031301</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-DQL3</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>SZIGETSZENTMIKLÓS</t>
+  </si>
+  <si>
+    <t>Folyandár utca</t>
+  </si>
+  <si>
+    <t>202610052602035301</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-FET5</t>
+  </si>
+  <si>
+    <t>Szánthó Géza utca</t>
+  </si>
+  <si>
+    <t>202610052602031001</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-K9MP</t>
+  </si>
+  <si>
+    <t>2143</t>
+  </si>
+  <si>
+    <t>KISTARCSA</t>
+  </si>
+  <si>
+    <t>Kinizsi utca</t>
+  </si>
+  <si>
+    <t>202610052602034601</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-M2ZN</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>Téglagyártó út</t>
+  </si>
+  <si>
+    <t>202610052602032801</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-PVWS</t>
+  </si>
+  <si>
+    <t>Izzó utca</t>
+  </si>
+  <si>
+    <t>202610052602033201</t>
+  </si>
+  <si>
+    <t>NFD6-10-02-ZHMN</t>
+  </si>
+  <si>
+    <t>Diófa utca</t>
+  </si>
+  <si>
+    <t>202610052602037401</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-386Q</t>
+  </si>
+  <si>
+    <t>2365</t>
+  </si>
+  <si>
+    <t>INÁRCS</t>
+  </si>
+  <si>
+    <t>Bajcsy-Zsilinszky út</t>
+  </si>
+  <si>
+    <t>202610052602038901</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-9FMY</t>
+  </si>
+  <si>
+    <t>2133</t>
+  </si>
+  <si>
+    <t>SZŐDLIGET</t>
+  </si>
+  <si>
+    <t>Rigó utca</t>
+  </si>
+  <si>
+    <t>202610052602038201</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-E8JB</t>
+  </si>
+  <si>
+    <t>Szakály Mátyás utca</t>
+  </si>
+  <si>
+    <t>202610052602039601</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-F4SA</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>Háló utca</t>
+  </si>
+  <si>
+    <t>202610052602039801</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-HWR7</t>
+  </si>
+  <si>
+    <t>Falemez utca</t>
+  </si>
+  <si>
+    <t>202610052602037601</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-KLSN</t>
+  </si>
+  <si>
+    <t>2318</t>
+  </si>
+  <si>
+    <t>SZIGETSZENTMÁRTON</t>
+  </si>
+  <si>
+    <t>Hatház utca</t>
+  </si>
+  <si>
+    <t>202610052602038501</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-LRJF</t>
+  </si>
+  <si>
+    <t>2120</t>
+  </si>
+  <si>
+    <t>DUNAKESZI</t>
+  </si>
+  <si>
+    <t>Barátság útja</t>
+  </si>
+  <si>
+    <t>202610052602040801</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-SMJR</t>
+  </si>
+  <si>
+    <t>2220</t>
+  </si>
+  <si>
+    <t>VECSÉS</t>
+  </si>
+  <si>
+    <t>Kellner Dr. utca</t>
+  </si>
+  <si>
+    <t>202610052602039101</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-VFNW</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>Simándi utca</t>
+  </si>
+  <si>
+    <t>202610052602039102</t>
+  </si>
+  <si>
+    <t>202610052602038601</t>
+  </si>
+  <si>
+    <t>NFD6-10-03-Y9XU</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>CEGLÉDBERCEL</t>
+  </si>
+  <si>
+    <t>Cserői út</t>
+  </si>
+  <si>
+    <t>202610052602042601</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-4K4N</t>
+  </si>
+  <si>
+    <t>Farkasfa utca</t>
+  </si>
+  <si>
+    <t>202610052602041901</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-7KFT</t>
+  </si>
+  <si>
+    <t>2241</t>
+  </si>
+  <si>
+    <t>SÜLYSÁP</t>
+  </si>
+  <si>
+    <t>Hunyadi utca</t>
+  </si>
+  <si>
+    <t>202610052602042801</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-9U6R</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>Kecsege utca</t>
+  </si>
+  <si>
+    <t>202610052602043201</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-CBP8</t>
+  </si>
+  <si>
+    <t>2092</t>
+  </si>
+  <si>
+    <t>BUDAKESZI</t>
+  </si>
+  <si>
+    <t>202610052602043401</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-DMC8</t>
+  </si>
+  <si>
+    <t>Bányatelep utca</t>
+  </si>
+  <si>
+    <t>202610052602041501</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-EHBB</t>
+  </si>
+  <si>
+    <t>Katona József utca</t>
+  </si>
+  <si>
+    <t>202610052602041801</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-H7RV</t>
+  </si>
+  <si>
+    <t>Batthyány Lajos utca</t>
+  </si>
+  <si>
+    <t>202610052602042301</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-MVRL</t>
+  </si>
+  <si>
+    <t>Kriván utca</t>
+  </si>
+  <si>
+    <t>202610052602042901</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-RJVL</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>POMÁZ</t>
+  </si>
+  <si>
+    <t>202610052602044601</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-SHUJ</t>
+  </si>
+  <si>
+    <t>202610052602042701</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-WDAT</t>
+  </si>
+  <si>
+    <t>Lujza utca</t>
+  </si>
+  <si>
+    <t>202610052602042501</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-WKDH</t>
+  </si>
+  <si>
+    <t>Zimonyi utca</t>
+  </si>
+  <si>
+    <t>202610062602051201</t>
+  </si>
+  <si>
+    <t>NFD6-10-05-KFFS</t>
+  </si>
+  <si>
+    <t>Gyöngyösi utca</t>
+  </si>
+  <si>
+    <t>202610022602024801</t>
+  </si>
+  <si>
+    <t>NFE6-10-01-BJRH</t>
+  </si>
+  <si>
+    <t>Fodros utca</t>
+  </si>
+  <si>
+    <t>202610052602033701</t>
+  </si>
+  <si>
+    <t>NFE6-10-02-45DB</t>
+  </si>
+  <si>
+    <t>Orczy út</t>
+  </si>
+  <si>
+    <t>202610052602034201</t>
+  </si>
+  <si>
+    <t>NFE6-10-02-9GCU</t>
+  </si>
+  <si>
+    <t>1221</t>
+  </si>
+  <si>
+    <t>202610052602033901</t>
+  </si>
+  <si>
+    <t>NFE6-10-02-AVYM</t>
+  </si>
+  <si>
+    <t>2163</t>
+  </si>
+  <si>
+    <t>VÁCRÁTÓT</t>
+  </si>
+  <si>
+    <t>Bornemissza Gergely utca</t>
+  </si>
+  <si>
+    <t>202610052602030701</t>
+  </si>
+  <si>
+    <t>NFE6-10-02-ELWR</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>CSOBÁNKA</t>
+  </si>
+  <si>
+    <t>202610052602034701</t>
+  </si>
+  <si>
+    <t>NFE6-10-02-MKYX</t>
+  </si>
+  <si>
+    <t>Szilágyi Erzsébet fasor</t>
+  </si>
+  <si>
+    <t>202610052602035801</t>
+  </si>
+  <si>
+    <t>NFE6-10-03-TEJS</t>
+  </si>
+  <si>
+    <t>202610052602045001</t>
+  </si>
+  <si>
+    <t>NFE6-10-04-DADS</t>
+  </si>
+  <si>
+    <t>Szobor utca</t>
+  </si>
+  <si>
+    <t>159995579544811945</t>
+  </si>
+  <si>
+    <t>R438087</t>
+  </si>
+  <si>
+    <t>Jászkisér utca</t>
   </si>
 </sst>
 </file>
@@ -2181,15 +2193,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2218,91 +2230,91 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -2310,22 +2322,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
@@ -2333,22 +2345,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
@@ -2356,22 +2368,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
@@ -2379,22 +2391,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -2402,22 +2414,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -2425,22 +2437,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
@@ -2448,22 +2460,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="H12" t="s">
         <v>10</v>
@@ -2471,850 +2483,850 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
         <v>122</v>
       </c>
-      <c r="D18" t="s">
-        <v>170</v>
-      </c>
       <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s">
         <v>123</v>
       </c>
-      <c r="F18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" t="s">
-        <v>171</v>
-      </c>
       <c r="H18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="H19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="H20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="D23" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="G24" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="H24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="F25" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="H25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="H26" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="D27" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
       </c>
       <c r="G27" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="H27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F28" t="s">
         <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="H28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="F29" t="s">
         <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="H29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
-        <v>197</v>
+        <v>22</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
       </c>
       <c r="G30" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="H30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="C31" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="F31" t="s">
-        <v>203</v>
+        <v>7</v>
       </c>
       <c r="G31" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="H31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>203</v>
+        <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="H32" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E33" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="E34" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="H34" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="E35" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="E36" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="H36" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
       </c>
       <c r="G37" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="H37" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>22</v>
       </c>
       <c r="F38" t="s">
-        <v>225</v>
+        <v>7</v>
       </c>
       <c r="G38" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="H38" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s">
-        <v>225</v>
+        <v>7</v>
       </c>
       <c r="G39" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="H39" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="G40" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="H40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="E41" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="F41" t="s">
-        <v>236</v>
+        <v>7</v>
       </c>
       <c r="G41" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="H41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
-        <v>236</v>
+        <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="H42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="E43" t="s">
-        <v>242</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>243</v>
+        <v>7</v>
       </c>
       <c r="G43" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="H43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="E44" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
       </c>
       <c r="G44" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="H44" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="E45" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
       </c>
       <c r="G45" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="H45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="E46" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="F46" t="s">
-        <v>253</v>
+        <v>7</v>
       </c>
       <c r="G46" t="s">
-        <v>254</v>
+        <v>210</v>
       </c>
       <c r="H46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="E47" t="s">
-        <v>257</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>258</v>
+        <v>7</v>
       </c>
       <c r="G47" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="H47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="E48" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="F48" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="G48" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="H48" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="E49" t="s">
-        <v>99</v>
+        <v>221</v>
       </c>
       <c r="F49" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G49" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -3322,22 +3334,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G50" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -3345,22 +3357,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="D51" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="E51" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
       </c>
       <c r="G51" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -3368,22 +3380,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="E52" t="s">
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
       </c>
       <c r="G52" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -3391,22 +3403,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>234</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="G53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -3414,22 +3426,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>236</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="D54" t="s">
-        <v>96</v>
+        <v>237</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>238</v>
       </c>
       <c r="F54" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
       <c r="G54" t="s">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -3437,22 +3449,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="E55" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
+        <v>244</v>
       </c>
       <c r="G55" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -3460,22 +3472,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="E56" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="F56" t="s">
-        <v>281</v>
+        <v>7</v>
       </c>
       <c r="G56" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -3483,22 +3495,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D57" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="E57" t="s">
-        <v>285</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -3506,22 +3518,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="C58" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="F58" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="G58" t="s">
-        <v>289</v>
+        <v>59</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -3529,22 +3541,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D59" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="E59" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="F59" t="s">
-        <v>293</v>
+        <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>38</v>
+        <v>260</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -3552,22 +3564,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="C60" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="D60" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="E60" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -3575,22 +3587,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D61" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="E61" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="F61" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -3598,22 +3610,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="D62" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="E62" t="s">
-        <v>305</v>
+        <v>74</v>
       </c>
       <c r="F62" t="s">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="G62" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -3621,22 +3633,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D63" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="E63" t="s">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="F63" t="s">
-        <v>306</v>
+        <v>244</v>
       </c>
       <c r="G63" t="s">
-        <v>307</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -3644,22 +3656,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="C64" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D64" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="E64" t="s">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
       </c>
       <c r="G64" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -3667,22 +3679,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D65" t="s">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="E65" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="F65" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G65" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -3690,22 +3702,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="C66" t="s">
-        <v>316</v>
+        <v>85</v>
       </c>
       <c r="D66" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="E66" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="F66" t="s">
-        <v>319</v>
+        <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -3713,22 +3725,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="F67" t="s">
-        <v>323</v>
+        <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -3736,22 +3748,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="E68" t="s">
-        <v>327</v>
+        <v>45</v>
       </c>
       <c r="F68" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G68" t="s">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -3759,22 +3771,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>329</v>
+        <v>284</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="E69" t="s">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="F69" t="s">
-        <v>332</v>
+        <v>287</v>
       </c>
       <c r="G69" t="s">
-        <v>333</v>
+        <v>288</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -3782,22 +3794,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="D70" t="s">
-        <v>335</v>
+        <v>290</v>
       </c>
       <c r="E70" t="s">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="F70" t="s">
-        <v>7</v>
+        <v>292</v>
       </c>
       <c r="G70" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -3805,22 +3817,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="E71" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
       </c>
       <c r="G71" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -3828,22 +3840,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="E72" t="s">
-        <v>336</v>
+        <v>119</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
       </c>
       <c r="G72" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -3851,22 +3863,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>302</v>
       </c>
       <c r="E73" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G73" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -3874,22 +3886,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="D74" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="E74" t="s">
-        <v>345</v>
+        <v>225</v>
       </c>
       <c r="F74" t="s">
-        <v>346</v>
+        <v>7</v>
       </c>
       <c r="G74" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -3897,22 +3909,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D75" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="E75" t="s">
-        <v>350</v>
+        <v>225</v>
       </c>
       <c r="F75" t="s">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="G75" t="s">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -3920,22 +3932,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D76" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="E76" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="F76" t="s">
-        <v>356</v>
+        <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>357</v>
+        <v>310</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -3943,22 +3955,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="E77" t="s">
-        <v>355</v>
+        <v>313</v>
       </c>
       <c r="F77" t="s">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="G77" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -3966,22 +3978,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="D78" t="s">
-        <v>360</v>
+        <v>317</v>
       </c>
       <c r="E78" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="F78" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="G78" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -3989,22 +4001,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="C79" t="s">
-        <v>364</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="E79" t="s">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="F79" t="s">
-        <v>367</v>
+        <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
+        <v>324</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -4012,22 +4024,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>368</v>
+        <v>325</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>369</v>
+        <v>322</v>
       </c>
       <c r="E80" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
       <c r="F80" t="s">
         <v>7</v>
       </c>
       <c r="G80" t="s">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -4035,22 +4047,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="C81" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="D81" t="s">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="E81" t="s">
-        <v>374</v>
+        <v>205</v>
       </c>
       <c r="F81" t="s">
-        <v>375</v>
+        <v>7</v>
       </c>
       <c r="G81" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -4058,22 +4070,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>377</v>
+        <v>329</v>
       </c>
       <c r="C82" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="D82" t="s">
-        <v>373</v>
+        <v>330</v>
       </c>
       <c r="E82" t="s">
-        <v>374</v>
+        <v>167</v>
       </c>
       <c r="F82" t="s">
-        <v>375</v>
+        <v>7</v>
       </c>
       <c r="G82" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -4081,22 +4093,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="D83" t="s">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="E83" t="s">
-        <v>380</v>
+        <v>167</v>
       </c>
       <c r="F83" t="s">
-        <v>381</v>
+        <v>7</v>
       </c>
       <c r="G83" t="s">
-        <v>382</v>
+        <v>331</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -4104,22 +4116,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="C84" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="E84" t="s">
-        <v>385</v>
+        <v>87</v>
       </c>
       <c r="F84" t="s">
-        <v>386</v>
+        <v>7</v>
       </c>
       <c r="G84" t="s">
-        <v>387</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -4127,22 +4139,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>388</v>
+        <v>335</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="E85" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="F85" t="s">
-        <v>391</v>
+        <v>7</v>
       </c>
       <c r="G85" t="s">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -4150,22 +4162,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D86" t="s">
-        <v>394</v>
+        <v>340</v>
       </c>
       <c r="E86" t="s">
-        <v>395</v>
+        <v>205</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G86" t="s">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -4173,22 +4185,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="C87" t="s">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>398</v>
+        <v>343</v>
       </c>
       <c r="E87" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="F87" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G87" t="s">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -4196,22 +4208,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>401</v>
+        <v>345</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="E88" t="s">
-        <v>180</v>
+        <v>347</v>
       </c>
       <c r="F88" t="s">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="G88" t="s">
-        <v>403</v>
+        <v>348</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -4219,22 +4231,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D89" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="E89" t="s">
-        <v>180</v>
+        <v>347</v>
       </c>
       <c r="F89" t="s">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="G89" t="s">
-        <v>403</v>
+        <v>348</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -4242,22 +4254,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>405</v>
+        <v>350</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="D90" t="s">
-        <v>406</v>
+        <v>346</v>
       </c>
       <c r="E90" t="s">
-        <v>276</v>
+        <v>347</v>
       </c>
       <c r="F90" t="s">
         <v>7</v>
       </c>
       <c r="G90" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -4265,22 +4277,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>408</v>
+        <v>351</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="D91" t="s">
-        <v>409</v>
+        <v>352</v>
       </c>
       <c r="E91" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="F91" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -4288,22 +4300,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>411</v>
+        <v>354</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D92" t="s">
-        <v>412</v>
+        <v>355</v>
       </c>
       <c r="E92" t="s">
-        <v>413</v>
+        <v>356</v>
       </c>
       <c r="F92" t="s">
-        <v>414</v>
+        <v>357</v>
       </c>
       <c r="G92" t="s">
-        <v>415</v>
+        <v>358</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -4311,22 +4323,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>416</v>
+        <v>359</v>
       </c>
       <c r="C93" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="D93" t="s">
-        <v>417</v>
+        <v>360</v>
       </c>
       <c r="E93" t="s">
-        <v>34</v>
+        <v>361</v>
       </c>
       <c r="F93" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G93" t="s">
-        <v>418</v>
+        <v>362</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -4334,22 +4346,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>419</v>
+        <v>363</v>
       </c>
       <c r="C94" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D94" t="s">
-        <v>420</v>
+        <v>364</v>
       </c>
       <c r="E94" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F94" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G94" t="s">
-        <v>421</v>
+        <v>365</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -4357,22 +4369,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>422</v>
+        <v>366</v>
       </c>
       <c r="C95" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D95" t="s">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="E95" t="s">
-        <v>37</v>
+        <v>368</v>
       </c>
       <c r="F95" t="s">
-        <v>7</v>
+        <v>369</v>
       </c>
       <c r="G95" t="s">
-        <v>424</v>
+        <v>206</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -4380,22 +4392,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>425</v>
+        <v>370</v>
       </c>
       <c r="C96" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="D96" t="s">
-        <v>426</v>
+        <v>371</v>
       </c>
       <c r="E96" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="F96" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="G96" t="s">
-        <v>427</v>
+        <v>372</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -4403,22 +4415,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>428</v>
+        <v>373</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
-        <v>429</v>
+        <v>374</v>
       </c>
       <c r="E97" t="s">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="F97" t="s">
         <v>7</v>
       </c>
       <c r="G97" t="s">
-        <v>430</v>
+        <v>64</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -4426,22 +4438,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>431</v>
+        <v>376</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
       <c r="D98" t="s">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="E98" t="s">
-        <v>30</v>
+        <v>378</v>
       </c>
       <c r="F98" t="s">
-        <v>31</v>
+        <v>379</v>
       </c>
       <c r="G98" t="s">
-        <v>433</v>
+        <v>380</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -4449,22 +4461,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>434</v>
+        <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D99" t="s">
-        <v>435</v>
+        <v>56</v>
       </c>
       <c r="E99" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
         <v>7</v>
       </c>
       <c r="G99" t="s">
-        <v>436</v>
+        <v>57</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -4472,22 +4484,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>437</v>
+        <v>58</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D100" t="s">
-        <v>435</v>
+        <v>56</v>
       </c>
       <c r="E100" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="F100" t="s">
         <v>7</v>
       </c>
       <c r="G100" t="s">
-        <v>436</v>
+        <v>57</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -4495,22 +4507,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="C101" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D101" t="s">
-        <v>439</v>
+        <v>382</v>
       </c>
       <c r="E101" t="s">
-        <v>53</v>
+        <v>383</v>
       </c>
       <c r="F101" t="s">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="G101" t="s">
-        <v>440</v>
+        <v>59</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -4518,22 +4530,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>441</v>
+        <v>385</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="D102" t="s">
-        <v>442</v>
+        <v>386</v>
       </c>
       <c r="E102" t="s">
-        <v>443</v>
+        <v>318</v>
       </c>
       <c r="F102" t="s">
-        <v>444</v>
+        <v>319</v>
       </c>
       <c r="G102" t="s">
-        <v>39</v>
+        <v>387</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -4541,22 +4553,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>445</v>
+        <v>388</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="D103" t="s">
-        <v>442</v>
+        <v>386</v>
       </c>
       <c r="E103" t="s">
-        <v>443</v>
+        <v>318</v>
       </c>
       <c r="F103" t="s">
-        <v>444</v>
+        <v>319</v>
       </c>
       <c r="G103" t="s">
-        <v>39</v>
+        <v>387</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -4564,22 +4576,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>446</v>
+        <v>389</v>
       </c>
       <c r="C104" t="s">
-        <v>447</v>
+        <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>448</v>
+        <v>390</v>
       </c>
       <c r="E104" t="s">
-        <v>449</v>
+        <v>391</v>
       </c>
       <c r="F104" t="s">
-        <v>450</v>
+        <v>7</v>
       </c>
       <c r="G104" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -4587,22 +4599,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="D105" t="s">
-        <v>453</v>
+        <v>394</v>
       </c>
       <c r="E105" t="s">
-        <v>78</v>
+        <v>395</v>
       </c>
       <c r="F105" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>454</v>
+        <v>396</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -4610,22 +4622,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>455</v>
+        <v>397</v>
       </c>
       <c r="C106" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D106" t="s">
-        <v>456</v>
+        <v>398</v>
       </c>
       <c r="E106" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F106" t="s">
-        <v>68</v>
+        <v>217</v>
       </c>
       <c r="G106" t="s">
-        <v>457</v>
+        <v>399</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -4633,22 +4645,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D107" t="s">
-        <v>459</v>
+        <v>401</v>
       </c>
       <c r="E107" t="s">
-        <v>460</v>
+        <v>259</v>
       </c>
       <c r="F107" t="s">
-        <v>461</v>
+        <v>7</v>
       </c>
       <c r="G107" t="s">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -4656,22 +4668,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>462</v>
+        <v>403</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D108" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="E108" t="s">
-        <v>464</v>
+        <v>259</v>
       </c>
       <c r="F108" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G108" t="s">
-        <v>465</v>
+        <v>402</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -4679,22 +4691,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="D109" t="s">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="E109" t="s">
-        <v>468</v>
+        <v>406</v>
       </c>
       <c r="F109" t="s">
-        <v>469</v>
+        <v>7</v>
       </c>
       <c r="G109" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -4702,22 +4714,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>471</v>
+        <v>409</v>
       </c>
       <c r="E110" t="s">
-        <v>472</v>
+        <v>410</v>
       </c>
       <c r="F110" t="s">
-        <v>473</v>
+        <v>7</v>
       </c>
       <c r="G110" t="s">
-        <v>474</v>
+        <v>411</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -4725,22 +4737,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>475</v>
+        <v>412</v>
       </c>
       <c r="C111" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="D111" t="s">
-        <v>476</v>
+        <v>413</v>
       </c>
       <c r="E111" t="s">
-        <v>477</v>
+        <v>155</v>
       </c>
       <c r="F111" t="s">
-        <v>478</v>
+        <v>7</v>
       </c>
       <c r="G111" t="s">
-        <v>479</v>
+        <v>14</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -4748,22 +4760,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="C112" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D112" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="E112" t="s">
-        <v>88</v>
+        <v>416</v>
       </c>
       <c r="F112" t="s">
-        <v>7</v>
+        <v>417</v>
       </c>
       <c r="G112" t="s">
-        <v>482</v>
+        <v>418</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -4771,22 +4783,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>483</v>
+        <v>419</v>
       </c>
       <c r="C113" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
-        <v>484</v>
+        <v>420</v>
       </c>
       <c r="E113" t="s">
-        <v>485</v>
+        <v>146</v>
       </c>
       <c r="F113" t="s">
-        <v>486</v>
+        <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>487</v>
+        <v>421</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -4794,22 +4806,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>488</v>
+        <v>422</v>
       </c>
       <c r="C114" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D114" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="E114" t="s">
-        <v>51</v>
+        <v>424</v>
       </c>
       <c r="F114" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G114" t="s">
-        <v>490</v>
+        <v>425</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -4817,22 +4829,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="C115" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D115" t="s">
-        <v>492</v>
+        <v>427</v>
       </c>
       <c r="E115" t="s">
-        <v>493</v>
+        <v>130</v>
       </c>
       <c r="F115" t="s">
-        <v>461</v>
+        <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>494</v>
+        <v>428</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -4840,22 +4852,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="C116" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="D116" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="E116" t="s">
-        <v>497</v>
+        <v>431</v>
       </c>
       <c r="F116" t="s">
-        <v>498</v>
+        <v>7</v>
       </c>
       <c r="G116" t="s">
-        <v>499</v>
+        <v>432</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -4863,22 +4875,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>500</v>
+        <v>433</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="D117" t="s">
-        <v>501</v>
+        <v>430</v>
       </c>
       <c r="E117" t="s">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="F117" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="G117" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -4886,22 +4898,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>502</v>
+        <v>434</v>
       </c>
       <c r="C118" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D118" t="s">
-        <v>503</v>
+        <v>435</v>
       </c>
       <c r="E118" t="s">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="F118" t="s">
         <v>7</v>
       </c>
       <c r="G118" t="s">
-        <v>504</v>
+        <v>436</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -4909,22 +4921,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>505</v>
+        <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="D119" t="s">
-        <v>506</v>
+        <v>438</v>
       </c>
       <c r="E119" t="s">
-        <v>507</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
         <v>7</v>
       </c>
       <c r="G119" t="s">
-        <v>508</v>
+        <v>439</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -4932,22 +4944,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>509</v>
+        <v>440</v>
       </c>
       <c r="C120" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="D120" t="s">
-        <v>510</v>
+        <v>438</v>
       </c>
       <c r="E120" t="s">
-        <v>71</v>
+        <v>279</v>
       </c>
       <c r="F120" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G120" t="s">
-        <v>511</v>
+        <v>439</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -4955,22 +4967,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>512</v>
+        <v>441</v>
       </c>
       <c r="C121" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="D121" t="s">
-        <v>513</v>
+        <v>442</v>
       </c>
       <c r="E121" t="s">
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="F121" t="s">
-        <v>515</v>
+        <v>7</v>
       </c>
       <c r="G121" t="s">
-        <v>92</v>
+        <v>443</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -4978,22 +4990,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>516</v>
+        <v>444</v>
       </c>
       <c r="C122" t="s">
-        <v>316</v>
+        <v>85</v>
       </c>
       <c r="D122" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
       <c r="E122" t="s">
-        <v>518</v>
+        <v>446</v>
       </c>
       <c r="F122" t="s">
-        <v>519</v>
+        <v>7</v>
       </c>
       <c r="G122" t="s">
-        <v>520</v>
+        <v>447</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -5001,22 +5013,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>521</v>
+        <v>448</v>
       </c>
       <c r="C123" t="s">
-        <v>316</v>
+        <v>85</v>
       </c>
       <c r="D123" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
       <c r="E123" t="s">
-        <v>518</v>
+        <v>446</v>
       </c>
       <c r="F123" t="s">
-        <v>519</v>
+        <v>7</v>
       </c>
       <c r="G123" t="s">
-        <v>520</v>
+        <v>447</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -5024,22 +5036,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>522</v>
+        <v>449</v>
       </c>
       <c r="C124" t="s">
-        <v>316</v>
+        <v>136</v>
       </c>
       <c r="D124" t="s">
-        <v>517</v>
+        <v>450</v>
       </c>
       <c r="E124" t="s">
-        <v>518</v>
+        <v>39</v>
       </c>
       <c r="F124" t="s">
-        <v>519</v>
+        <v>7</v>
       </c>
       <c r="G124" t="s">
-        <v>520</v>
+        <v>59</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -5047,22 +5059,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>523</v>
+        <v>451</v>
       </c>
       <c r="C125" t="s">
+        <v>31</v>
+      </c>
+      <c r="D125" t="s">
+        <v>452</v>
+      </c>
+      <c r="E125" t="s">
+        <v>453</v>
+      </c>
+      <c r="F125" t="s">
+        <v>454</v>
+      </c>
+      <c r="G125" t="s">
         <v>11</v>
-      </c>
-      <c r="D125" t="s">
-        <v>524</v>
-      </c>
-      <c r="E125" t="s">
-        <v>525</v>
-      </c>
-      <c r="F125" t="s">
-        <v>526</v>
-      </c>
-      <c r="G125" t="s">
-        <v>14</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -5070,669 +5082,945 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>527</v>
+        <v>455</v>
       </c>
       <c r="C126" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D126" t="s">
-        <v>528</v>
+        <v>456</v>
       </c>
       <c r="E126" t="s">
-        <v>529</v>
+        <v>457</v>
       </c>
       <c r="F126" t="s">
-        <v>530</v>
+        <v>7</v>
       </c>
       <c r="G126" t="s">
-        <v>531</v>
+        <v>458</v>
       </c>
       <c r="H126" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>532</v>
+        <v>459</v>
       </c>
       <c r="C127" t="s">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="D127" t="s">
-        <v>533</v>
+        <v>460</v>
       </c>
       <c r="E127" t="s">
-        <v>276</v>
+        <v>461</v>
       </c>
       <c r="F127" t="s">
-        <v>7</v>
+        <v>462</v>
       </c>
       <c r="G127" t="s">
-        <v>534</v>
+        <v>463</v>
       </c>
       <c r="H127" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>535</v>
+        <v>464</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D128" t="s">
-        <v>536</v>
+        <v>465</v>
       </c>
       <c r="E128" t="s">
-        <v>537</v>
+        <v>466</v>
       </c>
       <c r="F128" t="s">
-        <v>22</v>
+        <v>467</v>
       </c>
       <c r="G128" t="s">
-        <v>538</v>
+        <v>468</v>
       </c>
       <c r="H128" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>539</v>
+        <v>469</v>
       </c>
       <c r="C129" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="E129" t="s">
-        <v>537</v>
+        <v>171</v>
       </c>
       <c r="F129" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G129" t="s">
-        <v>538</v>
+        <v>471</v>
       </c>
       <c r="H129" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>540</v>
+        <v>472</v>
       </c>
       <c r="C130" t="s">
         <v>21</v>
       </c>
       <c r="D130" t="s">
-        <v>536</v>
+        <v>473</v>
       </c>
       <c r="E130" t="s">
-        <v>537</v>
+        <v>474</v>
       </c>
       <c r="F130" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="G130" t="s">
-        <v>538</v>
+        <v>476</v>
       </c>
       <c r="H130" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>541</v>
+        <v>477</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="D131" t="s">
-        <v>536</v>
+        <v>478</v>
       </c>
       <c r="E131" t="s">
-        <v>537</v>
+        <v>479</v>
       </c>
       <c r="F131" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G131" t="s">
-        <v>538</v>
+        <v>480</v>
       </c>
       <c r="H131" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>542</v>
+        <v>481</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D132" t="s">
-        <v>536</v>
+        <v>482</v>
       </c>
       <c r="E132" t="s">
-        <v>537</v>
+        <v>197</v>
       </c>
       <c r="F132" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G132" t="s">
-        <v>538</v>
+        <v>483</v>
       </c>
       <c r="H132" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>543</v>
+        <v>484</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D133" t="s">
-        <v>544</v>
+        <v>485</v>
       </c>
       <c r="E133" t="s">
-        <v>63</v>
+        <v>474</v>
       </c>
       <c r="F133" t="s">
-        <v>7</v>
+        <v>475</v>
       </c>
       <c r="G133" t="s">
-        <v>545</v>
+        <v>486</v>
       </c>
       <c r="H133" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>546</v>
+        <v>487</v>
       </c>
       <c r="C134" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s">
-        <v>547</v>
+        <v>488</v>
       </c>
       <c r="E134" t="s">
-        <v>548</v>
+        <v>489</v>
       </c>
       <c r="F134" t="s">
-        <v>549</v>
+        <v>490</v>
       </c>
       <c r="G134" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="H134" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>550</v>
+        <v>492</v>
       </c>
       <c r="C135" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D135" t="s">
-        <v>551</v>
+        <v>493</v>
       </c>
       <c r="E135" t="s">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="F135" t="s">
-        <v>7</v>
+        <v>495</v>
       </c>
       <c r="G135" t="s">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="H135" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>553</v>
+        <v>497</v>
       </c>
       <c r="C136" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="D136" t="s">
-        <v>554</v>
+        <v>498</v>
       </c>
       <c r="E136" t="s">
-        <v>555</v>
+        <v>461</v>
       </c>
       <c r="F136" t="s">
-        <v>7</v>
+        <v>462</v>
       </c>
       <c r="G136" t="s">
-        <v>556</v>
+        <v>499</v>
       </c>
       <c r="H136" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D137" t="s">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="E137" t="s">
-        <v>89</v>
+        <v>502</v>
       </c>
       <c r="F137" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>102</v>
+        <v>503</v>
       </c>
       <c r="H137" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>557</v>
+        <v>504</v>
       </c>
       <c r="C138" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D138" t="s">
-        <v>558</v>
+        <v>505</v>
       </c>
       <c r="E138" t="s">
-        <v>559</v>
+        <v>347</v>
       </c>
       <c r="F138" t="s">
-        <v>560</v>
+        <v>7</v>
       </c>
       <c r="G138" t="s">
-        <v>561</v>
+        <v>506</v>
       </c>
       <c r="H138" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>562</v>
+        <v>507</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D139" t="s">
-        <v>558</v>
+        <v>508</v>
       </c>
       <c r="E139" t="s">
-        <v>559</v>
+        <v>509</v>
       </c>
       <c r="F139" t="s">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="G139" t="s">
-        <v>561</v>
+        <v>511</v>
       </c>
       <c r="H139" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>563</v>
+        <v>512</v>
       </c>
       <c r="C140" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D140" t="s">
-        <v>564</v>
+        <v>513</v>
       </c>
       <c r="E140" t="s">
-        <v>49</v>
+        <v>514</v>
       </c>
       <c r="F140" t="s">
-        <v>7</v>
+        <v>515</v>
       </c>
       <c r="G140" t="s">
-        <v>565</v>
+        <v>516</v>
       </c>
       <c r="H140" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>566</v>
+        <v>517</v>
       </c>
       <c r="C141" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="D141" t="s">
-        <v>567</v>
+        <v>518</v>
       </c>
       <c r="E141" t="s">
-        <v>568</v>
+        <v>519</v>
       </c>
       <c r="F141" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="G141" t="s">
-        <v>569</v>
+        <v>521</v>
       </c>
       <c r="H141" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>570</v>
+        <v>522</v>
       </c>
       <c r="C142" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D142" t="s">
-        <v>571</v>
+        <v>523</v>
       </c>
       <c r="E142" t="s">
-        <v>572</v>
+        <v>524</v>
       </c>
       <c r="F142" t="s">
-        <v>573</v>
+        <v>7</v>
       </c>
       <c r="G142" t="s">
-        <v>574</v>
+        <v>525</v>
       </c>
       <c r="H142" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>575</v>
+        <v>526</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D143" t="s">
-        <v>576</v>
+        <v>523</v>
       </c>
       <c r="E143" t="s">
-        <v>47</v>
+        <v>524</v>
       </c>
       <c r="F143" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G143" t="s">
-        <v>577</v>
+        <v>525</v>
       </c>
       <c r="H143" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>578</v>
+        <v>527</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="D144" t="s">
-        <v>576</v>
+        <v>528</v>
       </c>
       <c r="E144" t="s">
-        <v>47</v>
+        <v>529</v>
       </c>
       <c r="F144" t="s">
-        <v>48</v>
+        <v>530</v>
       </c>
       <c r="G144" t="s">
-        <v>577</v>
+        <v>531</v>
       </c>
       <c r="H144" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="C145" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D145" t="s">
-        <v>576</v>
+        <v>533</v>
       </c>
       <c r="E145" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="F145" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G145" t="s">
-        <v>577</v>
+        <v>534</v>
       </c>
       <c r="H145" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>580</v>
+        <v>535</v>
       </c>
       <c r="C146" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D146" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="E146" t="s">
-        <v>497</v>
+        <v>537</v>
       </c>
       <c r="F146" t="s">
-        <v>498</v>
+        <v>538</v>
       </c>
       <c r="G146" t="s">
-        <v>582</v>
+        <v>539</v>
       </c>
       <c r="H146" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>583</v>
+        <v>540</v>
       </c>
       <c r="C147" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D147" t="s">
-        <v>584</v>
+        <v>541</v>
       </c>
       <c r="E147" t="s">
-        <v>585</v>
+        <v>542</v>
       </c>
       <c r="F147" t="s">
-        <v>586</v>
+        <v>7</v>
       </c>
       <c r="G147" t="s">
-        <v>55</v>
+        <v>543</v>
       </c>
       <c r="H147" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D148" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="E148" t="s">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="F148" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="G148" t="s">
-        <v>55</v>
+        <v>315</v>
       </c>
       <c r="H148" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="C149" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D149" t="s">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="E149" t="s">
-        <v>585</v>
+        <v>60</v>
       </c>
       <c r="F149" t="s">
-        <v>586</v>
+        <v>61</v>
       </c>
       <c r="G149" t="s">
-        <v>55</v>
+        <v>550</v>
       </c>
       <c r="H149" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>589</v>
+        <v>551</v>
       </c>
       <c r="C150" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D150" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="E150" t="s">
-        <v>585</v>
+        <v>62</v>
       </c>
       <c r="F150" t="s">
-        <v>586</v>
+        <v>63</v>
       </c>
       <c r="G150" t="s">
-        <v>55</v>
+        <v>553</v>
       </c>
       <c r="H150" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="D151" t="s">
-        <v>584</v>
+        <v>555</v>
       </c>
       <c r="E151" t="s">
-        <v>585</v>
+        <v>49</v>
       </c>
       <c r="F151" t="s">
-        <v>586</v>
+        <v>7</v>
       </c>
       <c r="G151" t="s">
-        <v>55</v>
+        <v>556</v>
       </c>
       <c r="H151" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>591</v>
+        <v>557</v>
       </c>
       <c r="C152" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="D152" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="E152" t="s">
-        <v>593</v>
+        <v>542</v>
       </c>
       <c r="F152" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>594</v>
+        <v>559</v>
       </c>
       <c r="H152" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>595</v>
+        <v>560</v>
       </c>
       <c r="C153" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>596</v>
+        <v>561</v>
       </c>
       <c r="E153" t="s">
-        <v>331</v>
+        <v>562</v>
       </c>
       <c r="F153" t="s">
-        <v>332</v>
+        <v>563</v>
       </c>
       <c r="G153" t="s">
-        <v>597</v>
+        <v>486</v>
       </c>
       <c r="H153" t="s">
-        <v>598</v>
+        <v>18</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>564</v>
+      </c>
+      <c r="C154" t="s">
+        <v>50</v>
+      </c>
+      <c r="D154" t="s">
+        <v>565</v>
+      </c>
+      <c r="E154" t="s">
+        <v>347</v>
+      </c>
+      <c r="F154" t="s">
+        <v>7</v>
+      </c>
+      <c r="G154" t="s">
+        <v>348</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>566</v>
+      </c>
+      <c r="C155" t="s">
+        <v>153</v>
+      </c>
+      <c r="D155" t="s">
+        <v>567</v>
+      </c>
+      <c r="E155" t="s">
+        <v>431</v>
+      </c>
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155" t="s">
+        <v>568</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>569</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156" t="s">
+        <v>570</v>
+      </c>
+      <c r="E156" t="s">
+        <v>171</v>
+      </c>
+      <c r="F156" t="s">
+        <v>7</v>
+      </c>
+      <c r="G156" t="s">
+        <v>571</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>572</v>
+      </c>
+      <c r="C157" t="s">
+        <v>40</v>
+      </c>
+      <c r="D157" t="s">
+        <v>573</v>
+      </c>
+      <c r="E157" t="s">
+        <v>15</v>
+      </c>
+      <c r="F157" t="s">
+        <v>16</v>
+      </c>
+      <c r="G157" t="s">
+        <v>574</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>575</v>
+      </c>
+      <c r="C158" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" t="s">
+        <v>576</v>
+      </c>
+      <c r="E158" t="s">
+        <v>461</v>
+      </c>
+      <c r="F158" t="s">
+        <v>462</v>
+      </c>
+      <c r="G158" t="s">
+        <v>577</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>578</v>
+      </c>
+      <c r="C159" t="s">
+        <v>149</v>
+      </c>
+      <c r="D159" t="s">
+        <v>579</v>
+      </c>
+      <c r="E159" t="s">
+        <v>279</v>
+      </c>
+      <c r="F159" t="s">
+        <v>7</v>
+      </c>
+      <c r="G159" t="s">
+        <v>580</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>581</v>
+      </c>
+      <c r="C160" t="s">
+        <v>99</v>
+      </c>
+      <c r="D160" t="s">
+        <v>582</v>
+      </c>
+      <c r="E160" t="s">
+        <v>583</v>
+      </c>
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+      <c r="G160" t="s">
+        <v>54</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>584</v>
+      </c>
+      <c r="C161" t="s">
+        <v>94</v>
+      </c>
+      <c r="D161" t="s">
+        <v>585</v>
+      </c>
+      <c r="E161" t="s">
+        <v>586</v>
+      </c>
+      <c r="F161" t="s">
+        <v>587</v>
+      </c>
+      <c r="G161" t="s">
+        <v>588</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>589</v>
+      </c>
+      <c r="C162" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" t="s">
+        <v>590</v>
+      </c>
+      <c r="E162" t="s">
+        <v>591</v>
+      </c>
+      <c r="F162" t="s">
+        <v>592</v>
+      </c>
+      <c r="G162" t="s">
+        <v>32</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>593</v>
+      </c>
+      <c r="C163" t="s">
+        <v>35</v>
+      </c>
+      <c r="D163" t="s">
+        <v>594</v>
+      </c>
+      <c r="E163" t="s">
+        <v>160</v>
+      </c>
+      <c r="F163" t="s">
+        <v>7</v>
+      </c>
+      <c r="G163" t="s">
+        <v>595</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>596</v>
+      </c>
+      <c r="C164" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" t="s">
+        <v>597</v>
+      </c>
+      <c r="E164" t="s">
+        <v>27</v>
+      </c>
+      <c r="F164" t="s">
+        <v>7</v>
+      </c>
+      <c r="G164" t="s">
+        <v>47</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>598</v>
+      </c>
+      <c r="C165" t="s">
+        <v>72</v>
+      </c>
+      <c r="D165" t="s">
         <v>599</v>
       </c>
-      <c r="C154" t="s">
-        <v>28</v>
-      </c>
-      <c r="D154" t="s">
-        <v>596</v>
-      </c>
-      <c r="E154" t="s">
-        <v>331</v>
-      </c>
-      <c r="F154" t="s">
-        <v>332</v>
-      </c>
-      <c r="G154" t="s">
-        <v>597</v>
-      </c>
-      <c r="H154" t="s">
-        <v>598</v>
+      <c r="E165" t="s">
+        <v>74</v>
+      </c>
+      <c r="F165" t="s">
+        <v>7</v>
+      </c>
+      <c r="G165" t="s">
+        <v>600</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>601</v>
+      </c>
+      <c r="C166" t="s">
+        <v>23</v>
+      </c>
+      <c r="D166" t="s">
+        <v>602</v>
+      </c>
+      <c r="E166" t="s">
+        <v>48</v>
+      </c>
+      <c r="F166" t="s">
+        <v>7</v>
+      </c>
+      <c r="G166" t="s">
+        <v>603</v>
+      </c>
+      <c r="H166" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501029B5-C962-4109-84E6-B3701A70417B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D84ACC0-F5C7-4828-918B-0BACB4760332}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$A$1:$J$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$A$1:$J$431</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="1236">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -405,12 +405,6 @@
     <t>1152</t>
   </si>
   <si>
-    <t>9223</t>
-  </si>
-  <si>
-    <t>BEZENYE</t>
-  </si>
-  <si>
     <t>1134</t>
   </si>
   <si>
@@ -429,9 +423,6 @@
     <t>VERESEGYHÁZ</t>
   </si>
   <si>
-    <t>3535</t>
-  </si>
-  <si>
     <t>SZ-827</t>
   </si>
   <si>
@@ -534,12 +525,6 @@
     <t>Ceglédi út</t>
   </si>
   <si>
-    <t>4241</t>
-  </si>
-  <si>
-    <t>BOCSKAIKERT</t>
-  </si>
-  <si>
     <t>3532</t>
   </si>
   <si>
@@ -909,15 +894,6 @@
     <t>6ac66ffa219e3d74bbe4ecf9</t>
   </si>
   <si>
-    <t>6abe0dfd219e3d74bbe46130</t>
-  </si>
-  <si>
-    <t>260925-W00012500</t>
-  </si>
-  <si>
-    <t>Kuruc utca</t>
-  </si>
-  <si>
     <t>6ab92f86219e3d74bbe400c9</t>
   </si>
   <si>
@@ -1116,18 +1092,6 @@
     <t>Mátyás király utca</t>
   </si>
   <si>
-    <t>6ac009d5219e3d74bbe48a15</t>
-  </si>
-  <si>
-    <t>261002-W00012830</t>
-  </si>
-  <si>
-    <t>4700</t>
-  </si>
-  <si>
-    <t>MÁTÉSZALKA</t>
-  </si>
-  <si>
     <t>Petőfi utca</t>
   </si>
   <si>
@@ -1419,15 +1383,6 @@
     <t>GYŐRVÁR</t>
   </si>
   <si>
-    <t>6ac4e8ab219e3d74bbe4c968</t>
-  </si>
-  <si>
-    <t>261006-W00007203</t>
-  </si>
-  <si>
-    <t>Tölgyfa út</t>
-  </si>
-  <si>
     <t>6ac4ec3e219e3d74bbe4ca07</t>
   </si>
   <si>
@@ -1716,18 +1671,6 @@
     <t>Sámsoni utca</t>
   </si>
   <si>
-    <t>6ac651a2219e3d74bbe4e8a4</t>
-  </si>
-  <si>
-    <t>261007-W00008593</t>
-  </si>
-  <si>
-    <t>8712</t>
-  </si>
-  <si>
-    <t>BALATONÚJLAK</t>
-  </si>
-  <si>
     <t>6ac66337219e3d74bbe4eb44</t>
   </si>
   <si>
@@ -2235,18 +2178,9 @@
     <t>Jós utca</t>
   </si>
   <si>
-    <t>6ac7ca137c818f22ee6efe3a</t>
-  </si>
-  <si>
-    <t>261008-W00012127</t>
-  </si>
-  <si>
     <t>5000</t>
   </si>
   <si>
-    <t>Vásárhelyi Pál út</t>
-  </si>
-  <si>
     <t>6ac7ddc17c818f22ee6effca</t>
   </si>
   <si>
@@ -2257,12 +2191,6 @@
   </si>
   <si>
     <t>Gyenes utca</t>
-  </si>
-  <si>
-    <t>6ac7dc9e7c818f22ee6effc1</t>
-  </si>
-  <si>
-    <t>261008-W00013413</t>
   </si>
   <si>
     <t>6ac7def27c818f22ee6effdf</t>
@@ -4161,7 +4089,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -4198,16 +4126,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -4216,21 +4144,21 @@
         <v>96</v>
       </c>
       <c r="H2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -4239,18 +4167,18 @@
         <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>76</v>
@@ -4259,7 +4187,7 @@
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
@@ -4267,22 +4195,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -4290,22 +4218,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
@@ -4313,22 +4241,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
@@ -4336,13 +4264,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E8" t="s">
         <v>103</v>
@@ -4351,7 +4279,7 @@
         <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
@@ -4359,22 +4287,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E9" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -4382,22 +4310,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G10" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -4405,22 +4333,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F11" t="s">
         <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -4428,19 +4356,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="G12" t="s">
         <v>65</v>
@@ -4451,19 +4379,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E13" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F13" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="G13" t="s">
         <v>65</v>
@@ -4474,22 +4402,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
         <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E14" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F14" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G14" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -4497,22 +4425,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -4520,13 +4448,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
         <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -4535,7 +4463,7 @@
         <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -4543,13 +4471,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
         <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E17" t="s">
         <v>62</v>
@@ -4558,7 +4486,7 @@
         <v>63</v>
       </c>
       <c r="G17" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -4566,22 +4494,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E18" t="s">
-        <v>133</v>
+        <v>290</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>291</v>
       </c>
       <c r="G18" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -4589,22 +4517,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19" t="s">
+        <v>295</v>
+      </c>
+      <c r="F19" t="s">
         <v>296</v>
       </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>297</v>
-      </c>
-      <c r="E19" t="s">
-        <v>298</v>
-      </c>
-      <c r="F19" t="s">
-        <v>299</v>
-      </c>
-      <c r="G19" t="s">
-        <v>300</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -4612,22 +4540,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C20" t="s">
+        <v>299</v>
+      </c>
+      <c r="D20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" t="s">
         <v>301</v>
       </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>302</v>
       </c>
-      <c r="E20" t="s">
-        <v>303</v>
-      </c>
-      <c r="F20" t="s">
-        <v>304</v>
-      </c>
       <c r="G20" t="s">
-        <v>305</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -4635,22 +4563,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E21" t="s">
+        <v>305</v>
+      </c>
+      <c r="F21" t="s">
         <v>306</v>
       </c>
-      <c r="C21" t="s">
+      <c r="G21" t="s">
         <v>307</v>
-      </c>
-      <c r="D21" t="s">
-        <v>308</v>
-      </c>
-      <c r="E21" t="s">
-        <v>309</v>
-      </c>
-      <c r="F21" t="s">
-        <v>310</v>
-      </c>
-      <c r="G21" t="s">
-        <v>92</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -4658,22 +4586,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>309</v>
+      </c>
+      <c r="E22" t="s">
+        <v>310</v>
+      </c>
+      <c r="F22" t="s">
         <v>311</v>
       </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
         <v>312</v>
-      </c>
-      <c r="E22" t="s">
-        <v>313</v>
-      </c>
-      <c r="F22" t="s">
-        <v>314</v>
-      </c>
-      <c r="G22" t="s">
-        <v>315</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -4681,22 +4609,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>314</v>
+      </c>
+      <c r="E23" t="s">
+        <v>315</v>
+      </c>
+      <c r="F23" t="s">
         <v>316</v>
       </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>317</v>
-      </c>
-      <c r="E23" t="s">
-        <v>318</v>
-      </c>
-      <c r="F23" t="s">
-        <v>319</v>
-      </c>
-      <c r="G23" t="s">
-        <v>320</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -4704,22 +4632,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>318</v>
+      </c>
+      <c r="C24" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" t="s">
+        <v>319</v>
+      </c>
+      <c r="E24" t="s">
+        <v>320</v>
+      </c>
+      <c r="F24" t="s">
         <v>321</v>
       </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="G24" t="s">
         <v>322</v>
-      </c>
-      <c r="E24" t="s">
-        <v>323</v>
-      </c>
-      <c r="F24" t="s">
-        <v>324</v>
-      </c>
-      <c r="G24" t="s">
-        <v>325</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -4727,22 +4655,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
+        <v>324</v>
+      </c>
+      <c r="E25" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" t="s">
         <v>326</v>
       </c>
-      <c r="C25" t="s">
-        <v>277</v>
-      </c>
-      <c r="D25" t="s">
-        <v>327</v>
-      </c>
-      <c r="E25" t="s">
-        <v>328</v>
-      </c>
-      <c r="F25" t="s">
-        <v>329</v>
-      </c>
       <c r="G25" t="s">
-        <v>330</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -4750,22 +4678,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E26" t="s">
-        <v>333</v>
+        <v>116</v>
       </c>
       <c r="F26" t="s">
-        <v>334</v>
+        <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -4773,22 +4701,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="E27" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G27" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -4796,22 +4724,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E28" t="s">
-        <v>152</v>
+        <v>333</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>334</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -4819,22 +4747,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E29" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="F29" t="s">
-        <v>342</v>
+        <v>196</v>
       </c>
       <c r="G29" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -4842,22 +4770,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>338</v>
       </c>
       <c r="D30" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="G30" t="s">
-        <v>177</v>
+        <v>340</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -4865,22 +4793,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C31" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="D31" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -4888,22 +4816,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C32" t="s">
-        <v>307</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>345</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -4911,22 +4839,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="G33" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -4934,22 +4862,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>351</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>352</v>
       </c>
       <c r="G34" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -4957,22 +4885,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>355</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>356</v>
+      </c>
+      <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
+        <v>181</v>
+      </c>
+      <c r="G35" t="s">
         <v>357</v>
-      </c>
-      <c r="C35" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" t="s">
-        <v>358</v>
-      </c>
-      <c r="E35" t="s">
-        <v>359</v>
-      </c>
-      <c r="F35" t="s">
-        <v>360</v>
-      </c>
-      <c r="G35" t="s">
-        <v>361</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -4980,22 +4908,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>358</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>359</v>
+      </c>
+      <c r="E36" t="s">
+        <v>360</v>
+      </c>
+      <c r="F36" t="s">
+        <v>361</v>
+      </c>
+      <c r="G36" t="s">
         <v>362</v>
-      </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" t="s">
-        <v>363</v>
-      </c>
-      <c r="E36" t="s">
-        <v>364</v>
-      </c>
-      <c r="F36" t="s">
-        <v>365</v>
-      </c>
-      <c r="G36" t="s">
-        <v>366</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -5003,22 +4931,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>367</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>368</v>
+        <v>163</v>
       </c>
       <c r="E37" t="s">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="G37" t="s">
-        <v>369</v>
+        <v>164</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -5026,22 +4954,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="D38" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E38" t="s">
-        <v>372</v>
+        <v>45</v>
       </c>
       <c r="F38" t="s">
-        <v>373</v>
+        <v>46</v>
       </c>
       <c r="G38" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -5049,22 +4977,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>367</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>368</v>
       </c>
       <c r="F39" t="s">
-        <v>48</v>
+        <v>369</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>370</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -5072,22 +5000,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>368</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="G40" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -5095,22 +5023,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>378</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>379</v>
+        <v>168</v>
       </c>
       <c r="E41" t="s">
-        <v>380</v>
+        <v>126</v>
       </c>
       <c r="F41" t="s">
-        <v>381</v>
+        <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>382</v>
+        <v>169</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -5118,22 +5046,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E42" t="s">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="F42" t="s">
-        <v>381</v>
+        <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -5141,22 +5069,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>376</v>
       </c>
       <c r="E43" t="s">
-        <v>128</v>
+        <v>377</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>378</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -5164,22 +5092,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C44" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>381</v>
       </c>
       <c r="F44" t="s">
-        <v>7</v>
+        <v>382</v>
       </c>
       <c r="G44" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -5187,22 +5115,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C45" t="s">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="D45" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="E45" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="F45" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="G45" t="s">
-        <v>97</v>
+        <v>383</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -5210,22 +5138,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E46" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F46" t="s">
-        <v>394</v>
+        <v>7</v>
       </c>
       <c r="G46" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -5233,22 +5161,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E47" t="s">
-        <v>393</v>
+        <v>120</v>
       </c>
       <c r="F47" t="s">
-        <v>394</v>
+        <v>121</v>
       </c>
       <c r="G47" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -5256,22 +5184,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E48" t="s">
-        <v>399</v>
+        <v>173</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="G48" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -5279,22 +5207,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E49" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="F49" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="G49" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -5302,22 +5230,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="D50" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E50" t="s">
-        <v>178</v>
+        <v>398</v>
       </c>
       <c r="F50" t="s">
-        <v>179</v>
+        <v>399</v>
       </c>
       <c r="G50" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -5325,22 +5253,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E51" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="F51" t="s">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -5348,22 +5276,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E52" t="s">
-        <v>410</v>
+        <v>305</v>
       </c>
       <c r="F52" t="s">
-        <v>411</v>
+        <v>306</v>
       </c>
       <c r="G52" t="s">
-        <v>412</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -5371,22 +5299,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="D53" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E53" t="s">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -5394,22 +5322,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E54" t="s">
-        <v>313</v>
+        <v>411</v>
       </c>
       <c r="F54" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="G54" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -5417,22 +5345,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E55" t="s">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="F55" t="s">
-        <v>80</v>
+        <v>416</v>
       </c>
       <c r="G55" t="s">
-        <v>420</v>
+        <v>16</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -5440,22 +5368,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>417</v>
+      </c>
+      <c r="C56" t="s">
+        <v>418</v>
+      </c>
+      <c r="D56" t="s">
+        <v>419</v>
+      </c>
+      <c r="E56" t="s">
+        <v>420</v>
+      </c>
+      <c r="F56" t="s">
         <v>421</v>
       </c>
-      <c r="C56" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" t="s">
-        <v>422</v>
-      </c>
-      <c r="E56" t="s">
-        <v>423</v>
-      </c>
-      <c r="F56" t="s">
-        <v>424</v>
-      </c>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -5463,22 +5391,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>422</v>
+      </c>
+      <c r="C57" t="s">
+        <v>423</v>
+      </c>
+      <c r="D57" t="s">
+        <v>424</v>
+      </c>
+      <c r="E57" t="s">
         <v>425</v>
       </c>
-      <c r="C57" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" t="s">
         <v>426</v>
-      </c>
-      <c r="E57" t="s">
-        <v>427</v>
-      </c>
-      <c r="F57" t="s">
-        <v>428</v>
-      </c>
-      <c r="G57" t="s">
-        <v>16</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -5486,22 +5414,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>427</v>
+      </c>
+      <c r="C58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s">
+        <v>428</v>
+      </c>
+      <c r="E58" t="s">
         <v>429</v>
       </c>
-      <c r="C58" t="s">
+      <c r="F58" t="s">
         <v>430</v>
       </c>
-      <c r="D58" t="s">
+      <c r="G58" t="s">
         <v>431</v>
-      </c>
-      <c r="E58" t="s">
-        <v>432</v>
-      </c>
-      <c r="F58" t="s">
-        <v>433</v>
-      </c>
-      <c r="G58" t="s">
-        <v>94</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -5509,22 +5437,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>432</v>
+      </c>
+      <c r="C59" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" t="s">
+        <v>433</v>
+      </c>
+      <c r="E59" t="s">
         <v>434</v>
       </c>
-      <c r="C59" t="s">
+      <c r="F59" t="s">
         <v>435</v>
       </c>
-      <c r="D59" t="s">
-        <v>436</v>
-      </c>
-      <c r="E59" t="s">
-        <v>437</v>
-      </c>
-      <c r="F59" t="s">
-        <v>26</v>
-      </c>
       <c r="G59" t="s">
-        <v>438</v>
+        <v>170</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -5532,22 +5460,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>436</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="s">
+        <v>437</v>
+      </c>
+      <c r="E60" t="s">
+        <v>438</v>
+      </c>
+      <c r="F60" t="s">
         <v>439</v>
       </c>
-      <c r="C60" t="s">
-        <v>27</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="G60" t="s">
         <v>440</v>
-      </c>
-      <c r="E60" t="s">
-        <v>441</v>
-      </c>
-      <c r="F60" t="s">
-        <v>442</v>
-      </c>
-      <c r="G60" t="s">
-        <v>443</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -5555,22 +5483,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>441</v>
+      </c>
+      <c r="C61" t="s">
+        <v>156</v>
+      </c>
+      <c r="D61" t="s">
+        <v>442</v>
+      </c>
+      <c r="E61" t="s">
+        <v>443</v>
+      </c>
+      <c r="F61" t="s">
         <v>444</v>
       </c>
-      <c r="C61" t="s">
-        <v>134</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="G61" t="s">
         <v>445</v>
-      </c>
-      <c r="E61" t="s">
-        <v>446</v>
-      </c>
-      <c r="F61" t="s">
-        <v>447</v>
-      </c>
-      <c r="G61" t="s">
-        <v>175</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -5578,22 +5506,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>446</v>
+      </c>
+      <c r="C62" t="s">
+        <v>447</v>
+      </c>
+      <c r="D62" t="s">
         <v>448</v>
       </c>
-      <c r="C62" t="s">
-        <v>18</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>449</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>450</v>
       </c>
-      <c r="F62" t="s">
-        <v>451</v>
-      </c>
       <c r="G62" t="s">
-        <v>452</v>
+        <v>178</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -5601,22 +5529,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>451</v>
+      </c>
+      <c r="C63" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" t="s">
+        <v>452</v>
+      </c>
+      <c r="E63" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" t="s">
+        <v>212</v>
+      </c>
+      <c r="G63" t="s">
         <v>453</v>
-      </c>
-      <c r="C63" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" t="s">
-        <v>454</v>
-      </c>
-      <c r="E63" t="s">
-        <v>455</v>
-      </c>
-      <c r="F63" t="s">
-        <v>456</v>
-      </c>
-      <c r="G63" t="s">
-        <v>457</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -5624,22 +5552,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C64" t="s">
-        <v>459</v>
+        <v>131</v>
       </c>
       <c r="D64" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E64" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F64" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G64" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -5647,22 +5575,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E65" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F65" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="G65" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -5670,22 +5598,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E66" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F66" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="G66" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -5693,22 +5621,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>469</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>447</v>
       </c>
       <c r="D67" t="s">
-        <v>470</v>
+        <v>201</v>
       </c>
       <c r="E67" t="s">
-        <v>471</v>
+        <v>202</v>
       </c>
       <c r="F67" t="s">
-        <v>472</v>
+        <v>203</v>
       </c>
       <c r="G67" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -5716,22 +5644,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>473</v>
+        <v>205</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>474</v>
+        <v>206</v>
       </c>
       <c r="E68" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G68" t="s">
-        <v>475</v>
+        <v>207</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -5739,22 +5667,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
       </c>
       <c r="D69" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="E69" t="s">
-        <v>187</v>
+        <v>464</v>
       </c>
       <c r="F69" t="s">
-        <v>188</v>
+        <v>465</v>
       </c>
       <c r="G69" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -5762,22 +5690,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>205</v>
+        <v>467</v>
       </c>
       <c r="C70" t="s">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>206</v>
+        <v>468</v>
       </c>
       <c r="E70" t="s">
-        <v>207</v>
+        <v>469</v>
       </c>
       <c r="F70" t="s">
-        <v>208</v>
+        <v>470</v>
       </c>
       <c r="G70" t="s">
-        <v>209</v>
+        <v>471</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -5785,22 +5713,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>210</v>
+        <v>472</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>211</v>
+        <v>473</v>
       </c>
       <c r="E71" t="s">
-        <v>190</v>
+        <v>474</v>
       </c>
       <c r="F71" t="s">
-        <v>191</v>
+        <v>475</v>
       </c>
       <c r="G71" t="s">
-        <v>212</v>
+        <v>476</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -5811,7 +5739,7 @@
         <v>477</v>
       </c>
       <c r="C72" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D72" t="s">
         <v>478</v>
@@ -5820,10 +5748,10 @@
         <v>479</v>
       </c>
       <c r="F72" t="s">
-        <v>480</v>
+        <v>118</v>
       </c>
       <c r="G72" t="s">
-        <v>481</v>
+        <v>322</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -5831,22 +5759,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>480</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
+        <v>481</v>
+      </c>
+      <c r="E73" t="s">
+        <v>194</v>
+      </c>
+      <c r="F73" t="s">
+        <v>7</v>
+      </c>
+      <c r="G73" t="s">
         <v>482</v>
-      </c>
-      <c r="C73" t="s">
-        <v>21</v>
-      </c>
-      <c r="D73" t="s">
-        <v>483</v>
-      </c>
-      <c r="E73" t="s">
-        <v>484</v>
-      </c>
-      <c r="F73" t="s">
-        <v>485</v>
-      </c>
-      <c r="G73" t="s">
-        <v>486</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -5854,22 +5782,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C74" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E74" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F74" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G74" t="s">
-        <v>491</v>
+        <v>65</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -5877,22 +5805,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C75" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D75" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E75" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F75" t="s">
-        <v>118</v>
+        <v>490</v>
       </c>
       <c r="G75" t="s">
-        <v>330</v>
+        <v>97</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -5900,22 +5828,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C76" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="D76" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E76" t="s">
-        <v>199</v>
+        <v>489</v>
       </c>
       <c r="F76" t="s">
-        <v>7</v>
+        <v>490</v>
       </c>
       <c r="G76" t="s">
-        <v>497</v>
+        <v>97</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -5923,22 +5851,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D77" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E77" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F77" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="G77" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -5946,22 +5874,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="E78" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="F78" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="G78" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -5969,22 +5897,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>498</v>
       </c>
       <c r="D79" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E79" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F79" t="s">
-        <v>505</v>
-      </c>
-      <c r="G79" t="s">
-        <v>97</v>
+        <v>501</v>
+      </c>
+      <c r="G79" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -5992,22 +5920,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D80" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="E80" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F80" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G80" t="s">
-        <v>73</v>
+        <v>506</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -6015,10 +5943,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
         <v>508</v>
@@ -6030,7 +5958,7 @@
         <v>510</v>
       </c>
       <c r="G81" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -6038,22 +5966,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C82" t="s">
-        <v>513</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E82" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F82" t="s">
-        <v>516</v>
-      </c>
-      <c r="G82" t="e">
-        <v>#NUM!</v>
+        <v>510</v>
+      </c>
+      <c r="G82" t="s">
+        <v>93</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -6061,22 +5989,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C83" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E83" t="s">
-        <v>519</v>
+        <v>86</v>
       </c>
       <c r="F83" t="s">
-        <v>520</v>
+        <v>87</v>
       </c>
       <c r="G83" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -6084,22 +6012,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E84" t="s">
-        <v>524</v>
+        <v>278</v>
       </c>
       <c r="F84" t="s">
-        <v>525</v>
+        <v>279</v>
       </c>
       <c r="G84" t="s">
-        <v>93</v>
+        <v>517</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -6107,22 +6035,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C85" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E85" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F85" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G85" t="s">
-        <v>93</v>
+        <v>522</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -6130,22 +6058,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D86" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E86" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="F86" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="G86" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -6153,22 +6081,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>526</v>
+      </c>
+      <c r="C87" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>527</v>
+      </c>
+      <c r="E87" t="s">
+        <v>528</v>
+      </c>
+      <c r="F87" t="s">
+        <v>529</v>
+      </c>
+      <c r="G87" t="s">
         <v>530</v>
-      </c>
-      <c r="C87" t="s">
-        <v>33</v>
-      </c>
-      <c r="D87" t="s">
-        <v>531</v>
-      </c>
-      <c r="E87" t="s">
-        <v>283</v>
-      </c>
-      <c r="F87" t="s">
-        <v>284</v>
-      </c>
-      <c r="G87" t="s">
-        <v>532</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -6176,22 +6104,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>531</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" t="s">
+        <v>532</v>
+      </c>
+      <c r="E88" t="s">
         <v>533</v>
       </c>
-      <c r="C88" t="s">
-        <v>22</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="F88" t="s">
         <v>534</v>
       </c>
-      <c r="E88" t="s">
-        <v>535</v>
-      </c>
-      <c r="F88" t="s">
-        <v>536</v>
-      </c>
       <c r="G88" t="s">
-        <v>537</v>
+        <v>476</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -6199,22 +6127,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>535</v>
+      </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
+        <v>536</v>
+      </c>
+      <c r="E89" t="s">
+        <v>537</v>
+      </c>
+      <c r="F89" t="s">
         <v>538</v>
       </c>
-      <c r="C89" t="s">
-        <v>69</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="G89" t="s">
         <v>539</v>
-      </c>
-      <c r="E89" t="s">
-        <v>141</v>
-      </c>
-      <c r="F89" t="s">
-        <v>142</v>
-      </c>
-      <c r="G89" t="s">
-        <v>540</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -6222,22 +6150,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>540</v>
+      </c>
+      <c r="C90" t="s">
+        <v>498</v>
+      </c>
+      <c r="D90" t="s">
         <v>541</v>
       </c>
-      <c r="C90" t="s">
-        <v>24</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
+        <v>425</v>
+      </c>
+      <c r="F90" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" t="s">
         <v>542</v>
-      </c>
-      <c r="E90" t="s">
-        <v>543</v>
-      </c>
-      <c r="F90" t="s">
-        <v>544</v>
-      </c>
-      <c r="G90" t="s">
-        <v>545</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -6245,22 +6173,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>498</v>
       </c>
       <c r="D91" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E91" t="s">
-        <v>548</v>
+        <v>425</v>
       </c>
       <c r="F91" t="s">
-        <v>549</v>
+        <v>26</v>
       </c>
       <c r="G91" t="s">
-        <v>491</v>
+        <v>542</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -6268,22 +6196,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D92" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E92" t="s">
-        <v>552</v>
+        <v>99</v>
       </c>
       <c r="F92" t="s">
-        <v>553</v>
+        <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -6291,22 +6219,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C93" t="s">
-        <v>513</v>
+        <v>58</v>
       </c>
       <c r="D93" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="E93" t="s">
-        <v>437</v>
+        <v>549</v>
       </c>
       <c r="F93" t="s">
-        <v>26</v>
+        <v>550</v>
       </c>
       <c r="G93" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -6314,22 +6242,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="C94" t="s">
-        <v>513</v>
+        <v>70</v>
       </c>
       <c r="D94" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E94" t="s">
-        <v>437</v>
+        <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="G94" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -6337,22 +6265,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>555</v>
+      </c>
+      <c r="C95" t="s">
+        <v>447</v>
+      </c>
+      <c r="D95" t="s">
+        <v>556</v>
+      </c>
+      <c r="E95" t="s">
+        <v>557</v>
+      </c>
+      <c r="F95" t="s">
+        <v>558</v>
+      </c>
+      <c r="G95" t="s">
         <v>559</v>
-      </c>
-      <c r="C95" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95" t="s">
-        <v>560</v>
-      </c>
-      <c r="E95" t="s">
-        <v>99</v>
-      </c>
-      <c r="F95" t="s">
-        <v>100</v>
-      </c>
-      <c r="G95" t="s">
-        <v>561</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -6360,22 +6288,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>560</v>
+      </c>
+      <c r="C96" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" t="s">
+        <v>561</v>
+      </c>
+      <c r="E96" t="s">
         <v>562</v>
       </c>
-      <c r="C96" t="s">
-        <v>69</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
         <v>563</v>
       </c>
-      <c r="E96" t="s">
-        <v>564</v>
-      </c>
-      <c r="F96" t="s">
-        <v>565</v>
-      </c>
       <c r="G96" t="s">
-        <v>228</v>
+        <v>140</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -6383,22 +6311,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="E97" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F97" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="G97" t="s">
-        <v>570</v>
+        <v>140</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -6406,22 +6334,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C98" t="s">
-        <v>70</v>
+        <v>447</v>
       </c>
       <c r="D98" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="E98" t="s">
-        <v>112</v>
+        <v>567</v>
       </c>
       <c r="F98" t="s">
-        <v>113</v>
+        <v>568</v>
       </c>
       <c r="G98" t="s">
-        <v>573</v>
+        <v>36</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -6429,22 +6357,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C99" t="s">
-        <v>459</v>
+        <v>58</v>
       </c>
       <c r="D99" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E99" t="s">
-        <v>576</v>
+        <v>176</v>
       </c>
       <c r="F99" t="s">
-        <v>577</v>
+        <v>177</v>
       </c>
       <c r="G99" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -6452,22 +6380,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="C100" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="D100" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="E100" t="s">
-        <v>581</v>
+        <v>176</v>
       </c>
       <c r="F100" t="s">
-        <v>582</v>
+        <v>177</v>
       </c>
       <c r="G100" t="s">
-        <v>143</v>
+        <v>571</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -6475,22 +6403,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="D101" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="E101" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="F101" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="G101" t="s">
-        <v>143</v>
+        <v>577</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -6498,22 +6426,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C102" t="s">
-        <v>459</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E102" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="F102" t="s">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="G102" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -6521,22 +6449,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C103" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="D103" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E103" t="s">
-        <v>181</v>
+        <v>583</v>
       </c>
       <c r="F103" t="s">
-        <v>182</v>
+        <v>584</v>
       </c>
       <c r="G103" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -6544,22 +6472,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C104" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D104" t="s">
+        <v>587</v>
+      </c>
+      <c r="E104" t="s">
+        <v>588</v>
+      </c>
+      <c r="F104" t="s">
         <v>589</v>
       </c>
-      <c r="E104" t="s">
-        <v>181</v>
-      </c>
-      <c r="F104" t="s">
-        <v>182</v>
-      </c>
       <c r="G104" t="s">
-        <v>590</v>
+        <v>97</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -6567,22 +6495,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C105" t="s">
-        <v>430</v>
+        <v>22</v>
       </c>
       <c r="D105" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E105" t="s">
-        <v>594</v>
+        <v>132</v>
       </c>
       <c r="F105" t="s">
-        <v>595</v>
+        <v>133</v>
       </c>
       <c r="G105" t="s">
-        <v>596</v>
+        <v>36</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -6590,22 +6518,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C106" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D106" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="E106" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="F106" t="s">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="G106" t="s">
-        <v>93</v>
+        <v>596</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -6613,22 +6541,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C107" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="D107" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="E107" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="F107" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="G107" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -6636,22 +6564,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D108" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="E108" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="F108" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="G108" t="s">
-        <v>97</v>
+        <v>596</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -6659,22 +6587,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C109" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E109" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="F109" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="G109" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -6682,22 +6610,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="E110" t="s">
-        <v>613</v>
+        <v>86</v>
       </c>
       <c r="F110" t="s">
-        <v>614</v>
+        <v>87</v>
       </c>
       <c r="G110" t="s">
-        <v>615</v>
+        <v>408</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -6705,22 +6633,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D111" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E111" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="F111" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="G111" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -6728,22 +6656,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D112" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E112" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="F112" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="G112" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -6751,22 +6679,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="D113" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="E113" t="s">
-        <v>86</v>
+        <v>610</v>
       </c>
       <c r="F113" t="s">
-        <v>87</v>
+        <v>611</v>
       </c>
       <c r="G113" t="s">
-        <v>420</v>
+        <v>612</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -6774,22 +6702,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D114" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="E114" t="s">
-        <v>86</v>
+        <v>219</v>
       </c>
       <c r="F114" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="G114" t="s">
-        <v>420</v>
+        <v>615</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -6797,22 +6725,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D115" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="E115" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="F115" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G115" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -6820,10 +6748,10 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C116" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D116" t="s">
         <v>622</v>
@@ -6835,7 +6763,7 @@
         <v>624</v>
       </c>
       <c r="G116" t="s">
-        <v>625</v>
+        <v>36</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -6843,22 +6771,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>625</v>
+      </c>
+      <c r="C117" t="s">
+        <v>153</v>
+      </c>
+      <c r="D117" t="s">
+        <v>626</v>
+      </c>
+      <c r="E117" t="s">
         <v>627</v>
       </c>
-      <c r="C117" t="s">
-        <v>70</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
         <v>628</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>629</v>
-      </c>
-      <c r="F117" t="s">
-        <v>630</v>
-      </c>
-      <c r="G117" t="s">
-        <v>631</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -6866,19 +6794,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C118" t="s">
         <v>19</v>
       </c>
       <c r="D118" t="s">
+        <v>631</v>
+      </c>
+      <c r="E118" t="s">
+        <v>632</v>
+      </c>
+      <c r="F118" t="s">
         <v>633</v>
-      </c>
-      <c r="E118" t="s">
-        <v>224</v>
-      </c>
-      <c r="F118" t="s">
-        <v>225</v>
       </c>
       <c r="G118" t="s">
         <v>634</v>
@@ -6892,19 +6820,19 @@
         <v>635</v>
       </c>
       <c r="C119" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="D119" t="s">
         <v>636</v>
       </c>
       <c r="E119" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119" t="s">
+        <v>7</v>
+      </c>
+      <c r="G119" t="s">
         <v>637</v>
-      </c>
-      <c r="F119" t="s">
-        <v>638</v>
-      </c>
-      <c r="G119" t="s">
-        <v>639</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -6912,22 +6840,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>638</v>
+      </c>
+      <c r="C120" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" t="s">
+        <v>639</v>
+      </c>
+      <c r="E120" t="s">
         <v>640</v>
       </c>
-      <c r="C120" t="s">
-        <v>24</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="F120" t="s">
         <v>641</v>
       </c>
-      <c r="E120" t="s">
-        <v>642</v>
-      </c>
-      <c r="F120" t="s">
-        <v>643</v>
-      </c>
       <c r="G120" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -6935,22 +6863,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C121" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="E121" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="F121" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G121" t="s">
-        <v>648</v>
+        <v>93</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -6958,22 +6886,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C122" t="s">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="D122" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E122" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="F122" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="G122" t="s">
-        <v>653</v>
+        <v>73</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -6981,22 +6909,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C123" t="s">
-        <v>105</v>
+        <v>418</v>
       </c>
       <c r="D123" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="E123" t="s">
-        <v>83</v>
+        <v>645</v>
       </c>
       <c r="F123" t="s">
-        <v>7</v>
+        <v>646</v>
       </c>
       <c r="G123" t="s">
-        <v>656</v>
+        <v>73</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -7004,22 +6932,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C124" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="E124" t="s">
-        <v>659</v>
+        <v>194</v>
       </c>
       <c r="F124" t="s">
-        <v>660</v>
+        <v>7</v>
       </c>
       <c r="G124" t="s">
-        <v>93</v>
+        <v>650</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -7027,22 +6955,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C125" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D125" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="E125" t="s">
-        <v>659</v>
+        <v>194</v>
       </c>
       <c r="F125" t="s">
-        <v>660</v>
+        <v>7</v>
       </c>
       <c r="G125" t="s">
-        <v>93</v>
+        <v>650</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -7050,22 +6978,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="C126" t="s">
-        <v>430</v>
+        <v>9</v>
       </c>
       <c r="D126" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="E126" t="s">
-        <v>664</v>
+        <v>194</v>
       </c>
       <c r="F126" t="s">
-        <v>665</v>
+        <v>7</v>
       </c>
       <c r="G126" t="s">
-        <v>73</v>
+        <v>650</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -7073,22 +7001,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C127" t="s">
-        <v>430</v>
+        <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="E127" t="s">
-        <v>664</v>
+        <v>194</v>
       </c>
       <c r="F127" t="s">
-        <v>665</v>
+        <v>7</v>
       </c>
       <c r="G127" t="s">
-        <v>73</v>
+        <v>650</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -7096,22 +7024,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="C128" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D128" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="E128" t="s">
-        <v>199</v>
+        <v>656</v>
       </c>
       <c r="F128" t="s">
-        <v>7</v>
+        <v>657</v>
       </c>
       <c r="G128" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -7119,22 +7047,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D129" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="E129" t="s">
-        <v>199</v>
+        <v>661</v>
       </c>
       <c r="F129" t="s">
-        <v>7</v>
+        <v>662</v>
       </c>
       <c r="G129" t="s">
-        <v>669</v>
+        <v>59</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -7142,22 +7070,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C130" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="D130" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E130" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="F130" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="G130" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -7165,22 +7093,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C131" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s">
+        <v>667</v>
+      </c>
+      <c r="E131" t="s">
         <v>668</v>
       </c>
-      <c r="E131" t="s">
-        <v>199</v>
-      </c>
       <c r="F131" t="s">
-        <v>7</v>
+        <v>669</v>
       </c>
       <c r="G131" t="s">
-        <v>669</v>
+        <v>94</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -7188,22 +7116,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>670</v>
+      </c>
+      <c r="C132" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" t="s">
+        <v>671</v>
+      </c>
+      <c r="E132" t="s">
+        <v>672</v>
+      </c>
+      <c r="F132" t="s">
         <v>673</v>
       </c>
-      <c r="C132" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" t="s">
-        <v>674</v>
-      </c>
-      <c r="E132" t="s">
-        <v>675</v>
-      </c>
-      <c r="F132" t="s">
-        <v>676</v>
-      </c>
       <c r="G132" t="s">
-        <v>677</v>
+        <v>354</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -7211,22 +7139,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C133" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="D133" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E133" t="s">
-        <v>680</v>
+        <v>583</v>
       </c>
       <c r="F133" t="s">
-        <v>681</v>
+        <v>584</v>
       </c>
       <c r="G133" t="s">
-        <v>59</v>
+        <v>676</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -7234,22 +7162,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="C134" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E134" t="s">
-        <v>47</v>
+        <v>679</v>
       </c>
       <c r="F134" t="s">
-        <v>48</v>
+        <v>680</v>
       </c>
       <c r="G134" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -7257,22 +7185,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>682</v>
+      </c>
+      <c r="C135" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" t="s">
+        <v>683</v>
+      </c>
+      <c r="E135" t="s">
+        <v>684</v>
+      </c>
+      <c r="F135" t="s">
         <v>685</v>
       </c>
-      <c r="C135" t="s">
-        <v>31</v>
-      </c>
-      <c r="D135" t="s">
+      <c r="G135" t="s">
         <v>686</v>
-      </c>
-      <c r="E135" t="s">
-        <v>687</v>
-      </c>
-      <c r="F135" t="s">
-        <v>688</v>
-      </c>
-      <c r="G135" t="s">
-        <v>94</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -7280,22 +7208,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>687</v>
+      </c>
+      <c r="C136" t="s">
+        <v>418</v>
+      </c>
+      <c r="D136" t="s">
+        <v>688</v>
+      </c>
+      <c r="E136" t="s">
         <v>689</v>
       </c>
-      <c r="C136" t="s">
-        <v>19</v>
-      </c>
-      <c r="D136" t="s">
+      <c r="F136" t="s">
         <v>690</v>
       </c>
-      <c r="E136" t="s">
+      <c r="G136" t="s">
         <v>691</v>
-      </c>
-      <c r="F136" t="s">
-        <v>692</v>
-      </c>
-      <c r="G136" t="s">
-        <v>366</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -7303,22 +7231,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>692</v>
+      </c>
+      <c r="C137" t="s">
+        <v>153</v>
+      </c>
+      <c r="D137" t="s">
         <v>693</v>
       </c>
-      <c r="C137" t="s">
-        <v>134</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
+        <v>45</v>
+      </c>
+      <c r="F137" t="s">
+        <v>46</v>
+      </c>
+      <c r="G137" t="s">
         <v>694</v>
-      </c>
-      <c r="E137" t="s">
-        <v>602</v>
-      </c>
-      <c r="F137" t="s">
-        <v>603</v>
-      </c>
-      <c r="G137" t="s">
-        <v>695</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -7326,22 +7254,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>695</v>
+      </c>
+      <c r="C138" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" t="s">
         <v>696</v>
       </c>
-      <c r="C138" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>697</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
+        <v>7</v>
+      </c>
+      <c r="G138" t="s">
         <v>698</v>
-      </c>
-      <c r="F138" t="s">
-        <v>699</v>
-      </c>
-      <c r="G138" t="s">
-        <v>700</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -7349,22 +7277,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>699</v>
+      </c>
+      <c r="C139" t="s">
+        <v>299</v>
+      </c>
+      <c r="D139" t="s">
+        <v>700</v>
+      </c>
+      <c r="E139" t="s">
         <v>701</v>
       </c>
-      <c r="C139" t="s">
-        <v>22</v>
-      </c>
-      <c r="D139" t="s">
+      <c r="F139" t="s">
         <v>702</v>
       </c>
-      <c r="E139" t="s">
-        <v>703</v>
-      </c>
-      <c r="F139" t="s">
-        <v>704</v>
-      </c>
       <c r="G139" t="s">
-        <v>705</v>
+        <v>175</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -7372,22 +7300,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>703</v>
+      </c>
+      <c r="C140" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" t="s">
+        <v>704</v>
+      </c>
+      <c r="E140" t="s">
+        <v>705</v>
+      </c>
+      <c r="F140" t="s">
         <v>706</v>
       </c>
-      <c r="C140" t="s">
-        <v>430</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="G140" t="s">
         <v>707</v>
-      </c>
-      <c r="E140" t="s">
-        <v>708</v>
-      </c>
-      <c r="F140" t="s">
-        <v>709</v>
-      </c>
-      <c r="G140" t="s">
-        <v>710</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -7395,22 +7323,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C141" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="D141" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E141" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="F141" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>713</v>
+        <v>91</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -7418,22 +7346,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C142" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="D142" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="E142" t="s">
-        <v>716</v>
+        <v>189</v>
       </c>
       <c r="F142" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="G142" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -7441,22 +7369,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C143" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
       <c r="D143" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="E143" t="s">
-        <v>720</v>
+        <v>387</v>
       </c>
       <c r="F143" t="s">
-        <v>721</v>
+        <v>7</v>
       </c>
       <c r="G143" t="s">
-        <v>180</v>
+        <v>715</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -7464,22 +7392,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C144" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="E144" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F144" t="s">
-        <v>725</v>
+        <v>7</v>
       </c>
       <c r="G144" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -7487,22 +7415,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C145" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D145" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E145" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
       <c r="F145" t="s">
-        <v>7</v>
+        <v>158</v>
       </c>
       <c r="G145" t="s">
-        <v>91</v>
+        <v>723</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -7510,22 +7438,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C146" t="s">
-        <v>149</v>
+        <v>272</v>
       </c>
       <c r="D146" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="E146" t="s">
-        <v>194</v>
+        <v>726</v>
       </c>
       <c r="F146" t="s">
-        <v>195</v>
+        <v>727</v>
       </c>
       <c r="G146" t="s">
-        <v>731</v>
+        <v>29</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -7533,22 +7461,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C147" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="D147" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="E147" t="s">
-        <v>399</v>
+        <v>726</v>
       </c>
       <c r="F147" t="s">
-        <v>7</v>
+        <v>727</v>
       </c>
       <c r="G147" t="s">
-        <v>734</v>
+        <v>29</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -7556,22 +7484,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C148" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D148" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E148" t="s">
-        <v>737</v>
+        <v>278</v>
       </c>
       <c r="F148" t="s">
-        <v>52</v>
+        <v>279</v>
       </c>
       <c r="G148" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -7579,22 +7507,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C149" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D149" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="E149" t="s">
-        <v>741</v>
+        <v>278</v>
       </c>
       <c r="F149" t="s">
-        <v>7</v>
+        <v>279</v>
       </c>
       <c r="G149" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -7602,22 +7530,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="C150" t="s">
-        <v>513</v>
+        <v>58</v>
       </c>
       <c r="D150" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="E150" t="s">
-        <v>125</v>
+        <v>735</v>
       </c>
       <c r="F150" t="s">
-        <v>126</v>
+        <v>736</v>
       </c>
       <c r="G150" t="s">
-        <v>521</v>
+        <v>737</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -7625,22 +7553,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C151" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D151" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="E151" t="s">
-        <v>160</v>
+        <v>735</v>
       </c>
       <c r="F151" t="s">
-        <v>161</v>
+        <v>736</v>
       </c>
       <c r="G151" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -7648,22 +7576,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="C152" t="s">
-        <v>277</v>
+        <v>33</v>
       </c>
       <c r="D152" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="E152" t="s">
-        <v>750</v>
+        <v>278</v>
       </c>
       <c r="F152" t="s">
-        <v>751</v>
+        <v>279</v>
       </c>
       <c r="G152" t="s">
-        <v>29</v>
+        <v>741</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -7671,22 +7599,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="C153" t="s">
-        <v>277</v>
+        <v>33</v>
       </c>
       <c r="D153" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="E153" t="s">
-        <v>750</v>
+        <v>278</v>
       </c>
       <c r="F153" t="s">
-        <v>751</v>
+        <v>279</v>
       </c>
       <c r="G153" t="s">
-        <v>29</v>
+        <v>741</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -7694,22 +7622,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="C154" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D154" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="E154" t="s">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="F154" t="s">
-        <v>284</v>
+        <v>188</v>
       </c>
       <c r="G154" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -7717,22 +7645,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="C155" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D155" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="E155" t="s">
-        <v>283</v>
+        <v>748</v>
       </c>
       <c r="F155" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="G155" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -7740,22 +7668,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="C156" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D156" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="E156" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="F156" t="s">
-        <v>760</v>
+        <v>7</v>
       </c>
       <c r="G156" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -7763,22 +7691,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="C157" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D157" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="E157" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="F157" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="G157" t="s">
-        <v>761</v>
+        <v>95</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -7786,22 +7714,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="C158" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D158" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="E158" t="s">
-        <v>283</v>
+        <v>753</v>
       </c>
       <c r="F158" t="s">
-        <v>284</v>
+        <v>754</v>
       </c>
       <c r="G158" t="s">
-        <v>765</v>
+        <v>95</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -7809,22 +7737,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C159" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D159" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="E159" t="s">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="F159" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="G159" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -7832,22 +7760,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="C160" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D160" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="E160" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="F160" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="G160" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -7855,22 +7783,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="C161" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D161" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="E161" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="F161" t="s">
-        <v>7</v>
+        <v>765</v>
       </c>
       <c r="G161" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -7878,22 +7806,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="C162" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D162" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="E162" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="F162" t="s">
-        <v>7</v>
+        <v>765</v>
       </c>
       <c r="G162" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -7901,22 +7829,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C163" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D163" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E163" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="F163" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="G163" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -7924,22 +7852,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="C164" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D164" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E164" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="F164" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="G164" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -7947,22 +7875,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="C165" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D165" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="E165" t="s">
-        <v>84</v>
+        <v>775</v>
       </c>
       <c r="F165" t="s">
-        <v>7</v>
+        <v>776</v>
       </c>
       <c r="G165" t="s">
-        <v>782</v>
+        <v>471</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -7970,22 +7898,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C166" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="D166" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="E166" t="s">
-        <v>233</v>
+        <v>64</v>
       </c>
       <c r="F166" t="s">
-        <v>234</v>
+        <v>7</v>
       </c>
       <c r="G166" t="s">
-        <v>785</v>
+        <v>227</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -7993,22 +7921,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="C167" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="D167" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="E167" t="s">
-        <v>788</v>
+        <v>64</v>
       </c>
       <c r="F167" t="s">
-        <v>789</v>
+        <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>790</v>
+        <v>227</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -8016,22 +7944,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="C168" t="s">
-        <v>58</v>
+        <v>447</v>
       </c>
       <c r="D168" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="E168" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F168" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="G168" t="s">
-        <v>790</v>
+        <v>43</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -8039,22 +7967,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="C169" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D169" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="E169" t="s">
-        <v>794</v>
+        <v>81</v>
       </c>
       <c r="F169" t="s">
-        <v>795</v>
+        <v>7</v>
       </c>
       <c r="G169" t="s">
-        <v>37</v>
+        <v>786</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -8062,22 +7990,22 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="C170" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D170" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="E170" t="s">
-        <v>794</v>
+        <v>360</v>
       </c>
       <c r="F170" t="s">
-        <v>795</v>
+        <v>361</v>
       </c>
       <c r="G170" t="s">
-        <v>37</v>
+        <v>789</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -8085,22 +8013,22 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="C171" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="D171" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="E171" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="F171" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="G171" t="s">
-        <v>486</v>
+        <v>117</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -8108,22 +8036,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="C172" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="D172" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E172" t="s">
-        <v>64</v>
+        <v>796</v>
       </c>
       <c r="F172" t="s">
-        <v>7</v>
+        <v>797</v>
       </c>
       <c r="G172" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -8131,22 +8059,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C173" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="D173" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E173" t="s">
-        <v>64</v>
+        <v>796</v>
       </c>
       <c r="F173" t="s">
-        <v>7</v>
+        <v>797</v>
       </c>
       <c r="G173" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -8154,22 +8082,22 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C174" t="s">
-        <v>459</v>
+        <v>105</v>
       </c>
       <c r="D174" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E174" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F174" t="s">
-        <v>807</v>
+        <v>7</v>
       </c>
       <c r="G174" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -8177,22 +8105,22 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C175" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D175" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E175" t="s">
-        <v>81</v>
+        <v>804</v>
       </c>
       <c r="F175" t="s">
-        <v>7</v>
+        <v>805</v>
       </c>
       <c r="G175" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -8200,255 +8128,255 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C176" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="D176" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E176" t="s">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="F176" t="s">
-        <v>373</v>
+        <v>7</v>
       </c>
       <c r="G176" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="H176" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C177" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="D177" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E177" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="F177" t="s">
-        <v>817</v>
+        <v>7</v>
       </c>
       <c r="G177" t="s">
-        <v>117</v>
+        <v>813</v>
       </c>
       <c r="H177" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="C178" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="D178" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E178" t="s">
-        <v>820</v>
+        <v>101</v>
       </c>
       <c r="F178" t="s">
-        <v>821</v>
+        <v>102</v>
       </c>
       <c r="G178" t="s">
-        <v>212</v>
+        <v>816</v>
       </c>
       <c r="H178" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C179" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="D179" t="s">
+        <v>818</v>
+      </c>
+      <c r="E179" t="s">
+        <v>264</v>
+      </c>
+      <c r="F179" t="s">
+        <v>7</v>
+      </c>
+      <c r="G179" t="s">
         <v>819</v>
       </c>
-      <c r="E179" t="s">
-        <v>820</v>
-      </c>
-      <c r="F179" t="s">
-        <v>821</v>
-      </c>
-      <c r="G179" t="s">
-        <v>212</v>
-      </c>
       <c r="H179" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>820</v>
+      </c>
+      <c r="C180" t="s">
+        <v>61</v>
+      </c>
+      <c r="D180" t="s">
+        <v>821</v>
+      </c>
+      <c r="E180" t="s">
+        <v>822</v>
+      </c>
+      <c r="F180" t="s">
         <v>823</v>
       </c>
-      <c r="C180" t="s">
-        <v>105</v>
-      </c>
-      <c r="D180" t="s">
+      <c r="G180" t="s">
         <v>824</v>
       </c>
-      <c r="E180" t="s">
-        <v>825</v>
-      </c>
-      <c r="F180" t="s">
-        <v>7</v>
-      </c>
-      <c r="G180" t="s">
-        <v>204</v>
-      </c>
       <c r="H180" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>825</v>
+      </c>
+      <c r="C181" t="s">
+        <v>30</v>
+      </c>
+      <c r="D181" t="s">
         <v>826</v>
       </c>
-      <c r="C181" t="s">
-        <v>58</v>
-      </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>827</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>828</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>829</v>
       </c>
-      <c r="G181" t="s">
-        <v>830</v>
-      </c>
       <c r="H181" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>830</v>
+      </c>
+      <c r="C182" t="s">
+        <v>42</v>
+      </c>
+      <c r="D182" t="s">
         <v>831</v>
       </c>
-      <c r="C182" t="s">
-        <v>105</v>
-      </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>832</v>
       </c>
-      <c r="E182" t="s">
-        <v>83</v>
-      </c>
       <c r="F182" t="s">
-        <v>7</v>
+        <v>833</v>
       </c>
       <c r="G182" t="s">
-        <v>833</v>
+        <v>612</v>
       </c>
       <c r="H182" t="s">
-        <v>54</v>
+        <v>834</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>835</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" t="s">
+        <v>836</v>
+      </c>
+      <c r="E183" t="s">
+        <v>837</v>
+      </c>
+      <c r="F183" t="s">
+        <v>838</v>
+      </c>
+      <c r="G183" t="s">
+        <v>839</v>
+      </c>
+      <c r="H183" t="s">
         <v>834</v>
-      </c>
-      <c r="C183" t="s">
-        <v>90</v>
-      </c>
-      <c r="D183" t="s">
-        <v>835</v>
-      </c>
-      <c r="E183" t="s">
-        <v>836</v>
-      </c>
-      <c r="F183" t="s">
-        <v>7</v>
-      </c>
-      <c r="G183" t="s">
-        <v>837</v>
-      </c>
-      <c r="H183" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C184" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D184" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E184" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="F184" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="G184" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="H184" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C185" t="s">
         <v>13</v>
       </c>
       <c r="D185" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E185" t="s">
-        <v>269</v>
+        <v>845</v>
       </c>
       <c r="F185" t="s">
         <v>7</v>
       </c>
       <c r="G185" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H185" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C186" t="s">
-        <v>61</v>
+        <v>338</v>
       </c>
       <c r="D186" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E186" t="s">
-        <v>846</v>
+        <v>129</v>
       </c>
       <c r="F186" t="s">
-        <v>847</v>
+        <v>130</v>
       </c>
       <c r="G186" t="s">
-        <v>848</v>
+        <v>210</v>
       </c>
       <c r="H186" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -8456,22 +8384,22 @@
         <v>849</v>
       </c>
       <c r="C187" t="s">
-        <v>30</v>
+        <v>850</v>
       </c>
       <c r="D187" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E187" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F187" t="s">
-        <v>852</v>
+        <v>7</v>
       </c>
       <c r="G187" t="s">
         <v>853</v>
       </c>
       <c r="H187" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -8479,65 +8407,65 @@
         <v>854</v>
       </c>
       <c r="C188" t="s">
-        <v>42</v>
+        <v>850</v>
       </c>
       <c r="D188" t="s">
         <v>855</v>
       </c>
       <c r="E188" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="F188" t="s">
-        <v>857</v>
+        <v>7</v>
       </c>
       <c r="G188" t="s">
-        <v>631</v>
+        <v>191</v>
       </c>
       <c r="H188" t="s">
-        <v>858</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C189" t="s">
-        <v>18</v>
+        <v>850</v>
       </c>
       <c r="D189" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="E189" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="F189" t="s">
-        <v>862</v>
+        <v>7</v>
       </c>
       <c r="G189" t="s">
-        <v>863</v>
+        <v>191</v>
       </c>
       <c r="H189" t="s">
-        <v>858</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="C190" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D190" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="E190" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="F190" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="G190" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="H190" t="s">
         <v>10</v>
@@ -8545,22 +8473,22 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C191" t="s">
         <v>13</v>
       </c>
       <c r="D191" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="E191" t="s">
-        <v>869</v>
+        <v>845</v>
       </c>
       <c r="F191" t="s">
         <v>7</v>
       </c>
       <c r="G191" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="H191" t="s">
         <v>10</v>
@@ -8568,22 +8496,22 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="C192" t="s">
-        <v>346</v>
+        <v>70</v>
       </c>
       <c r="D192" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="E192" t="s">
-        <v>131</v>
+        <v>865</v>
       </c>
       <c r="F192" t="s">
-        <v>132</v>
+        <v>866</v>
       </c>
       <c r="G192" t="s">
-        <v>215</v>
+        <v>867</v>
       </c>
       <c r="H192" t="s">
         <v>10</v>
@@ -8591,22 +8519,22 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="C193" t="s">
-        <v>874</v>
+        <v>90</v>
       </c>
       <c r="D193" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="E193" t="s">
-        <v>876</v>
+        <v>812</v>
       </c>
       <c r="F193" t="s">
         <v>7</v>
       </c>
       <c r="G193" t="s">
-        <v>877</v>
+        <v>241</v>
       </c>
       <c r="H193" t="s">
         <v>10</v>
@@ -8614,22 +8542,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>878</v>
+        <v>215</v>
       </c>
       <c r="C194" t="s">
-        <v>874</v>
+        <v>34</v>
       </c>
       <c r="D194" t="s">
-        <v>879</v>
+        <v>216</v>
       </c>
       <c r="E194" t="s">
-        <v>876</v>
+        <v>165</v>
       </c>
       <c r="F194" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G194" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="H194" t="s">
         <v>10</v>
@@ -8637,22 +8565,22 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="C195" t="s">
-        <v>874</v>
+        <v>61</v>
       </c>
       <c r="D195" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="E195" t="s">
-        <v>876</v>
+        <v>60</v>
       </c>
       <c r="F195" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G195" t="s">
-        <v>196</v>
+        <v>872</v>
       </c>
       <c r="H195" t="s">
         <v>10</v>
@@ -8660,22 +8588,22 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C196" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="D196" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="E196" t="s">
-        <v>86</v>
+        <v>875</v>
       </c>
       <c r="F196" t="s">
-        <v>87</v>
+        <v>876</v>
       </c>
       <c r="G196" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="H196" t="s">
         <v>10</v>
@@ -8683,22 +8611,22 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="C197" t="s">
         <v>13</v>
       </c>
       <c r="D197" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="E197" t="s">
-        <v>869</v>
+        <v>50</v>
       </c>
       <c r="F197" t="s">
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="H197" t="s">
         <v>10</v>
@@ -8706,22 +8634,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C198" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D198" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="E198" t="s">
-        <v>889</v>
+        <v>50</v>
       </c>
       <c r="F198" t="s">
-        <v>890</v>
+        <v>7</v>
       </c>
       <c r="G198" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="H198" t="s">
         <v>10</v>
@@ -8729,22 +8657,22 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="C199" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="D199" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="E199" t="s">
-        <v>836</v>
+        <v>106</v>
       </c>
       <c r="F199" t="s">
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>246</v>
+        <v>884</v>
       </c>
       <c r="H199" t="s">
         <v>10</v>
@@ -8752,22 +8680,22 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>220</v>
+        <v>885</v>
       </c>
       <c r="C200" t="s">
-        <v>34</v>
+        <v>886</v>
       </c>
       <c r="D200" t="s">
-        <v>221</v>
+        <v>887</v>
       </c>
       <c r="E200" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="F200" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G200" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H200" t="s">
         <v>10</v>
@@ -8775,22 +8703,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="C201" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D201" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="E201" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="F201" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="G201" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="H201" t="s">
         <v>10</v>
@@ -8798,22 +8726,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="C202" t="s">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="D202" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="E202" t="s">
-        <v>899</v>
+        <v>208</v>
       </c>
       <c r="F202" t="s">
-        <v>900</v>
+        <v>209</v>
       </c>
       <c r="G202" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="H202" t="s">
         <v>10</v>
@@ -8821,22 +8749,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="C203" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="D203" t="s">
-        <v>903</v>
+        <v>893</v>
       </c>
       <c r="E203" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F203" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G203" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
       <c r="H203" t="s">
         <v>10</v>
@@ -8844,22 +8772,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="C204" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D204" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="E204" t="s">
-        <v>50</v>
+        <v>194</v>
       </c>
       <c r="F204" t="s">
         <v>7</v>
       </c>
       <c r="G204" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="H204" t="s">
         <v>10</v>
@@ -8867,22 +8795,22 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>906</v>
+        <v>230</v>
       </c>
       <c r="C205" t="s">
-        <v>134</v>
+        <v>850</v>
       </c>
       <c r="D205" t="s">
-        <v>907</v>
+        <v>231</v>
       </c>
       <c r="E205" t="s">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="F205" t="s">
         <v>7</v>
       </c>
       <c r="G205" t="s">
-        <v>908</v>
+        <v>232</v>
       </c>
       <c r="H205" t="s">
         <v>10</v>
@@ -8890,22 +8818,22 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="C206" t="s">
-        <v>910</v>
+        <v>90</v>
       </c>
       <c r="D206" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="E206" t="s">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="F206" t="s">
         <v>7</v>
       </c>
       <c r="G206" t="s">
-        <v>230</v>
+        <v>901</v>
       </c>
       <c r="H206" t="s">
         <v>10</v>
@@ -8913,22 +8841,22 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D207" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="E207" t="s">
-        <v>213</v>
+        <v>900</v>
       </c>
       <c r="F207" t="s">
-        <v>214</v>
+        <v>7</v>
       </c>
       <c r="G207" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="H207" t="s">
         <v>10</v>
@@ -8936,22 +8864,22 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="C208" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D208" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="E208" t="s">
-        <v>213</v>
+        <v>900</v>
       </c>
       <c r="F208" t="s">
-        <v>214</v>
+        <v>7</v>
       </c>
       <c r="G208" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="H208" t="s">
         <v>10</v>
@@ -8959,13 +8887,13 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="C209" t="s">
         <v>107</v>
       </c>
       <c r="D209" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="E209" t="s">
         <v>45</v>
@@ -8974,7 +8902,7 @@
         <v>46</v>
       </c>
       <c r="G209" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="H209" t="s">
         <v>10</v>
@@ -8982,22 +8910,22 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>919</v>
+        <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>9</v>
+        <v>886</v>
       </c>
       <c r="D210" t="s">
-        <v>920</v>
+        <v>234</v>
       </c>
       <c r="E210" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="F210" t="s">
         <v>7</v>
       </c>
       <c r="G210" t="s">
-        <v>921</v>
+        <v>236</v>
       </c>
       <c r="H210" t="s">
         <v>10</v>
@@ -9005,22 +8933,22 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>235</v>
+        <v>907</v>
       </c>
       <c r="C211" t="s">
-        <v>874</v>
+        <v>44</v>
       </c>
       <c r="D211" t="s">
-        <v>236</v>
+        <v>908</v>
       </c>
       <c r="E211" t="s">
-        <v>219</v>
+        <v>909</v>
       </c>
       <c r="F211" t="s">
         <v>7</v>
       </c>
       <c r="G211" t="s">
-        <v>237</v>
+        <v>910</v>
       </c>
       <c r="H211" t="s">
         <v>10</v>
@@ -9028,22 +8956,22 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="C212" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="D212" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="E212" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="F212" t="s">
         <v>7</v>
       </c>
       <c r="G212" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="H212" t="s">
         <v>10</v>
@@ -9051,22 +8979,22 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="C213" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="D213" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="E213" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="F213" t="s">
         <v>7</v>
       </c>
       <c r="G213" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="H213" t="s">
         <v>10</v>
@@ -9074,22 +9002,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="C214" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D214" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="E214" t="s">
-        <v>924</v>
+        <v>845</v>
       </c>
       <c r="F214" t="s">
         <v>7</v>
       </c>
       <c r="G214" t="s">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="H214" t="s">
         <v>10</v>
@@ -9097,22 +9025,22 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="C215" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D215" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="E215" t="s">
-        <v>45</v>
+        <v>411</v>
       </c>
       <c r="F215" t="s">
-        <v>46</v>
+        <v>412</v>
       </c>
       <c r="G215" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="H215" t="s">
         <v>10</v>
@@ -9120,22 +9048,22 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>238</v>
+        <v>919</v>
       </c>
       <c r="C216" t="s">
-        <v>910</v>
+        <v>12</v>
       </c>
       <c r="D216" t="s">
-        <v>239</v>
+        <v>917</v>
       </c>
       <c r="E216" t="s">
-        <v>240</v>
+        <v>411</v>
       </c>
       <c r="F216" t="s">
-        <v>7</v>
+        <v>412</v>
       </c>
       <c r="G216" t="s">
-        <v>241</v>
+        <v>918</v>
       </c>
       <c r="H216" t="s">
         <v>10</v>
@@ -9143,22 +9071,22 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="C217" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="D217" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="E217" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="F217" t="s">
-        <v>7</v>
+        <v>923</v>
       </c>
       <c r="G217" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="H217" t="s">
         <v>10</v>
@@ -9166,22 +9094,22 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="C218" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="D218" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="E218" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="F218" t="s">
-        <v>7</v>
+        <v>923</v>
       </c>
       <c r="G218" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="H218" t="s">
         <v>10</v>
@@ -9189,22 +9117,22 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
       <c r="C219" t="s">
-        <v>44</v>
+        <v>447</v>
       </c>
       <c r="D219" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="E219" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="F219" t="s">
-        <v>7</v>
+        <v>929</v>
       </c>
       <c r="G219" t="s">
-        <v>934</v>
+        <v>223</v>
       </c>
       <c r="H219" t="s">
         <v>10</v>
@@ -9212,22 +9140,22 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="C220" t="s">
-        <v>13</v>
+        <v>886</v>
       </c>
       <c r="D220" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="E220" t="s">
-        <v>869</v>
+        <v>66</v>
       </c>
       <c r="F220" t="s">
         <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="H220" t="s">
         <v>10</v>
@@ -9235,22 +9163,22 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="C221" t="s">
-        <v>12</v>
+        <v>886</v>
       </c>
       <c r="D221" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
       <c r="E221" t="s">
-        <v>423</v>
+        <v>66</v>
       </c>
       <c r="F221" t="s">
-        <v>424</v>
+        <v>7</v>
       </c>
       <c r="G221" t="s">
-        <v>942</v>
+        <v>932</v>
       </c>
       <c r="H221" t="s">
         <v>10</v>
@@ -9258,22 +9186,22 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="C222" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D222" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="E222" t="s">
-        <v>423</v>
+        <v>936</v>
       </c>
       <c r="F222" t="s">
-        <v>424</v>
+        <v>7</v>
       </c>
       <c r="G222" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="H222" t="s">
         <v>10</v>
@@ -9281,22 +9209,22 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="C223" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="D223" t="s">
-        <v>945</v>
+        <v>935</v>
       </c>
       <c r="E223" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="F223" t="s">
-        <v>947</v>
+        <v>7</v>
       </c>
       <c r="G223" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="H223" t="s">
         <v>10</v>
@@ -9304,22 +9232,22 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>949</v>
+        <v>939</v>
       </c>
       <c r="C224" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="D224" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="E224" t="s">
-        <v>946</v>
+        <v>845</v>
       </c>
       <c r="F224" t="s">
-        <v>947</v>
+        <v>7</v>
       </c>
       <c r="G224" t="s">
-        <v>948</v>
+        <v>846</v>
       </c>
       <c r="H224" t="s">
         <v>10</v>
@@ -9327,22 +9255,22 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="C225" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="D225" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="E225" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="F225" t="s">
-        <v>953</v>
+        <v>26</v>
       </c>
       <c r="G225" t="s">
-        <v>228</v>
+        <v>944</v>
       </c>
       <c r="H225" t="s">
         <v>10</v>
@@ -9350,22 +9278,22 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="C226" t="s">
-        <v>910</v>
+        <v>423</v>
       </c>
       <c r="D226" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="E226" t="s">
-        <v>66</v>
+        <v>943</v>
       </c>
       <c r="F226" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G226" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="H226" t="s">
         <v>10</v>
@@ -9373,22 +9301,22 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="C227" t="s">
-        <v>910</v>
+        <v>272</v>
       </c>
       <c r="D227" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="E227" t="s">
-        <v>66</v>
+        <v>948</v>
       </c>
       <c r="F227" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="G227" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="H227" t="s">
         <v>10</v>
@@ -9396,22 +9324,22 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C228" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D228" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="E228" t="s">
-        <v>960</v>
+        <v>224</v>
       </c>
       <c r="F228" t="s">
         <v>7</v>
       </c>
       <c r="G228" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="H228" t="s">
         <v>10</v>
@@ -9419,22 +9347,22 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="C229" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="D229" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="E229" t="s">
-        <v>960</v>
+        <v>197</v>
       </c>
       <c r="F229" t="s">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="G229" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="H229" t="s">
         <v>10</v>
@@ -9442,22 +9370,22 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="C230" t="s">
-        <v>13</v>
+        <v>447</v>
       </c>
       <c r="D230" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="E230" t="s">
-        <v>869</v>
+        <v>74</v>
       </c>
       <c r="F230" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="G230" t="s">
-        <v>870</v>
+        <v>179</v>
       </c>
       <c r="H230" t="s">
         <v>10</v>
@@ -9465,22 +9393,22 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="C231" t="s">
-        <v>435</v>
+        <v>13</v>
       </c>
       <c r="D231" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="E231" t="s">
-        <v>967</v>
+        <v>845</v>
       </c>
       <c r="F231" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G231" t="s">
-        <v>968</v>
+        <v>846</v>
       </c>
       <c r="H231" t="s">
         <v>10</v>
@@ -9488,22 +9416,22 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="C232" t="s">
-        <v>435</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="E232" t="s">
-        <v>967</v>
+        <v>147</v>
       </c>
       <c r="F232" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="G232" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="H232" t="s">
         <v>10</v>
@@ -9511,22 +9439,22 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="C233" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="E233" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="F233" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="G233" t="s">
-        <v>973</v>
+        <v>71</v>
       </c>
       <c r="H233" t="s">
         <v>10</v>
@@ -9534,22 +9462,22 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="C234" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="D234" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="E234" t="s">
-        <v>229</v>
+        <v>968</v>
       </c>
       <c r="F234" t="s">
-        <v>7</v>
+        <v>969</v>
       </c>
       <c r="G234" t="s">
-        <v>976</v>
+        <v>29</v>
       </c>
       <c r="H234" t="s">
         <v>10</v>
@@ -9557,22 +9485,22 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="C235" t="s">
-        <v>264</v>
+        <v>90</v>
       </c>
       <c r="D235" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="E235" t="s">
-        <v>202</v>
+        <v>972</v>
       </c>
       <c r="F235" t="s">
-        <v>203</v>
+        <v>7</v>
       </c>
       <c r="G235" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="H235" t="s">
         <v>10</v>
@@ -9580,22 +9508,22 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="C236" t="s">
-        <v>459</v>
+        <v>28</v>
       </c>
       <c r="D236" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="E236" t="s">
-        <v>74</v>
+        <v>976</v>
       </c>
       <c r="F236" t="s">
-        <v>75</v>
+        <v>977</v>
       </c>
       <c r="G236" t="s">
-        <v>184</v>
+        <v>978</v>
       </c>
       <c r="H236" t="s">
         <v>10</v>
@@ -9603,22 +9531,22 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C237" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="D237" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="E237" t="s">
-        <v>869</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>7</v>
       </c>
       <c r="G237" t="s">
-        <v>870</v>
+        <v>981</v>
       </c>
       <c r="H237" t="s">
         <v>10</v>
@@ -9626,22 +9554,22 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C238" t="s">
-        <v>264</v>
+        <v>338</v>
       </c>
       <c r="D238" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E238" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="F238" t="s">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="H238" t="s">
         <v>10</v>
@@ -9649,22 +9577,22 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C239" t="s">
-        <v>264</v>
+        <v>338</v>
       </c>
       <c r="D239" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="E239" t="s">
-        <v>989</v>
+        <v>128</v>
       </c>
       <c r="F239" t="s">
         <v>7</v>
       </c>
       <c r="G239" t="s">
-        <v>71</v>
+        <v>981</v>
       </c>
       <c r="H239" t="s">
         <v>10</v>
@@ -9672,22 +9600,22 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C240" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D240" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="E240" t="s">
-        <v>992</v>
+        <v>222</v>
       </c>
       <c r="F240" t="s">
-        <v>993</v>
+        <v>7</v>
       </c>
       <c r="G240" t="s">
-        <v>29</v>
+        <v>986</v>
       </c>
       <c r="H240" t="s">
         <v>10</v>
@@ -9695,22 +9623,22 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="C241" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D241" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="E241" t="s">
-        <v>996</v>
+        <v>161</v>
       </c>
       <c r="F241" t="s">
         <v>7</v>
       </c>
       <c r="G241" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="H241" t="s">
         <v>10</v>
@@ -9718,22 +9646,22 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="C242" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D242" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="E242" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="F242" t="s">
-        <v>1001</v>
+        <v>7</v>
       </c>
       <c r="G242" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="H242" t="s">
         <v>10</v>
@@ -9741,22 +9669,22 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="C243" t="s">
-        <v>346</v>
+        <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="E243" t="s">
-        <v>130</v>
+        <v>996</v>
       </c>
       <c r="F243" t="s">
         <v>7</v>
       </c>
       <c r="G243" t="s">
-        <v>1005</v>
+        <v>530</v>
       </c>
       <c r="H243" t="s">
         <v>10</v>
@@ -9764,22 +9692,22 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="C244" t="s">
-        <v>346</v>
+        <v>131</v>
       </c>
       <c r="D244" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="E244" t="s">
-        <v>130</v>
+        <v>999</v>
       </c>
       <c r="F244" t="s">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="G244" t="s">
-        <v>1005</v>
+        <v>353</v>
       </c>
       <c r="H244" t="s">
         <v>10</v>
@@ -9787,22 +9715,22 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="C245" t="s">
-        <v>346</v>
+        <v>105</v>
       </c>
       <c r="D245" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E245" t="s">
-        <v>130</v>
+        <v>1003</v>
       </c>
       <c r="F245" t="s">
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H245" t="s">
         <v>10</v>
@@ -9810,22 +9738,22 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C246" t="s">
-        <v>42</v>
+        <v>886</v>
       </c>
       <c r="D246" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E246" t="s">
-        <v>227</v>
+        <v>1007</v>
       </c>
       <c r="F246" t="s">
         <v>7</v>
       </c>
       <c r="G246" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="H246" t="s">
         <v>10</v>
@@ -9833,22 +9761,22 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C247" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="D247" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E247" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F247" t="s">
         <v>7</v>
       </c>
       <c r="G247" t="s">
-        <v>1013</v>
+        <v>244</v>
       </c>
       <c r="H247" t="s">
         <v>10</v>
@@ -9856,22 +9784,22 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C248" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="D248" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E248" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F248" t="s">
         <v>7</v>
       </c>
       <c r="G248" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="H248" t="s">
         <v>10</v>
@@ -9879,22 +9807,22 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C249" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E249" t="s">
-        <v>1020</v>
+        <v>221</v>
       </c>
       <c r="F249" t="s">
         <v>7</v>
       </c>
       <c r="G249" t="s">
-        <v>545</v>
+        <v>1017</v>
       </c>
       <c r="H249" t="s">
         <v>10</v>
@@ -9902,22 +9830,22 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C250" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="D250" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E250" t="s">
-        <v>1023</v>
+        <v>822</v>
       </c>
       <c r="F250" t="s">
-        <v>1024</v>
+        <v>823</v>
       </c>
       <c r="G250" t="s">
-        <v>361</v>
+        <v>1020</v>
       </c>
       <c r="H250" t="s">
         <v>10</v>
@@ -9925,22 +9853,22 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C251" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D251" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="E251" t="s">
-        <v>1027</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>7</v>
       </c>
       <c r="G251" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="H251" t="s">
         <v>10</v>
@@ -9948,22 +9876,22 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="C252" t="s">
-        <v>910</v>
+        <v>13</v>
       </c>
       <c r="D252" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="E252" t="s">
-        <v>1031</v>
+        <v>264</v>
       </c>
       <c r="F252" t="s">
         <v>7</v>
       </c>
       <c r="G252" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="H252" t="s">
         <v>10</v>
@@ -9971,22 +9899,22 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="C253" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D253" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="E253" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="F253" t="s">
         <v>7</v>
       </c>
       <c r="G253" t="s">
-        <v>249</v>
+        <v>1026</v>
       </c>
       <c r="H253" t="s">
         <v>10</v>
@@ -9994,22 +9922,22 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="C254" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D254" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="E254" t="s">
-        <v>1037</v>
+        <v>49</v>
       </c>
       <c r="F254" t="s">
         <v>7</v>
       </c>
       <c r="G254" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="H254" t="s">
         <v>10</v>
@@ -10017,22 +9945,22 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="C255" t="s">
         <v>15</v>
       </c>
       <c r="D255" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="E255" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F255" t="s">
         <v>7</v>
       </c>
       <c r="G255" t="s">
-        <v>1041</v>
+        <v>67</v>
       </c>
       <c r="H255" t="s">
         <v>10</v>
@@ -10040,22 +9968,22 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
       <c r="C256" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="D256" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="E256" t="s">
-        <v>846</v>
+        <v>83</v>
       </c>
       <c r="F256" t="s">
-        <v>847</v>
+        <v>7</v>
       </c>
       <c r="G256" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="H256" t="s">
         <v>10</v>
@@ -10063,22 +9991,22 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="C257" t="s">
-        <v>68</v>
+        <v>498</v>
       </c>
       <c r="D257" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E257" t="s">
-        <v>127</v>
+        <v>1038</v>
       </c>
       <c r="F257" t="s">
-        <v>7</v>
+        <v>1039</v>
       </c>
       <c r="G257" t="s">
-        <v>1047</v>
+        <v>238</v>
       </c>
       <c r="H257" t="s">
         <v>10</v>
@@ -10086,22 +10014,22 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="C258" t="s">
-        <v>13</v>
+        <v>498</v>
       </c>
       <c r="D258" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="E258" t="s">
-        <v>269</v>
+        <v>1042</v>
       </c>
       <c r="F258" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G258" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="H258" t="s">
         <v>10</v>
@@ -10109,22 +10037,22 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="C259" t="s">
-        <v>13</v>
+        <v>850</v>
       </c>
       <c r="D259" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E259" t="s">
-        <v>269</v>
+        <v>114</v>
       </c>
       <c r="F259" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="G259" t="s">
-        <v>1050</v>
+        <v>23</v>
       </c>
       <c r="H259" t="s">
         <v>10</v>
@@ -10132,22 +10060,22 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="C260" t="s">
-        <v>17</v>
+        <v>338</v>
       </c>
       <c r="D260" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="E260" t="s">
-        <v>49</v>
+        <v>1048</v>
       </c>
       <c r="F260" t="s">
-        <v>7</v>
+        <v>1049</v>
       </c>
       <c r="G260" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="H260" t="s">
         <v>10</v>
@@ -10155,22 +10083,22 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C261" t="s">
+        <v>57</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G261" t="s">
         <v>1055</v>
-      </c>
-      <c r="C261" t="s">
-        <v>15</v>
-      </c>
-      <c r="D261" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E261" t="s">
-        <v>226</v>
-      </c>
-      <c r="F261" t="s">
-        <v>7</v>
-      </c>
-      <c r="G261" t="s">
-        <v>67</v>
       </c>
       <c r="H261" t="s">
         <v>10</v>
@@ -10178,19 +10106,19 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C262" t="s">
+        <v>17</v>
+      </c>
+      <c r="D262" t="s">
         <v>1057</v>
       </c>
-      <c r="C262" t="s">
-        <v>105</v>
-      </c>
-      <c r="D262" t="s">
+      <c r="E262" t="s">
         <v>1058</v>
       </c>
-      <c r="E262" t="s">
-        <v>83</v>
-      </c>
       <c r="F262" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="G262" t="s">
         <v>1059</v>
@@ -10204,19 +10132,19 @@
         <v>1060</v>
       </c>
       <c r="C263" t="s">
-        <v>513</v>
+        <v>27</v>
       </c>
       <c r="D263" t="s">
         <v>1061</v>
       </c>
       <c r="E263" t="s">
+        <v>429</v>
+      </c>
+      <c r="F263" t="s">
+        <v>430</v>
+      </c>
+      <c r="G263" t="s">
         <v>1062</v>
-      </c>
-      <c r="F263" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G263" t="s">
-        <v>243</v>
       </c>
       <c r="H263" t="s">
         <v>10</v>
@@ -10224,22 +10152,22 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C264" t="s">
+        <v>30</v>
+      </c>
+      <c r="D264" t="s">
         <v>1064</v>
       </c>
-      <c r="C264" t="s">
-        <v>513</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1065</v>
-      </c>
       <c r="E264" t="s">
-        <v>1066</v>
+        <v>143</v>
       </c>
       <c r="F264" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="G264" t="s">
-        <v>1067</v>
+        <v>14</v>
       </c>
       <c r="H264" t="s">
         <v>10</v>
@@ -10247,22 +10175,22 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C265" t="s">
-        <v>874</v>
+        <v>31</v>
       </c>
       <c r="D265" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="E265" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="F265" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="G265" t="s">
-        <v>23</v>
+        <v>1067</v>
       </c>
       <c r="H265" t="s">
         <v>10</v>
@@ -10270,22 +10198,22 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C266" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D266" t="s">
         <v>1070</v>
       </c>
-      <c r="C266" t="s">
-        <v>346</v>
-      </c>
-      <c r="D266" t="s">
-        <v>1071</v>
-      </c>
       <c r="E266" t="s">
-        <v>1072</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
-        <v>1073</v>
+        <v>7</v>
       </c>
       <c r="G266" t="s">
-        <v>1074</v>
+        <v>239</v>
       </c>
       <c r="H266" t="s">
         <v>10</v>
@@ -10293,22 +10221,22 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C267" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D267" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="E267" t="s">
-        <v>1077</v>
+        <v>47</v>
       </c>
       <c r="F267" t="s">
-        <v>1078</v>
+        <v>48</v>
       </c>
       <c r="G267" t="s">
-        <v>1079</v>
+        <v>94</v>
       </c>
       <c r="H267" t="s">
         <v>10</v>
@@ -10316,22 +10244,22 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="C268" t="s">
-        <v>17</v>
+        <v>1074</v>
       </c>
       <c r="D268" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="E268" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="F268" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="G268" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="H268" t="s">
         <v>10</v>
@@ -10339,22 +10267,22 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="C269" t="s">
-        <v>27</v>
+        <v>1079</v>
       </c>
       <c r="D269" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="E269" t="s">
-        <v>441</v>
+        <v>992</v>
       </c>
       <c r="F269" t="s">
-        <v>442</v>
+        <v>7</v>
       </c>
       <c r="G269" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="H269" t="s">
         <v>10</v>
@@ -10362,22 +10290,22 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="C270" t="s">
-        <v>30</v>
+        <v>886</v>
       </c>
       <c r="D270" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="E270" t="s">
-        <v>146</v>
+        <v>1084</v>
       </c>
       <c r="F270" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="G270" t="s">
-        <v>14</v>
+        <v>237</v>
       </c>
       <c r="H270" t="s">
         <v>10</v>
@@ -10385,22 +10313,22 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C271" t="s">
-        <v>31</v>
+        <v>299</v>
       </c>
       <c r="D271" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="E271" t="s">
-        <v>77</v>
+        <v>1087</v>
       </c>
       <c r="F271" t="s">
-        <v>78</v>
+        <v>1088</v>
       </c>
       <c r="G271" t="s">
-        <v>1091</v>
+        <v>29</v>
       </c>
       <c r="H271" t="s">
         <v>10</v>
@@ -10408,22 +10336,22 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C272" t="s">
-        <v>1093</v>
+        <v>299</v>
       </c>
       <c r="D272" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="E272" t="s">
-        <v>119</v>
+        <v>1087</v>
       </c>
       <c r="F272" t="s">
-        <v>7</v>
+        <v>1088</v>
       </c>
       <c r="G272" t="s">
-        <v>244</v>
+        <v>29</v>
       </c>
       <c r="H272" t="s">
         <v>10</v>
@@ -10431,22 +10359,22 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="C273" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D273" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="E273" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="F273" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G273" t="s">
-        <v>94</v>
+        <v>1092</v>
       </c>
       <c r="H273" t="s">
         <v>10</v>
@@ -10454,22 +10382,22 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="C274" t="s">
-        <v>1098</v>
+        <v>13</v>
       </c>
       <c r="D274" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="E274" t="s">
-        <v>1100</v>
+        <v>264</v>
       </c>
       <c r="F274" t="s">
         <v>7</v>
       </c>
       <c r="G274" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="H274" t="s">
         <v>10</v>
@@ -10477,22 +10405,22 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="C275" t="s">
-        <v>1103</v>
+        <v>110</v>
       </c>
       <c r="D275" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="E275" t="s">
-        <v>1016</v>
+        <v>108</v>
       </c>
       <c r="F275" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="G275" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="H275" t="s">
         <v>10</v>
@@ -10500,22 +10428,22 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="C276" t="s">
-        <v>910</v>
+        <v>72</v>
       </c>
       <c r="D276" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
       <c r="E276" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="F276" t="s">
-        <v>7</v>
+        <v>1102</v>
       </c>
       <c r="G276" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="H276" t="s">
         <v>10</v>
@@ -10523,22 +10451,22 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="C277" t="s">
-        <v>307</v>
+        <v>27</v>
       </c>
       <c r="D277" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="E277" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="F277" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="G277" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H277" t="s">
         <v>10</v>
@@ -10546,22 +10474,22 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="C278" t="s">
-        <v>307</v>
+        <v>27</v>
       </c>
       <c r="D278" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="E278" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="F278" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="G278" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H278" t="s">
         <v>10</v>
@@ -10569,22 +10497,22 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="C279" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D279" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="E279" t="s">
-        <v>163</v>
+        <v>1110</v>
       </c>
       <c r="F279" t="s">
-        <v>25</v>
+        <v>1111</v>
       </c>
       <c r="G279" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="H279" t="s">
         <v>10</v>
@@ -10592,22 +10520,22 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C280" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D280" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="E280" t="s">
-        <v>269</v>
+        <v>464</v>
       </c>
       <c r="F280" t="s">
-        <v>7</v>
+        <v>465</v>
       </c>
       <c r="G280" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="H280" t="s">
         <v>10</v>
@@ -10615,22 +10543,22 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="C281" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="D281" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="E281" t="s">
-        <v>108</v>
+        <v>716</v>
       </c>
       <c r="F281" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="G281" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="H281" t="s">
         <v>10</v>
@@ -10638,22 +10566,22 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C282" t="s">
+        <v>153</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E282" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G282" t="s">
         <v>1123</v>
-      </c>
-      <c r="C282" t="s">
-        <v>72</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1124</v>
-      </c>
-      <c r="E282" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F282" t="s">
-        <v>1126</v>
-      </c>
-      <c r="G282" t="s">
-        <v>177</v>
       </c>
       <c r="H282" t="s">
         <v>10</v>
@@ -10661,22 +10589,22 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C283" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="D283" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="E283" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="F283" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
       <c r="G283" t="s">
-        <v>16</v>
+        <v>1123</v>
       </c>
       <c r="H283" t="s">
         <v>10</v>
@@ -10684,22 +10612,22 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="C284" t="s">
-        <v>27</v>
+        <v>447</v>
       </c>
       <c r="D284" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F284" t="s">
         <v>1128</v>
       </c>
-      <c r="E284" t="s">
+      <c r="G284" t="s">
         <v>1129</v>
-      </c>
-      <c r="F284" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G284" t="s">
-        <v>16</v>
       </c>
       <c r="H284" t="s">
         <v>10</v>
@@ -10707,22 +10635,22 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E285" t="s">
+        <v>119</v>
+      </c>
+      <c r="F285" t="s">
+        <v>7</v>
+      </c>
+      <c r="G285" t="s">
         <v>1132</v>
-      </c>
-      <c r="C285" t="s">
-        <v>27</v>
-      </c>
-      <c r="D285" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F285" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G285" t="s">
-        <v>1136</v>
       </c>
       <c r="H285" t="s">
         <v>10</v>
@@ -10730,22 +10658,22 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C286" t="s">
+        <v>338</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E286" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F286" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G286" t="s">
         <v>1137</v>
-      </c>
-      <c r="C286" t="s">
-        <v>22</v>
-      </c>
-      <c r="D286" t="s">
-        <v>1138</v>
-      </c>
-      <c r="E286" t="s">
-        <v>479</v>
-      </c>
-      <c r="F286" t="s">
-        <v>480</v>
-      </c>
-      <c r="G286" t="s">
-        <v>1139</v>
       </c>
       <c r="H286" t="s">
         <v>10</v>
@@ -10753,22 +10681,22 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C287" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D287" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E287" t="s">
-        <v>737</v>
+        <v>192</v>
       </c>
       <c r="F287" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="G287" t="s">
-        <v>1142</v>
+        <v>145</v>
       </c>
       <c r="H287" t="s">
         <v>10</v>
@@ -10776,22 +10704,22 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="C288" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="D288" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E288" t="s">
-        <v>1145</v>
+        <v>429</v>
       </c>
       <c r="F288" t="s">
-        <v>1146</v>
+        <v>430</v>
       </c>
       <c r="G288" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="H288" t="s">
         <v>10</v>
@@ -10799,10 +10727,10 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="C289" t="s">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="D289" t="s">
         <v>1144</v>
@@ -10811,10 +10739,10 @@
         <v>1145</v>
       </c>
       <c r="F289" t="s">
+        <v>41</v>
+      </c>
+      <c r="G289" t="s">
         <v>1146</v>
-      </c>
-      <c r="G289" t="s">
-        <v>1147</v>
       </c>
       <c r="H289" t="s">
         <v>10</v>
@@ -10822,22 +10750,22 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C290" t="s">
+        <v>447</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E290" t="s">
         <v>1149</v>
       </c>
-      <c r="C290" t="s">
-        <v>459</v>
-      </c>
-      <c r="D290" t="s">
+      <c r="F290" t="s">
         <v>1150</v>
       </c>
-      <c r="E290" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F290" t="s">
-        <v>1152</v>
-      </c>
       <c r="G290" t="s">
-        <v>1153</v>
+        <v>23</v>
       </c>
       <c r="H290" t="s">
         <v>10</v>
@@ -10845,22 +10773,22 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="C291" t="s">
-        <v>1093</v>
+        <v>58</v>
       </c>
       <c r="D291" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="E291" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="F291" t="s">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="G291" t="s">
-        <v>1156</v>
+        <v>322</v>
       </c>
       <c r="H291" t="s">
         <v>10</v>
@@ -10868,22 +10796,22 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="C292" t="s">
-        <v>346</v>
+        <v>153</v>
       </c>
       <c r="D292" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E292" t="s">
-        <v>1159</v>
+        <v>45</v>
       </c>
       <c r="F292" t="s">
-        <v>1160</v>
+        <v>46</v>
       </c>
       <c r="G292" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="H292" t="s">
         <v>10</v>
@@ -10891,22 +10819,22 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="C293" t="s">
-        <v>22</v>
+        <v>423</v>
       </c>
       <c r="D293" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="E293" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="F293" t="s">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="G293" t="s">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="H293" t="s">
         <v>10</v>
@@ -10914,22 +10842,22 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="C294" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D294" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="E294" t="s">
-        <v>441</v>
+        <v>804</v>
       </c>
       <c r="F294" t="s">
-        <v>442</v>
+        <v>805</v>
       </c>
       <c r="G294" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="H294" t="s">
         <v>10</v>
@@ -10937,22 +10865,22 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="C295" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D295" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="E295" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="F295" t="s">
-        <v>41</v>
+        <v>1164</v>
       </c>
       <c r="G295" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="H295" t="s">
         <v>10</v>
@@ -10960,22 +10888,22 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="C296" t="s">
-        <v>459</v>
+        <v>299</v>
       </c>
       <c r="D296" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="E296" t="s">
-        <v>1173</v>
+        <v>154</v>
       </c>
       <c r="F296" t="s">
-        <v>1174</v>
+        <v>155</v>
       </c>
       <c r="G296" t="s">
-        <v>23</v>
+        <v>1168</v>
       </c>
       <c r="H296" t="s">
         <v>10</v>
@@ -10983,22 +10911,22 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="C297" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D297" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="E297" t="s">
-        <v>144</v>
+        <v>716</v>
       </c>
       <c r="F297" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="G297" t="s">
-        <v>330</v>
+        <v>1171</v>
       </c>
       <c r="H297" t="s">
         <v>10</v>
@@ -11006,22 +10934,22 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="C298" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="D298" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
       <c r="E298" t="s">
-        <v>45</v>
+        <v>716</v>
       </c>
       <c r="F298" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G298" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
       <c r="H298" t="s">
         <v>10</v>
@@ -11029,22 +10957,22 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="C299" t="s">
-        <v>435</v>
+        <v>21</v>
       </c>
       <c r="D299" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="E299" t="s">
-        <v>122</v>
+        <v>716</v>
       </c>
       <c r="F299" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="G299" t="s">
-        <v>231</v>
+        <v>1171</v>
       </c>
       <c r="H299" t="s">
         <v>10</v>
@@ -11052,22 +10980,22 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
       <c r="C300" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D300" t="s">
-        <v>1183</v>
+        <v>1170</v>
       </c>
       <c r="E300" t="s">
-        <v>828</v>
+        <v>716</v>
       </c>
       <c r="F300" t="s">
-        <v>829</v>
+        <v>52</v>
       </c>
       <c r="G300" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
       <c r="H300" t="s">
         <v>10</v>
@@ -11075,22 +11003,22 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="C301" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="D301" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
       <c r="E301" t="s">
-        <v>1187</v>
+        <v>122</v>
       </c>
       <c r="F301" t="s">
-        <v>1188</v>
+        <v>123</v>
       </c>
       <c r="G301" t="s">
-        <v>1189</v>
+        <v>322</v>
       </c>
       <c r="H301" t="s">
         <v>10</v>
@@ -11098,22 +11026,22 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1190</v>
+        <v>1177</v>
       </c>
       <c r="C302" t="s">
-        <v>307</v>
+        <v>9</v>
       </c>
       <c r="D302" t="s">
-        <v>1191</v>
+        <v>1178</v>
       </c>
       <c r="E302" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="F302" t="s">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="G302" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="H302" t="s">
         <v>10</v>
@@ -11121,160 +11049,160 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
       <c r="C303" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D303" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
       <c r="E303" t="s">
-        <v>737</v>
+        <v>1182</v>
       </c>
       <c r="F303" t="s">
-        <v>52</v>
+        <v>1183</v>
       </c>
       <c r="G303" t="s">
-        <v>1195</v>
+        <v>1184</v>
       </c>
       <c r="H303" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="C304" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D304" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="E304" t="s">
-        <v>737</v>
+        <v>697</v>
       </c>
       <c r="F304" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="H304" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1197</v>
+        <v>1188</v>
       </c>
       <c r="C305" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="D305" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="E305" t="s">
-        <v>737</v>
+        <v>1190</v>
       </c>
       <c r="F305" t="s">
-        <v>52</v>
+        <v>1191</v>
       </c>
       <c r="G305" t="s">
-        <v>1195</v>
+        <v>56</v>
       </c>
       <c r="H305" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C306" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D306" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E306" t="s">
-        <v>737</v>
+        <v>211</v>
       </c>
       <c r="F306" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="G306" t="s">
-        <v>1195</v>
+        <v>85</v>
       </c>
       <c r="H306" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="C307" t="s">
-        <v>435</v>
+        <v>17</v>
       </c>
       <c r="D307" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="E307" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="F307" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="G307" t="s">
-        <v>330</v>
+        <v>408</v>
       </c>
       <c r="H307" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="C308" t="s">
-        <v>9</v>
+        <v>338</v>
       </c>
       <c r="D308" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="E308" t="s">
-        <v>199</v>
+        <v>1198</v>
       </c>
       <c r="F308" t="s">
-        <v>7</v>
+        <v>1199</v>
       </c>
       <c r="G308" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="H308" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C309" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="D309" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="E309" t="s">
-        <v>1206</v>
+        <v>88</v>
       </c>
       <c r="F309" t="s">
-        <v>1207</v>
+        <v>7</v>
       </c>
       <c r="G309" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="H309" t="s">
         <v>11</v>
@@ -11282,22 +11210,22 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="C310" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D310" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="E310" t="s">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="F310" t="s">
         <v>7</v>
       </c>
       <c r="G310" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="H310" t="s">
         <v>11</v>
@@ -11305,22 +11233,22 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="C311" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D311" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="E311" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="F311" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G311" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="H311" t="s">
         <v>11</v>
@@ -11328,22 +11256,22 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="C312" t="s">
-        <v>134</v>
+        <v>850</v>
       </c>
       <c r="D312" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="E312" t="s">
-        <v>216</v>
+        <v>1213</v>
       </c>
       <c r="F312" t="s">
-        <v>217</v>
+        <v>1214</v>
       </c>
       <c r="G312" t="s">
-        <v>85</v>
+        <v>1215</v>
       </c>
       <c r="H312" t="s">
         <v>11</v>
@@ -11351,22 +11279,22 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C313" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D313" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="E313" t="s">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="F313" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="G313" t="s">
-        <v>420</v>
+        <v>506</v>
       </c>
       <c r="H313" t="s">
         <v>11</v>
@@ -11374,22 +11302,22 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C314" t="s">
+        <v>259</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E314" t="s">
+        <v>88</v>
+      </c>
+      <c r="F314" t="s">
+        <v>7</v>
+      </c>
+      <c r="G314" t="s">
         <v>1220</v>
-      </c>
-      <c r="C314" t="s">
-        <v>346</v>
-      </c>
-      <c r="D314" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E314" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F314" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G314" t="s">
-        <v>1224</v>
       </c>
       <c r="H314" t="s">
         <v>11</v>
@@ -11397,22 +11325,22 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="C315" t="s">
-        <v>264</v>
+        <v>107</v>
       </c>
       <c r="D315" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E315" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="F315" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G315" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="H315" t="s">
         <v>11</v>
@@ -11420,22 +11348,22 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="C316" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="D316" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="E316" t="s">
-        <v>772</v>
+        <v>129</v>
       </c>
       <c r="F316" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="G316" t="s">
-        <v>1230</v>
+        <v>213</v>
       </c>
       <c r="H316" t="s">
         <v>11</v>
@@ -11443,236 +11371,98 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="C317" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="D317" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="E317" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="F317" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="G317" t="s">
-        <v>94</v>
+        <v>1230</v>
       </c>
       <c r="H317" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="C318" t="s">
-        <v>874</v>
+        <v>69</v>
       </c>
       <c r="D318" t="s">
-        <v>1236</v>
+        <v>1227</v>
       </c>
       <c r="E318" t="s">
-        <v>1237</v>
+        <v>1228</v>
       </c>
       <c r="F318" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="G318" t="s">
-        <v>1239</v>
+        <v>1230</v>
       </c>
       <c r="H318" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="C319" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D319" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="E319" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="F319" t="s">
-        <v>7</v>
+        <v>243</v>
       </c>
       <c r="G319" t="s">
-        <v>521</v>
+        <v>1234</v>
       </c>
       <c r="H319" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="C320" t="s">
-        <v>264</v>
+        <v>58</v>
       </c>
       <c r="D320" t="s">
-        <v>1243</v>
+        <v>1233</v>
       </c>
       <c r="E320" t="s">
-        <v>88</v>
+        <v>242</v>
       </c>
       <c r="F320" t="s">
-        <v>7</v>
+        <v>243</v>
       </c>
       <c r="G320" t="s">
-        <v>1244</v>
+        <v>1234</v>
       </c>
       <c r="H320" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C321" t="s">
-        <v>107</v>
-      </c>
-      <c r="D321" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E321" t="s">
-        <v>45</v>
-      </c>
-      <c r="F321" t="s">
-        <v>46</v>
-      </c>
-      <c r="G321" t="s">
-        <v>1247</v>
-      </c>
-      <c r="H321" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C322" t="s">
-        <v>346</v>
-      </c>
-      <c r="D322" t="s">
-        <v>1249</v>
-      </c>
-      <c r="E322" t="s">
-        <v>131</v>
-      </c>
-      <c r="F322" t="s">
-        <v>132</v>
-      </c>
-      <c r="G322" t="s">
-        <v>218</v>
-      </c>
-      <c r="H322" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C323" t="s">
-        <v>69</v>
-      </c>
-      <c r="D323" t="s">
-        <v>1251</v>
-      </c>
-      <c r="E323" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F323" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G323" t="s">
-        <v>1254</v>
-      </c>
-      <c r="H323" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C324" t="s">
-        <v>69</v>
-      </c>
-      <c r="D324" t="s">
-        <v>1251</v>
-      </c>
-      <c r="E324" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F324" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G324" t="s">
-        <v>1254</v>
-      </c>
-      <c r="H324" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C325" t="s">
-        <v>58</v>
-      </c>
-      <c r="D325" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E325" t="s">
-        <v>247</v>
-      </c>
-      <c r="F325" t="s">
-        <v>248</v>
-      </c>
-      <c r="G325" t="s">
-        <v>1258</v>
-      </c>
-      <c r="H325" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C326" t="s">
-        <v>58</v>
-      </c>
-      <c r="D326" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E326" t="s">
-        <v>247</v>
-      </c>
-      <c r="F326" t="s">
-        <v>248</v>
-      </c>
-      <c r="G326" t="s">
-        <v>1258</v>
-      </c>
-      <c r="H326" t="s">
-        <v>51</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J437" xr:uid="{D011BFE1-40D7-4CA7-AA88-0703902A8881}"/>
+  <autoFilter ref="A1:J431" xr:uid="{D011BFE1-40D7-4CA7-AA88-0703902A8881}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952B859D-0BC1-4298-BAA1-E9E6B0F4B577}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7323A5C5-F60D-4892-A61E-319C1D3C9643}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3493" uniqueCount="1780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3497" uniqueCount="1781">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -5368,6 +5368,9 @@
   </si>
   <si>
     <t>HÍD UTCA</t>
+  </si>
+  <si>
+    <t>CSÖMÖDÉR</t>
   </si>
 </sst>
 </file>
@@ -5721,7 +5724,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H499"/>
+  <dimension ref="A1:H500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -17210,6 +17213,29 @@
         <v>10</v>
       </c>
     </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>332443959</v>
+      </c>
+      <c r="C500" t="s">
+        <v>52</v>
+      </c>
+      <c r="D500">
+        <v>332443959</v>
+      </c>
+      <c r="E500">
+        <v>8957</v>
+      </c>
+      <c r="F500" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G500" t="s">
+        <v>13</v>
+      </c>
+      <c r="H500" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J414" xr:uid="{D011BFE1-40D7-4CA7-AA88-0703902A8881}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCA2047-104A-48B0-92E2-B43D5945DBCB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29C69CA-64D5-4C4D-98D7-D7CFFBFC0D01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$C$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="1230">
   <si>
     <t>CSOMAGSZAM</t>
   </si>
@@ -300,12 +300,6 @@
     <t>K-902</t>
   </si>
   <si>
-    <t>2400</t>
-  </si>
-  <si>
-    <t>DUNAÚJVÁROS</t>
-  </si>
-  <si>
     <t>KAPOSVÁR</t>
   </si>
   <si>
@@ -486,12 +480,6 @@
     <t>SZANY</t>
   </si>
   <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>MOSONMAGYARÓVÁR</t>
-  </si>
-  <si>
     <t>Gárdonyi Géza utca</t>
   </si>
   <si>
@@ -513,12 +501,6 @@
     <t>Bem utca</t>
   </si>
   <si>
-    <t>2836</t>
-  </si>
-  <si>
-    <t>BAJ</t>
-  </si>
-  <si>
     <t>Deák Ferenc utca</t>
   </si>
   <si>
@@ -711,15 +693,6 @@
     <t>Akácfa utca</t>
   </si>
   <si>
-    <t>6ad0a7bd2ed61dd3c9d3fd93</t>
-  </si>
-  <si>
-    <t>260924-F00009220-1</t>
-  </si>
-  <si>
-    <t>Lejtős út</t>
-  </si>
-  <si>
     <t>6acda1457c818f22ee6f5b30</t>
   </si>
   <si>
@@ -771,12 +744,6 @@
     <t>Ipar utca</t>
   </si>
   <si>
-    <t>6ac8d1e77c818f22ee6f0f2a</t>
-  </si>
-  <si>
-    <t>261002-F00010483</t>
-  </si>
-  <si>
     <t>Irinyi János utca</t>
   </si>
   <si>
@@ -846,24 +813,9 @@
     <t>Hunyadi utca</t>
   </si>
   <si>
-    <t>6acfc6987c818f22ee6f9679</t>
-  </si>
-  <si>
     <t>K-929</t>
   </si>
   <si>
-    <t>261007-F00002747</t>
-  </si>
-  <si>
-    <t>5200</t>
-  </si>
-  <si>
-    <t>TÖRÖKSZENTMIKLÓS</t>
-  </si>
-  <si>
-    <t>Bajza József utca</t>
-  </si>
-  <si>
     <t>6ac908c67c818f22ee6f1859</t>
   </si>
   <si>
@@ -1164,12 +1116,6 @@
     <t>Harmat utca</t>
   </si>
   <si>
-    <t>6ad0d8592ed61dd3c9d40615</t>
-  </si>
-  <si>
-    <t>261013-F00002151</t>
-  </si>
-  <si>
     <t>6ace1d597c818f22ee6f6bc7</t>
   </si>
   <si>
@@ -1239,15 +1185,6 @@
     <t>TÚRRICSE</t>
   </si>
   <si>
-    <t>6ace70887c818f22ee6f7811</t>
-  </si>
-  <si>
-    <t>261013-F00016484</t>
-  </si>
-  <si>
-    <t>Tulipán utca</t>
-  </si>
-  <si>
     <t>6acf9c8c7c818f22ee6f927c</t>
   </si>
   <si>
@@ -2136,21 +2073,12 @@
     <t>261015-W00008595</t>
   </si>
   <si>
-    <t>6ad113b72ed61dd3c9d40cab</t>
-  </si>
-  <si>
-    <t>261015-W00009730</t>
-  </si>
-  <si>
     <t>2060</t>
   </si>
   <si>
     <t>BICSKE</t>
   </si>
   <si>
-    <t>Bogya Károly utca</t>
-  </si>
-  <si>
     <t>6ad10c812ed61dd3c9d40c35</t>
   </si>
   <si>
@@ -2310,15 +2238,6 @@
     <t>iskola ut</t>
   </si>
   <si>
-    <t>1449-323291</t>
-  </si>
-  <si>
-    <t>267014686</t>
-  </si>
-  <si>
-    <t>Zrinyi M. u.</t>
-  </si>
-  <si>
     <t>1449-697695</t>
   </si>
   <si>
@@ -2494,18 +2413,6 @@
   </si>
   <si>
     <t>Telkes utca</t>
-  </si>
-  <si>
-    <t>332673359/1</t>
-  </si>
-  <si>
-    <t>332673359</t>
-  </si>
-  <si>
-    <t>2887</t>
-  </si>
-  <si>
-    <t>ÁCSTESZÉR</t>
   </si>
   <si>
     <t>332673490/1</t>
@@ -4164,7 +4071,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FE293-6B58-4929-8DC5-419BC0EC57BF}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -4201,45 +4108,45 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H3" t="s">
         <v>9</v>
@@ -4247,22 +4154,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -4270,22 +4177,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
@@ -4293,22 +4200,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -4316,22 +4223,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="F7" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="G7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="H7" t="s">
         <v>9</v>
@@ -4339,22 +4246,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="F8" t="s">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H8" t="s">
         <v>9</v>
@@ -4362,22 +4269,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G9" t="s">
         <v>243</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E9" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" t="s">
-        <v>246</v>
       </c>
       <c r="H9" t="s">
         <v>9</v>
@@ -4385,22 +4292,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F10" t="s">
         <v>247</v>
       </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
         <v>248</v>
-      </c>
-      <c r="E10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G10" t="s">
-        <v>249</v>
       </c>
       <c r="H10" t="s">
         <v>9</v>
@@ -4408,22 +4315,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
         <v>250</v>
       </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>251</v>
-      </c>
       <c r="E11" t="s">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="G11" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
         <v>9</v>
@@ -4431,22 +4338,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E12" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" t="s">
+        <v>254</v>
+      </c>
+      <c r="G12" t="s">
         <v>255</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E12" t="s">
-        <v>257</v>
-      </c>
-      <c r="F12" t="s">
-        <v>258</v>
-      </c>
-      <c r="G12" t="s">
-        <v>259</v>
       </c>
       <c r="H12" t="s">
         <v>9</v>
@@ -4454,22 +4361,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G13" t="s">
         <v>260</v>
-      </c>
-      <c r="C13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F13" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
       </c>
       <c r="H13" t="s">
         <v>9</v>
@@ -4480,19 +4387,19 @@
         <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
         <v>263</v>
       </c>
       <c r="E14" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" t="s">
         <v>264</v>
-      </c>
-      <c r="F14" t="s">
-        <v>265</v>
-      </c>
-      <c r="G14" t="s">
-        <v>266</v>
       </c>
       <c r="H14" t="s">
         <v>9</v>
@@ -4500,22 +4407,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" t="s">
         <v>267</v>
       </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" t="s">
         <v>268</v>
-      </c>
-      <c r="E15" t="s">
-        <v>269</v>
-      </c>
-      <c r="F15" t="s">
-        <v>270</v>
-      </c>
-      <c r="G15" t="s">
-        <v>271</v>
       </c>
       <c r="H15" t="s">
         <v>9</v>
@@ -4523,22 +4430,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>273</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>123</v>
       </c>
       <c r="F16" t="s">
-        <v>276</v>
+        <v>124</v>
       </c>
       <c r="G16" t="s">
-        <v>277</v>
+        <v>125</v>
       </c>
       <c r="H16" t="s">
         <v>9</v>
@@ -4546,22 +4453,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>272</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E17" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="F17" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="G17" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H17" t="s">
         <v>9</v>
@@ -4569,22 +4476,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>272</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E18" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="G18" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="H18" t="s">
         <v>9</v>
@@ -4592,22 +4499,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
@@ -4615,22 +4522,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E20" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F20" t="s">
-        <v>291</v>
+        <v>63</v>
       </c>
       <c r="G20" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H20" t="s">
         <v>9</v>
@@ -4638,22 +4545,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>286</v>
+      </c>
+      <c r="E21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" t="s">
         <v>288</v>
-      </c>
-      <c r="D21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E21" t="s">
-        <v>290</v>
-      </c>
-      <c r="F21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G21" t="s">
-        <v>292</v>
       </c>
       <c r="H21" t="s">
         <v>9</v>
@@ -4661,22 +4565,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>291</v>
       </c>
       <c r="F22" t="s">
-        <v>102</v>
+        <v>292</v>
       </c>
       <c r="G22" t="s">
-        <v>296</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
         <v>9</v>
@@ -4684,22 +4588,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E23" t="s">
-        <v>299</v>
+        <v>181</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="G23" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H23" t="s">
         <v>9</v>
@@ -4707,19 +4611,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E24" t="s">
-        <v>303</v>
+        <v>179</v>
       </c>
       <c r="F24" t="s">
-        <v>304</v>
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
+        <v>298</v>
       </c>
       <c r="H24" t="s">
         <v>9</v>
@@ -4727,22 +4634,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>300</v>
       </c>
       <c r="D25" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E25" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F25" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
@@ -4750,22 +4657,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E26" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
@@ -4773,22 +4680,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="H27" t="s">
         <v>9</v>
@@ -4796,22 +4703,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C28" t="s">
-        <v>316</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E28" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F28" t="s">
-        <v>319</v>
+        <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H28" t="s">
         <v>9</v>
@@ -4819,22 +4726,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E29" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="F29" t="s">
-        <v>136</v>
+        <v>316</v>
       </c>
       <c r="G29" t="s">
-        <v>323</v>
+        <v>157</v>
       </c>
       <c r="H29" t="s">
         <v>9</v>
@@ -4842,22 +4749,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="F30" t="s">
-        <v>136</v>
+        <v>316</v>
       </c>
       <c r="G30" t="s">
-        <v>323</v>
+        <v>157</v>
       </c>
       <c r="H30" t="s">
         <v>9</v>
@@ -4865,22 +4772,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E31" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>321</v>
       </c>
       <c r="G31" t="s">
-        <v>328</v>
+        <v>66</v>
       </c>
       <c r="H31" t="s">
         <v>9</v>
@@ -4888,22 +4795,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="E32" t="s">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
-        <v>332</v>
+        <v>138</v>
       </c>
       <c r="G32" t="s">
-        <v>163</v>
+        <v>324</v>
       </c>
       <c r="H32" t="s">
         <v>9</v>
@@ -4911,22 +4818,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E33" t="s">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H33" t="s">
         <v>9</v>
@@ -4934,22 +4841,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="E34" t="s">
-        <v>336</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>337</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>329</v>
       </c>
       <c r="H34" t="s">
         <v>9</v>
@@ -4957,22 +4864,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>331</v>
       </c>
       <c r="D35" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E35" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="F35" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="G35" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="H35" t="s">
         <v>9</v>
@@ -4980,22 +4887,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="G36" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H36" t="s">
         <v>9</v>
@@ -5003,22 +4910,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>336</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>337</v>
       </c>
       <c r="G37" t="s">
-        <v>345</v>
+        <v>161</v>
       </c>
       <c r="H37" t="s">
         <v>9</v>
@@ -5026,22 +4933,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C38" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D38" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
-        <v>208</v>
+        <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="H38" t="s">
         <v>9</v>
@@ -5049,22 +4956,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D39" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E39" t="s">
-        <v>352</v>
+        <v>68</v>
       </c>
       <c r="F39" t="s">
-        <v>353</v>
+        <v>69</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="H39" t="s">
         <v>9</v>
@@ -5072,22 +4979,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E40" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F40" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G40" t="s">
-        <v>167</v>
+        <v>349</v>
       </c>
       <c r="H40" t="s">
         <v>9</v>
@@ -5095,22 +5002,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C41" t="s">
-        <v>356</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>352</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G41" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="H41" t="s">
         <v>9</v>
@@ -5118,22 +5025,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C42" t="s">
         <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>356</v>
       </c>
       <c r="F42" t="s">
-        <v>69</v>
+        <v>357</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>195</v>
       </c>
       <c r="H42" t="s">
         <v>9</v>
@@ -5141,22 +5048,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>358</v>
+      </c>
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" t="s">
+        <v>359</v>
+      </c>
+      <c r="E43" t="s">
+        <v>360</v>
+      </c>
+      <c r="F43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" t="s">
         <v>361</v>
-      </c>
-      <c r="C43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D43" t="s">
-        <v>362</v>
-      </c>
-      <c r="E43" t="s">
-        <v>363</v>
-      </c>
-      <c r="F43" t="s">
-        <v>364</v>
-      </c>
-      <c r="G43" t="s">
-        <v>365</v>
       </c>
       <c r="H43" t="s">
         <v>9</v>
@@ -5164,22 +5071,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E44" t="s">
-        <v>368</v>
+        <v>52</v>
       </c>
       <c r="F44" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="G44" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H44" t="s">
         <v>9</v>
@@ -5187,22 +5094,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>365</v>
+      </c>
+      <c r="C45" t="s">
+        <v>366</v>
+      </c>
+      <c r="D45" t="s">
+        <v>367</v>
+      </c>
+      <c r="E45" t="s">
+        <v>368</v>
+      </c>
+      <c r="F45" t="s">
+        <v>369</v>
+      </c>
+      <c r="G45" t="s">
         <v>370</v>
-      </c>
-      <c r="C45" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" t="s">
-        <v>371</v>
-      </c>
-      <c r="E45" t="s">
-        <v>372</v>
-      </c>
-      <c r="F45" t="s">
-        <v>373</v>
-      </c>
-      <c r="G45" t="s">
-        <v>201</v>
       </c>
       <c r="H45" t="s">
         <v>9</v>
@@ -5210,22 +5117,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E46" t="s">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="F46" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H46" t="s">
         <v>9</v>
@@ -5233,22 +5140,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E47" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="H47" t="s">
         <v>9</v>
@@ -5256,22 +5163,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>375</v>
+      </c>
+      <c r="C48" t="s">
+        <v>376</v>
+      </c>
+      <c r="D48" t="s">
+        <v>377</v>
+      </c>
+      <c r="E48" t="s">
+        <v>378</v>
+      </c>
+      <c r="F48" t="s">
+        <v>379</v>
+      </c>
+      <c r="G48" t="s">
         <v>380</v>
-      </c>
-      <c r="C48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>381</v>
-      </c>
-      <c r="E48" t="s">
-        <v>52</v>
-      </c>
-      <c r="F48" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" t="s">
-        <v>382</v>
       </c>
       <c r="H48" t="s">
         <v>9</v>
@@ -5279,22 +5186,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>381</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" t="s">
+        <v>382</v>
+      </c>
+      <c r="E49" t="s">
         <v>383</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
         <v>384</v>
       </c>
-      <c r="D49" t="s">
-        <v>385</v>
-      </c>
-      <c r="E49" t="s">
-        <v>386</v>
-      </c>
-      <c r="F49" t="s">
-        <v>387</v>
-      </c>
       <c r="G49" t="s">
-        <v>388</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s">
         <v>9</v>
@@ -5302,22 +5209,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="D50" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E50" t="s">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="F50" t="s">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="G50" t="s">
-        <v>391</v>
+        <v>22</v>
       </c>
       <c r="H50" t="s">
         <v>9</v>
@@ -5325,22 +5232,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D51" t="s">
         <v>390</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="F51" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H51" t="s">
         <v>9</v>
@@ -5351,19 +5258,19 @@
         <v>393</v>
       </c>
       <c r="C52" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" t="s">
         <v>394</v>
       </c>
-      <c r="D52" t="s">
-        <v>395</v>
-      </c>
       <c r="E52" t="s">
-        <v>396</v>
+        <v>148</v>
       </c>
       <c r="F52" t="s">
-        <v>397</v>
+        <v>149</v>
       </c>
       <c r="G52" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="H52" t="s">
         <v>9</v>
@@ -5371,22 +5278,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E53" t="s">
-        <v>401</v>
+        <v>126</v>
       </c>
       <c r="F53" t="s">
-        <v>402</v>
+        <v>127</v>
       </c>
       <c r="G53" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="H53" t="s">
         <v>9</v>
@@ -5394,22 +5301,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C54" t="s">
-        <v>273</v>
+        <v>398</v>
       </c>
       <c r="D54" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E54" t="s">
-        <v>275</v>
+        <v>400</v>
       </c>
       <c r="F54" t="s">
-        <v>276</v>
+        <v>401</v>
       </c>
       <c r="G54" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H54" t="s">
         <v>9</v>
@@ -5417,22 +5324,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>403</v>
+      </c>
+      <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" t="s">
+        <v>404</v>
+      </c>
+      <c r="E55" t="s">
+        <v>405</v>
+      </c>
+      <c r="F55" t="s">
         <v>406</v>
       </c>
-      <c r="C55" t="s">
-        <v>149</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="G55" t="s">
         <v>407</v>
-      </c>
-      <c r="E55" t="s">
-        <v>408</v>
-      </c>
-      <c r="F55" t="s">
-        <v>409</v>
-      </c>
-      <c r="G55" t="s">
-        <v>22</v>
       </c>
       <c r="H55" t="s">
         <v>9</v>
@@ -5440,22 +5347,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>408</v>
+      </c>
+      <c r="C56" t="s">
+        <v>409</v>
+      </c>
+      <c r="D56" t="s">
         <v>410</v>
       </c>
-      <c r="C56" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>411</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" t="s">
         <v>412</v>
-      </c>
-      <c r="F56" t="s">
-        <v>63</v>
-      </c>
-      <c r="G56" t="s">
-        <v>413</v>
       </c>
       <c r="H56" t="s">
         <v>9</v>
@@ -5463,22 +5370,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>413</v>
+      </c>
+      <c r="C57" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" t="s">
         <v>414</v>
       </c>
-      <c r="C57" t="s">
-        <v>149</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>415</v>
       </c>
-      <c r="E57" t="s">
-        <v>150</v>
-      </c>
       <c r="F57" t="s">
-        <v>151</v>
+        <v>416</v>
       </c>
       <c r="G57" t="s">
-        <v>365</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s">
         <v>9</v>
@@ -5486,22 +5393,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>417</v>
+      </c>
+      <c r="C58" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" t="s">
+        <v>414</v>
+      </c>
+      <c r="E58" t="s">
+        <v>415</v>
+      </c>
+      <c r="F58" t="s">
         <v>416</v>
       </c>
-      <c r="C58" t="s">
-        <v>30</v>
-      </c>
-      <c r="D58" t="s">
-        <v>417</v>
-      </c>
-      <c r="E58" t="s">
-        <v>128</v>
-      </c>
-      <c r="F58" t="s">
-        <v>129</v>
-      </c>
       <c r="G58" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s">
         <v>9</v>
@@ -5535,7 +5442,7 @@
         <v>424</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
         <v>425</v>
@@ -5544,10 +5451,10 @@
         <v>426</v>
       </c>
       <c r="F60" t="s">
+        <v>106</v>
+      </c>
+      <c r="G60" t="s">
         <v>427</v>
-      </c>
-      <c r="G60" t="s">
-        <v>428</v>
       </c>
       <c r="H60" t="s">
         <v>9</v>
@@ -5555,22 +5462,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C61" t="s">
-        <v>430</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E61" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="G61" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="H61" t="s">
         <v>9</v>
@@ -5578,22 +5485,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E62" t="s">
-        <v>436</v>
+        <v>47</v>
       </c>
       <c r="F62" t="s">
-        <v>437</v>
+        <v>48</v>
       </c>
       <c r="G62" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="H62" t="s">
         <v>9</v>
@@ -5601,22 +5508,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E63" t="s">
-        <v>436</v>
+        <v>47</v>
       </c>
       <c r="F63" t="s">
-        <v>437</v>
+        <v>48</v>
       </c>
       <c r="G63" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="H63" t="s">
         <v>9</v>
@@ -5624,22 +5531,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C64" t="s">
-        <v>440</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E64" t="s">
-        <v>442</v>
+        <v>197</v>
       </c>
       <c r="F64" t="s">
-        <v>443</v>
+        <v>198</v>
       </c>
       <c r="G64" t="s">
-        <v>444</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s">
         <v>9</v>
@@ -5647,22 +5554,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C65" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="E65" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="F65" t="s">
-        <v>108</v>
+        <v>437</v>
       </c>
       <c r="G65" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -5670,22 +5577,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E66" t="s">
-        <v>447</v>
+        <v>71</v>
       </c>
       <c r="F66" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="G66" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="H66" t="s">
         <v>9</v>
@@ -5693,22 +5600,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D67" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E67" t="s">
-        <v>47</v>
+        <v>391</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G67" t="s">
-        <v>49</v>
+        <v>444</v>
       </c>
       <c r="H67" t="s">
         <v>9</v>
@@ -5716,22 +5623,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>340</v>
       </c>
       <c r="D68" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E68" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="F68" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="G68" t="s">
-        <v>49</v>
+        <v>447</v>
       </c>
       <c r="H68" t="s">
         <v>9</v>
@@ -5739,22 +5646,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="F69" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="G69" t="s">
-        <v>96</v>
+        <v>450</v>
       </c>
       <c r="H69" t="s">
         <v>9</v>
@@ -5762,22 +5669,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="E70" t="s">
-        <v>457</v>
+        <v>47</v>
       </c>
       <c r="F70" t="s">
-        <v>458</v>
+        <v>48</v>
       </c>
       <c r="G70" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="H70" t="s">
         <v>9</v>
@@ -5785,22 +5692,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>453</v>
       </c>
       <c r="D71" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="E71" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F71" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="G71" t="s">
-        <v>462</v>
+        <v>238</v>
       </c>
       <c r="H71" t="s">
         <v>9</v>
@@ -5808,22 +5715,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C72" t="s">
-        <v>70</v>
+        <v>376</v>
       </c>
       <c r="D72" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="E72" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="F72" t="s">
-        <v>63</v>
+        <v>458</v>
       </c>
       <c r="G72" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="H72" t="s">
         <v>9</v>
@@ -5831,22 +5738,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C73" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="D73" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="E73" t="s">
-        <v>176</v>
+        <v>457</v>
       </c>
       <c r="F73" t="s">
-        <v>177</v>
+        <v>458</v>
       </c>
       <c r="G73" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="H73" t="s">
         <v>9</v>
@@ -5854,22 +5761,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C74" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E74" t="s">
-        <v>47</v>
+        <v>360</v>
       </c>
       <c r="F74" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G74" t="s">
-        <v>471</v>
+        <v>361</v>
       </c>
       <c r="H74" t="s">
         <v>9</v>
@@ -5877,22 +5784,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E75" t="s">
-        <v>47</v>
+        <v>360</v>
       </c>
       <c r="F75" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G75" t="s">
-        <v>471</v>
+        <v>361</v>
       </c>
       <c r="H75" t="s">
         <v>9</v>
@@ -5900,22 +5807,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C76" t="s">
-        <v>474</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="E76" t="s">
-        <v>130</v>
+        <v>466</v>
       </c>
       <c r="F76" t="s">
-        <v>131</v>
+        <v>467</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>468</v>
       </c>
       <c r="H76" t="s">
         <v>9</v>
@@ -5923,22 +5830,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C77" t="s">
-        <v>394</v>
+        <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="E77" t="s">
-        <v>478</v>
+        <v>208</v>
       </c>
       <c r="F77" t="s">
-        <v>479</v>
+        <v>106</v>
       </c>
       <c r="G77" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="H77" t="s">
         <v>9</v>
@@ -5946,22 +5853,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C78" t="s">
-        <v>394</v>
+        <v>222</v>
       </c>
       <c r="D78" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E78" t="s">
-        <v>478</v>
+        <v>99</v>
       </c>
       <c r="F78" t="s">
-        <v>479</v>
+        <v>100</v>
       </c>
       <c r="G78" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="H78" t="s">
         <v>9</v>
@@ -5969,22 +5876,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D79" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E79" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="F79" t="s">
-        <v>7</v>
+        <v>478</v>
       </c>
       <c r="G79" t="s">
-        <v>377</v>
+        <v>479</v>
       </c>
       <c r="H79" t="s">
         <v>9</v>
@@ -5992,22 +5899,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>480</v>
+      </c>
+      <c r="C80" t="s">
+        <v>80</v>
+      </c>
+      <c r="D80" t="s">
+        <v>481</v>
+      </c>
+      <c r="E80" t="s">
+        <v>482</v>
+      </c>
+      <c r="F80" t="s">
+        <v>483</v>
+      </c>
+      <c r="G80" t="s">
         <v>484</v>
-      </c>
-      <c r="C80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D80" t="s">
-        <v>483</v>
-      </c>
-      <c r="E80" t="s">
-        <v>376</v>
-      </c>
-      <c r="F80" t="s">
-        <v>7</v>
-      </c>
-      <c r="G80" t="s">
-        <v>377</v>
       </c>
       <c r="H80" t="s">
         <v>9</v>
@@ -6018,19 +5925,19 @@
         <v>485</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E81" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F81" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G81" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="H81" t="s">
         <v>9</v>
@@ -6038,22 +5945,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="E82" t="s">
-        <v>214</v>
+        <v>482</v>
       </c>
       <c r="F82" t="s">
-        <v>108</v>
+        <v>483</v>
       </c>
       <c r="G82" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="H82" t="s">
         <v>9</v>
@@ -6061,22 +5968,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C83" t="s">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="D83" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E83" t="s">
-        <v>101</v>
+        <v>489</v>
       </c>
       <c r="F83" t="s">
-        <v>102</v>
+        <v>490</v>
       </c>
       <c r="G83" t="s">
-        <v>495</v>
+        <v>76</v>
       </c>
       <c r="H83" t="s">
         <v>9</v>
@@ -6084,22 +5991,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C84" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="D84" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E84" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F84" t="s">
-        <v>499</v>
+        <v>7</v>
       </c>
       <c r="G84" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="H84" t="s">
         <v>9</v>
@@ -6107,22 +6014,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C85" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D85" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E85" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F85" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="G85" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="H85" t="s">
         <v>9</v>
@@ -6130,22 +6037,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C86" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="D86" t="s">
+        <v>501</v>
+      </c>
+      <c r="E86" t="s">
+        <v>196</v>
+      </c>
+      <c r="F86" t="s">
+        <v>159</v>
+      </c>
+      <c r="G86" t="s">
         <v>502</v>
-      </c>
-      <c r="E86" t="s">
-        <v>503</v>
-      </c>
-      <c r="F86" t="s">
-        <v>504</v>
-      </c>
-      <c r="G86" t="s">
-        <v>505</v>
       </c>
       <c r="H86" t="s">
         <v>9</v>
@@ -6153,22 +6060,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C87" t="s">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="D87" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E87" t="s">
-        <v>503</v>
+        <v>50</v>
       </c>
       <c r="F87" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G87" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H87" t="s">
         <v>9</v>
@@ -6176,22 +6083,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C88" t="s">
-        <v>75</v>
+        <v>331</v>
       </c>
       <c r="D88" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E88" t="s">
-        <v>510</v>
+        <v>50</v>
       </c>
       <c r="F88" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>506</v>
       </c>
       <c r="H88" t="s">
         <v>9</v>
@@ -6199,22 +6106,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C89" t="s">
-        <v>54</v>
+        <v>331</v>
       </c>
       <c r="D89" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="E89" t="s">
-        <v>514</v>
+        <v>50</v>
       </c>
       <c r="F89" t="s">
-        <v>7</v>
+        <v>505</v>
       </c>
       <c r="G89" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="H89" t="s">
         <v>9</v>
@@ -6222,22 +6129,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>272</v>
       </c>
       <c r="D90" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="E90" t="s">
-        <v>518</v>
+        <v>45</v>
       </c>
       <c r="F90" t="s">
-        <v>519</v>
+        <v>46</v>
       </c>
       <c r="G90" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="H90" t="s">
         <v>9</v>
@@ -6245,22 +6152,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C91" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="E91" t="s">
-        <v>202</v>
+        <v>514</v>
       </c>
       <c r="F91" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="H91" t="s">
         <v>9</v>
@@ -6268,22 +6175,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C92" t="s">
-        <v>347</v>
+        <v>222</v>
       </c>
       <c r="D92" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="E92" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="F92" t="s">
-        <v>526</v>
+        <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>527</v>
+        <v>10</v>
       </c>
       <c r="H92" t="s">
         <v>9</v>
@@ -6291,22 +6198,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C93" t="s">
-        <v>347</v>
+        <v>222</v>
       </c>
       <c r="D93" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="E93" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="F93" t="s">
-        <v>526</v>
+        <v>100</v>
       </c>
       <c r="G93" t="s">
-        <v>527</v>
+        <v>10</v>
       </c>
       <c r="H93" t="s">
         <v>9</v>
@@ -6314,22 +6221,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C94" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="D94" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E94" t="s">
-        <v>50</v>
+        <v>521</v>
       </c>
       <c r="F94" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G94" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H94" t="s">
         <v>9</v>
@@ -6337,22 +6244,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C95" t="s">
-        <v>288</v>
+        <v>105</v>
       </c>
       <c r="D95" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E95" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="F95" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="G95" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="H95" t="s">
         <v>9</v>
@@ -6360,22 +6267,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D96" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E96" t="s">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="F96" t="s">
-        <v>7</v>
+        <v>498</v>
       </c>
       <c r="G96" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="H96" t="s">
         <v>9</v>
@@ -6383,22 +6290,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C97" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="D97" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="E97" t="s">
-        <v>101</v>
+        <v>497</v>
       </c>
       <c r="F97" t="s">
-        <v>102</v>
+        <v>498</v>
       </c>
       <c r="G97" t="s">
-        <v>10</v>
+        <v>529</v>
       </c>
       <c r="H97" t="s">
         <v>9</v>
@@ -6406,22 +6313,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C98" t="s">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="D98" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E98" t="s">
-        <v>101</v>
+        <v>533</v>
       </c>
       <c r="F98" t="s">
-        <v>102</v>
+        <v>534</v>
       </c>
       <c r="G98" t="s">
-        <v>10</v>
+        <v>535</v>
       </c>
       <c r="H98" t="s">
         <v>9</v>
@@ -6429,22 +6336,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C99" t="s">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="D99" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E99" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="F99" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="G99" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="H99" t="s">
         <v>9</v>
@@ -6452,22 +6359,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D100" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="E100" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
       <c r="F100" t="s">
-        <v>110</v>
+        <v>534</v>
       </c>
       <c r="G100" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -6475,22 +6382,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D101" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="E101" t="s">
-        <v>518</v>
+        <v>205</v>
       </c>
       <c r="F101" t="s">
-        <v>519</v>
+        <v>206</v>
       </c>
       <c r="G101" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="H101" t="s">
         <v>9</v>
@@ -6498,22 +6405,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D102" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E102" t="s">
-        <v>518</v>
+        <v>133</v>
       </c>
       <c r="F102" t="s">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="G102" t="s">
-        <v>550</v>
+        <v>150</v>
       </c>
       <c r="H102" t="s">
         <v>9</v>
@@ -6521,22 +6428,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C103" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="D103" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E103" t="s">
-        <v>554</v>
+        <v>130</v>
       </c>
       <c r="F103" t="s">
-        <v>555</v>
+        <v>131</v>
       </c>
       <c r="G103" t="s">
-        <v>556</v>
+        <v>114</v>
       </c>
       <c r="H103" t="s">
         <v>9</v>
@@ -6544,22 +6451,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C104" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D104" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E104" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="F104" t="s">
-        <v>555</v>
+        <v>106</v>
       </c>
       <c r="G104" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="H104" t="s">
         <v>9</v>
@@ -6567,22 +6474,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="C105" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="D105" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E105" t="s">
-        <v>554</v>
+        <v>140</v>
       </c>
       <c r="F105" t="s">
-        <v>555</v>
+        <v>141</v>
       </c>
       <c r="G105" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="H105" t="s">
         <v>9</v>
@@ -6590,22 +6497,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C106" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D106" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E106" t="s">
-        <v>211</v>
+        <v>554</v>
       </c>
       <c r="F106" t="s">
-        <v>212</v>
+        <v>555</v>
       </c>
       <c r="G106" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="H106" t="s">
         <v>9</v>
@@ -6613,22 +6520,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C107" t="s">
         <v>73</v>
       </c>
       <c r="D107" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="E107" t="s">
-        <v>135</v>
+        <v>559</v>
       </c>
       <c r="F107" t="s">
-        <v>136</v>
+        <v>560</v>
       </c>
       <c r="G107" t="s">
-        <v>154</v>
+        <v>561</v>
       </c>
       <c r="H107" t="s">
         <v>9</v>
@@ -6636,22 +6543,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>562</v>
+      </c>
+      <c r="C108" t="s">
+        <v>261</v>
+      </c>
+      <c r="D108" t="s">
+        <v>563</v>
+      </c>
+      <c r="E108" t="s">
         <v>564</v>
       </c>
-      <c r="C108" t="s">
-        <v>113</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
         <v>565</v>
       </c>
-      <c r="E108" t="s">
-        <v>132</v>
-      </c>
-      <c r="F108" t="s">
-        <v>133</v>
-      </c>
       <c r="G108" t="s">
-        <v>116</v>
+        <v>566</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -6659,22 +6566,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>567</v>
+      </c>
+      <c r="C109" t="s">
+        <v>261</v>
+      </c>
+      <c r="D109" t="s">
+        <v>563</v>
+      </c>
+      <c r="E109" t="s">
+        <v>564</v>
+      </c>
+      <c r="F109" t="s">
+        <v>565</v>
+      </c>
+      <c r="G109" t="s">
         <v>566</v>
-      </c>
-      <c r="C109" t="s">
-        <v>87</v>
-      </c>
-      <c r="D109" t="s">
-        <v>567</v>
-      </c>
-      <c r="E109" t="s">
-        <v>568</v>
-      </c>
-      <c r="F109" t="s">
-        <v>108</v>
-      </c>
-      <c r="G109" t="s">
-        <v>569</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
@@ -6682,22 +6589,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C110" t="s">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="D110" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E110" t="s">
-        <v>142</v>
+        <v>564</v>
       </c>
       <c r="F110" t="s">
-        <v>143</v>
+        <v>565</v>
       </c>
       <c r="G110" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="H110" t="s">
         <v>9</v>
@@ -6705,22 +6612,22 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>569</v>
+      </c>
+      <c r="C111" t="s">
+        <v>95</v>
+      </c>
+      <c r="D111" t="s">
+        <v>570</v>
+      </c>
+      <c r="E111" t="s">
+        <v>571</v>
+      </c>
+      <c r="F111" t="s">
+        <v>572</v>
+      </c>
+      <c r="G111" t="s">
         <v>573</v>
-      </c>
-      <c r="C111" t="s">
-        <v>75</v>
-      </c>
-      <c r="D111" t="s">
-        <v>574</v>
-      </c>
-      <c r="E111" t="s">
-        <v>575</v>
-      </c>
-      <c r="F111" t="s">
-        <v>576</v>
-      </c>
-      <c r="G111" t="s">
-        <v>577</v>
       </c>
       <c r="H111" t="s">
         <v>9</v>
@@ -6728,22 +6635,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>574</v>
+      </c>
+      <c r="C112" t="s">
+        <v>98</v>
+      </c>
+      <c r="D112" t="s">
+        <v>575</v>
+      </c>
+      <c r="E112" t="s">
+        <v>576</v>
+      </c>
+      <c r="F112" t="s">
+        <v>577</v>
+      </c>
+      <c r="G112" t="s">
         <v>578</v>
-      </c>
-      <c r="C112" t="s">
-        <v>73</v>
-      </c>
-      <c r="D112" t="s">
-        <v>579</v>
-      </c>
-      <c r="E112" t="s">
-        <v>580</v>
-      </c>
-      <c r="F112" t="s">
-        <v>581</v>
-      </c>
-      <c r="G112" t="s">
-        <v>582</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -6751,22 +6658,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C113" t="s">
-        <v>273</v>
+        <v>64</v>
       </c>
       <c r="D113" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E113" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F113" t="s">
-        <v>586</v>
+        <v>7</v>
       </c>
       <c r="G113" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="H113" t="s">
         <v>9</v>
@@ -6774,10 +6681,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C114" t="s">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="D114" t="s">
         <v>584</v>
@@ -6789,7 +6696,7 @@
         <v>586</v>
       </c>
       <c r="G114" t="s">
-        <v>587</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s">
         <v>9</v>
@@ -6797,22 +6704,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>587</v>
+      </c>
+      <c r="C115" t="s">
+        <v>84</v>
+      </c>
+      <c r="D115" t="s">
+        <v>588</v>
+      </c>
+      <c r="E115" t="s">
         <v>589</v>
       </c>
-      <c r="C115" t="s">
-        <v>273</v>
-      </c>
-      <c r="D115" t="s">
-        <v>584</v>
-      </c>
-      <c r="E115" t="s">
-        <v>585</v>
-      </c>
       <c r="F115" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G115" t="s">
-        <v>587</v>
+        <v>10</v>
       </c>
       <c r="H115" t="s">
         <v>9</v>
@@ -6820,22 +6727,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C116" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D116" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E116" t="s">
-        <v>592</v>
+        <v>81</v>
       </c>
       <c r="F116" t="s">
+        <v>82</v>
+      </c>
+      <c r="G116" t="s">
         <v>593</v>
-      </c>
-      <c r="G116" t="s">
-        <v>594</v>
       </c>
       <c r="H116" t="s">
         <v>9</v>
@@ -6843,22 +6750,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C117" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D117" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E117" t="s">
-        <v>597</v>
+        <v>81</v>
       </c>
       <c r="F117" t="s">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="G117" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="H117" t="s">
         <v>9</v>
@@ -6866,22 +6773,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C118" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="D118" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="E118" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="F118" t="s">
-        <v>7</v>
+        <v>598</v>
       </c>
       <c r="G118" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="H118" t="s">
         <v>9</v>
@@ -6889,22 +6796,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D119" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E119" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F119" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G119" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -6912,22 +6819,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C120" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D120" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E120" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="F120" t="s">
-        <v>611</v>
+        <v>7</v>
       </c>
       <c r="G120" t="s">
-        <v>10</v>
+        <v>607</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -6935,22 +6842,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>608</v>
+      </c>
+      <c r="C121" t="s">
+        <v>340</v>
+      </c>
+      <c r="D121" t="s">
+        <v>609</v>
+      </c>
+      <c r="E121" t="s">
+        <v>610</v>
+      </c>
+      <c r="F121" t="s">
+        <v>611</v>
+      </c>
+      <c r="G121" t="s">
         <v>612</v>
-      </c>
-      <c r="C121" t="s">
-        <v>80</v>
-      </c>
-      <c r="D121" t="s">
-        <v>613</v>
-      </c>
-      <c r="E121" t="s">
-        <v>81</v>
-      </c>
-      <c r="F121" t="s">
-        <v>82</v>
-      </c>
-      <c r="G121" t="s">
-        <v>614</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -6958,22 +6865,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C122" t="s">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="D122" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E122" t="s">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="F122" t="s">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="G122" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -6981,22 +6888,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>614</v>
+      </c>
+      <c r="C123" t="s">
+        <v>105</v>
+      </c>
+      <c r="D123" t="s">
+        <v>615</v>
+      </c>
+      <c r="E123" t="s">
         <v>616</v>
       </c>
-      <c r="C123" t="s">
-        <v>113</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="F123" t="s">
         <v>617</v>
       </c>
-      <c r="E123" t="s">
-        <v>618</v>
-      </c>
-      <c r="F123" t="s">
-        <v>619</v>
-      </c>
       <c r="G123" t="s">
-        <v>620</v>
+        <v>94</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -7004,22 +6911,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>618</v>
+      </c>
+      <c r="C124" t="s">
+        <v>376</v>
+      </c>
+      <c r="D124" t="s">
+        <v>619</v>
+      </c>
+      <c r="E124" t="s">
+        <v>620</v>
+      </c>
+      <c r="F124" t="s">
         <v>621</v>
       </c>
-      <c r="C124" t="s">
-        <v>59</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="G124" t="s">
         <v>622</v>
-      </c>
-      <c r="E124" t="s">
-        <v>623</v>
-      </c>
-      <c r="F124" t="s">
-        <v>624</v>
-      </c>
-      <c r="G124" t="s">
-        <v>134</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -7027,22 +6934,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>623</v>
+      </c>
+      <c r="C125" t="s">
+        <v>624</v>
+      </c>
+      <c r="D125" t="s">
         <v>625</v>
       </c>
-      <c r="C125" t="s">
-        <v>32</v>
-      </c>
-      <c r="D125" t="s">
-        <v>626</v>
-      </c>
       <c r="E125" t="s">
-        <v>627</v>
+        <v>267</v>
       </c>
       <c r="F125" t="s">
         <v>7</v>
       </c>
       <c r="G125" t="s">
-        <v>628</v>
+        <v>211</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -7050,22 +6957,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>626</v>
+      </c>
+      <c r="C126" t="s">
+        <v>300</v>
+      </c>
+      <c r="D126" t="s">
+        <v>627</v>
+      </c>
+      <c r="E126" t="s">
+        <v>628</v>
+      </c>
+      <c r="F126" t="s">
         <v>629</v>
       </c>
-      <c r="C126" t="s">
-        <v>356</v>
-      </c>
-      <c r="D126" t="s">
-        <v>630</v>
-      </c>
-      <c r="E126" t="s">
-        <v>631</v>
-      </c>
-      <c r="F126" t="s">
-        <v>632</v>
-      </c>
       <c r="G126" t="s">
-        <v>633</v>
+        <v>12</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -7073,22 +6980,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>630</v>
+      </c>
+      <c r="C127" t="s">
+        <v>91</v>
+      </c>
+      <c r="D127" t="s">
+        <v>631</v>
+      </c>
+      <c r="E127" t="s">
+        <v>632</v>
+      </c>
+      <c r="F127" t="s">
+        <v>633</v>
+      </c>
+      <c r="G127" t="s">
         <v>634</v>
-      </c>
-      <c r="C127" t="s">
-        <v>356</v>
-      </c>
-      <c r="D127" t="s">
-        <v>630</v>
-      </c>
-      <c r="E127" t="s">
-        <v>631</v>
-      </c>
-      <c r="F127" t="s">
-        <v>632</v>
-      </c>
-      <c r="G127" t="s">
-        <v>633</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -7099,19 +7006,19 @@
         <v>635</v>
       </c>
       <c r="C128" t="s">
-        <v>107</v>
+        <v>636</v>
       </c>
       <c r="D128" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E128" t="s">
-        <v>637</v>
+        <v>199</v>
       </c>
       <c r="F128" t="s">
+        <v>200</v>
+      </c>
+      <c r="G128" t="s">
         <v>638</v>
-      </c>
-      <c r="G128" t="s">
-        <v>96</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -7122,7 +7029,7 @@
         <v>639</v>
       </c>
       <c r="C129" t="s">
-        <v>394</v>
+        <v>35</v>
       </c>
       <c r="D129" t="s">
         <v>640</v>
@@ -7134,7 +7041,7 @@
         <v>642</v>
       </c>
       <c r="G129" t="s">
-        <v>643</v>
+        <v>76</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -7142,22 +7049,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C130" t="s">
-        <v>645</v>
+        <v>35</v>
       </c>
       <c r="D130" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E130" t="s">
-        <v>283</v>
+        <v>641</v>
       </c>
       <c r="F130" t="s">
-        <v>7</v>
+        <v>642</v>
       </c>
       <c r="G130" t="s">
-        <v>217</v>
+        <v>76</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -7165,22 +7072,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>644</v>
+      </c>
+      <c r="C131" t="s">
+        <v>645</v>
+      </c>
+      <c r="D131" t="s">
+        <v>646</v>
+      </c>
+      <c r="E131" t="s">
+        <v>193</v>
+      </c>
+      <c r="F131" t="s">
+        <v>194</v>
+      </c>
+      <c r="G131" t="s">
         <v>647</v>
-      </c>
-      <c r="C131" t="s">
-        <v>316</v>
-      </c>
-      <c r="D131" t="s">
-        <v>648</v>
-      </c>
-      <c r="E131" t="s">
-        <v>649</v>
-      </c>
-      <c r="F131" t="s">
-        <v>650</v>
-      </c>
-      <c r="G131" t="s">
-        <v>12</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -7188,22 +7095,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C132" t="s">
-        <v>93</v>
+        <v>300</v>
       </c>
       <c r="D132" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E132" t="s">
-        <v>653</v>
+        <v>302</v>
       </c>
       <c r="F132" t="s">
-        <v>654</v>
+        <v>303</v>
       </c>
       <c r="G132" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -7211,22 +7118,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C133" t="s">
-        <v>657</v>
+        <v>261</v>
       </c>
       <c r="D133" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E133" t="s">
-        <v>205</v>
+        <v>653</v>
       </c>
       <c r="F133" t="s">
-        <v>206</v>
+        <v>654</v>
       </c>
       <c r="G133" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -7234,22 +7141,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C134" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D134" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E134" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F134" t="s">
-        <v>663</v>
+        <v>7</v>
       </c>
       <c r="G134" t="s">
-        <v>76</v>
+        <v>593</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -7257,22 +7164,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C135" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D135" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E135" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F135" t="s">
-        <v>663</v>
+        <v>7</v>
       </c>
       <c r="G135" t="s">
-        <v>76</v>
+        <v>593</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -7280,22 +7187,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C136" t="s">
-        <v>666</v>
+        <v>21</v>
       </c>
       <c r="D136" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="E136" t="s">
-        <v>199</v>
+        <v>658</v>
       </c>
       <c r="F136" t="s">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>668</v>
+        <v>593</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -7303,22 +7210,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C137" t="s">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="D137" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="E137" t="s">
-        <v>318</v>
+        <v>663</v>
       </c>
       <c r="F137" t="s">
-        <v>319</v>
+        <v>90</v>
       </c>
       <c r="G137" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -7326,22 +7233,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="C138" t="s">
-        <v>273</v>
+        <v>95</v>
       </c>
       <c r="D138" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="E138" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="F138" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="G138" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -7349,22 +7256,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C139" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D139" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="E139" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="F139" t="s">
-        <v>7</v>
+        <v>668</v>
       </c>
       <c r="G139" t="s">
-        <v>614</v>
+        <v>669</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -7372,22 +7279,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="C140" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="D140" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E140" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="F140" t="s">
         <v>7</v>
       </c>
       <c r="G140" t="s">
-        <v>614</v>
+        <v>674</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -7395,22 +7302,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="D141" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E141" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="F141" t="s">
         <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>614</v>
+        <v>674</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -7418,22 +7325,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C142" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D142" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="E142" t="s">
-        <v>684</v>
+        <v>493</v>
       </c>
       <c r="F142" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="G142" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -7441,22 +7348,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="C143" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D143" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="E143" t="s">
-        <v>688</v>
+        <v>405</v>
       </c>
       <c r="F143" t="s">
-        <v>689</v>
+        <v>406</v>
       </c>
       <c r="G143" t="s">
-        <v>690</v>
+        <v>76</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -7464,22 +7371,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="C144" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D144" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E144" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F144" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G144" t="s">
-        <v>690</v>
+        <v>72</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -7487,22 +7394,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C145" t="s">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="D145" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="E145" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="F145" t="s">
-        <v>7</v>
+        <v>686</v>
       </c>
       <c r="G145" t="s">
-        <v>695</v>
+        <v>72</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -7510,22 +7417,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C146" t="s">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E146" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F146" t="s">
         <v>7</v>
       </c>
       <c r="G146" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -7533,22 +7440,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C147" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D147" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="E147" t="s">
-        <v>514</v>
+        <v>694</v>
       </c>
       <c r="F147" t="s">
-        <v>7</v>
+        <v>695</v>
       </c>
       <c r="G147" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -7556,22 +7463,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>697</v>
+      </c>
+      <c r="C148" t="s">
+        <v>35</v>
+      </c>
+      <c r="D148" t="s">
+        <v>698</v>
+      </c>
+      <c r="E148" t="s">
+        <v>699</v>
+      </c>
+      <c r="F148" t="s">
+        <v>7</v>
+      </c>
+      <c r="G148" t="s">
         <v>700</v>
-      </c>
-      <c r="C148" t="s">
-        <v>106</v>
-      </c>
-      <c r="D148" t="s">
-        <v>701</v>
-      </c>
-      <c r="E148" t="s">
-        <v>426</v>
-      </c>
-      <c r="F148" t="s">
-        <v>427</v>
-      </c>
-      <c r="G148" t="s">
-        <v>76</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -7579,22 +7486,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>701</v>
+      </c>
+      <c r="C149" t="s">
+        <v>83</v>
+      </c>
+      <c r="D149" t="s">
         <v>702</v>
       </c>
-      <c r="C149" t="s">
-        <v>84</v>
-      </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
+        <v>153</v>
+      </c>
+      <c r="F149" t="s">
+        <v>154</v>
+      </c>
+      <c r="G149" t="s">
         <v>703</v>
-      </c>
-      <c r="E149" t="s">
-        <v>704</v>
-      </c>
-      <c r="F149" t="s">
-        <v>705</v>
-      </c>
-      <c r="G149" t="s">
-        <v>706</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -7602,22 +7509,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>704</v>
+      </c>
+      <c r="C150" t="s">
+        <v>261</v>
+      </c>
+      <c r="D150" t="s">
+        <v>705</v>
+      </c>
+      <c r="E150" t="s">
+        <v>706</v>
+      </c>
+      <c r="F150" t="s">
         <v>707</v>
       </c>
-      <c r="C150" t="s">
-        <v>104</v>
-      </c>
-      <c r="D150" t="s">
-        <v>708</v>
-      </c>
-      <c r="E150" t="s">
-        <v>709</v>
-      </c>
-      <c r="F150" t="s">
-        <v>710</v>
-      </c>
       <c r="G150" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -7625,22 +7532,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C151" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D151" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E151" t="s">
-        <v>709</v>
+        <v>168</v>
       </c>
       <c r="F151" t="s">
+        <v>169</v>
+      </c>
+      <c r="G151" t="s">
         <v>710</v>
-      </c>
-      <c r="G151" t="s">
-        <v>72</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -7648,22 +7555,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>711</v>
+      </c>
+      <c r="C152" t="s">
+        <v>104</v>
+      </c>
+      <c r="D152" t="s">
         <v>712</v>
       </c>
-      <c r="C152" t="s">
-        <v>18</v>
-      </c>
-      <c r="D152" t="s">
+      <c r="E152" t="s">
+        <v>52</v>
+      </c>
+      <c r="F152" t="s">
+        <v>53</v>
+      </c>
+      <c r="G152" t="s">
         <v>713</v>
-      </c>
-      <c r="E152" t="s">
-        <v>714</v>
-      </c>
-      <c r="F152" t="s">
-        <v>7</v>
-      </c>
-      <c r="G152" t="s">
-        <v>715</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -7671,22 +7578,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C153" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="D153" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E153" t="s">
-        <v>718</v>
+        <v>163</v>
       </c>
       <c r="F153" t="s">
-        <v>719</v>
+        <v>164</v>
       </c>
       <c r="G153" t="s">
-        <v>720</v>
+        <v>74</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -7694,22 +7601,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C154" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D154" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="E154" t="s">
-        <v>723</v>
+        <v>192</v>
       </c>
       <c r="F154" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G154" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -7717,22 +7624,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C155" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D155" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E155" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="F155" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="G155" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -7740,22 +7647,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="C156" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E156" t="s">
-        <v>730</v>
+        <v>143</v>
       </c>
       <c r="F156" t="s">
-        <v>731</v>
+        <v>144</v>
       </c>
       <c r="G156" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -7763,117 +7670,117 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="C157" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D157" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="E157" t="s">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="F157" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="G157" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="H157" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="C158" t="s">
-        <v>106</v>
+        <v>726</v>
       </c>
       <c r="D158" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="E158" t="s">
-        <v>52</v>
+        <v>728</v>
       </c>
       <c r="F158" t="s">
-        <v>53</v>
+        <v>729</v>
       </c>
       <c r="G158" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="H158" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="C159" t="s">
-        <v>156</v>
+        <v>300</v>
       </c>
       <c r="D159" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="E159" t="s">
-        <v>169</v>
+        <v>733</v>
       </c>
       <c r="F159" t="s">
-        <v>170</v>
+        <v>734</v>
       </c>
       <c r="G159" t="s">
-        <v>74</v>
+        <v>735</v>
       </c>
       <c r="H159" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>736</v>
+      </c>
+      <c r="C160" t="s">
+        <v>59</v>
+      </c>
+      <c r="D160" t="s">
+        <v>737</v>
+      </c>
+      <c r="E160" t="s">
+        <v>738</v>
+      </c>
+      <c r="F160" t="s">
+        <v>739</v>
+      </c>
+      <c r="G160" t="s">
         <v>740</v>
       </c>
-      <c r="C160" t="s">
-        <v>61</v>
-      </c>
-      <c r="D160" t="s">
-        <v>741</v>
-      </c>
-      <c r="E160" t="s">
-        <v>198</v>
-      </c>
-      <c r="F160" t="s">
-        <v>63</v>
-      </c>
-      <c r="G160" t="s">
-        <v>742</v>
-      </c>
       <c r="H160" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C161" t="s">
         <v>61</v>
       </c>
       <c r="D161" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E161" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="F161" t="s">
         <v>63</v>
       </c>
       <c r="G161" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H161" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
@@ -7881,42 +7788,42 @@
         <v>744</v>
       </c>
       <c r="C162" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="D162" t="s">
         <v>745</v>
       </c>
       <c r="E162" t="s">
-        <v>145</v>
+        <v>746</v>
       </c>
       <c r="F162" t="s">
-        <v>146</v>
+        <v>747</v>
       </c>
       <c r="G162" t="s">
-        <v>159</v>
+        <v>748</v>
       </c>
       <c r="H162" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C163" t="s">
-        <v>30</v>
+        <v>726</v>
       </c>
       <c r="D163" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E163" t="s">
-        <v>55</v>
+        <v>728</v>
       </c>
       <c r="F163" t="s">
-        <v>56</v>
+        <v>729</v>
       </c>
       <c r="G163" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="H163" t="s">
         <v>15</v>
@@ -7924,22 +7831,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C164" t="s">
+        <v>726</v>
+      </c>
+      <c r="D164" t="s">
         <v>750</v>
       </c>
-      <c r="D164" t="s">
-        <v>751</v>
-      </c>
       <c r="E164" t="s">
-        <v>752</v>
+        <v>728</v>
       </c>
       <c r="F164" t="s">
-        <v>753</v>
+        <v>729</v>
       </c>
       <c r="G164" t="s">
-        <v>754</v>
+        <v>730</v>
       </c>
       <c r="H164" t="s">
         <v>15</v>
@@ -7947,22 +7854,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>752</v>
+      </c>
+      <c r="C165" t="s">
+        <v>27</v>
+      </c>
+      <c r="D165" t="s">
+        <v>753</v>
+      </c>
+      <c r="E165" t="s">
+        <v>754</v>
+      </c>
+      <c r="F165" t="s">
         <v>755</v>
       </c>
-      <c r="C165" t="s">
-        <v>316</v>
-      </c>
-      <c r="D165" t="s">
+      <c r="G165" t="s">
         <v>756</v>
-      </c>
-      <c r="E165" t="s">
-        <v>757</v>
-      </c>
-      <c r="F165" t="s">
-        <v>758</v>
-      </c>
-      <c r="G165" t="s">
-        <v>759</v>
       </c>
       <c r="H165" t="s">
         <v>15</v>
@@ -7970,22 +7877,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>757</v>
+      </c>
+      <c r="C166" t="s">
+        <v>95</v>
+      </c>
+      <c r="D166" t="s">
+        <v>758</v>
+      </c>
+      <c r="E166" t="s">
+        <v>759</v>
+      </c>
+      <c r="F166" t="s">
         <v>760</v>
       </c>
-      <c r="C166" t="s">
-        <v>59</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="G166" t="s">
         <v>761</v>
-      </c>
-      <c r="E166" t="s">
-        <v>152</v>
-      </c>
-      <c r="F166" t="s">
-        <v>153</v>
-      </c>
-      <c r="G166" t="s">
-        <v>762</v>
       </c>
       <c r="H166" t="s">
         <v>15</v>
@@ -7993,22 +7900,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>762</v>
+      </c>
+      <c r="C167" t="s">
+        <v>75</v>
+      </c>
+      <c r="D167" t="s">
         <v>763</v>
       </c>
-      <c r="C167" t="s">
-        <v>59</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>764</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>765</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>766</v>
-      </c>
-      <c r="G167" t="s">
-        <v>767</v>
       </c>
       <c r="H167" t="s">
         <v>15</v>
@@ -8016,183 +7923,183 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>767</v>
+      </c>
+      <c r="C168" t="s">
+        <v>272</v>
+      </c>
+      <c r="D168" t="s">
         <v>768</v>
       </c>
-      <c r="C168" t="s">
-        <v>61</v>
-      </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
+        <v>42</v>
+      </c>
+      <c r="F168" t="s">
+        <v>7</v>
+      </c>
+      <c r="G168" t="s">
         <v>769</v>
       </c>
-      <c r="E168" t="s">
-        <v>62</v>
-      </c>
-      <c r="F168" t="s">
-        <v>63</v>
-      </c>
-      <c r="G168" t="s">
-        <v>770</v>
-      </c>
       <c r="H168" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C169" t="s">
-        <v>93</v>
+        <v>272</v>
       </c>
       <c r="D169" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E169" t="s">
-        <v>773</v>
+        <v>42</v>
       </c>
       <c r="F169" t="s">
-        <v>774</v>
+        <v>7</v>
       </c>
       <c r="G169" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="H169" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C170" t="s">
-        <v>750</v>
+        <v>23</v>
       </c>
       <c r="D170" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E170" t="s">
-        <v>752</v>
+        <v>172</v>
       </c>
       <c r="F170" t="s">
-        <v>753</v>
+        <v>173</v>
       </c>
       <c r="G170" t="s">
-        <v>754</v>
+        <v>773</v>
       </c>
       <c r="H170" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C171" t="s">
-        <v>750</v>
+        <v>23</v>
       </c>
       <c r="D171" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E171" t="s">
-        <v>752</v>
+        <v>172</v>
       </c>
       <c r="F171" t="s">
-        <v>753</v>
+        <v>173</v>
       </c>
       <c r="G171" t="s">
-        <v>754</v>
+        <v>773</v>
       </c>
       <c r="H171" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C172" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D172" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="E172" t="s">
-        <v>781</v>
+        <v>172</v>
       </c>
       <c r="F172" t="s">
-        <v>782</v>
+        <v>173</v>
       </c>
       <c r="G172" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="H172" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C173" t="s">
-        <v>97</v>
+        <v>777</v>
       </c>
       <c r="D173" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="E173" t="s">
-        <v>786</v>
+        <v>175</v>
       </c>
       <c r="F173" t="s">
-        <v>787</v>
+        <v>176</v>
       </c>
       <c r="G173" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="H173" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="C174" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="D174" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="E174" t="s">
-        <v>791</v>
+        <v>175</v>
       </c>
       <c r="F174" t="s">
-        <v>792</v>
+        <v>176</v>
       </c>
       <c r="G174" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="H174" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="C175" t="s">
-        <v>288</v>
+        <v>453</v>
       </c>
       <c r="D175" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="E175" t="s">
-        <v>42</v>
+        <v>783</v>
       </c>
       <c r="F175" t="s">
-        <v>7</v>
+        <v>784</v>
       </c>
       <c r="G175" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -8200,22 +8107,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="C176" t="s">
-        <v>288</v>
+        <v>453</v>
       </c>
       <c r="D176" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="E176" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="F176" t="s">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="G176" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -8223,22 +8130,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="C177" t="s">
-        <v>23</v>
+        <v>453</v>
       </c>
       <c r="D177" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="E177" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="F177" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="G177" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -8246,22 +8153,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="C178" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D178" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="E178" t="s">
-        <v>178</v>
+        <v>792</v>
       </c>
       <c r="F178" t="s">
-        <v>179</v>
+        <v>793</v>
       </c>
       <c r="G178" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -8269,22 +8176,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E179" t="s">
-        <v>178</v>
+        <v>797</v>
       </c>
       <c r="F179" t="s">
-        <v>179</v>
+        <v>7</v>
       </c>
       <c r="G179" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -8292,22 +8199,22 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C180" t="s">
-        <v>804</v>
+        <v>174</v>
       </c>
       <c r="D180" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E180" t="s">
-        <v>181</v>
+        <v>801</v>
       </c>
       <c r="F180" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G180" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -8315,22 +8222,22 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C181" t="s">
+        <v>77</v>
+      </c>
+      <c r="D181" t="s">
         <v>804</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>805</v>
       </c>
-      <c r="E181" t="s">
-        <v>181</v>
-      </c>
       <c r="F181" t="s">
-        <v>182</v>
+        <v>806</v>
       </c>
       <c r="G181" t="s">
-        <v>806</v>
+        <v>260</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -8338,22 +8245,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>807</v>
+      </c>
+      <c r="C182" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" t="s">
         <v>808</v>
       </c>
-      <c r="C182" t="s">
-        <v>474</v>
-      </c>
-      <c r="D182" t="s">
-        <v>809</v>
-      </c>
       <c r="E182" t="s">
-        <v>810</v>
+        <v>43</v>
       </c>
       <c r="F182" t="s">
-        <v>811</v>
+        <v>44</v>
       </c>
       <c r="G182" t="s">
-        <v>812</v>
+        <v>444</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -8361,22 +8268,22 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C183" t="s">
-        <v>474</v>
+        <v>30</v>
       </c>
       <c r="D183" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E183" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="F183" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="G183" t="s">
-        <v>815</v>
+        <v>280</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -8384,22 +8291,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="C184" t="s">
-        <v>474</v>
+        <v>21</v>
       </c>
       <c r="D184" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E184" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="F184" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="G184" t="s">
-        <v>815</v>
+        <v>85</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -8407,22 +8314,22 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C185" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D185" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="E185" t="s">
-        <v>819</v>
+        <v>43</v>
       </c>
       <c r="F185" t="s">
-        <v>820</v>
+        <v>44</v>
       </c>
       <c r="G185" t="s">
-        <v>821</v>
+        <v>85</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -8430,22 +8337,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="C186" t="s">
-        <v>73</v>
+        <v>409</v>
       </c>
       <c r="D186" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="E186" t="s">
-        <v>824</v>
+        <v>411</v>
       </c>
       <c r="F186" t="s">
-        <v>825</v>
+        <v>7</v>
       </c>
       <c r="G186" t="s">
-        <v>12</v>
+        <v>816</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -8453,22 +8360,22 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="C187" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D187" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="E187" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="F187" t="s">
-        <v>7</v>
+        <v>820</v>
       </c>
       <c r="G187" t="s">
-        <v>829</v>
+        <v>28</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -8476,22 +8383,22 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="C188" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="D188" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="E188" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="F188" t="s">
-        <v>192</v>
+        <v>820</v>
       </c>
       <c r="G188" t="s">
-        <v>833</v>
+        <v>28</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -8499,22 +8406,22 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="C189" t="s">
-        <v>77</v>
+        <v>645</v>
       </c>
       <c r="D189" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="E189" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="F189" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="G189" t="s">
-        <v>271</v>
+        <v>826</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -8522,22 +8429,22 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="C190" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="D190" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="E190" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F190" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="G190" t="s">
-        <v>465</v>
+        <v>829</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -8545,22 +8452,22 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="C191" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="D191" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="E191" t="s">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="F191" t="s">
-        <v>56</v>
+        <v>577</v>
       </c>
       <c r="G191" t="s">
-        <v>296</v>
+        <v>832</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -8568,22 +8475,22 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C192" t="s">
-        <v>21</v>
+        <v>777</v>
       </c>
       <c r="D192" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="E192" t="s">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="F192" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G192" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -8591,22 +8498,22 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="C193" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D193" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="E193" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="F193" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="G193" t="s">
-        <v>85</v>
+        <v>837</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -8614,22 +8521,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="C194" t="s">
-        <v>430</v>
+        <v>218</v>
       </c>
       <c r="D194" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="E194" t="s">
-        <v>432</v>
+        <v>840</v>
       </c>
       <c r="F194" t="s">
         <v>7</v>
       </c>
       <c r="G194" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -8637,22 +8544,22 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="C195" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D195" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="E195" t="s">
-        <v>850</v>
+        <v>13</v>
       </c>
       <c r="F195" t="s">
-        <v>851</v>
+        <v>14</v>
       </c>
       <c r="G195" t="s">
-        <v>28</v>
+        <v>844</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -8660,22 +8567,22 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="C196" t="s">
-        <v>73</v>
+        <v>409</v>
       </c>
       <c r="D196" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E196" t="s">
-        <v>850</v>
+        <v>162</v>
       </c>
       <c r="F196" t="s">
-        <v>851</v>
+        <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>28</v>
+        <v>847</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -8683,22 +8590,22 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C197" t="s">
-        <v>666</v>
+        <v>30</v>
       </c>
       <c r="D197" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="E197" t="s">
-        <v>855</v>
+        <v>55</v>
       </c>
       <c r="F197" t="s">
-        <v>856</v>
+        <v>56</v>
       </c>
       <c r="G197" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -8706,22 +8613,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="C198" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="D198" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="E198" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="F198" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="G198" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -8729,22 +8636,22 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="C199" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D199" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E199" t="s">
-        <v>597</v>
+        <v>41</v>
       </c>
       <c r="F199" t="s">
-        <v>598</v>
+        <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -8752,22 +8659,22 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="C200" t="s">
-        <v>804</v>
+        <v>21</v>
       </c>
       <c r="D200" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="E200" t="s">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="F200" t="s">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="G200" t="s">
-        <v>11</v>
+        <v>857</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -8775,22 +8682,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C201" t="s">
-        <v>93</v>
+        <v>645</v>
       </c>
       <c r="D201" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="E201" t="s">
-        <v>123</v>
+        <v>860</v>
       </c>
       <c r="F201" t="s">
-        <v>124</v>
+        <v>861</v>
       </c>
       <c r="G201" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -8798,22 +8705,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C202" t="s">
-        <v>224</v>
+        <v>27</v>
       </c>
       <c r="D202" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="E202" t="s">
-        <v>871</v>
+        <v>47</v>
       </c>
       <c r="F202" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="G202" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -8821,22 +8728,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C203" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D203" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="E203" t="s">
-        <v>13</v>
+        <v>868</v>
       </c>
       <c r="F203" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G203" t="s">
-        <v>875</v>
+        <v>484</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -8844,22 +8751,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C204" t="s">
-        <v>430</v>
+        <v>23</v>
       </c>
       <c r="D204" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="E204" t="s">
-        <v>168</v>
+        <v>868</v>
       </c>
       <c r="F204" t="s">
         <v>7</v>
       </c>
       <c r="G204" t="s">
-        <v>878</v>
+        <v>484</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -8867,22 +8774,22 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C205" t="s">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="D205" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="E205" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F205" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G205" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -8890,22 +8797,22 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="C206" t="s">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="D206" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="E206" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F206" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G206" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -8913,22 +8820,22 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="D207" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="E207" t="s">
-        <v>41</v>
+        <v>876</v>
       </c>
       <c r="F207" t="s">
         <v>7</v>
       </c>
       <c r="G207" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -8936,13 +8843,13 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="C208" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D208" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="E208" t="s">
         <v>43</v>
@@ -8951,7 +8858,7 @@
         <v>44</v>
       </c>
       <c r="G208" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -8959,22 +8866,22 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C209" t="s">
-        <v>666</v>
+        <v>24</v>
       </c>
       <c r="D209" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="E209" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="F209" t="s">
-        <v>892</v>
+        <v>7</v>
       </c>
       <c r="G209" t="s">
-        <v>893</v>
+        <v>187</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -8982,22 +8889,22 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="C210" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="D210" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="E210" t="s">
-        <v>47</v>
+        <v>886</v>
       </c>
       <c r="F210" t="s">
-        <v>48</v>
+        <v>887</v>
       </c>
       <c r="G210" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -9005,22 +8912,22 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="C211" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D211" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="E211" t="s">
-        <v>899</v>
+        <v>47</v>
       </c>
       <c r="F211" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="G211" t="s">
-        <v>505</v>
+        <v>891</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -9028,22 +8935,22 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="C212" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D212" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="E212" t="s">
-        <v>899</v>
+        <v>47</v>
       </c>
       <c r="F212" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>891</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -9051,22 +8958,22 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="C213" t="s">
-        <v>645</v>
+        <v>218</v>
       </c>
       <c r="D213" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="E213" t="s">
-        <v>33</v>
+        <v>895</v>
       </c>
       <c r="F213" t="s">
         <v>7</v>
       </c>
       <c r="G213" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -9074,22 +8981,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="C214" t="s">
-        <v>645</v>
+        <v>35</v>
       </c>
       <c r="D214" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E214" t="s">
-        <v>33</v>
+        <v>899</v>
       </c>
       <c r="F214" t="s">
         <v>7</v>
       </c>
       <c r="G214" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -9097,22 +9004,22 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C215" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="D215" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="E215" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="F215" t="s">
         <v>7</v>
       </c>
       <c r="G215" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -9120,22 +9027,22 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C216" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D216" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="E216" t="s">
-        <v>43</v>
+        <v>899</v>
       </c>
       <c r="F216" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G216" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -9143,22 +9050,22 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="C217" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D217" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="E217" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="F217" t="s">
-        <v>7</v>
+        <v>189</v>
       </c>
       <c r="G217" t="s">
-        <v>193</v>
+        <v>906</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -9166,22 +9073,22 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="C218" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="D218" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="E218" t="s">
-        <v>917</v>
+        <v>356</v>
       </c>
       <c r="F218" t="s">
-        <v>918</v>
+        <v>357</v>
       </c>
       <c r="G218" t="s">
-        <v>919</v>
+        <v>101</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -9189,22 +9096,22 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="C219" t="s">
-        <v>27</v>
+        <v>331</v>
       </c>
       <c r="D219" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="E219" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F219" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G219" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -9212,22 +9119,22 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="C220" t="s">
-        <v>27</v>
+        <v>331</v>
       </c>
       <c r="D220" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="E220" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F220" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -9235,22 +9142,22 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="C221" t="s">
-        <v>224</v>
+        <v>331</v>
       </c>
       <c r="D221" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="E221" t="s">
-        <v>926</v>
+        <v>31</v>
       </c>
       <c r="F221" t="s">
         <v>7</v>
       </c>
       <c r="G221" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -9258,22 +9165,22 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="C222" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D222" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="E222" t="s">
-        <v>930</v>
+        <v>37</v>
       </c>
       <c r="F222" t="s">
         <v>7</v>
       </c>
       <c r="G222" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -9281,22 +9188,22 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="C223" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="D223" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="E223" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="F223" t="s">
         <v>7</v>
       </c>
       <c r="G223" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -9304,22 +9211,22 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="C224" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="D224" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="E224" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="F224" t="s">
-        <v>7</v>
+        <v>924</v>
       </c>
       <c r="G224" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -9327,22 +9234,22 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="C225" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="D225" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="E225" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="F225" t="s">
-        <v>195</v>
+        <v>7</v>
       </c>
       <c r="G225" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -9350,22 +9257,22 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="C226" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D226" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="E226" t="s">
-        <v>372</v>
+        <v>928</v>
       </c>
       <c r="F226" t="s">
-        <v>373</v>
+        <v>7</v>
       </c>
       <c r="G226" t="s">
-        <v>103</v>
+        <v>929</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -9373,22 +9280,22 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="C227" t="s">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="D227" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="E227" t="s">
-        <v>31</v>
+        <v>933</v>
       </c>
       <c r="F227" t="s">
         <v>7</v>
       </c>
       <c r="G227" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -9396,22 +9303,22 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="C228" t="s">
-        <v>347</v>
+        <v>645</v>
       </c>
       <c r="D228" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="E228" t="s">
-        <v>31</v>
+        <v>824</v>
       </c>
       <c r="F228" t="s">
-        <v>7</v>
+        <v>825</v>
       </c>
       <c r="G228" t="s">
-        <v>942</v>
+        <v>185</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -9419,22 +9326,22 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="C229" t="s">
-        <v>347</v>
+        <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="E229" t="s">
-        <v>31</v>
+        <v>514</v>
       </c>
       <c r="F229" t="s">
         <v>7</v>
       </c>
       <c r="G229" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -9442,22 +9349,22 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="C230" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="D230" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="E230" t="s">
-        <v>37</v>
+        <v>942</v>
       </c>
       <c r="F230" t="s">
         <v>7</v>
       </c>
       <c r="G230" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -9465,22 +9372,22 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C231" t="s">
-        <v>141</v>
+        <v>636</v>
       </c>
       <c r="D231" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="E231" t="s">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="F231" t="s">
         <v>7</v>
       </c>
       <c r="G231" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -9488,22 +9395,22 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="C232" t="s">
-        <v>288</v>
+        <v>636</v>
       </c>
       <c r="D232" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="E232" t="s">
-        <v>954</v>
+        <v>34</v>
       </c>
       <c r="F232" t="s">
-        <v>955</v>
+        <v>7</v>
       </c>
       <c r="G232" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -9511,22 +9418,22 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="C233" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="D233" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="E233" t="s">
-        <v>959</v>
+        <v>160</v>
       </c>
       <c r="F233" t="s">
         <v>7</v>
       </c>
       <c r="G233" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -9534,22 +9441,22 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="C234" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="D234" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="E234" t="s">
-        <v>959</v>
+        <v>606</v>
       </c>
       <c r="F234" t="s">
         <v>7</v>
       </c>
       <c r="G234" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -9557,22 +9464,22 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="C235" t="s">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="D235" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="E235" t="s">
-        <v>964</v>
+        <v>19</v>
       </c>
       <c r="F235" t="s">
         <v>7</v>
       </c>
       <c r="G235" t="s">
-        <v>965</v>
+        <v>484</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -9580,22 +9487,22 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="C236" t="s">
-        <v>666</v>
+        <v>18</v>
       </c>
       <c r="D236" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="E236" t="s">
-        <v>855</v>
+        <v>179</v>
       </c>
       <c r="F236" t="s">
-        <v>856</v>
+        <v>7</v>
       </c>
       <c r="G236" t="s">
-        <v>191</v>
+        <v>298</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -9603,22 +9510,22 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C237" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D237" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="E237" t="s">
-        <v>535</v>
+        <v>179</v>
       </c>
       <c r="F237" t="s">
         <v>7</v>
       </c>
       <c r="G237" t="s">
-        <v>970</v>
+        <v>298</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -9626,22 +9533,22 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="C238" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D238" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="E238" t="s">
-        <v>973</v>
+        <v>876</v>
       </c>
       <c r="F238" t="s">
         <v>7</v>
       </c>
       <c r="G238" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -9649,22 +9556,22 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="C239" t="s">
-        <v>657</v>
+        <v>331</v>
       </c>
       <c r="D239" t="s">
-        <v>976</v>
+        <v>963</v>
       </c>
       <c r="E239" t="s">
-        <v>34</v>
+        <v>964</v>
       </c>
       <c r="F239" t="s">
-        <v>7</v>
+        <v>965</v>
       </c>
       <c r="G239" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -9672,22 +9579,22 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="C240" t="s">
-        <v>657</v>
+        <v>27</v>
       </c>
       <c r="D240" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="E240" t="s">
-        <v>34</v>
+        <v>969</v>
       </c>
       <c r="F240" t="s">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="G240" t="s">
-        <v>977</v>
+        <v>209</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -9695,22 +9602,22 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="C241" t="s">
-        <v>21</v>
+        <v>624</v>
       </c>
       <c r="D241" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="E241" t="s">
-        <v>166</v>
+        <v>973</v>
       </c>
       <c r="F241" t="s">
         <v>7</v>
       </c>
       <c r="G241" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -9718,22 +9625,22 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="C242" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D242" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="E242" t="s">
-        <v>627</v>
+        <v>977</v>
       </c>
       <c r="F242" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="G242" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -9741,22 +9648,22 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="C243" t="s">
-        <v>347</v>
+        <v>61</v>
       </c>
       <c r="D243" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="E243" t="s">
-        <v>19</v>
+        <v>981</v>
       </c>
       <c r="F243" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G243" t="s">
-        <v>505</v>
+        <v>982</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -9764,22 +9671,22 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C244" t="s">
-        <v>18</v>
+        <v>409</v>
       </c>
       <c r="D244" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="E244" t="s">
-        <v>185</v>
+        <v>411</v>
       </c>
       <c r="F244" t="s">
         <v>7</v>
       </c>
       <c r="G244" t="s">
-        <v>314</v>
+        <v>985</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -9787,22 +9694,22 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C245" t="s">
-        <v>18</v>
+        <v>340</v>
       </c>
       <c r="D245" t="s">
+        <v>987</v>
+      </c>
+      <c r="E245" t="s">
+        <v>38</v>
+      </c>
+      <c r="F245" t="s">
+        <v>39</v>
+      </c>
+      <c r="G245" t="s">
         <v>988</v>
-      </c>
-      <c r="E245" t="s">
-        <v>185</v>
-      </c>
-      <c r="F245" t="s">
-        <v>7</v>
-      </c>
-      <c r="G245" t="s">
-        <v>314</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -9810,22 +9717,22 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
+        <v>989</v>
+      </c>
+      <c r="C246" t="s">
+        <v>61</v>
+      </c>
+      <c r="D246" t="s">
         <v>990</v>
       </c>
-      <c r="C246" t="s">
-        <v>141</v>
-      </c>
-      <c r="D246" t="s">
-        <v>991</v>
-      </c>
       <c r="E246" t="s">
-        <v>907</v>
+        <v>981</v>
       </c>
       <c r="F246" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G246" t="s">
-        <v>992</v>
+        <v>120</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -9833,22 +9740,22 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
+        <v>991</v>
+      </c>
+      <c r="C247" t="s">
+        <v>27</v>
+      </c>
+      <c r="D247" t="s">
+        <v>992</v>
+      </c>
+      <c r="E247" t="s">
         <v>993</v>
       </c>
-      <c r="C247" t="s">
-        <v>347</v>
-      </c>
-      <c r="D247" t="s">
+      <c r="F247" t="s">
         <v>994</v>
       </c>
-      <c r="E247" t="s">
-        <v>995</v>
-      </c>
-      <c r="F247" t="s">
-        <v>996</v>
-      </c>
       <c r="G247" t="s">
-        <v>997</v>
+        <v>178</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -9856,22 +9763,22 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C248" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D248" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E248" t="s">
-        <v>1000</v>
+        <v>109</v>
       </c>
       <c r="F248" t="s">
-        <v>1001</v>
+        <v>110</v>
       </c>
       <c r="G248" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -9879,22 +9786,22 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="C249" t="s">
-        <v>645</v>
+        <v>70</v>
       </c>
       <c r="D249" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="E249" t="s">
-        <v>1004</v>
+        <v>71</v>
       </c>
       <c r="F249" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G249" t="s">
-        <v>1005</v>
+        <v>72</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -9902,22 +9809,22 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="C250" t="s">
         <v>51</v>
       </c>
       <c r="D250" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="E250" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="F250" t="s">
-        <v>108</v>
+        <v>1002</v>
       </c>
       <c r="G250" t="s">
-        <v>1009</v>
+        <v>36</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -9925,22 +9832,22 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="C251" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D251" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="E251" t="s">
-        <v>1012</v>
+        <v>41</v>
       </c>
       <c r="F251" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="G251" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -9948,22 +9855,22 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="C252" t="s">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="D252" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="E252" t="s">
-        <v>432</v>
+        <v>1008</v>
       </c>
       <c r="F252" t="s">
         <v>7</v>
       </c>
       <c r="G252" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -9971,22 +9878,22 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="C253" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="D253" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="E253" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F253" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G253" t="s">
-        <v>1019</v>
+        <v>117</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -9994,22 +9901,22 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="C254" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D254" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="E254" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F254" t="s">
-        <v>63</v>
+        <v>1015</v>
       </c>
       <c r="G254" t="s">
-        <v>122</v>
+        <v>1016</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -10017,22 +9924,22 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C255" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D255" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="E255" t="s">
-        <v>1024</v>
+        <v>118</v>
       </c>
       <c r="F255" t="s">
-        <v>1025</v>
+        <v>119</v>
       </c>
       <c r="G255" t="s">
-        <v>184</v>
+        <v>1019</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -10040,22 +9947,22 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="C256" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D256" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="E256" t="s">
-        <v>111</v>
+        <v>1008</v>
       </c>
       <c r="F256" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="G256" t="s">
-        <v>173</v>
+        <v>1022</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -10063,22 +9970,22 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="C257" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D257" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E257" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="F257" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="G257" t="s">
-        <v>72</v>
+        <v>1025</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -10086,22 +9993,22 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C258" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="D258" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="E258" t="s">
-        <v>1032</v>
+        <v>759</v>
       </c>
       <c r="F258" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G258" t="s">
-        <v>36</v>
+        <v>402</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -10109,22 +10016,22 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="C259" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="D259" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="E259" t="s">
-        <v>41</v>
+        <v>1031</v>
       </c>
       <c r="F259" t="s">
-        <v>7</v>
+        <v>1032</v>
       </c>
       <c r="G259" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -10132,22 +10039,22 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C260" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D260" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E260" t="s">
-        <v>1039</v>
+        <v>135</v>
       </c>
       <c r="F260" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="G260" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -10155,22 +10062,22 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C261" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D261" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="E261" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F261" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>119</v>
+        <v>1039</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -10178,22 +10085,22 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C262" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D262" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E262" t="s">
-        <v>1045</v>
+        <v>47</v>
       </c>
       <c r="F262" t="s">
-        <v>1046</v>
+        <v>48</v>
       </c>
       <c r="G262" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -10201,22 +10108,22 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C263" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="D263" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="E263" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="F263" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="G263" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -10224,22 +10131,22 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="C264" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D264" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="E264" t="s">
-        <v>1039</v>
+        <v>581</v>
       </c>
       <c r="F264" t="s">
         <v>7</v>
       </c>
       <c r="G264" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -10247,22 +10154,22 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="C265" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D265" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="E265" t="s">
-        <v>37</v>
+        <v>1051</v>
       </c>
       <c r="F265" t="s">
-        <v>7</v>
+        <v>1052</v>
       </c>
       <c r="G265" t="s">
-        <v>1056</v>
+        <v>177</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -10270,22 +10177,22 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="C266" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D266" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="E266" t="s">
-        <v>786</v>
+        <v>681</v>
       </c>
       <c r="F266" t="s">
-        <v>1059</v>
+        <v>682</v>
       </c>
       <c r="G266" t="s">
-        <v>423</v>
+        <v>1055</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -10293,22 +10200,22 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="C267" t="s">
-        <v>316</v>
+        <v>54</v>
       </c>
       <c r="D267" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="E267" t="s">
-        <v>1062</v>
+        <v>17</v>
       </c>
       <c r="F267" t="s">
-        <v>1063</v>
+        <v>7</v>
       </c>
       <c r="G267" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -10316,22 +10223,22 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="C268" t="s">
-        <v>27</v>
+        <v>331</v>
       </c>
       <c r="D268" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="E268" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="F268" t="s">
-        <v>138</v>
+        <v>7</v>
       </c>
       <c r="G268" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -10339,22 +10246,22 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="C269" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="D269" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="E269" t="s">
-        <v>17</v>
+        <v>933</v>
       </c>
       <c r="F269" t="s">
         <v>7</v>
       </c>
       <c r="G269" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -10362,22 +10269,22 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="C270" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D270" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="E270" t="s">
-        <v>47</v>
+        <v>1067</v>
       </c>
       <c r="F270" t="s">
-        <v>48</v>
+        <v>1068</v>
       </c>
       <c r="G270" t="s">
-        <v>1073</v>
+        <v>22</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -10385,22 +10292,22 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="C271" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D271" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="E271" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F271" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G271" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -10408,22 +10315,22 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="C272" t="s">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="D272" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="E272" t="s">
-        <v>602</v>
+        <v>42</v>
       </c>
       <c r="F272" t="s">
         <v>7</v>
       </c>
       <c r="G272" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -10431,22 +10338,22 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C273" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D273" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="E273" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="F273" t="s">
-        <v>1083</v>
+        <v>7</v>
       </c>
       <c r="G273" t="s">
-        <v>183</v>
+        <v>1019</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -10454,91 +10361,91 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="C274" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="D274" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="E274" t="s">
-        <v>704</v>
+        <v>1080</v>
       </c>
       <c r="F274" t="s">
-        <v>705</v>
+        <v>7</v>
       </c>
       <c r="G274" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="H274" t="s">
-        <v>8</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="C275" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="D275" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
       <c r="E275" t="s">
-        <v>17</v>
+        <v>1080</v>
       </c>
       <c r="F275" t="s">
         <v>7</v>
       </c>
       <c r="G275" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="H275" t="s">
-        <v>8</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="C276" t="s">
-        <v>347</v>
+        <v>139</v>
       </c>
       <c r="D276" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="E276" t="s">
-        <v>19</v>
+        <v>1080</v>
       </c>
       <c r="F276" t="s">
         <v>7</v>
       </c>
       <c r="G276" t="s">
-        <v>1092</v>
+        <v>1081</v>
       </c>
       <c r="H276" t="s">
-        <v>8</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="C277" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D277" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="E277" t="s">
-        <v>964</v>
+        <v>55</v>
       </c>
       <c r="F277" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="G277" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -10546,229 +10453,229 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="C278" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="D278" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="E278" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="F278" t="s">
-        <v>1099</v>
+        <v>7</v>
       </c>
       <c r="G278" t="s">
-        <v>22</v>
+        <v>1091</v>
       </c>
       <c r="H278" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C279" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="D279" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
       <c r="E279" t="s">
-        <v>37</v>
+        <v>1094</v>
       </c>
       <c r="F279" t="s">
-        <v>7</v>
+        <v>1095</v>
       </c>
       <c r="G279" t="s">
-        <v>1102</v>
+        <v>26</v>
       </c>
       <c r="H279" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="C280" t="s">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="D280" t="s">
-        <v>1104</v>
+        <v>1093</v>
       </c>
       <c r="E280" t="s">
-        <v>42</v>
+        <v>1094</v>
       </c>
       <c r="F280" t="s">
-        <v>7</v>
+        <v>1095</v>
       </c>
       <c r="G280" t="s">
-        <v>1105</v>
+        <v>26</v>
       </c>
       <c r="H280" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
       <c r="C281" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="E281" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="F281" t="s">
         <v>7</v>
       </c>
       <c r="G281" t="s">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="H281" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="C282" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="E282" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="F282" t="s">
         <v>7</v>
       </c>
       <c r="G282" t="s">
-        <v>1112</v>
+        <v>156</v>
       </c>
       <c r="H282" t="s">
-        <v>1113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
       <c r="C283" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="E283" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="F283" t="s">
         <v>7</v>
       </c>
       <c r="G283" t="s">
-        <v>1112</v>
+        <v>156</v>
       </c>
       <c r="H283" t="s">
-        <v>1113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="C284" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="D284" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="E284" t="s">
-        <v>1111</v>
+        <v>145</v>
       </c>
       <c r="F284" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="G284" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="H284" t="s">
-        <v>1113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="C285" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
       <c r="E285" t="s">
-        <v>55</v>
+        <v>1110</v>
       </c>
       <c r="F285" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G285" t="s">
-        <v>1118</v>
+        <v>280</v>
       </c>
       <c r="H285" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
       <c r="C286" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D286" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="E286" t="s">
-        <v>1121</v>
+        <v>933</v>
       </c>
       <c r="F286" t="s">
         <v>7</v>
       </c>
       <c r="G286" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="H286" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="C287" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D287" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="E287" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
       <c r="F287" t="s">
-        <v>1126</v>
+        <v>106</v>
       </c>
       <c r="G287" t="s">
-        <v>26</v>
+        <v>1117</v>
       </c>
       <c r="H287" t="s">
         <v>16</v>
@@ -10776,22 +10683,22 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="C288" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="D288" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="E288" t="s">
-        <v>1125</v>
+        <v>192</v>
       </c>
       <c r="F288" t="s">
-        <v>1126</v>
+        <v>63</v>
       </c>
       <c r="G288" t="s">
-        <v>26</v>
+        <v>1120</v>
       </c>
       <c r="H288" t="s">
         <v>16</v>
@@ -10799,22 +10706,22 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="C289" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D289" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="E289" t="s">
-        <v>1130</v>
+        <v>207</v>
       </c>
       <c r="F289" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="G289" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
       <c r="H289" t="s">
         <v>16</v>
@@ -10822,22 +10729,22 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="C290" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="D290" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="E290" t="s">
-        <v>1134</v>
+        <v>40</v>
       </c>
       <c r="F290" t="s">
         <v>7</v>
       </c>
       <c r="G290" t="s">
-        <v>160</v>
+        <v>1126</v>
       </c>
       <c r="H290" t="s">
         <v>16</v>
@@ -10845,22 +10752,22 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="C291" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="D291" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="E291" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="F291" t="s">
-        <v>7</v>
+        <v>1130</v>
       </c>
       <c r="G291" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="H291" t="s">
         <v>16</v>
@@ -10868,22 +10775,22 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="C292" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="D292" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="E292" t="s">
-        <v>147</v>
+        <v>1133</v>
       </c>
       <c r="F292" t="s">
-        <v>148</v>
+        <v>1134</v>
       </c>
       <c r="G292" t="s">
-        <v>1138</v>
+        <v>125</v>
       </c>
       <c r="H292" t="s">
         <v>16</v>
@@ -10891,22 +10798,22 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C293" t="s">
-        <v>25</v>
+        <v>636</v>
       </c>
       <c r="D293" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="E293" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="F293" t="s">
-        <v>7</v>
+        <v>1138</v>
       </c>
       <c r="G293" t="s">
-        <v>296</v>
+        <v>151</v>
       </c>
       <c r="H293" t="s">
         <v>16</v>
@@ -10914,22 +10821,22 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C294" t="s">
+        <v>331</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F294" t="s">
         <v>1142</v>
       </c>
-      <c r="C294" t="s">
-        <v>20</v>
-      </c>
-      <c r="D294" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E294" t="s">
-        <v>964</v>
-      </c>
-      <c r="F294" t="s">
-        <v>7</v>
-      </c>
       <c r="G294" t="s">
-        <v>1144</v>
+        <v>280</v>
       </c>
       <c r="H294" t="s">
         <v>16</v>
@@ -10937,22 +10844,22 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C295" t="s">
+        <v>139</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E295" t="s">
         <v>1145</v>
       </c>
-      <c r="C295" t="s">
-        <v>87</v>
-      </c>
-      <c r="D295" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E295" t="s">
-        <v>1147</v>
-      </c>
       <c r="F295" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="G295" t="s">
-        <v>1148</v>
+        <v>97</v>
       </c>
       <c r="H295" t="s">
         <v>16</v>
@@ -10960,22 +10867,22 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E296" t="s">
         <v>1149</v>
       </c>
-      <c r="C296" t="s">
-        <v>70</v>
-      </c>
-      <c r="D296" t="s">
+      <c r="F296" t="s">
+        <v>7</v>
+      </c>
+      <c r="G296" t="s">
         <v>1150</v>
-      </c>
-      <c r="E296" t="s">
-        <v>198</v>
-      </c>
-      <c r="F296" t="s">
-        <v>63</v>
-      </c>
-      <c r="G296" t="s">
-        <v>1151</v>
       </c>
       <c r="H296" t="s">
         <v>16</v>
@@ -10983,22 +10890,22 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C297" t="s">
+        <v>139</v>
+      </c>
+      <c r="D297" t="s">
         <v>1152</v>
       </c>
-      <c r="C297" t="s">
-        <v>70</v>
-      </c>
-      <c r="D297" t="s">
-        <v>1153</v>
-      </c>
       <c r="E297" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="F297" t="s">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="G297" t="s">
-        <v>1154</v>
+        <v>158</v>
       </c>
       <c r="H297" t="s">
         <v>16</v>
@@ -11006,19 +10913,19 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C298" t="s">
+        <v>453</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E298" t="s">
         <v>1155</v>
       </c>
-      <c r="C298" t="s">
-        <v>86</v>
-      </c>
-      <c r="D298" t="s">
+      <c r="F298" t="s">
         <v>1156</v>
-      </c>
-      <c r="E298" t="s">
-        <v>40</v>
-      </c>
-      <c r="F298" t="s">
-        <v>7</v>
       </c>
       <c r="G298" t="s">
         <v>1157</v>
@@ -11032,7 +10939,7 @@
         <v>1158</v>
       </c>
       <c r="C299" t="s">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="D299" t="s">
         <v>1159</v>
@@ -11044,7 +10951,7 @@
         <v>1161</v>
       </c>
       <c r="G299" t="s">
-        <v>76</v>
+        <v>1162</v>
       </c>
       <c r="H299" t="s">
         <v>16</v>
@@ -11052,22 +10959,22 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C300" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D300" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E300" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F300" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G300" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="H300" t="s">
         <v>16</v>
@@ -11075,22 +10982,22 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C301" t="s">
-        <v>657</v>
+        <v>20</v>
       </c>
       <c r="D301" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E301" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F301" t="s">
-        <v>1169</v>
+        <v>7</v>
       </c>
       <c r="G301" t="s">
-        <v>155</v>
+        <v>934</v>
       </c>
       <c r="H301" t="s">
         <v>16</v>
@@ -11101,19 +11008,19 @@
         <v>1170</v>
       </c>
       <c r="C302" t="s">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="D302" t="s">
         <v>1171</v>
       </c>
       <c r="E302" t="s">
+        <v>43</v>
+      </c>
+      <c r="F302" t="s">
+        <v>44</v>
+      </c>
+      <c r="G302" t="s">
         <v>1172</v>
-      </c>
-      <c r="F302" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G302" t="s">
-        <v>296</v>
       </c>
       <c r="H302" t="s">
         <v>16</v>
@@ -11121,22 +11028,22 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C303" t="s">
+        <v>24</v>
+      </c>
+      <c r="D303" t="s">
         <v>1174</v>
       </c>
-      <c r="C303" t="s">
-        <v>141</v>
-      </c>
-      <c r="D303" t="s">
-        <v>1175</v>
-      </c>
       <c r="E303" t="s">
-        <v>1176</v>
+        <v>311</v>
       </c>
       <c r="F303" t="s">
         <v>7</v>
       </c>
       <c r="G303" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="H303" t="s">
         <v>16</v>
@@ -11144,22 +11051,22 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E304" t="s">
         <v>1177</v>
-      </c>
-      <c r="C304" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D304" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E304" t="s">
-        <v>1180</v>
       </c>
       <c r="F304" t="s">
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="H304" t="s">
         <v>16</v>
@@ -11167,22 +11074,22 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C305" t="s">
+        <v>409</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E305" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F305" t="s">
+        <v>7</v>
+      </c>
+      <c r="G305" t="s">
         <v>1182</v>
-      </c>
-      <c r="C305" t="s">
-        <v>141</v>
-      </c>
-      <c r="D305" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E305" t="s">
-        <v>196</v>
-      </c>
-      <c r="F305" t="s">
-        <v>197</v>
-      </c>
-      <c r="G305" t="s">
-        <v>164</v>
       </c>
       <c r="H305" t="s">
         <v>16</v>
@@ -11190,22 +11097,22 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C306" t="s">
+        <v>261</v>
+      </c>
+      <c r="D306" t="s">
         <v>1184</v>
       </c>
-      <c r="C306" t="s">
-        <v>474</v>
-      </c>
-      <c r="D306" t="s">
+      <c r="E306" t="s">
+        <v>116</v>
+      </c>
+      <c r="F306" t="s">
+        <v>103</v>
+      </c>
+      <c r="G306" t="s">
         <v>1185</v>
-      </c>
-      <c r="E306" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F306" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G306" t="s">
-        <v>1188</v>
       </c>
       <c r="H306" t="s">
         <v>16</v>
@@ -11213,22 +11120,22 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C307" t="s">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="D307" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E307" t="s">
-        <v>1191</v>
+        <v>253</v>
       </c>
       <c r="F307" t="s">
-        <v>1192</v>
+        <v>254</v>
       </c>
       <c r="G307" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="H307" t="s">
         <v>16</v>
@@ -11236,22 +11143,22 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="C308" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="D308" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="E308" t="s">
-        <v>1196</v>
+        <v>253</v>
       </c>
       <c r="F308" t="s">
-        <v>1197</v>
+        <v>254</v>
       </c>
       <c r="G308" t="s">
-        <v>22</v>
+        <v>1188</v>
       </c>
       <c r="H308" t="s">
         <v>16</v>
@@ -11259,22 +11166,22 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="C309" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D309" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="E309" t="s">
-        <v>1200</v>
+        <v>581</v>
       </c>
       <c r="F309" t="s">
         <v>7</v>
       </c>
       <c r="G309" t="s">
-        <v>965</v>
+        <v>988</v>
       </c>
       <c r="H309" t="s">
         <v>16</v>
@@ -11282,22 +11189,22 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>1201</v>
+        <v>1192</v>
       </c>
       <c r="C310" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="D310" t="s">
-        <v>1202</v>
+        <v>1193</v>
       </c>
       <c r="E310" t="s">
-        <v>43</v>
+        <v>1194</v>
       </c>
       <c r="F310" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G310" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="H310" t="s">
         <v>16</v>
@@ -11305,22 +11212,22 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="C311" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D311" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="E311" t="s">
-        <v>327</v>
+        <v>55</v>
       </c>
       <c r="F311" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="G311" t="s">
-        <v>117</v>
+        <v>1198</v>
       </c>
       <c r="H311" t="s">
         <v>16</v>
@@ -11328,22 +11235,22 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="C312" t="s">
-        <v>1178</v>
+        <v>111</v>
       </c>
       <c r="D312" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="E312" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="F312" t="s">
-        <v>7</v>
+        <v>1202</v>
       </c>
       <c r="G312" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="H312" t="s">
         <v>16</v>
@@ -11351,22 +11258,22 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C313" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D313" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="E313" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="F313" t="s">
-        <v>7</v>
+        <v>1207</v>
       </c>
       <c r="G313" t="s">
-        <v>1213</v>
+        <v>12</v>
       </c>
       <c r="H313" t="s">
         <v>16</v>
@@ -11374,22 +11281,22 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="C314" t="s">
-        <v>273</v>
+        <v>51</v>
       </c>
       <c r="D314" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="E314" t="s">
-        <v>118</v>
+        <v>1210</v>
       </c>
       <c r="F314" t="s">
-        <v>105</v>
+        <v>1211</v>
       </c>
       <c r="G314" t="s">
-        <v>1216</v>
+        <v>183</v>
       </c>
       <c r="H314" t="s">
         <v>16</v>
@@ -11397,356 +11304,172 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="C315" t="s">
-        <v>113</v>
+        <v>261</v>
       </c>
       <c r="D315" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="E315" t="s">
-        <v>264</v>
+        <v>203</v>
       </c>
       <c r="F315" t="s">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="G315" t="s">
-        <v>1219</v>
+        <v>184</v>
       </c>
       <c r="H315" t="s">
-        <v>16</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="C316" t="s">
-        <v>113</v>
+        <v>261</v>
       </c>
       <c r="D316" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="E316" t="s">
-        <v>264</v>
+        <v>203</v>
       </c>
       <c r="F316" t="s">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="G316" t="s">
-        <v>1219</v>
+        <v>184</v>
       </c>
       <c r="H316" t="s">
-        <v>16</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="C317" t="s">
-        <v>64</v>
+        <v>624</v>
       </c>
       <c r="D317" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="E317" t="s">
-        <v>602</v>
+        <v>973</v>
       </c>
       <c r="F317" t="s">
         <v>7</v>
       </c>
       <c r="G317" t="s">
-        <v>1019</v>
+        <v>1217</v>
       </c>
       <c r="H317" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="C318" t="s">
-        <v>224</v>
+        <v>624</v>
       </c>
       <c r="D318" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
       <c r="E318" t="s">
-        <v>1225</v>
+        <v>973</v>
       </c>
       <c r="F318" t="s">
         <v>7</v>
       </c>
       <c r="G318" t="s">
-        <v>1226</v>
+        <v>1217</v>
       </c>
       <c r="H318" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="C319" t="s">
-        <v>30</v>
+        <v>453</v>
       </c>
       <c r="D319" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="E319" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="F319" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="G319" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="H319" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="C320" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D320" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="E320" t="s">
-        <v>1232</v>
+        <v>188</v>
       </c>
       <c r="F320" t="s">
-        <v>1233</v>
+        <v>60</v>
       </c>
       <c r="G320" t="s">
-        <v>1234</v>
+        <v>1224</v>
       </c>
       <c r="H320" t="s">
-        <v>16</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>1235</v>
+        <v>1226</v>
       </c>
       <c r="C321" t="s">
-        <v>440</v>
+        <v>89</v>
       </c>
       <c r="D321" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E321" t="s">
-        <v>1237</v>
-      </c>
-      <c r="F321" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G321" t="s">
-        <v>12</v>
+        <v>1225</v>
       </c>
       <c r="H321" t="s">
-        <v>16</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>1239</v>
+        <v>1229</v>
       </c>
       <c r="C322" t="s">
-        <v>51</v>
+        <v>453</v>
       </c>
       <c r="D322" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E322" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F322" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G322" t="s">
-        <v>189</v>
+        <v>1228</v>
       </c>
       <c r="H322" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C323" t="s">
-        <v>273</v>
-      </c>
-      <c r="D323" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E323" t="s">
-        <v>209</v>
-      </c>
-      <c r="F323" t="s">
-        <v>210</v>
-      </c>
-      <c r="G323" t="s">
-        <v>190</v>
-      </c>
-      <c r="H323" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C324" t="s">
-        <v>273</v>
-      </c>
-      <c r="D324" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E324" t="s">
-        <v>209</v>
-      </c>
-      <c r="F324" t="s">
-        <v>210</v>
-      </c>
-      <c r="G324" t="s">
-        <v>190</v>
-      </c>
-      <c r="H324" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A325" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C325" t="s">
-        <v>645</v>
-      </c>
-      <c r="D325" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E325" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F325" t="s">
-        <v>7</v>
-      </c>
-      <c r="G325" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H325" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C326" t="s">
-        <v>645</v>
-      </c>
-      <c r="D326" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E326" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F326" t="s">
-        <v>7</v>
-      </c>
-      <c r="G326" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H326" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C327" t="s">
-        <v>474</v>
-      </c>
-      <c r="D327" t="s">
-        <v>1251</v>
-      </c>
-      <c r="E327" t="s">
-        <v>94</v>
-      </c>
-      <c r="F327" t="s">
-        <v>95</v>
-      </c>
-      <c r="G327" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H327" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A328" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C328" t="s">
-        <v>98</v>
-      </c>
-      <c r="D328" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E328" t="s">
-        <v>194</v>
-      </c>
-      <c r="F328" t="s">
-        <v>60</v>
-      </c>
-      <c r="G328" t="s">
-        <v>1255</v>
-      </c>
-      <c r="H328" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A329" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C329" t="s">
-        <v>89</v>
-      </c>
-      <c r="D329" t="s">
-        <v>1256</v>
-      </c>
-      <c r="H329" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A330" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C330" t="s">
-        <v>474</v>
-      </c>
-      <c r="D330" t="s">
-        <v>1259</v>
-      </c>
-      <c r="H330" t="s">
-        <v>1258</v>
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:H8" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
+  <autoFilter ref="C1:H7" xr:uid="{0BF940D7-F4D0-4FE4-A568-1C48F4F63E64}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E9279D-5376-44DD-91F3-FF6CAF8204B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D723C5EC-E2E5-4D74-8D37-CC0CB7F80EE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{7554E8E7-35ED-4ADF-885F-CD992EB76141}"/>
   </bookViews>
